--- a/artfynd/A 16493-2025 artfynd.xlsx
+++ b/artfynd/A 16493-2025 artfynd.xlsx
@@ -991,10 +991,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124701352</v>
+        <v>124691533</v>
       </c>
       <c r="B5" t="n">
-        <v>79892</v>
+        <v>79891</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1007,39 +1007,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>2081</v>
+        <v>6458</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Tjärnflon, Tjärnflon, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>452657</v>
+        <v>452427</v>
       </c>
       <c r="R5" t="n">
-        <v>6990499</v>
+        <v>6990925</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1072,11 +1067,6 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-05-02</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Rikligt med skrovellav, APOTECHIER på en av bålarna</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1103,10 +1093,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124691533</v>
+        <v>124701352</v>
       </c>
       <c r="B6" t="n">
-        <v>79891</v>
+        <v>79892</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1119,34 +1109,39 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Tjärnflon, Tjärnflon, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>452427</v>
+        <v>452657</v>
       </c>
       <c r="R6" t="n">
-        <v>6990925</v>
+        <v>6990499</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1179,6 +1174,11 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-05-02</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Rikligt med skrovellav, APOTECHIER på en av bålarna</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -5669,10 +5669,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>124756758</v>
+        <v>124753627</v>
       </c>
       <c r="B49" t="n">
-        <v>90962</v>
+        <v>98101</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5681,25 +5681,25 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>112</v>
+        <v>220787</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Stjärntagging</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Asterodon ferruginosus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>Pat.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5709,10 +5709,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>452509</v>
+        <v>452608</v>
       </c>
       <c r="R49" t="n">
-        <v>6990778</v>
+        <v>6990927</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5742,19 +5742,14 @@
           <t>2025-05-03</t>
         </is>
       </c>
-      <c r="Z49" t="inlineStr">
-        <is>
-          <t>11:40</t>
-        </is>
-      </c>
       <c r="AA49" t="inlineStr">
         <is>
           <t>2025-05-03</t>
         </is>
       </c>
-      <c r="AB49" t="inlineStr">
-        <is>
-          <t>11:40</t>
+      <c r="AC49" t="inlineStr">
+        <is>
+          <t>Minst 50</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5769,22 +5764,22 @@
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>124756731</v>
+        <v>124756775</v>
       </c>
       <c r="B50" t="n">
-        <v>91012</v>
+        <v>79891</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -5797,21 +5792,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5821,10 +5816,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>452672</v>
+        <v>452308</v>
       </c>
       <c r="R50" t="n">
-        <v>6990427</v>
+        <v>6990943</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5856,7 +5851,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>14:19</t>
+          <t>10:22</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -5866,7 +5861,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>14:19</t>
+          <t>10:22</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5893,10 +5888,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>124756746</v>
+        <v>124756766</v>
       </c>
       <c r="B51" t="n">
-        <v>91012</v>
+        <v>79891</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -5909,21 +5904,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5933,10 +5928,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>452639</v>
+        <v>452396</v>
       </c>
       <c r="R51" t="n">
-        <v>6990537</v>
+        <v>6990981</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5968,7 +5963,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>13:36</t>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -5978,7 +5973,7 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>13:36</t>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6005,7 +6000,7 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>124756775</v>
+        <v>124753609</v>
       </c>
       <c r="B52" t="n">
         <v>79891</v>
@@ -6045,10 +6040,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>452308</v>
+        <v>452528</v>
       </c>
       <c r="R52" t="n">
-        <v>6990943</v>
+        <v>6990710</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6078,19 +6073,9 @@
           <t>2025-05-03</t>
         </is>
       </c>
-      <c r="Z52" t="inlineStr">
-        <is>
-          <t>10:22</t>
-        </is>
-      </c>
       <c r="AA52" t="inlineStr">
         <is>
           <t>2025-05-03</t>
-        </is>
-      </c>
-      <c r="AB52" t="inlineStr">
-        <is>
-          <t>10:22</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6105,22 +6090,22 @@
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>124756766</v>
+        <v>124756758</v>
       </c>
       <c r="B53" t="n">
-        <v>79891</v>
+        <v>90962</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6133,21 +6118,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6458</v>
+        <v>112</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Stjärntagging</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Asterodon ferruginosus</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Pat.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -6157,10 +6142,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>452396</v>
+        <v>452509</v>
       </c>
       <c r="R53" t="n">
-        <v>6990981</v>
+        <v>6990778</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6192,7 +6177,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>10:58</t>
+          <t>11:40</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6202,7 +6187,7 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>10:58</t>
+          <t>11:40</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6229,10 +6214,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>124753609</v>
+        <v>124756731</v>
       </c>
       <c r="B54" t="n">
-        <v>79891</v>
+        <v>91012</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6245,21 +6230,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6269,10 +6254,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>452528</v>
+        <v>452672</v>
       </c>
       <c r="R54" t="n">
-        <v>6990710</v>
+        <v>6990427</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6302,9 +6287,19 @@
           <t>2025-05-03</t>
         </is>
       </c>
+      <c r="Z54" t="inlineStr">
+        <is>
+          <t>14:19</t>
+        </is>
+      </c>
       <c r="AA54" t="inlineStr">
         <is>
           <t>2025-05-03</t>
+        </is>
+      </c>
+      <c r="AB54" t="inlineStr">
+        <is>
+          <t>14:19</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6319,22 +6314,22 @@
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>124753627</v>
+        <v>124756746</v>
       </c>
       <c r="B55" t="n">
-        <v>98101</v>
+        <v>91012</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6343,25 +6338,25 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6371,10 +6366,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>452608</v>
+        <v>452639</v>
       </c>
       <c r="R55" t="n">
-        <v>6990927</v>
+        <v>6990537</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6404,14 +6399,19 @@
           <t>2025-05-03</t>
         </is>
       </c>
+      <c r="Z55" t="inlineStr">
+        <is>
+          <t>13:36</t>
+        </is>
+      </c>
       <c r="AA55" t="inlineStr">
         <is>
           <t>2025-05-03</t>
         </is>
       </c>
-      <c r="AC55" t="inlineStr">
-        <is>
-          <t>Minst 50</t>
+      <c r="AB55" t="inlineStr">
+        <is>
+          <t>13:36</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6426,12 +6426,12 @@
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
@@ -7926,10 +7926,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>124753631</v>
+        <v>124753578</v>
       </c>
       <c r="B70" t="n">
-        <v>98101</v>
+        <v>91012</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -7938,25 +7938,25 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -7966,10 +7966,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>452526</v>
+        <v>452743</v>
       </c>
       <c r="R70" t="n">
-        <v>6990943</v>
+        <v>6990405</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -8002,11 +8002,6 @@
       <c r="AA70" t="inlineStr">
         <is>
           <t>2025-05-03</t>
-        </is>
-      </c>
-      <c r="AC70" t="inlineStr">
-        <is>
-          <t>Minst 20</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8033,10 +8028,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>124756750</v>
+        <v>124756721</v>
       </c>
       <c r="B71" t="n">
-        <v>98101</v>
+        <v>79891</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -8045,50 +8040,38 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I71" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J71" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K71" t="inlineStr"/>
-      <c r="L71" t="inlineStr"/>
-      <c r="N71" t="inlineStr"/>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
           <t>Häggsåsen N, Jmt</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>452617</v>
+        <v>452823</v>
       </c>
       <c r="R71" t="n">
-        <v>6990549</v>
+        <v>6990261</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -8120,7 +8103,7 @@
       </c>
       <c r="Z71" t="inlineStr">
         <is>
-          <t>12:28</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
@@ -8130,7 +8113,7 @@
       </c>
       <c r="AB71" t="inlineStr">
         <is>
-          <t>12:28</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -8139,9 +8122,23 @@
       <c r="AE71" t="b">
         <v>0</v>
       </c>
-      <c r="AF71" t="inlineStr"/>
       <c r="AG71" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ71" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK71" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO71" t="inlineStr">
+        <is>
+          <t>Omkullfallen grov stam # Salix caprea</t>
+        </is>
       </c>
       <c r="AT71" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
@@ -8158,7 +8155,7 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>124756730</v>
+        <v>124753631</v>
       </c>
       <c r="B72" t="n">
         <v>98101</v>
@@ -8191,29 +8188,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I72" t="inlineStr">
-        <is>
-          <t>200</t>
-        </is>
-      </c>
-      <c r="J72" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K72" t="inlineStr"/>
-      <c r="L72" t="inlineStr"/>
-      <c r="N72" t="inlineStr"/>
+      <c r="I72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
           <t>Häggsåsen N, Jmt</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>452675</v>
+        <v>452526</v>
       </c>
       <c r="R72" t="n">
-        <v>6990411</v>
+        <v>6990943</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8243,24 +8228,14 @@
           <t>2025-05-03</t>
         </is>
       </c>
-      <c r="Z72" t="inlineStr">
-        <is>
-          <t>14:20</t>
-        </is>
-      </c>
       <c r="AA72" t="inlineStr">
         <is>
           <t>2025-05-03</t>
         </is>
       </c>
-      <c r="AB72" t="inlineStr">
-        <is>
-          <t>14:20</t>
-        </is>
-      </c>
       <c r="AC72" t="inlineStr">
         <is>
-          <t>Min antal</t>
+          <t>Minst 20</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8269,29 +8244,28 @@
       <c r="AE72" t="b">
         <v>0</v>
       </c>
-      <c r="AF72" t="inlineStr"/>
       <c r="AG72" t="b">
         <v>0</v>
       </c>
       <c r="AT72" t="inlineStr"/>
       <c r="AW72" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX72" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>124753578</v>
+        <v>124756730</v>
       </c>
       <c r="B73" t="n">
-        <v>91012</v>
+        <v>98101</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -8300,38 +8274,50 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I73" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="J73" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K73" t="inlineStr"/>
+      <c r="L73" t="inlineStr"/>
+      <c r="N73" t="inlineStr"/>
       <c r="P73" t="inlineStr">
         <is>
           <t>Häggsåsen N, Jmt</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>452743</v>
+        <v>452675</v>
       </c>
       <c r="R73" t="n">
-        <v>6990405</v>
+        <v>6990411</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8361,39 +8347,55 @@
           <t>2025-05-03</t>
         </is>
       </c>
+      <c r="Z73" t="inlineStr">
+        <is>
+          <t>14:20</t>
+        </is>
+      </c>
       <c r="AA73" t="inlineStr">
         <is>
           <t>2025-05-03</t>
         </is>
       </c>
+      <c r="AB73" t="inlineStr">
+        <is>
+          <t>14:20</t>
+        </is>
+      </c>
+      <c r="AC73" t="inlineStr">
+        <is>
+          <t>Min antal</t>
+        </is>
+      </c>
       <c r="AD73" t="b">
         <v>0</v>
       </c>
       <c r="AE73" t="b">
         <v>0</v>
       </c>
+      <c r="AF73" t="inlineStr"/>
       <c r="AG73" t="b">
         <v>0</v>
       </c>
       <c r="AT73" t="inlineStr"/>
       <c r="AW73" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>124756721</v>
+        <v>124756750</v>
       </c>
       <c r="B74" t="n">
-        <v>79891</v>
+        <v>98101</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -8402,38 +8404,50 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I74" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J74" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K74" t="inlineStr"/>
+      <c r="L74" t="inlineStr"/>
+      <c r="N74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
           <t>Häggsåsen N, Jmt</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>452823</v>
+        <v>452617</v>
       </c>
       <c r="R74" t="n">
-        <v>6990261</v>
+        <v>6990549</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8465,7 +8479,7 @@
       </c>
       <c r="Z74" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
@@ -8475,7 +8489,7 @@
       </c>
       <c r="AB74" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8484,23 +8498,9 @@
       <c r="AE74" t="b">
         <v>0</v>
       </c>
+      <c r="AF74" t="inlineStr"/>
       <c r="AG74" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ74" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK74" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AO74" t="inlineStr">
-        <is>
-          <t>Omkullfallen grov stam # Salix caprea</t>
-        </is>
       </c>
       <c r="AT74" t="inlineStr"/>
       <c r="AW74" t="inlineStr">
@@ -15261,10 +15261,10 @@
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>124756777</v>
+        <v>124753580</v>
       </c>
       <c r="B135" t="n">
-        <v>98101</v>
+        <v>91012</v>
       </c>
       <c r="C135" t="inlineStr">
         <is>
@@ -15273,50 +15273,38 @@
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E135" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I135" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J135" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K135" t="inlineStr"/>
-      <c r="L135" t="inlineStr"/>
-      <c r="N135" t="inlineStr"/>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I135" t="inlineStr"/>
       <c r="P135" t="inlineStr">
         <is>
           <t>Häggsåsen N, Jmt</t>
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>452146</v>
+        <v>452693</v>
       </c>
       <c r="R135" t="n">
-        <v>6990839</v>
+        <v>6990472</v>
       </c>
       <c r="S135" t="n">
         <v>10</v>
@@ -15346,50 +15334,39 @@
           <t>2025-05-03</t>
         </is>
       </c>
-      <c r="Z135" t="inlineStr">
-        <is>
-          <t>10:06</t>
-        </is>
-      </c>
       <c r="AA135" t="inlineStr">
         <is>
           <t>2025-05-03</t>
         </is>
       </c>
-      <c r="AB135" t="inlineStr">
-        <is>
-          <t>10:06</t>
-        </is>
-      </c>
       <c r="AD135" t="b">
         <v>0</v>
       </c>
       <c r="AE135" t="b">
         <v>0</v>
       </c>
-      <c r="AF135" t="inlineStr"/>
       <c r="AG135" t="b">
         <v>0</v>
       </c>
       <c r="AT135" t="inlineStr"/>
       <c r="AW135" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX135" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY135" t="inlineStr"/>
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>124753580</v>
+        <v>124756761</v>
       </c>
       <c r="B136" t="n">
-        <v>91012</v>
+        <v>78810</v>
       </c>
       <c r="C136" t="inlineStr">
         <is>
@@ -15402,21 +15379,21 @@
         </is>
       </c>
       <c r="E136" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I136" t="inlineStr"/>
@@ -15426,10 +15403,10 @@
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>452693</v>
+        <v>452532</v>
       </c>
       <c r="R136" t="n">
-        <v>6990472</v>
+        <v>6990825</v>
       </c>
       <c r="S136" t="n">
         <v>10</v>
@@ -15459,9 +15436,19 @@
           <t>2025-05-03</t>
         </is>
       </c>
+      <c r="Z136" t="inlineStr">
+        <is>
+          <t>11:26</t>
+        </is>
+      </c>
       <c r="AA136" t="inlineStr">
         <is>
           <t>2025-05-03</t>
+        </is>
+      </c>
+      <c r="AB136" t="inlineStr">
+        <is>
+          <t>11:26</t>
         </is>
       </c>
       <c r="AD136" t="b">
@@ -15476,22 +15463,22 @@
       <c r="AT136" t="inlineStr"/>
       <c r="AW136" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX136" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY136" t="inlineStr"/>
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>124756761</v>
+        <v>124756777</v>
       </c>
       <c r="B137" t="n">
-        <v>78810</v>
+        <v>98101</v>
       </c>
       <c r="C137" t="inlineStr">
         <is>
@@ -15500,38 +15487,50 @@
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E137" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I137" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I137" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J137" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K137" t="inlineStr"/>
+      <c r="L137" t="inlineStr"/>
+      <c r="N137" t="inlineStr"/>
       <c r="P137" t="inlineStr">
         <is>
           <t>Häggsåsen N, Jmt</t>
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>452532</v>
+        <v>452146</v>
       </c>
       <c r="R137" t="n">
-        <v>6990825</v>
+        <v>6990839</v>
       </c>
       <c r="S137" t="n">
         <v>10</v>
@@ -15563,7 +15562,7 @@
       </c>
       <c r="Z137" t="inlineStr">
         <is>
-          <t>11:26</t>
+          <t>10:06</t>
         </is>
       </c>
       <c r="AA137" t="inlineStr">
@@ -15573,7 +15572,7 @@
       </c>
       <c r="AB137" t="inlineStr">
         <is>
-          <t>11:26</t>
+          <t>10:06</t>
         </is>
       </c>
       <c r="AD137" t="b">
@@ -15582,6 +15581,7 @@
       <c r="AE137" t="b">
         <v>0</v>
       </c>
+      <c r="AF137" t="inlineStr"/>
       <c r="AG137" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 16493-2025 artfynd.xlsx
+++ b/artfynd/A 16493-2025 artfynd.xlsx
@@ -4134,10 +4134,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>124705584</v>
+        <v>124689645</v>
       </c>
       <c r="B35" t="n">
-        <v>91030</v>
+        <v>91012</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4150,34 +4150,34 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>5432</v>
+        <v>1202</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Häggsåsen, Häggsåsen, Jmt</t>
+          <t>Tjärnflon, Tjärnflon, Jmt</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>452865</v>
+        <v>452311</v>
       </c>
       <c r="R35" t="n">
-        <v>6990382</v>
+        <v>6990960</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4236,10 +4236,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>124721354</v>
+        <v>124691814</v>
       </c>
       <c r="B36" t="n">
-        <v>57513</v>
+        <v>56714</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4252,16 +4252,16 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>100109</v>
+        <v>102612</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -4269,10 +4269,14 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I36" t="inlineStr"/>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>förbiflygande</t>
         </is>
       </c>
       <c r="P36" t="inlineStr">
@@ -4281,10 +4285,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>452514</v>
+        <v>452489</v>
       </c>
       <c r="R36" t="n">
-        <v>6990587</v>
+        <v>6990896</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4317,11 +4321,6 @@
       <c r="AA36" t="inlineStr">
         <is>
           <t>2025-05-02</t>
-        </is>
-      </c>
-      <c r="AC36" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4348,10 +4347,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>124705813</v>
+        <v>124705584</v>
       </c>
       <c r="B37" t="n">
-        <v>57513</v>
+        <v>91030</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4364,29 +4363,24 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
-      <c r="M37" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
       <c r="P37" t="inlineStr">
         <is>
           <t>Häggsåsen, Häggsåsen, Jmt</t>
@@ -4396,7 +4390,7 @@
         <v>452865</v>
       </c>
       <c r="R37" t="n">
-        <v>6990385</v>
+        <v>6990382</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4429,11 +4423,6 @@
       <c r="AA37" t="inlineStr">
         <is>
           <t>2025-05-02</t>
-        </is>
-      </c>
-      <c r="AC37" t="inlineStr">
-        <is>
-          <t>Möjligt gammalt bo 3m upp i granstubbe med granticka på</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4460,7 +4449,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>124706864</v>
+        <v>124721354</v>
       </c>
       <c r="B38" t="n">
         <v>57513</v>
@@ -4496,19 +4485,19 @@
       <c r="I38" t="inlineStr"/>
       <c r="M38" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Häggsåsen, Häggsåsen, Jmt</t>
+          <t>Tjärnflon, Tjärnflon, Jmt</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>453007</v>
+        <v>452514</v>
       </c>
       <c r="R38" t="n">
-        <v>6990356</v>
+        <v>6990587</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4572,10 +4561,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>124689645</v>
+        <v>124705813</v>
       </c>
       <c r="B39" t="n">
-        <v>91012</v>
+        <v>57513</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4588,34 +4577,39 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Tjärnflon, Tjärnflon, Jmt</t>
+          <t>Häggsåsen, Häggsåsen, Jmt</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>452311</v>
+        <v>452865</v>
       </c>
       <c r="R39" t="n">
-        <v>6990960</v>
+        <v>6990385</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4648,6 +4642,11 @@
       <c r="AA39" t="inlineStr">
         <is>
           <t>2025-05-02</t>
+        </is>
+      </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>Möjligt gammalt bo 3m upp i granstubbe med granticka på</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4674,10 +4673,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>124691814</v>
+        <v>124706864</v>
       </c>
       <c r="B40" t="n">
-        <v>56714</v>
+        <v>57513</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4690,16 +4689,16 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>102612</v>
+        <v>100109</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
@@ -4707,26 +4706,22 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I40" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I40" t="inlineStr"/>
       <c r="M40" t="inlineStr">
         <is>
-          <t>förbiflygande</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Tjärnflon, Tjärnflon, Jmt</t>
+          <t>Häggsåsen, Häggsåsen, Jmt</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>452489</v>
+        <v>453007</v>
       </c>
       <c r="R40" t="n">
-        <v>6990896</v>
+        <v>6990356</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4759,6 +4754,11 @@
       <c r="AA40" t="inlineStr">
         <is>
           <t>2025-05-02</t>
+        </is>
+      </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5009,10 +5009,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>124756762</v>
+        <v>124756755</v>
       </c>
       <c r="B43" t="n">
-        <v>78810</v>
+        <v>91299</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5025,21 +5025,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6425</v>
+        <v>658</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5049,10 +5049,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>452508</v>
+        <v>452538</v>
       </c>
       <c r="R43" t="n">
-        <v>6990903</v>
+        <v>6990659</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5084,7 +5084,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>11:58</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5094,7 +5094,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>11:58</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5121,10 +5121,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>124756755</v>
+        <v>124756762</v>
       </c>
       <c r="B44" t="n">
-        <v>91299</v>
+        <v>78810</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5137,21 +5137,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>658</v>
+        <v>6425</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5161,10 +5161,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>452538</v>
+        <v>452508</v>
       </c>
       <c r="R44" t="n">
-        <v>6990659</v>
+        <v>6990903</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5196,7 +5196,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>11:58</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5206,7 +5206,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>11:58</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5233,10 +5233,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>124753620</v>
+        <v>124756741</v>
       </c>
       <c r="B45" t="n">
-        <v>98101</v>
+        <v>79851</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5245,25 +5245,25 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>220787</v>
+        <v>229497</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5273,10 +5273,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>452554</v>
+        <v>452682</v>
       </c>
       <c r="R45" t="n">
-        <v>6990657</v>
+        <v>6990476</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5306,14 +5306,19 @@
           <t>2025-05-03</t>
         </is>
       </c>
+      <c r="Z45" t="inlineStr">
+        <is>
+          <t>13:54</t>
+        </is>
+      </c>
       <c r="AA45" t="inlineStr">
         <is>
           <t>2025-05-03</t>
         </is>
       </c>
-      <c r="AC45" t="inlineStr">
-        <is>
-          <t>Minst 30</t>
+      <c r="AB45" t="inlineStr">
+        <is>
+          <t>13:54</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5324,26 +5329,41 @@
       </c>
       <c r="AG45" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ45" t="inlineStr">
+        <is>
+          <t>rönn</t>
+        </is>
+      </c>
+      <c r="AK45" t="inlineStr">
+        <is>
+          <t>Sorbus aucuparia</t>
+        </is>
+      </c>
+      <c r="AO45" t="inlineStr">
+        <is>
+          <t>Sorbus aucuparia</t>
+        </is>
       </c>
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>124756741</v>
+        <v>124753620</v>
       </c>
       <c r="B46" t="n">
-        <v>79851</v>
+        <v>98101</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5352,25 +5372,25 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>229497</v>
+        <v>220787</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5380,10 +5400,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>452682</v>
+        <v>452554</v>
       </c>
       <c r="R46" t="n">
-        <v>6990476</v>
+        <v>6990657</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5413,19 +5433,14 @@
           <t>2025-05-03</t>
         </is>
       </c>
-      <c r="Z46" t="inlineStr">
-        <is>
-          <t>13:54</t>
-        </is>
-      </c>
       <c r="AA46" t="inlineStr">
         <is>
           <t>2025-05-03</t>
         </is>
       </c>
-      <c r="AB46" t="inlineStr">
-        <is>
-          <t>13:54</t>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>Minst 30</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5436,41 +5451,26 @@
       </c>
       <c r="AG46" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ46" t="inlineStr">
-        <is>
-          <t>rönn</t>
-        </is>
-      </c>
-      <c r="AK46" t="inlineStr">
-        <is>
-          <t>Sorbus aucuparia</t>
-        </is>
-      </c>
-      <c r="AO46" t="inlineStr">
-        <is>
-          <t>Sorbus aucuparia</t>
-        </is>
       </c>
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>124753639</v>
+        <v>124753621</v>
       </c>
       <c r="B47" t="n">
-        <v>78810</v>
+        <v>98101</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5479,25 +5479,25 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5507,10 +5507,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>452511</v>
+        <v>452506</v>
       </c>
       <c r="R47" t="n">
-        <v>6990733</v>
+        <v>6990758</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5543,6 +5543,11 @@
       <c r="AA47" t="inlineStr">
         <is>
           <t>2025-05-03</t>
+        </is>
+      </c>
+      <c r="AC47" t="inlineStr">
+        <is>
+          <t>Minst 60</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5569,10 +5574,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>124756727</v>
+        <v>124753639</v>
       </c>
       <c r="B48" t="n">
-        <v>79920</v>
+        <v>78810</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5581,25 +5586,25 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5609,10 +5614,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>452745</v>
+        <v>452511</v>
       </c>
       <c r="R48" t="n">
-        <v>6990359</v>
+        <v>6990733</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5642,19 +5647,9 @@
           <t>2025-05-03</t>
         </is>
       </c>
-      <c r="Z48" t="inlineStr">
-        <is>
-          <t>14:31</t>
-        </is>
-      </c>
       <c r="AA48" t="inlineStr">
         <is>
           <t>2025-05-03</t>
-        </is>
-      </c>
-      <c r="AB48" t="inlineStr">
-        <is>
-          <t>14:31</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5669,22 +5664,22 @@
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>124756734</v>
+        <v>124756727</v>
       </c>
       <c r="B49" t="n">
-        <v>79891</v>
+        <v>79920</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5693,25 +5688,25 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6458</v>
+        <v>6462</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5721,10 +5716,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>452675</v>
+        <v>452745</v>
       </c>
       <c r="R49" t="n">
-        <v>6990435</v>
+        <v>6990359</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5756,7 +5751,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -5766,7 +5761,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5777,21 +5772,6 @@
       </c>
       <c r="AG49" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ49" t="inlineStr">
-        <is>
-          <t>rönn</t>
-        </is>
-      </c>
-      <c r="AK49" t="inlineStr">
-        <is>
-          <t>Sorbus aucuparia</t>
-        </is>
-      </c>
-      <c r="AO49" t="inlineStr">
-        <is>
-          <t>Sorbus aucuparia</t>
-        </is>
       </c>
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
@@ -5808,10 +5788,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>124753634</v>
+        <v>124756734</v>
       </c>
       <c r="B50" t="n">
-        <v>91008</v>
+        <v>79891</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -5824,21 +5804,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>1108</v>
+        <v>6458</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5848,10 +5828,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>452750</v>
+        <v>452675</v>
       </c>
       <c r="R50" t="n">
-        <v>6990344</v>
+        <v>6990435</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5881,11 +5861,21 @@
           <t>2025-05-03</t>
         </is>
       </c>
+      <c r="Z50" t="inlineStr">
+        <is>
+          <t>14:14</t>
+        </is>
+      </c>
       <c r="AA50" t="inlineStr">
         <is>
           <t>2025-05-03</t>
         </is>
       </c>
+      <c r="AB50" t="inlineStr">
+        <is>
+          <t>14:14</t>
+        </is>
+      </c>
       <c r="AD50" t="b">
         <v>0</v>
       </c>
@@ -5894,26 +5884,41 @@
       </c>
       <c r="AG50" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ50" t="inlineStr">
+        <is>
+          <t>rönn</t>
+        </is>
+      </c>
+      <c r="AK50" t="inlineStr">
+        <is>
+          <t>Sorbus aucuparia</t>
+        </is>
+      </c>
+      <c r="AO50" t="inlineStr">
+        <is>
+          <t>Sorbus aucuparia</t>
+        </is>
       </c>
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>124753621</v>
+        <v>124753634</v>
       </c>
       <c r="B51" t="n">
-        <v>98101</v>
+        <v>91008</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -5922,25 +5927,25 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>220787</v>
+        <v>1108</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5950,10 +5955,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>452506</v>
+        <v>452750</v>
       </c>
       <c r="R51" t="n">
-        <v>6990758</v>
+        <v>6990344</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5986,11 +5991,6 @@
       <c r="AA51" t="inlineStr">
         <is>
           <t>2025-05-03</t>
-        </is>
-      </c>
-      <c r="AC51" t="inlineStr">
-        <is>
-          <t>Minst 60</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -7726,10 +7726,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>124753604</v>
+        <v>124756774</v>
       </c>
       <c r="B67" t="n">
-        <v>79892</v>
+        <v>98101</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -7738,38 +7738,50 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>2081</v>
+        <v>220787</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
-        </is>
-      </c>
-      <c r="I67" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J67" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K67" t="inlineStr"/>
+      <c r="L67" t="inlineStr"/>
+      <c r="N67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
           <t>Häggsåsen N, Jmt</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>452435</v>
+        <v>452308</v>
       </c>
       <c r="R67" t="n">
-        <v>6990938</v>
+        <v>6990943</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7799,39 +7811,50 @@
           <t>2025-05-03</t>
         </is>
       </c>
+      <c r="Z67" t="inlineStr">
+        <is>
+          <t>10:23</t>
+        </is>
+      </c>
       <c r="AA67" t="inlineStr">
         <is>
           <t>2025-05-03</t>
         </is>
       </c>
+      <c r="AB67" t="inlineStr">
+        <is>
+          <t>10:23</t>
+        </is>
+      </c>
       <c r="AD67" t="b">
         <v>0</v>
       </c>
       <c r="AE67" t="b">
         <v>0</v>
       </c>
+      <c r="AF67" t="inlineStr"/>
       <c r="AG67" t="b">
         <v>0</v>
       </c>
       <c r="AT67" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>124753592</v>
+        <v>124756750</v>
       </c>
       <c r="B68" t="n">
-        <v>57513</v>
+        <v>98101</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -7840,38 +7863,50 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I68" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J68" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K68" t="inlineStr"/>
+      <c r="L68" t="inlineStr"/>
+      <c r="N68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
           <t>Häggsåsen N, Jmt</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>452396</v>
+        <v>452617</v>
       </c>
       <c r="R68" t="n">
-        <v>6990703</v>
+        <v>6990549</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7901,14 +7936,19 @@
           <t>2025-05-03</t>
         </is>
       </c>
+      <c r="Z68" t="inlineStr">
+        <is>
+          <t>12:28</t>
+        </is>
+      </c>
       <c r="AA68" t="inlineStr">
         <is>
           <t>2025-05-03</t>
         </is>
       </c>
-      <c r="AC68" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
+      <c r="AB68" t="inlineStr">
+        <is>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -7917,28 +7957,29 @@
       <c r="AE68" t="b">
         <v>0</v>
       </c>
+      <c r="AF68" t="inlineStr"/>
       <c r="AG68" t="b">
         <v>0</v>
       </c>
       <c r="AT68" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>124756774</v>
+        <v>124753592</v>
       </c>
       <c r="B69" t="n">
-        <v>98101</v>
+        <v>57513</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -7947,50 +7988,38 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I69" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="J69" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K69" t="inlineStr"/>
-      <c r="L69" t="inlineStr"/>
-      <c r="N69" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
           <t>Häggsåsen N, Jmt</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>452308</v>
+        <v>452396</v>
       </c>
       <c r="R69" t="n">
-        <v>6990943</v>
+        <v>6990703</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -8020,19 +8049,14 @@
           <t>2025-05-03</t>
         </is>
       </c>
-      <c r="Z69" t="inlineStr">
-        <is>
-          <t>10:23</t>
-        </is>
-      </c>
       <c r="AA69" t="inlineStr">
         <is>
           <t>2025-05-03</t>
         </is>
       </c>
-      <c r="AB69" t="inlineStr">
-        <is>
-          <t>10:23</t>
+      <c r="AC69" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -8041,29 +8065,28 @@
       <c r="AE69" t="b">
         <v>0</v>
       </c>
-      <c r="AF69" t="inlineStr"/>
       <c r="AG69" t="b">
         <v>0</v>
       </c>
       <c r="AT69" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX69" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>124756750</v>
+        <v>124753604</v>
       </c>
       <c r="B70" t="n">
-        <v>98101</v>
+        <v>79892</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -8072,50 +8095,38 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>220787</v>
+        <v>2081</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I70" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J70" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K70" t="inlineStr"/>
-      <c r="L70" t="inlineStr"/>
-      <c r="N70" t="inlineStr"/>
+          <t>(Scop.) DC.</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
           <t>Häggsåsen N, Jmt</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>452617</v>
+        <v>452435</v>
       </c>
       <c r="R70" t="n">
-        <v>6990549</v>
+        <v>6990938</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -8145,50 +8156,39 @@
           <t>2025-05-03</t>
         </is>
       </c>
-      <c r="Z70" t="inlineStr">
-        <is>
-          <t>12:28</t>
-        </is>
-      </c>
       <c r="AA70" t="inlineStr">
         <is>
           <t>2025-05-03</t>
         </is>
       </c>
-      <c r="AB70" t="inlineStr">
-        <is>
-          <t>12:28</t>
-        </is>
-      </c>
       <c r="AD70" t="b">
         <v>0</v>
       </c>
       <c r="AE70" t="b">
         <v>0</v>
       </c>
-      <c r="AF70" t="inlineStr"/>
       <c r="AG70" t="b">
         <v>0</v>
       </c>
       <c r="AT70" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>124756721</v>
+        <v>124756733</v>
       </c>
       <c r="B71" t="n">
-        <v>79891</v>
+        <v>79927</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -8197,25 +8197,25 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>6458</v>
+        <v>6464</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -8225,10 +8225,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>452823</v>
+        <v>452675</v>
       </c>
       <c r="R71" t="n">
-        <v>6990261</v>
+        <v>6990435</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -8260,7 +8260,7 @@
       </c>
       <c r="Z71" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
@@ -8270,7 +8270,7 @@
       </c>
       <c r="AB71" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -8284,17 +8284,17 @@
       </c>
       <c r="AJ71" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>rönn</t>
         </is>
       </c>
       <c r="AK71" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Sorbus aucuparia</t>
         </is>
       </c>
       <c r="AO71" t="inlineStr">
         <is>
-          <t>Omkullfallen grov stam # Salix caprea</t>
+          <t>Sorbus aucuparia</t>
         </is>
       </c>
       <c r="AT71" t="inlineStr"/>
@@ -8312,10 +8312,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>124756754</v>
+        <v>124756721</v>
       </c>
       <c r="B72" t="n">
-        <v>78810</v>
+        <v>79891</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -8328,21 +8328,21 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -8352,10 +8352,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>452544</v>
+        <v>452823</v>
       </c>
       <c r="R72" t="n">
-        <v>6990646</v>
+        <v>6990261</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8387,7 +8387,7 @@
       </c>
       <c r="Z72" t="inlineStr">
         <is>
-          <t>12:04</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
@@ -8397,7 +8397,7 @@
       </c>
       <c r="AB72" t="inlineStr">
         <is>
-          <t>12:04</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8408,6 +8408,21 @@
       </c>
       <c r="AG72" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ72" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK72" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO72" t="inlineStr">
+        <is>
+          <t>Omkullfallen grov stam # Salix caprea</t>
+        </is>
       </c>
       <c r="AT72" t="inlineStr"/>
       <c r="AW72" t="inlineStr">
@@ -8424,7 +8439,7 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>124756756</v>
+        <v>124756754</v>
       </c>
       <c r="B73" t="n">
         <v>78810</v>
@@ -8464,10 +8479,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>452545</v>
+        <v>452544</v>
       </c>
       <c r="R73" t="n">
-        <v>6990691</v>
+        <v>6990646</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8499,7 +8514,7 @@
       </c>
       <c r="Z73" t="inlineStr">
         <is>
-          <t>11:54</t>
+          <t>12:04</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
@@ -8509,7 +8524,7 @@
       </c>
       <c r="AB73" t="inlineStr">
         <is>
-          <t>11:54</t>
+          <t>12:04</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8536,10 +8551,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>124756733</v>
+        <v>124756756</v>
       </c>
       <c r="B74" t="n">
-        <v>79927</v>
+        <v>78810</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -8548,25 +8563,25 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>6464</v>
+        <v>6425</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -8576,10 +8591,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>452675</v>
+        <v>452545</v>
       </c>
       <c r="R74" t="n">
-        <v>6990435</v>
+        <v>6990691</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8611,7 +8626,7 @@
       </c>
       <c r="Z74" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>11:54</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
@@ -8621,7 +8636,7 @@
       </c>
       <c r="AB74" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>11:54</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8632,21 +8647,6 @@
       </c>
       <c r="AG74" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ74" t="inlineStr">
-        <is>
-          <t>rönn</t>
-        </is>
-      </c>
-      <c r="AK74" t="inlineStr">
-        <is>
-          <t>Sorbus aucuparia</t>
-        </is>
-      </c>
-      <c r="AO74" t="inlineStr">
-        <is>
-          <t>Sorbus aucuparia</t>
-        </is>
       </c>
       <c r="AT74" t="inlineStr"/>
       <c r="AW74" t="inlineStr">
@@ -8989,10 +8989,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>124756719</v>
+        <v>124753586</v>
       </c>
       <c r="B78" t="n">
-        <v>79927</v>
+        <v>91012</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -9001,25 +9001,25 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>6464</v>
+        <v>1202</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -9029,10 +9029,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>452823</v>
+        <v>452500</v>
       </c>
       <c r="R78" t="n">
-        <v>6990261</v>
+        <v>6990950</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -9062,19 +9062,9 @@
           <t>2025-05-03</t>
         </is>
       </c>
-      <c r="Z78" t="inlineStr">
-        <is>
-          <t>14:59</t>
-        </is>
-      </c>
       <c r="AA78" t="inlineStr">
         <is>
           <t>2025-05-03</t>
-        </is>
-      </c>
-      <c r="AB78" t="inlineStr">
-        <is>
-          <t>14:59</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -9089,22 +9079,22 @@
       <c r="AT78" t="inlineStr"/>
       <c r="AW78" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX78" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>124753608</v>
+        <v>124756758</v>
       </c>
       <c r="B79" t="n">
-        <v>79891</v>
+        <v>90962</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -9117,21 +9107,21 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>6458</v>
+        <v>112</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Stjärntagging</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Asterodon ferruginosus</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Pat.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -9141,10 +9131,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>452731</v>
+        <v>452509</v>
       </c>
       <c r="R79" t="n">
-        <v>6990377</v>
+        <v>6990778</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -9174,9 +9164,19 @@
           <t>2025-05-03</t>
         </is>
       </c>
+      <c r="Z79" t="inlineStr">
+        <is>
+          <t>11:40</t>
+        </is>
+      </c>
       <c r="AA79" t="inlineStr">
         <is>
           <t>2025-05-03</t>
+        </is>
+      </c>
+      <c r="AB79" t="inlineStr">
+        <is>
+          <t>11:40</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -9191,22 +9191,22 @@
       <c r="AT79" t="inlineStr"/>
       <c r="AW79" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX79" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>124756766</v>
+        <v>124756719</v>
       </c>
       <c r="B80" t="n">
-        <v>79891</v>
+        <v>79927</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
@@ -9215,25 +9215,25 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>6458</v>
+        <v>6464</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -9243,10 +9243,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>452396</v>
+        <v>452823</v>
       </c>
       <c r="R80" t="n">
-        <v>6990981</v>
+        <v>6990261</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -9278,7 +9278,7 @@
       </c>
       <c r="Z80" t="inlineStr">
         <is>
-          <t>10:58</t>
+          <t>14:59</t>
         </is>
       </c>
       <c r="AA80" t="inlineStr">
@@ -9288,7 +9288,7 @@
       </c>
       <c r="AB80" t="inlineStr">
         <is>
-          <t>10:58</t>
+          <t>14:59</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -9315,10 +9315,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>124756742</v>
+        <v>124753608</v>
       </c>
       <c r="B81" t="n">
-        <v>79927</v>
+        <v>79891</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
@@ -9327,25 +9327,25 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>6464</v>
+        <v>6458</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -9355,10 +9355,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>452682</v>
+        <v>452731</v>
       </c>
       <c r="R81" t="n">
-        <v>6990476</v>
+        <v>6990377</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -9388,21 +9388,11 @@
           <t>2025-05-03</t>
         </is>
       </c>
-      <c r="Z81" t="inlineStr">
-        <is>
-          <t>13:53</t>
-        </is>
-      </c>
       <c r="AA81" t="inlineStr">
         <is>
           <t>2025-05-03</t>
         </is>
       </c>
-      <c r="AB81" t="inlineStr">
-        <is>
-          <t>13:53</t>
-        </is>
-      </c>
       <c r="AD81" t="b">
         <v>0</v>
       </c>
@@ -9411,41 +9401,26 @@
       </c>
       <c r="AG81" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ81" t="inlineStr">
-        <is>
-          <t>rönn</t>
-        </is>
-      </c>
-      <c r="AK81" t="inlineStr">
-        <is>
-          <t>Sorbus aucuparia</t>
-        </is>
-      </c>
-      <c r="AO81" t="inlineStr">
-        <is>
-          <t>Sorbus aucuparia</t>
-        </is>
       </c>
       <c r="AT81" t="inlineStr"/>
       <c r="AW81" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX81" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>124753586</v>
+        <v>124756766</v>
       </c>
       <c r="B82" t="n">
-        <v>91012</v>
+        <v>79891</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
@@ -9458,21 +9433,21 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -9482,10 +9457,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>452500</v>
+        <v>452396</v>
       </c>
       <c r="R82" t="n">
-        <v>6990950</v>
+        <v>6990981</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -9515,9 +9490,19 @@
           <t>2025-05-03</t>
         </is>
       </c>
+      <c r="Z82" t="inlineStr">
+        <is>
+          <t>10:58</t>
+        </is>
+      </c>
       <c r="AA82" t="inlineStr">
         <is>
           <t>2025-05-03</t>
+        </is>
+      </c>
+      <c r="AB82" t="inlineStr">
+        <is>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -9532,22 +9517,22 @@
       <c r="AT82" t="inlineStr"/>
       <c r="AW82" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX82" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>124756758</v>
+        <v>124756742</v>
       </c>
       <c r="B83" t="n">
-        <v>90962</v>
+        <v>79927</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
@@ -9556,25 +9541,25 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>112</v>
+        <v>6464</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Stjärntagging</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Asterodon ferruginosus</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>Pat.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -9584,10 +9569,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>452509</v>
+        <v>452682</v>
       </c>
       <c r="R83" t="n">
-        <v>6990778</v>
+        <v>6990476</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9619,7 +9604,7 @@
       </c>
       <c r="Z83" t="inlineStr">
         <is>
-          <t>11:40</t>
+          <t>13:53</t>
         </is>
       </c>
       <c r="AA83" t="inlineStr">
@@ -9629,7 +9614,7 @@
       </c>
       <c r="AB83" t="inlineStr">
         <is>
-          <t>11:40</t>
+          <t>13:53</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -9640,6 +9625,21 @@
       </c>
       <c r="AG83" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ83" t="inlineStr">
+        <is>
+          <t>rönn</t>
+        </is>
+      </c>
+      <c r="AK83" t="inlineStr">
+        <is>
+          <t>Sorbus aucuparia</t>
+        </is>
+      </c>
+      <c r="AO83" t="inlineStr">
+        <is>
+          <t>Sorbus aucuparia</t>
+        </is>
       </c>
       <c r="AT83" t="inlineStr"/>
       <c r="AW83" t="inlineStr">
@@ -9656,10 +9656,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>124753605</v>
+        <v>124756775</v>
       </c>
       <c r="B84" t="n">
-        <v>79892</v>
+        <v>79891</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
@@ -9672,21 +9672,21 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>2081</v>
+        <v>6458</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -9696,10 +9696,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>452408</v>
+        <v>452308</v>
       </c>
       <c r="R84" t="n">
-        <v>6990952</v>
+        <v>6990943</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9729,9 +9729,19 @@
           <t>2025-05-03</t>
         </is>
       </c>
+      <c r="Z84" t="inlineStr">
+        <is>
+          <t>10:22</t>
+        </is>
+      </c>
       <c r="AA84" t="inlineStr">
         <is>
           <t>2025-05-03</t>
+        </is>
+      </c>
+      <c r="AB84" t="inlineStr">
+        <is>
+          <t>10:22</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -9746,22 +9756,22 @@
       <c r="AT84" t="inlineStr"/>
       <c r="AW84" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX84" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>124756731</v>
+        <v>124753605</v>
       </c>
       <c r="B85" t="n">
-        <v>91012</v>
+        <v>79892</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
@@ -9774,21 +9784,21 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>1202</v>
+        <v>2081</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -9798,10 +9808,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>452672</v>
+        <v>452408</v>
       </c>
       <c r="R85" t="n">
-        <v>6990427</v>
+        <v>6990952</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9831,19 +9841,9 @@
           <t>2025-05-03</t>
         </is>
       </c>
-      <c r="Z85" t="inlineStr">
-        <is>
-          <t>14:19</t>
-        </is>
-      </c>
       <c r="AA85" t="inlineStr">
         <is>
           <t>2025-05-03</t>
-        </is>
-      </c>
-      <c r="AB85" t="inlineStr">
-        <is>
-          <t>14:19</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -9858,19 +9858,19 @@
       <c r="AT85" t="inlineStr"/>
       <c r="AW85" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX85" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>124753580</v>
+        <v>124756731</v>
       </c>
       <c r="B86" t="n">
         <v>91012</v>
@@ -9910,10 +9910,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>452693</v>
+        <v>452672</v>
       </c>
       <c r="R86" t="n">
-        <v>6990472</v>
+        <v>6990427</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9943,9 +9943,19 @@
           <t>2025-05-03</t>
         </is>
       </c>
+      <c r="Z86" t="inlineStr">
+        <is>
+          <t>14:19</t>
+        </is>
+      </c>
       <c r="AA86" t="inlineStr">
         <is>
           <t>2025-05-03</t>
+        </is>
+      </c>
+      <c r="AB86" t="inlineStr">
+        <is>
+          <t>14:19</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -9960,22 +9970,22 @@
       <c r="AT86" t="inlineStr"/>
       <c r="AW86" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX86" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>124756775</v>
+        <v>124753580</v>
       </c>
       <c r="B87" t="n">
-        <v>79891</v>
+        <v>91012</v>
       </c>
       <c r="C87" t="inlineStr">
         <is>
@@ -9988,21 +9998,21 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
@@ -10012,10 +10022,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>452308</v>
+        <v>452693</v>
       </c>
       <c r="R87" t="n">
-        <v>6990943</v>
+        <v>6990472</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -10045,19 +10055,9 @@
           <t>2025-05-03</t>
         </is>
       </c>
-      <c r="Z87" t="inlineStr">
-        <is>
-          <t>10:22</t>
-        </is>
-      </c>
       <c r="AA87" t="inlineStr">
         <is>
           <t>2025-05-03</t>
-        </is>
-      </c>
-      <c r="AB87" t="inlineStr">
-        <is>
-          <t>10:22</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -10072,22 +10072,22 @@
       <c r="AT87" t="inlineStr"/>
       <c r="AW87" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX87" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>124756767</v>
+        <v>124756768</v>
       </c>
       <c r="B88" t="n">
-        <v>78810</v>
+        <v>77743</v>
       </c>
       <c r="C88" t="inlineStr">
         <is>
@@ -10100,21 +10100,21 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>6425</v>
+        <v>228579</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
@@ -10124,10 +10124,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>452362</v>
+        <v>452357</v>
       </c>
       <c r="R88" t="n">
-        <v>6991003</v>
+        <v>6990970</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -10159,7 +10159,7 @@
       </c>
       <c r="Z88" t="inlineStr">
         <is>
-          <t>10:55</t>
+          <t>10:52</t>
         </is>
       </c>
       <c r="AA88" t="inlineStr">
@@ -10169,7 +10169,7 @@
       </c>
       <c r="AB88" t="inlineStr">
         <is>
-          <t>10:55</t>
+          <t>10:52</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -10196,10 +10196,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>124756768</v>
+        <v>124753627</v>
       </c>
       <c r="B89" t="n">
-        <v>77743</v>
+        <v>98101</v>
       </c>
       <c r="C89" t="inlineStr">
         <is>
@@ -10208,25 +10208,25 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>228579</v>
+        <v>220787</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
@@ -10236,10 +10236,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>452357</v>
+        <v>452608</v>
       </c>
       <c r="R89" t="n">
-        <v>6990970</v>
+        <v>6990927</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -10269,19 +10269,14 @@
           <t>2025-05-03</t>
         </is>
       </c>
-      <c r="Z89" t="inlineStr">
-        <is>
-          <t>10:52</t>
-        </is>
-      </c>
       <c r="AA89" t="inlineStr">
         <is>
           <t>2025-05-03</t>
         </is>
       </c>
-      <c r="AB89" t="inlineStr">
-        <is>
-          <t>10:52</t>
+      <c r="AC89" t="inlineStr">
+        <is>
+          <t>Minst 50</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -10296,19 +10291,19 @@
       <c r="AT89" t="inlineStr"/>
       <c r="AW89" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX89" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>124753627</v>
+        <v>124753615</v>
       </c>
       <c r="B90" t="n">
         <v>98101</v>
@@ -10348,10 +10343,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>452608</v>
+        <v>452734</v>
       </c>
       <c r="R90" t="n">
-        <v>6990927</v>
+        <v>6990355</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -10388,7 +10383,7 @@
       </c>
       <c r="AC90" t="inlineStr">
         <is>
-          <t>Minst 50</t>
+          <t>Minst 30</t>
         </is>
       </c>
       <c r="AD90" t="b">
@@ -10415,10 +10410,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>124753615</v>
+        <v>124756749</v>
       </c>
       <c r="B91" t="n">
-        <v>98101</v>
+        <v>91012</v>
       </c>
       <c r="C91" t="inlineStr">
         <is>
@@ -10427,25 +10422,25 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
@@ -10455,10 +10450,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>452734</v>
+        <v>452609</v>
       </c>
       <c r="R91" t="n">
-        <v>6990355</v>
+        <v>6990543</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -10488,14 +10483,19 @@
           <t>2025-05-03</t>
         </is>
       </c>
+      <c r="Z91" t="inlineStr">
+        <is>
+          <t>12:29</t>
+        </is>
+      </c>
       <c r="AA91" t="inlineStr">
         <is>
           <t>2025-05-03</t>
         </is>
       </c>
-      <c r="AC91" t="inlineStr">
-        <is>
-          <t>Minst 30</t>
+      <c r="AB91" t="inlineStr">
+        <is>
+          <t>12:29</t>
         </is>
       </c>
       <c r="AD91" t="b">
@@ -10510,19 +10510,19 @@
       <c r="AT91" t="inlineStr"/>
       <c r="AW91" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX91" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>124756749</v>
+        <v>124753578</v>
       </c>
       <c r="B92" t="n">
         <v>91012</v>
@@ -10562,10 +10562,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>452609</v>
+        <v>452743</v>
       </c>
       <c r="R92" t="n">
-        <v>6990543</v>
+        <v>6990405</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -10595,19 +10595,9 @@
           <t>2025-05-03</t>
         </is>
       </c>
-      <c r="Z92" t="inlineStr">
-        <is>
-          <t>12:29</t>
-        </is>
-      </c>
       <c r="AA92" t="inlineStr">
         <is>
           <t>2025-05-03</t>
-        </is>
-      </c>
-      <c r="AB92" t="inlineStr">
-        <is>
-          <t>12:29</t>
         </is>
       </c>
       <c r="AD92" t="b">
@@ -10622,22 +10612,22 @@
       <c r="AT92" t="inlineStr"/>
       <c r="AW92" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX92" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>124753578</v>
+        <v>124756767</v>
       </c>
       <c r="B93" t="n">
-        <v>91012</v>
+        <v>78810</v>
       </c>
       <c r="C93" t="inlineStr">
         <is>
@@ -10650,21 +10640,21 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
@@ -10674,10 +10664,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>452743</v>
+        <v>452362</v>
       </c>
       <c r="R93" t="n">
-        <v>6990405</v>
+        <v>6991003</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -10707,9 +10697,19 @@
           <t>2025-05-03</t>
         </is>
       </c>
+      <c r="Z93" t="inlineStr">
+        <is>
+          <t>10:55</t>
+        </is>
+      </c>
       <c r="AA93" t="inlineStr">
         <is>
           <t>2025-05-03</t>
+        </is>
+      </c>
+      <c r="AB93" t="inlineStr">
+        <is>
+          <t>10:55</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -10724,12 +10724,12 @@
       <c r="AT93" t="inlineStr"/>
       <c r="AW93" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX93" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY93" t="inlineStr"/>
@@ -11635,10 +11635,10 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>124756763</v>
+        <v>124756724</v>
       </c>
       <c r="B102" t="n">
-        <v>98101</v>
+        <v>91012</v>
       </c>
       <c r="C102" t="inlineStr">
         <is>
@@ -11647,50 +11647,38 @@
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E102" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I102" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J102" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K102" t="inlineStr"/>
-      <c r="L102" t="inlineStr"/>
-      <c r="N102" t="inlineStr"/>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I102" t="inlineStr"/>
       <c r="P102" t="inlineStr">
         <is>
           <t>Häggsåsen N, Jmt</t>
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>452478</v>
+        <v>452793</v>
       </c>
       <c r="R102" t="n">
-        <v>6990887</v>
+        <v>6990262</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -11722,7 +11710,7 @@
       </c>
       <c r="Z102" t="inlineStr">
         <is>
-          <t>11:18</t>
+          <t>14:44</t>
         </is>
       </c>
       <c r="AA102" t="inlineStr">
@@ -11732,7 +11720,7 @@
       </c>
       <c r="AB102" t="inlineStr">
         <is>
-          <t>11:18</t>
+          <t>14:44</t>
         </is>
       </c>
       <c r="AD102" t="b">
@@ -11741,7 +11729,6 @@
       <c r="AE102" t="b">
         <v>0</v>
       </c>
-      <c r="AF102" t="inlineStr"/>
       <c r="AG102" t="b">
         <v>0</v>
       </c>
@@ -11760,7 +11747,7 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>124756724</v>
+        <v>124753584</v>
       </c>
       <c r="B103" t="n">
         <v>91012</v>
@@ -11800,10 +11787,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>452793</v>
+        <v>452444</v>
       </c>
       <c r="R103" t="n">
-        <v>6990262</v>
+        <v>6990774</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -11833,19 +11820,9 @@
           <t>2025-05-03</t>
         </is>
       </c>
-      <c r="Z103" t="inlineStr">
-        <is>
-          <t>14:44</t>
-        </is>
-      </c>
       <c r="AA103" t="inlineStr">
         <is>
           <t>2025-05-03</t>
-        </is>
-      </c>
-      <c r="AB103" t="inlineStr">
-        <is>
-          <t>14:44</t>
         </is>
       </c>
       <c r="AD103" t="b">
@@ -11860,19 +11837,19 @@
       <c r="AT103" t="inlineStr"/>
       <c r="AW103" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX103" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY103" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>124753584</v>
+        <v>124753581</v>
       </c>
       <c r="B104" t="n">
         <v>91012</v>
@@ -11912,10 +11889,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>452444</v>
+        <v>452643</v>
       </c>
       <c r="R104" t="n">
-        <v>6990774</v>
+        <v>6990504</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -11974,7 +11951,7 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>124753581</v>
+        <v>124753582</v>
       </c>
       <c r="B105" t="n">
         <v>91012</v>
@@ -12014,10 +11991,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>452643</v>
+        <v>452649</v>
       </c>
       <c r="R105" t="n">
-        <v>6990504</v>
+        <v>6990621</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -12076,10 +12053,10 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>124753582</v>
+        <v>124756763</v>
       </c>
       <c r="B106" t="n">
-        <v>91012</v>
+        <v>98101</v>
       </c>
       <c r="C106" t="inlineStr">
         <is>
@@ -12088,38 +12065,50 @@
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E106" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I106" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I106" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J106" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K106" t="inlineStr"/>
+      <c r="L106" t="inlineStr"/>
+      <c r="N106" t="inlineStr"/>
       <c r="P106" t="inlineStr">
         <is>
           <t>Häggsåsen N, Jmt</t>
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>452649</v>
+        <v>452478</v>
       </c>
       <c r="R106" t="n">
-        <v>6990621</v>
+        <v>6990887</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -12149,29 +12138,40 @@
           <t>2025-05-03</t>
         </is>
       </c>
+      <c r="Z106" t="inlineStr">
+        <is>
+          <t>11:18</t>
+        </is>
+      </c>
       <c r="AA106" t="inlineStr">
         <is>
           <t>2025-05-03</t>
         </is>
       </c>
+      <c r="AB106" t="inlineStr">
+        <is>
+          <t>11:18</t>
+        </is>
+      </c>
       <c r="AD106" t="b">
         <v>0</v>
       </c>
       <c r="AE106" t="b">
         <v>0</v>
       </c>
+      <c r="AF106" t="inlineStr"/>
       <c r="AG106" t="b">
         <v>0</v>
       </c>
       <c r="AT106" t="inlineStr"/>
       <c r="AW106" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX106" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY106" t="inlineStr"/>
@@ -12731,10 +12731,10 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>124756776</v>
+        <v>124753583</v>
       </c>
       <c r="B112" t="n">
-        <v>78810</v>
+        <v>91012</v>
       </c>
       <c r="C112" t="inlineStr">
         <is>
@@ -12747,21 +12747,21 @@
         </is>
       </c>
       <c r="E112" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I112" t="inlineStr"/>
@@ -12771,10 +12771,10 @@
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>452308</v>
+        <v>452606</v>
       </c>
       <c r="R112" t="n">
-        <v>6990943</v>
+        <v>6990623</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -12804,19 +12804,9 @@
           <t>2025-05-03</t>
         </is>
       </c>
-      <c r="Z112" t="inlineStr">
-        <is>
-          <t>10:21</t>
-        </is>
-      </c>
       <c r="AA112" t="inlineStr">
         <is>
           <t>2025-05-03</t>
-        </is>
-      </c>
-      <c r="AB112" t="inlineStr">
-        <is>
-          <t>10:21</t>
         </is>
       </c>
       <c r="AD112" t="b">
@@ -12831,22 +12821,22 @@
       <c r="AT112" t="inlineStr"/>
       <c r="AW112" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX112" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY112" t="inlineStr"/>
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>124753583</v>
+        <v>124756776</v>
       </c>
       <c r="B113" t="n">
-        <v>91012</v>
+        <v>78810</v>
       </c>
       <c r="C113" t="inlineStr">
         <is>
@@ -12859,21 +12849,21 @@
         </is>
       </c>
       <c r="E113" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
@@ -12883,10 +12873,10 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>452606</v>
+        <v>452308</v>
       </c>
       <c r="R113" t="n">
-        <v>6990623</v>
+        <v>6990943</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -12916,9 +12906,19 @@
           <t>2025-05-03</t>
         </is>
       </c>
+      <c r="Z113" t="inlineStr">
+        <is>
+          <t>10:21</t>
+        </is>
+      </c>
       <c r="AA113" t="inlineStr">
         <is>
           <t>2025-05-03</t>
+        </is>
+      </c>
+      <c r="AB113" t="inlineStr">
+        <is>
+          <t>10:21</t>
         </is>
       </c>
       <c r="AD113" t="b">
@@ -12933,12 +12933,12 @@
       <c r="AT113" t="inlineStr"/>
       <c r="AW113" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX113" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY113" t="inlineStr"/>

--- a/artfynd/A 16493-2025 artfynd.xlsx
+++ b/artfynd/A 16493-2025 artfynd.xlsx
@@ -5009,10 +5009,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>124756755</v>
+        <v>124756762</v>
       </c>
       <c r="B43" t="n">
-        <v>91299</v>
+        <v>78810</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5025,21 +5025,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>658</v>
+        <v>6425</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5049,10 +5049,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>452538</v>
+        <v>452508</v>
       </c>
       <c r="R43" t="n">
-        <v>6990659</v>
+        <v>6990903</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5084,7 +5084,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>11:58</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5094,7 +5094,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>11:58</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5121,10 +5121,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>124756762</v>
+        <v>124756755</v>
       </c>
       <c r="B44" t="n">
-        <v>78810</v>
+        <v>91299</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5137,21 +5137,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6425</v>
+        <v>658</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5161,10 +5161,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>452508</v>
+        <v>452538</v>
       </c>
       <c r="R44" t="n">
-        <v>6990903</v>
+        <v>6990659</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5196,7 +5196,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>11:58</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5206,7 +5206,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>11:58</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5233,10 +5233,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>124756741</v>
+        <v>124753620</v>
       </c>
       <c r="B45" t="n">
-        <v>79851</v>
+        <v>98101</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5245,25 +5245,25 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>229497</v>
+        <v>220787</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5273,10 +5273,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>452682</v>
+        <v>452554</v>
       </c>
       <c r="R45" t="n">
-        <v>6990476</v>
+        <v>6990657</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5306,19 +5306,14 @@
           <t>2025-05-03</t>
         </is>
       </c>
-      <c r="Z45" t="inlineStr">
-        <is>
-          <t>13:54</t>
-        </is>
-      </c>
       <c r="AA45" t="inlineStr">
         <is>
           <t>2025-05-03</t>
         </is>
       </c>
-      <c r="AB45" t="inlineStr">
-        <is>
-          <t>13:54</t>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>Minst 30</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5329,41 +5324,26 @@
       </c>
       <c r="AG45" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ45" t="inlineStr">
-        <is>
-          <t>rönn</t>
-        </is>
-      </c>
-      <c r="AK45" t="inlineStr">
-        <is>
-          <t>Sorbus aucuparia</t>
-        </is>
-      </c>
-      <c r="AO45" t="inlineStr">
-        <is>
-          <t>Sorbus aucuparia</t>
-        </is>
       </c>
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>124753620</v>
+        <v>124756741</v>
       </c>
       <c r="B46" t="n">
-        <v>98101</v>
+        <v>79851</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5372,25 +5352,25 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>220787</v>
+        <v>229497</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5400,10 +5380,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>452554</v>
+        <v>452682</v>
       </c>
       <c r="R46" t="n">
-        <v>6990657</v>
+        <v>6990476</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5433,14 +5413,19 @@
           <t>2025-05-03</t>
         </is>
       </c>
+      <c r="Z46" t="inlineStr">
+        <is>
+          <t>13:54</t>
+        </is>
+      </c>
       <c r="AA46" t="inlineStr">
         <is>
           <t>2025-05-03</t>
         </is>
       </c>
-      <c r="AC46" t="inlineStr">
-        <is>
-          <t>Minst 30</t>
+      <c r="AB46" t="inlineStr">
+        <is>
+          <t>13:54</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5451,26 +5436,41 @@
       </c>
       <c r="AG46" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ46" t="inlineStr">
+        <is>
+          <t>rönn</t>
+        </is>
+      </c>
+      <c r="AK46" t="inlineStr">
+        <is>
+          <t>Sorbus aucuparia</t>
+        </is>
+      </c>
+      <c r="AO46" t="inlineStr">
+        <is>
+          <t>Sorbus aucuparia</t>
+        </is>
       </c>
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>124753621</v>
+        <v>124753639</v>
       </c>
       <c r="B47" t="n">
-        <v>98101</v>
+        <v>78810</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5479,25 +5479,25 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5507,10 +5507,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>452506</v>
+        <v>452511</v>
       </c>
       <c r="R47" t="n">
-        <v>6990758</v>
+        <v>6990733</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5543,11 +5543,6 @@
       <c r="AA47" t="inlineStr">
         <is>
           <t>2025-05-03</t>
-        </is>
-      </c>
-      <c r="AC47" t="inlineStr">
-        <is>
-          <t>Minst 60</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5574,10 +5569,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>124753639</v>
+        <v>124753621</v>
       </c>
       <c r="B48" t="n">
-        <v>78810</v>
+        <v>98101</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5586,25 +5581,25 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5614,10 +5609,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>452511</v>
+        <v>452506</v>
       </c>
       <c r="R48" t="n">
-        <v>6990733</v>
+        <v>6990758</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5650,6 +5645,11 @@
       <c r="AA48" t="inlineStr">
         <is>
           <t>2025-05-03</t>
+        </is>
+      </c>
+      <c r="AC48" t="inlineStr">
+        <is>
+          <t>Minst 60</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -7069,10 +7069,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>124753588</v>
+        <v>124756743</v>
       </c>
       <c r="B61" t="n">
-        <v>91012</v>
+        <v>79891</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -7085,21 +7085,21 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -7109,10 +7109,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>452311</v>
+        <v>452682</v>
       </c>
       <c r="R61" t="n">
-        <v>6990887</v>
+        <v>6990476</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7142,11 +7142,21 @@
           <t>2025-05-03</t>
         </is>
       </c>
+      <c r="Z61" t="inlineStr">
+        <is>
+          <t>13:53</t>
+        </is>
+      </c>
       <c r="AA61" t="inlineStr">
         <is>
           <t>2025-05-03</t>
         </is>
       </c>
+      <c r="AB61" t="inlineStr">
+        <is>
+          <t>13:53</t>
+        </is>
+      </c>
       <c r="AD61" t="b">
         <v>0</v>
       </c>
@@ -7155,26 +7165,41 @@
       </c>
       <c r="AG61" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ61" t="inlineStr">
+        <is>
+          <t>rönn</t>
+        </is>
+      </c>
+      <c r="AK61" t="inlineStr">
+        <is>
+          <t>Sorbus aucuparia</t>
+        </is>
+      </c>
+      <c r="AO61" t="inlineStr">
+        <is>
+          <t>Sorbus aucuparia</t>
+        </is>
       </c>
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>124753585</v>
+        <v>124756779</v>
       </c>
       <c r="B62" t="n">
-        <v>91012</v>
+        <v>78810</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -7187,21 +7212,21 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -7211,10 +7236,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>452595</v>
+        <v>452143</v>
       </c>
       <c r="R62" t="n">
-        <v>6990913</v>
+        <v>6990780</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7244,9 +7269,19 @@
           <t>2025-05-03</t>
         </is>
       </c>
+      <c r="Z62" t="inlineStr">
+        <is>
+          <t>09:51</t>
+        </is>
+      </c>
       <c r="AA62" t="inlineStr">
         <is>
           <t>2025-05-03</t>
+        </is>
+      </c>
+      <c r="AB62" t="inlineStr">
+        <is>
+          <t>09:51</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7261,22 +7296,22 @@
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>124756743</v>
+        <v>124753629</v>
       </c>
       <c r="B63" t="n">
-        <v>79891</v>
+        <v>98101</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -7285,25 +7320,25 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -7313,10 +7348,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>452682</v>
+        <v>452576</v>
       </c>
       <c r="R63" t="n">
-        <v>6990476</v>
+        <v>6990924</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7346,19 +7381,14 @@
           <t>2025-05-03</t>
         </is>
       </c>
-      <c r="Z63" t="inlineStr">
-        <is>
-          <t>13:53</t>
-        </is>
-      </c>
       <c r="AA63" t="inlineStr">
         <is>
           <t>2025-05-03</t>
         </is>
       </c>
-      <c r="AB63" t="inlineStr">
-        <is>
-          <t>13:53</t>
+      <c r="AC63" t="inlineStr">
+        <is>
+          <t>Minst 30</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7369,41 +7399,26 @@
       </c>
       <c r="AG63" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ63" t="inlineStr">
-        <is>
-          <t>rönn</t>
-        </is>
-      </c>
-      <c r="AK63" t="inlineStr">
-        <is>
-          <t>Sorbus aucuparia</t>
-        </is>
-      </c>
-      <c r="AO63" t="inlineStr">
-        <is>
-          <t>Sorbus aucuparia</t>
-        </is>
       </c>
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>124756779</v>
+        <v>124753623</v>
       </c>
       <c r="B64" t="n">
-        <v>78810</v>
+        <v>98101</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7412,25 +7427,25 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7440,10 +7455,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>452143</v>
+        <v>452510</v>
       </c>
       <c r="R64" t="n">
-        <v>6990780</v>
+        <v>6990873</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7473,19 +7488,14 @@
           <t>2025-05-03</t>
         </is>
       </c>
-      <c r="Z64" t="inlineStr">
-        <is>
-          <t>09:51</t>
-        </is>
-      </c>
       <c r="AA64" t="inlineStr">
         <is>
           <t>2025-05-03</t>
         </is>
       </c>
-      <c r="AB64" t="inlineStr">
-        <is>
-          <t>09:51</t>
+      <c r="AC64" t="inlineStr">
+        <is>
+          <t>Minst 50</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7500,22 +7510,22 @@
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>124753629</v>
+        <v>124753588</v>
       </c>
       <c r="B65" t="n">
-        <v>98101</v>
+        <v>91012</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -7524,25 +7534,25 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7552,10 +7562,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>452576</v>
+        <v>452311</v>
       </c>
       <c r="R65" t="n">
-        <v>6990924</v>
+        <v>6990887</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7588,11 +7598,6 @@
       <c r="AA65" t="inlineStr">
         <is>
           <t>2025-05-03</t>
-        </is>
-      </c>
-      <c r="AC65" t="inlineStr">
-        <is>
-          <t>Minst 30</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7619,10 +7624,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>124753623</v>
+        <v>124753585</v>
       </c>
       <c r="B66" t="n">
-        <v>98101</v>
+        <v>91012</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -7631,25 +7636,25 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7659,10 +7664,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>452510</v>
+        <v>452595</v>
       </c>
       <c r="R66" t="n">
-        <v>6990873</v>
+        <v>6990913</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7695,11 +7700,6 @@
       <c r="AA66" t="inlineStr">
         <is>
           <t>2025-05-03</t>
-        </is>
-      </c>
-      <c r="AC66" t="inlineStr">
-        <is>
-          <t>Minst 50</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -12178,10 +12178,10 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>124756764</v>
+        <v>124753632</v>
       </c>
       <c r="B107" t="n">
-        <v>78810</v>
+        <v>98101</v>
       </c>
       <c r="C107" t="inlineStr">
         <is>
@@ -12190,25 +12190,25 @@
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E107" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
@@ -12218,10 +12218,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>452462</v>
+        <v>452455</v>
       </c>
       <c r="R107" t="n">
-        <v>6990915</v>
+        <v>6990942</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -12251,19 +12251,14 @@
           <t>2025-05-03</t>
         </is>
       </c>
-      <c r="Z107" t="inlineStr">
-        <is>
-          <t>11:11</t>
-        </is>
-      </c>
       <c r="AA107" t="inlineStr">
         <is>
           <t>2025-05-03</t>
         </is>
       </c>
-      <c r="AB107" t="inlineStr">
-        <is>
-          <t>11:11</t>
+      <c r="AC107" t="inlineStr">
+        <is>
+          <t>Minst 30</t>
         </is>
       </c>
       <c r="AD107" t="b">
@@ -12278,19 +12273,19 @@
       <c r="AT107" t="inlineStr"/>
       <c r="AW107" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX107" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY107" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>124753632</v>
+        <v>124753624</v>
       </c>
       <c r="B108" t="n">
         <v>98101</v>
@@ -12330,10 +12325,10 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>452455</v>
+        <v>452528</v>
       </c>
       <c r="R108" t="n">
-        <v>6990942</v>
+        <v>6990882</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -12397,7 +12392,7 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>124753624</v>
+        <v>124756739</v>
       </c>
       <c r="B109" t="n">
         <v>98101</v>
@@ -12430,17 +12425,29 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I109" t="inlineStr"/>
+      <c r="I109" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="J109" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K109" t="inlineStr"/>
+      <c r="L109" t="inlineStr"/>
+      <c r="N109" t="inlineStr"/>
       <c r="P109" t="inlineStr">
         <is>
           <t>Häggsåsen N, Jmt</t>
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>452528</v>
+        <v>452711</v>
       </c>
       <c r="R109" t="n">
-        <v>6990882</v>
+        <v>6990473</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -12470,14 +12477,19 @@
           <t>2025-05-03</t>
         </is>
       </c>
+      <c r="Z109" t="inlineStr">
+        <is>
+          <t>14:01</t>
+        </is>
+      </c>
       <c r="AA109" t="inlineStr">
         <is>
           <t>2025-05-03</t>
         </is>
       </c>
-      <c r="AC109" t="inlineStr">
-        <is>
-          <t>Minst 30</t>
+      <c r="AB109" t="inlineStr">
+        <is>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AD109" t="b">
@@ -12486,28 +12498,29 @@
       <c r="AE109" t="b">
         <v>0</v>
       </c>
+      <c r="AF109" t="inlineStr"/>
       <c r="AG109" t="b">
         <v>0</v>
       </c>
       <c r="AT109" t="inlineStr"/>
       <c r="AW109" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX109" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY109" t="inlineStr"/>
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>124756739</v>
+        <v>124756764</v>
       </c>
       <c r="B110" t="n">
-        <v>98101</v>
+        <v>78810</v>
       </c>
       <c r="C110" t="inlineStr">
         <is>
@@ -12516,50 +12529,38 @@
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E110" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I110" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="J110" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K110" t="inlineStr"/>
-      <c r="L110" t="inlineStr"/>
-      <c r="N110" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I110" t="inlineStr"/>
       <c r="P110" t="inlineStr">
         <is>
           <t>Häggsåsen N, Jmt</t>
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>452711</v>
+        <v>452462</v>
       </c>
       <c r="R110" t="n">
-        <v>6990473</v>
+        <v>6990915</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -12591,7 +12592,7 @@
       </c>
       <c r="Z110" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>11:11</t>
         </is>
       </c>
       <c r="AA110" t="inlineStr">
@@ -12601,7 +12602,7 @@
       </c>
       <c r="AB110" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>11:11</t>
         </is>
       </c>
       <c r="AD110" t="b">
@@ -12610,7 +12611,6 @@
       <c r="AE110" t="b">
         <v>0</v>
       </c>
-      <c r="AF110" t="inlineStr"/>
       <c r="AG110" t="b">
         <v>0</v>
       </c>
@@ -14153,10 +14153,10 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>124756740</v>
+        <v>124753637</v>
       </c>
       <c r="B125" t="n">
-        <v>91457</v>
+        <v>91030</v>
       </c>
       <c r="C125" t="inlineStr">
         <is>
@@ -14165,25 +14165,25 @@
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E125" t="n">
-        <v>1209</v>
+        <v>5432</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I125" t="inlineStr"/>
@@ -14193,10 +14193,10 @@
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>452701</v>
+        <v>452696</v>
       </c>
       <c r="R125" t="n">
-        <v>6990475</v>
+        <v>6990466</v>
       </c>
       <c r="S125" t="n">
         <v>10</v>
@@ -14226,19 +14226,9 @@
           <t>2025-05-03</t>
         </is>
       </c>
-      <c r="Z125" t="inlineStr">
-        <is>
-          <t>13:58</t>
-        </is>
-      </c>
       <c r="AA125" t="inlineStr">
         <is>
           <t>2025-05-03</t>
-        </is>
-      </c>
-      <c r="AB125" t="inlineStr">
-        <is>
-          <t>13:58</t>
         </is>
       </c>
       <c r="AD125" t="b">
@@ -14253,22 +14243,22 @@
       <c r="AT125" t="inlineStr"/>
       <c r="AW125" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX125" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY125" t="inlineStr"/>
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>124753614</v>
+        <v>124756740</v>
       </c>
       <c r="B126" t="n">
-        <v>98101</v>
+        <v>91457</v>
       </c>
       <c r="C126" t="inlineStr">
         <is>
@@ -14281,21 +14271,21 @@
         </is>
       </c>
       <c r="E126" t="n">
-        <v>220787</v>
+        <v>1209</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I126" t="inlineStr"/>
@@ -14305,10 +14295,10 @@
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>452751</v>
+        <v>452701</v>
       </c>
       <c r="R126" t="n">
-        <v>6990344</v>
+        <v>6990475</v>
       </c>
       <c r="S126" t="n">
         <v>10</v>
@@ -14338,14 +14328,19 @@
           <t>2025-05-03</t>
         </is>
       </c>
+      <c r="Z126" t="inlineStr">
+        <is>
+          <t>13:58</t>
+        </is>
+      </c>
       <c r="AA126" t="inlineStr">
         <is>
           <t>2025-05-03</t>
         </is>
       </c>
-      <c r="AC126" t="inlineStr">
-        <is>
-          <t>Minst 200</t>
+      <c r="AB126" t="inlineStr">
+        <is>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AD126" t="b">
@@ -14360,19 +14355,19 @@
       <c r="AT126" t="inlineStr"/>
       <c r="AW126" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX126" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY126" t="inlineStr"/>
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>124753630</v>
+        <v>124753614</v>
       </c>
       <c r="B127" t="n">
         <v>98101</v>
@@ -14412,10 +14407,10 @@
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>452273</v>
+        <v>452751</v>
       </c>
       <c r="R127" t="n">
-        <v>6990906</v>
+        <v>6990344</v>
       </c>
       <c r="S127" t="n">
         <v>10</v>
@@ -14452,7 +14447,7 @@
       </c>
       <c r="AC127" t="inlineStr">
         <is>
-          <t>Minst 10</t>
+          <t>Minst 200</t>
         </is>
       </c>
       <c r="AD127" t="b">
@@ -14479,7 +14474,7 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>124753613</v>
+        <v>124753630</v>
       </c>
       <c r="B128" t="n">
         <v>98101</v>
@@ -14519,10 +14514,10 @@
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>452777</v>
+        <v>452273</v>
       </c>
       <c r="R128" t="n">
-        <v>6990299</v>
+        <v>6990906</v>
       </c>
       <c r="S128" t="n">
         <v>10</v>
@@ -14559,7 +14554,7 @@
       </c>
       <c r="AC128" t="inlineStr">
         <is>
-          <t>Minst 100</t>
+          <t>Minst 10</t>
         </is>
       </c>
       <c r="AD128" t="b">
@@ -14586,10 +14581,10 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>124753637</v>
+        <v>124753613</v>
       </c>
       <c r="B129" t="n">
-        <v>91030</v>
+        <v>98101</v>
       </c>
       <c r="C129" t="inlineStr">
         <is>
@@ -14598,25 +14593,25 @@
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E129" t="n">
-        <v>5432</v>
+        <v>220787</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I129" t="inlineStr"/>
@@ -14626,10 +14621,10 @@
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>452696</v>
+        <v>452777</v>
       </c>
       <c r="R129" t="n">
-        <v>6990466</v>
+        <v>6990299</v>
       </c>
       <c r="S129" t="n">
         <v>10</v>
@@ -14662,6 +14657,11 @@
       <c r="AA129" t="inlineStr">
         <is>
           <t>2025-05-03</t>
+        </is>
+      </c>
+      <c r="AC129" t="inlineStr">
+        <is>
+          <t>Minst 100</t>
         </is>
       </c>
       <c r="AD129" t="b">
@@ -14910,10 +14910,10 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>124753587</v>
+        <v>124753611</v>
       </c>
       <c r="B132" t="n">
-        <v>91012</v>
+        <v>98101</v>
       </c>
       <c r="C132" t="inlineStr">
         <is>
@@ -14922,25 +14922,25 @@
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E132" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I132" t="inlineStr"/>
@@ -14950,10 +14950,10 @@
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>452331</v>
+        <v>452997</v>
       </c>
       <c r="R132" t="n">
-        <v>6990929</v>
+        <v>6990332</v>
       </c>
       <c r="S132" t="n">
         <v>10</v>
@@ -14986,6 +14986,11 @@
       <c r="AA132" t="inlineStr">
         <is>
           <t>2025-05-03</t>
+        </is>
+      </c>
+      <c r="AC132" t="inlineStr">
+        <is>
+          <t>Minst 100</t>
         </is>
       </c>
       <c r="AD132" t="b">
@@ -15012,10 +15017,10 @@
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>124756759</v>
+        <v>124756736</v>
       </c>
       <c r="B133" t="n">
-        <v>91012</v>
+        <v>98101</v>
       </c>
       <c r="C133" t="inlineStr">
         <is>
@@ -15024,38 +15029,50 @@
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E133" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I133" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I133" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J133" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K133" t="inlineStr"/>
+      <c r="L133" t="inlineStr"/>
+      <c r="N133" t="inlineStr"/>
       <c r="P133" t="inlineStr">
         <is>
           <t>Häggsåsen N, Jmt</t>
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>452509</v>
+        <v>452691</v>
       </c>
       <c r="R133" t="n">
-        <v>6990778</v>
+        <v>6990422</v>
       </c>
       <c r="S133" t="n">
         <v>10</v>
@@ -15087,7 +15104,7 @@
       </c>
       <c r="Z133" t="inlineStr">
         <is>
-          <t>11:39</t>
+          <t>14:13</t>
         </is>
       </c>
       <c r="AA133" t="inlineStr">
@@ -15097,7 +15114,7 @@
       </c>
       <c r="AB133" t="inlineStr">
         <is>
-          <t>11:39</t>
+          <t>14:13</t>
         </is>
       </c>
       <c r="AD133" t="b">
@@ -15106,6 +15123,7 @@
       <c r="AE133" t="b">
         <v>0</v>
       </c>
+      <c r="AF133" t="inlineStr"/>
       <c r="AG133" t="b">
         <v>0</v>
       </c>
@@ -15124,7 +15142,7 @@
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>124756753</v>
+        <v>124753587</v>
       </c>
       <c r="B134" t="n">
         <v>91012</v>
@@ -15164,10 +15182,10 @@
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>452608</v>
+        <v>452331</v>
       </c>
       <c r="R134" t="n">
-        <v>6990625</v>
+        <v>6990929</v>
       </c>
       <c r="S134" t="n">
         <v>10</v>
@@ -15197,19 +15215,9 @@
           <t>2025-05-03</t>
         </is>
       </c>
-      <c r="Z134" t="inlineStr">
-        <is>
-          <t>12:07</t>
-        </is>
-      </c>
       <c r="AA134" t="inlineStr">
         <is>
           <t>2025-05-03</t>
-        </is>
-      </c>
-      <c r="AB134" t="inlineStr">
-        <is>
-          <t>12:07</t>
         </is>
       </c>
       <c r="AD134" t="b">
@@ -15224,22 +15232,22 @@
       <c r="AT134" t="inlineStr"/>
       <c r="AW134" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX134" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY134" t="inlineStr"/>
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>124753611</v>
+        <v>124756759</v>
       </c>
       <c r="B135" t="n">
-        <v>98101</v>
+        <v>91012</v>
       </c>
       <c r="C135" t="inlineStr">
         <is>
@@ -15248,25 +15256,25 @@
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E135" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I135" t="inlineStr"/>
@@ -15276,10 +15284,10 @@
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>452997</v>
+        <v>452509</v>
       </c>
       <c r="R135" t="n">
-        <v>6990332</v>
+        <v>6990778</v>
       </c>
       <c r="S135" t="n">
         <v>10</v>
@@ -15309,14 +15317,19 @@
           <t>2025-05-03</t>
         </is>
       </c>
+      <c r="Z135" t="inlineStr">
+        <is>
+          <t>11:39</t>
+        </is>
+      </c>
       <c r="AA135" t="inlineStr">
         <is>
           <t>2025-05-03</t>
         </is>
       </c>
-      <c r="AC135" t="inlineStr">
-        <is>
-          <t>Minst 100</t>
+      <c r="AB135" t="inlineStr">
+        <is>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AD135" t="b">
@@ -15331,22 +15344,22 @@
       <c r="AT135" t="inlineStr"/>
       <c r="AW135" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX135" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY135" t="inlineStr"/>
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>124756736</v>
+        <v>124756753</v>
       </c>
       <c r="B136" t="n">
-        <v>98101</v>
+        <v>91012</v>
       </c>
       <c r="C136" t="inlineStr">
         <is>
@@ -15355,50 +15368,38 @@
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E136" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I136" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J136" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K136" t="inlineStr"/>
-      <c r="L136" t="inlineStr"/>
-      <c r="N136" t="inlineStr"/>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I136" t="inlineStr"/>
       <c r="P136" t="inlineStr">
         <is>
           <t>Häggsåsen N, Jmt</t>
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>452691</v>
+        <v>452608</v>
       </c>
       <c r="R136" t="n">
-        <v>6990422</v>
+        <v>6990625</v>
       </c>
       <c r="S136" t="n">
         <v>10</v>
@@ -15430,7 +15431,7 @@
       </c>
       <c r="Z136" t="inlineStr">
         <is>
-          <t>14:13</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AA136" t="inlineStr">
@@ -15440,7 +15441,7 @@
       </c>
       <c r="AB136" t="inlineStr">
         <is>
-          <t>14:13</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AD136" t="b">
@@ -15449,7 +15450,6 @@
       <c r="AE136" t="b">
         <v>0</v>
       </c>
-      <c r="AF136" t="inlineStr"/>
       <c r="AG136" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 16493-2025 artfynd.xlsx
+++ b/artfynd/A 16493-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124705584</v>
+        <v>124695424</v>
       </c>
       <c r="B2" t="n">
-        <v>91030</v>
+        <v>91012</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,34 +691,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5432</v>
+        <v>1202</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Häggsåsen, Häggsåsen, Jmt</t>
+          <t>Tjärnflon, Tjärnflon, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>452865</v>
+        <v>452642</v>
       </c>
       <c r="R2" t="n">
-        <v>6990382</v>
+        <v>6990548</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124695424</v>
+        <v>124705584</v>
       </c>
       <c r="B4" t="n">
-        <v>91012</v>
+        <v>91030</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -895,34 +895,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1202</v>
+        <v>5432</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Tjärnflon, Tjärnflon, Jmt</t>
+          <t>Häggsåsen, Häggsåsen, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>452642</v>
+        <v>452865</v>
       </c>
       <c r="R4" t="n">
-        <v>6990548</v>
+        <v>6990382</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -3964,10 +3964,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>124704726</v>
+        <v>124702530</v>
       </c>
       <c r="B33" t="n">
-        <v>91012</v>
+        <v>79891</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -3980,21 +3980,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4004,7 +4004,7 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>452828</v>
+        <v>452746</v>
       </c>
       <c r="R33" t="n">
         <v>6990384</v>
@@ -4066,10 +4066,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>124702530</v>
+        <v>124704726</v>
       </c>
       <c r="B34" t="n">
-        <v>79891</v>
+        <v>91012</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4082,21 +4082,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4106,7 +4106,7 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>452746</v>
+        <v>452828</v>
       </c>
       <c r="R34" t="n">
         <v>6990384</v>
@@ -5009,10 +5009,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>124753577</v>
+        <v>124756758</v>
       </c>
       <c r="B43" t="n">
-        <v>91012</v>
+        <v>90962</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5025,21 +5025,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>1202</v>
+        <v>112</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Stjärntagging</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Asterodon ferruginosus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Pat.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5049,10 +5049,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>452833</v>
+        <v>452509</v>
       </c>
       <c r="R43" t="n">
-        <v>6990388</v>
+        <v>6990778</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5082,9 +5082,19 @@
           <t>2025-05-03</t>
         </is>
       </c>
+      <c r="Z43" t="inlineStr">
+        <is>
+          <t>11:40</t>
+        </is>
+      </c>
       <c r="AA43" t="inlineStr">
         <is>
           <t>2025-05-03</t>
+        </is>
+      </c>
+      <c r="AB43" t="inlineStr">
+        <is>
+          <t>11:40</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5099,19 +5109,19 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>124753625</v>
+        <v>124756752</v>
       </c>
       <c r="B44" t="n">
         <v>98101</v>
@@ -5144,17 +5154,29 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I44" t="inlineStr"/>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr"/>
+      <c r="L44" t="inlineStr"/>
+      <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
           <t>Häggsåsen N, Jmt</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>452550</v>
+        <v>452608</v>
       </c>
       <c r="R44" t="n">
-        <v>6990907</v>
+        <v>6990625</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5184,14 +5206,19 @@
           <t>2025-05-03</t>
         </is>
       </c>
+      <c r="Z44" t="inlineStr">
+        <is>
+          <t>12:07</t>
+        </is>
+      </c>
       <c r="AA44" t="inlineStr">
         <is>
           <t>2025-05-03</t>
         </is>
       </c>
-      <c r="AC44" t="inlineStr">
-        <is>
-          <t>Minst 50</t>
+      <c r="AB44" t="inlineStr">
+        <is>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5200,28 +5227,29 @@
       <c r="AE44" t="b">
         <v>0</v>
       </c>
+      <c r="AF44" t="inlineStr"/>
       <c r="AG44" t="b">
         <v>0</v>
       </c>
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>124756758</v>
+        <v>124753625</v>
       </c>
       <c r="B45" t="n">
-        <v>90962</v>
+        <v>98101</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5230,25 +5258,25 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>112</v>
+        <v>220787</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Stjärntagging</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Asterodon ferruginosus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>Pat.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5258,10 +5286,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>452509</v>
+        <v>452550</v>
       </c>
       <c r="R45" t="n">
-        <v>6990778</v>
+        <v>6990907</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5291,19 +5319,14 @@
           <t>2025-05-03</t>
         </is>
       </c>
-      <c r="Z45" t="inlineStr">
-        <is>
-          <t>11:40</t>
-        </is>
-      </c>
       <c r="AA45" t="inlineStr">
         <is>
           <t>2025-05-03</t>
         </is>
       </c>
-      <c r="AB45" t="inlineStr">
-        <is>
-          <t>11:40</t>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>Minst 50</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5318,22 +5341,22 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>124756752</v>
+        <v>124753577</v>
       </c>
       <c r="B46" t="n">
-        <v>98101</v>
+        <v>91012</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5342,50 +5365,38 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J46" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K46" t="inlineStr"/>
-      <c r="L46" t="inlineStr"/>
-      <c r="N46" t="inlineStr"/>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
           <t>Häggsåsen N, Jmt</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>452608</v>
+        <v>452833</v>
       </c>
       <c r="R46" t="n">
-        <v>6990625</v>
+        <v>6990388</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5415,40 +5426,29 @@
           <t>2025-05-03</t>
         </is>
       </c>
-      <c r="Z46" t="inlineStr">
-        <is>
-          <t>12:07</t>
-        </is>
-      </c>
       <c r="AA46" t="inlineStr">
         <is>
           <t>2025-05-03</t>
         </is>
       </c>
-      <c r="AB46" t="inlineStr">
-        <is>
-          <t>12:07</t>
-        </is>
-      </c>
       <c r="AD46" t="b">
         <v>0</v>
       </c>
       <c r="AE46" t="b">
         <v>0</v>
       </c>
-      <c r="AF46" t="inlineStr"/>
       <c r="AG46" t="b">
         <v>0</v>
       </c>
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
@@ -7228,7 +7228,7 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>124753586</v>
+        <v>124756759</v>
       </c>
       <c r="B63" t="n">
         <v>91012</v>
@@ -7268,10 +7268,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>452500</v>
+        <v>452509</v>
       </c>
       <c r="R63" t="n">
-        <v>6990950</v>
+        <v>6990778</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7301,9 +7301,19 @@
           <t>2025-05-03</t>
         </is>
       </c>
+      <c r="Z63" t="inlineStr">
+        <is>
+          <t>11:39</t>
+        </is>
+      </c>
       <c r="AA63" t="inlineStr">
         <is>
           <t>2025-05-03</t>
+        </is>
+      </c>
+      <c r="AB63" t="inlineStr">
+        <is>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7318,22 +7328,22 @@
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>124756766</v>
+        <v>124753586</v>
       </c>
       <c r="B64" t="n">
-        <v>79891</v>
+        <v>91012</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7346,21 +7356,21 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7370,10 +7380,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>452396</v>
+        <v>452500</v>
       </c>
       <c r="R64" t="n">
-        <v>6990981</v>
+        <v>6990950</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7403,19 +7413,9 @@
           <t>2025-05-03</t>
         </is>
       </c>
-      <c r="Z64" t="inlineStr">
-        <is>
-          <t>10:58</t>
-        </is>
-      </c>
       <c r="AA64" t="inlineStr">
         <is>
           <t>2025-05-03</t>
-        </is>
-      </c>
-      <c r="AB64" t="inlineStr">
-        <is>
-          <t>10:58</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7430,22 +7430,22 @@
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>124756759</v>
+        <v>124756766</v>
       </c>
       <c r="B65" t="n">
-        <v>91012</v>
+        <v>79891</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -7458,21 +7458,21 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7482,10 +7482,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>452509</v>
+        <v>452396</v>
       </c>
       <c r="R65" t="n">
-        <v>6990778</v>
+        <v>6990981</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7517,7 +7517,7 @@
       </c>
       <c r="Z65" t="inlineStr">
         <is>
-          <t>11:39</t>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
@@ -7527,7 +7527,7 @@
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>11:39</t>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -8329,10 +8329,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>124756775</v>
+        <v>124756740</v>
       </c>
       <c r="B73" t="n">
-        <v>79891</v>
+        <v>91457</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -8341,25 +8341,25 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>6458</v>
+        <v>1209</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -8369,10 +8369,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>452308</v>
+        <v>452701</v>
       </c>
       <c r="R73" t="n">
-        <v>6990943</v>
+        <v>6990475</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8404,7 +8404,7 @@
       </c>
       <c r="Z73" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
@@ -8414,7 +8414,7 @@
       </c>
       <c r="AB73" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8441,10 +8441,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>124756740</v>
+        <v>124756775</v>
       </c>
       <c r="B74" t="n">
-        <v>91457</v>
+        <v>79891</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -8453,25 +8453,25 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>1209</v>
+        <v>6458</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -8481,10 +8481,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>452701</v>
+        <v>452308</v>
       </c>
       <c r="R74" t="n">
-        <v>6990475</v>
+        <v>6990943</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8516,7 +8516,7 @@
       </c>
       <c r="Z74" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>10:22</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
@@ -8526,7 +8526,7 @@
       </c>
       <c r="AB74" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>10:22</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -9093,10 +9093,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>124753608</v>
+        <v>124756756</v>
       </c>
       <c r="B80" t="n">
-        <v>79891</v>
+        <v>78810</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
@@ -9109,21 +9109,21 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -9133,10 +9133,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>452731</v>
+        <v>452545</v>
       </c>
       <c r="R80" t="n">
-        <v>6990377</v>
+        <v>6990691</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -9166,9 +9166,19 @@
           <t>2025-05-03</t>
         </is>
       </c>
+      <c r="Z80" t="inlineStr">
+        <is>
+          <t>11:54</t>
+        </is>
+      </c>
       <c r="AA80" t="inlineStr">
         <is>
           <t>2025-05-03</t>
+        </is>
+      </c>
+      <c r="AB80" t="inlineStr">
+        <is>
+          <t>11:54</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -9183,22 +9193,22 @@
       <c r="AT80" t="inlineStr"/>
       <c r="AW80" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX80" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>124753583</v>
+        <v>124756718</v>
       </c>
       <c r="B81" t="n">
-        <v>91012</v>
+        <v>91030</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
@@ -9211,21 +9221,21 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>1202</v>
+        <v>5432</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -9235,10 +9245,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>452606</v>
+        <v>452857</v>
       </c>
       <c r="R81" t="n">
-        <v>6990623</v>
+        <v>6990267</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -9268,9 +9278,19 @@
           <t>2025-05-03</t>
         </is>
       </c>
+      <c r="Z81" t="inlineStr">
+        <is>
+          <t>15:03</t>
+        </is>
+      </c>
       <c r="AA81" t="inlineStr">
         <is>
           <t>2025-05-03</t>
+        </is>
+      </c>
+      <c r="AB81" t="inlineStr">
+        <is>
+          <t>15:03</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -9285,22 +9305,22 @@
       <c r="AT81" t="inlineStr"/>
       <c r="AW81" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX81" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>124756756</v>
+        <v>124753608</v>
       </c>
       <c r="B82" t="n">
-        <v>78810</v>
+        <v>79891</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
@@ -9313,21 +9333,21 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -9337,10 +9357,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>452545</v>
+        <v>452731</v>
       </c>
       <c r="R82" t="n">
-        <v>6990691</v>
+        <v>6990377</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -9370,19 +9390,9 @@
           <t>2025-05-03</t>
         </is>
       </c>
-      <c r="Z82" t="inlineStr">
-        <is>
-          <t>11:54</t>
-        </is>
-      </c>
       <c r="AA82" t="inlineStr">
         <is>
           <t>2025-05-03</t>
-        </is>
-      </c>
-      <c r="AB82" t="inlineStr">
-        <is>
-          <t>11:54</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -9397,22 +9407,22 @@
       <c r="AT82" t="inlineStr"/>
       <c r="AW82" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX82" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>124756718</v>
+        <v>124753583</v>
       </c>
       <c r="B83" t="n">
-        <v>91030</v>
+        <v>91012</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
@@ -9425,21 +9435,21 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>5432</v>
+        <v>1202</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -9449,10 +9459,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>452857</v>
+        <v>452606</v>
       </c>
       <c r="R83" t="n">
-        <v>6990267</v>
+        <v>6990623</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9482,19 +9492,9 @@
           <t>2025-05-03</t>
         </is>
       </c>
-      <c r="Z83" t="inlineStr">
-        <is>
-          <t>15:03</t>
-        </is>
-      </c>
       <c r="AA83" t="inlineStr">
         <is>
           <t>2025-05-03</t>
-        </is>
-      </c>
-      <c r="AB83" t="inlineStr">
-        <is>
-          <t>15:03</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -9509,12 +9509,12 @@
       <c r="AT83" t="inlineStr"/>
       <c r="AW83" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX83" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY83" t="inlineStr"/>
@@ -11375,10 +11375,10 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>124756742</v>
+        <v>124756763</v>
       </c>
       <c r="B101" t="n">
-        <v>79927</v>
+        <v>98101</v>
       </c>
       <c r="C101" t="inlineStr">
         <is>
@@ -11387,38 +11387,50 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E101" t="n">
-        <v>6464</v>
+        <v>220787</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
-        </is>
-      </c>
-      <c r="I101" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I101" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J101" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K101" t="inlineStr"/>
+      <c r="L101" t="inlineStr"/>
+      <c r="N101" t="inlineStr"/>
       <c r="P101" t="inlineStr">
         <is>
           <t>Häggsåsen N, Jmt</t>
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>452682</v>
+        <v>452478</v>
       </c>
       <c r="R101" t="n">
-        <v>6990476</v>
+        <v>6990887</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -11450,7 +11462,7 @@
       </c>
       <c r="Z101" t="inlineStr">
         <is>
-          <t>13:53</t>
+          <t>11:18</t>
         </is>
       </c>
       <c r="AA101" t="inlineStr">
@@ -11460,7 +11472,7 @@
       </c>
       <c r="AB101" t="inlineStr">
         <is>
-          <t>13:53</t>
+          <t>11:18</t>
         </is>
       </c>
       <c r="AD101" t="b">
@@ -11469,23 +11481,9 @@
       <c r="AE101" t="b">
         <v>0</v>
       </c>
+      <c r="AF101" t="inlineStr"/>
       <c r="AG101" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ101" t="inlineStr">
-        <is>
-          <t>rönn</t>
-        </is>
-      </c>
-      <c r="AK101" t="inlineStr">
-        <is>
-          <t>Sorbus aucuparia</t>
-        </is>
-      </c>
-      <c r="AO101" t="inlineStr">
-        <is>
-          <t>Sorbus aucuparia</t>
-        </is>
       </c>
       <c r="AT101" t="inlineStr"/>
       <c r="AW101" t="inlineStr">
@@ -11502,7 +11500,7 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>124756763</v>
+        <v>124756751</v>
       </c>
       <c r="B102" t="n">
         <v>98101</v>
@@ -11537,7 +11535,7 @@
       </c>
       <c r="I102" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J102" t="inlineStr">
@@ -11554,10 +11552,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>452478</v>
+        <v>452638</v>
       </c>
       <c r="R102" t="n">
-        <v>6990887</v>
+        <v>6990559</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -11589,7 +11587,7 @@
       </c>
       <c r="Z102" t="inlineStr">
         <is>
-          <t>11:18</t>
+          <t>12:23</t>
         </is>
       </c>
       <c r="AA102" t="inlineStr">
@@ -11599,7 +11597,7 @@
       </c>
       <c r="AB102" t="inlineStr">
         <is>
-          <t>11:18</t>
+          <t>12:23</t>
         </is>
       </c>
       <c r="AD102" t="b">
@@ -11627,10 +11625,10 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>124756751</v>
+        <v>124753580</v>
       </c>
       <c r="B103" t="n">
-        <v>98101</v>
+        <v>91012</v>
       </c>
       <c r="C103" t="inlineStr">
         <is>
@@ -11639,50 +11637,38 @@
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E103" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I103" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J103" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K103" t="inlineStr"/>
-      <c r="L103" t="inlineStr"/>
-      <c r="N103" t="inlineStr"/>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I103" t="inlineStr"/>
       <c r="P103" t="inlineStr">
         <is>
           <t>Häggsåsen N, Jmt</t>
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>452638</v>
+        <v>452693</v>
       </c>
       <c r="R103" t="n">
-        <v>6990559</v>
+        <v>6990472</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -11712,50 +11698,39 @@
           <t>2025-05-03</t>
         </is>
       </c>
-      <c r="Z103" t="inlineStr">
-        <is>
-          <t>12:23</t>
-        </is>
-      </c>
       <c r="AA103" t="inlineStr">
         <is>
           <t>2025-05-03</t>
         </is>
       </c>
-      <c r="AB103" t="inlineStr">
-        <is>
-          <t>12:23</t>
-        </is>
-      </c>
       <c r="AD103" t="b">
         <v>0</v>
       </c>
       <c r="AE103" t="b">
         <v>0</v>
       </c>
-      <c r="AF103" t="inlineStr"/>
       <c r="AG103" t="b">
         <v>0</v>
       </c>
       <c r="AT103" t="inlineStr"/>
       <c r="AW103" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX103" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY103" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>124753582</v>
+        <v>124756725</v>
       </c>
       <c r="B104" t="n">
-        <v>91012</v>
+        <v>78810</v>
       </c>
       <c r="C104" t="inlineStr">
         <is>
@@ -11768,21 +11743,21 @@
         </is>
       </c>
       <c r="E104" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
@@ -11792,10 +11767,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>452649</v>
+        <v>452762</v>
       </c>
       <c r="R104" t="n">
-        <v>6990621</v>
+        <v>6990327</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -11825,9 +11800,19 @@
           <t>2025-05-03</t>
         </is>
       </c>
+      <c r="Z104" t="inlineStr">
+        <is>
+          <t>14:37</t>
+        </is>
+      </c>
       <c r="AA104" t="inlineStr">
         <is>
           <t>2025-05-03</t>
+        </is>
+      </c>
+      <c r="AB104" t="inlineStr">
+        <is>
+          <t>14:37</t>
         </is>
       </c>
       <c r="AD104" t="b">
@@ -11842,12 +11827,12 @@
       <c r="AT104" t="inlineStr"/>
       <c r="AW104" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX104" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY104" t="inlineStr"/>
@@ -12068,7 +12053,7 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>124753580</v>
+        <v>124753582</v>
       </c>
       <c r="B107" t="n">
         <v>91012</v>
@@ -12108,10 +12093,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>452693</v>
+        <v>452649</v>
       </c>
       <c r="R107" t="n">
-        <v>6990472</v>
+        <v>6990621</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -12170,10 +12155,10 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>124756725</v>
+        <v>124756742</v>
       </c>
       <c r="B108" t="n">
-        <v>78810</v>
+        <v>79927</v>
       </c>
       <c r="C108" t="inlineStr">
         <is>
@@ -12182,25 +12167,25 @@
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E108" t="n">
-        <v>6425</v>
+        <v>6464</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
@@ -12210,10 +12195,10 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>452762</v>
+        <v>452682</v>
       </c>
       <c r="R108" t="n">
-        <v>6990327</v>
+        <v>6990476</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -12245,7 +12230,7 @@
       </c>
       <c r="Z108" t="inlineStr">
         <is>
-          <t>14:37</t>
+          <t>13:53</t>
         </is>
       </c>
       <c r="AA108" t="inlineStr">
@@ -12255,7 +12240,7 @@
       </c>
       <c r="AB108" t="inlineStr">
         <is>
-          <t>14:37</t>
+          <t>13:53</t>
         </is>
       </c>
       <c r="AD108" t="b">
@@ -12266,6 +12251,21 @@
       </c>
       <c r="AG108" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ108" t="inlineStr">
+        <is>
+          <t>rönn</t>
+        </is>
+      </c>
+      <c r="AK108" t="inlineStr">
+        <is>
+          <t>Sorbus aucuparia</t>
+        </is>
+      </c>
+      <c r="AO108" t="inlineStr">
+        <is>
+          <t>Sorbus aucuparia</t>
+        </is>
       </c>
       <c r="AT108" t="inlineStr"/>
       <c r="AW108" t="inlineStr">
@@ -12282,10 +12282,10 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>124753622</v>
+        <v>124753635</v>
       </c>
       <c r="B109" t="n">
-        <v>98101</v>
+        <v>91030</v>
       </c>
       <c r="C109" t="inlineStr">
         <is>
@@ -12294,25 +12294,25 @@
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E109" t="n">
-        <v>220787</v>
+        <v>5432</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
@@ -12322,10 +12322,10 @@
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>452472</v>
+        <v>452732</v>
       </c>
       <c r="R109" t="n">
-        <v>6990821</v>
+        <v>6990486</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -12358,11 +12358,6 @@
       <c r="AA109" t="inlineStr">
         <is>
           <t>2025-05-03</t>
-        </is>
-      </c>
-      <c r="AC109" t="inlineStr">
-        <is>
-          <t>Minst 50</t>
         </is>
       </c>
       <c r="AD109" t="b">
@@ -12389,10 +12384,10 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>124753630</v>
+        <v>124756724</v>
       </c>
       <c r="B110" t="n">
-        <v>98101</v>
+        <v>91012</v>
       </c>
       <c r="C110" t="inlineStr">
         <is>
@@ -12401,25 +12396,25 @@
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E110" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
@@ -12429,10 +12424,10 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>452273</v>
+        <v>452793</v>
       </c>
       <c r="R110" t="n">
-        <v>6990906</v>
+        <v>6990262</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -12462,14 +12457,19 @@
           <t>2025-05-03</t>
         </is>
       </c>
+      <c r="Z110" t="inlineStr">
+        <is>
+          <t>14:44</t>
+        </is>
+      </c>
       <c r="AA110" t="inlineStr">
         <is>
           <t>2025-05-03</t>
         </is>
       </c>
-      <c r="AC110" t="inlineStr">
-        <is>
-          <t>Minst 10</t>
+      <c r="AB110" t="inlineStr">
+        <is>
+          <t>14:44</t>
         </is>
       </c>
       <c r="AD110" t="b">
@@ -12484,19 +12484,19 @@
       <c r="AT110" t="inlineStr"/>
       <c r="AW110" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX110" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY110" t="inlineStr"/>
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>124753615</v>
+        <v>124753622</v>
       </c>
       <c r="B111" t="n">
         <v>98101</v>
@@ -12536,10 +12536,10 @@
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>452734</v>
+        <v>452472</v>
       </c>
       <c r="R111" t="n">
-        <v>6990355</v>
+        <v>6990821</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -12576,7 +12576,7 @@
       </c>
       <c r="AC111" t="inlineStr">
         <is>
-          <t>Minst 30</t>
+          <t>Minst 50</t>
         </is>
       </c>
       <c r="AD111" t="b">
@@ -12603,10 +12603,10 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>124756724</v>
+        <v>124753630</v>
       </c>
       <c r="B112" t="n">
-        <v>91012</v>
+        <v>98101</v>
       </c>
       <c r="C112" t="inlineStr">
         <is>
@@ -12615,25 +12615,25 @@
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E112" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I112" t="inlineStr"/>
@@ -12643,10 +12643,10 @@
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>452793</v>
+        <v>452273</v>
       </c>
       <c r="R112" t="n">
-        <v>6990262</v>
+        <v>6990906</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -12676,19 +12676,14 @@
           <t>2025-05-03</t>
         </is>
       </c>
-      <c r="Z112" t="inlineStr">
-        <is>
-          <t>14:44</t>
-        </is>
-      </c>
       <c r="AA112" t="inlineStr">
         <is>
           <t>2025-05-03</t>
         </is>
       </c>
-      <c r="AB112" t="inlineStr">
-        <is>
-          <t>14:44</t>
+      <c r="AC112" t="inlineStr">
+        <is>
+          <t>Minst 10</t>
         </is>
       </c>
       <c r="AD112" t="b">
@@ -12703,22 +12698,22 @@
       <c r="AT112" t="inlineStr"/>
       <c r="AW112" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX112" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY112" t="inlineStr"/>
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>124753635</v>
+        <v>124753615</v>
       </c>
       <c r="B113" t="n">
-        <v>91030</v>
+        <v>98101</v>
       </c>
       <c r="C113" t="inlineStr">
         <is>
@@ -12727,25 +12722,25 @@
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E113" t="n">
-        <v>5432</v>
+        <v>220787</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
@@ -12755,10 +12750,10 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>452732</v>
+        <v>452734</v>
       </c>
       <c r="R113" t="n">
-        <v>6990486</v>
+        <v>6990355</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -12791,6 +12786,11 @@
       <c r="AA113" t="inlineStr">
         <is>
           <t>2025-05-03</t>
+        </is>
+      </c>
+      <c r="AC113" t="inlineStr">
+        <is>
+          <t>Minst 30</t>
         </is>
       </c>
       <c r="AD113" t="b">
@@ -13375,10 +13375,10 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>124756764</v>
+        <v>124753633</v>
       </c>
       <c r="B119" t="n">
-        <v>78810</v>
+        <v>91008</v>
       </c>
       <c r="C119" t="inlineStr">
         <is>
@@ -13391,21 +13391,21 @@
         </is>
       </c>
       <c r="E119" t="n">
-        <v>6425</v>
+        <v>1108</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I119" t="inlineStr"/>
@@ -13415,10 +13415,10 @@
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>452462</v>
+        <v>452772</v>
       </c>
       <c r="R119" t="n">
-        <v>6990915</v>
+        <v>6990321</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -13448,19 +13448,9 @@
           <t>2025-05-03</t>
         </is>
       </c>
-      <c r="Z119" t="inlineStr">
-        <is>
-          <t>11:11</t>
-        </is>
-      </c>
       <c r="AA119" t="inlineStr">
         <is>
           <t>2025-05-03</t>
-        </is>
-      </c>
-      <c r="AB119" t="inlineStr">
-        <is>
-          <t>11:11</t>
         </is>
       </c>
       <c r="AD119" t="b">
@@ -13475,22 +13465,22 @@
       <c r="AT119" t="inlineStr"/>
       <c r="AW119" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX119" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY119" t="inlineStr"/>
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>124756770</v>
+        <v>124756733</v>
       </c>
       <c r="B120" t="n">
-        <v>74899</v>
+        <v>79927</v>
       </c>
       <c r="C120" t="inlineStr">
         <is>
@@ -13499,41 +13489,38 @@
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E120" t="n">
-        <v>6486</v>
+        <v>6464</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Skuggnål</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Chaenotheca sphaerocephala</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>Nádv.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
-      <c r="J120" t="inlineStr"/>
-      <c r="K120" t="inlineStr"/>
-      <c r="N120" t="inlineStr"/>
       <c r="P120" t="inlineStr">
         <is>
           <t>Häggsåsen N, Jmt</t>
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>452339</v>
+        <v>452675</v>
       </c>
       <c r="R120" t="n">
-        <v>6990941</v>
+        <v>6990435</v>
       </c>
       <c r="S120" t="n">
         <v>10</v>
@@ -13565,7 +13552,7 @@
       </c>
       <c r="Z120" t="inlineStr">
         <is>
-          <t>10:44</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="AA120" t="inlineStr">
@@ -13575,7 +13562,7 @@
       </c>
       <c r="AB120" t="inlineStr">
         <is>
-          <t>10:44</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="AD120" t="b">
@@ -13584,42 +13571,22 @@
       <c r="AE120" t="b">
         <v>0</v>
       </c>
-      <c r="AF120" t="inlineStr">
-        <is>
-          <t>mikroskoperad</t>
-        </is>
-      </c>
       <c r="AG120" t="b">
         <v>0</v>
       </c>
-      <c r="AH120" t="inlineStr">
-        <is>
-          <t>Blåbärsgranskog</t>
-        </is>
-      </c>
-      <c r="AI120" t="inlineStr">
-        <is>
-          <t>I hålighet vid basen av gammal gran i fuktig granskog.</t>
-        </is>
-      </c>
       <c r="AJ120" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>rönn</t>
         </is>
       </c>
       <c r="AK120" t="inlineStr">
         <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM120" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
+          <t>Sorbus aucuparia</t>
         </is>
       </c>
       <c r="AO120" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Picea abies</t>
+          <t>Sorbus aucuparia</t>
         </is>
       </c>
       <c r="AT120" t="inlineStr"/>
@@ -13637,10 +13604,10 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>124756772</v>
+        <v>124756755</v>
       </c>
       <c r="B121" t="n">
-        <v>78810</v>
+        <v>91299</v>
       </c>
       <c r="C121" t="inlineStr">
         <is>
@@ -13653,21 +13620,21 @@
         </is>
       </c>
       <c r="E121" t="n">
-        <v>6425</v>
+        <v>658</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
@@ -13677,10 +13644,10 @@
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>452344</v>
+        <v>452538</v>
       </c>
       <c r="R121" t="n">
-        <v>6990942</v>
+        <v>6990659</v>
       </c>
       <c r="S121" t="n">
         <v>10</v>
@@ -13712,7 +13679,7 @@
       </c>
       <c r="Z121" t="inlineStr">
         <is>
-          <t>10:32</t>
+          <t>11:58</t>
         </is>
       </c>
       <c r="AA121" t="inlineStr">
@@ -13722,7 +13689,7 @@
       </c>
       <c r="AB121" t="inlineStr">
         <is>
-          <t>10:32</t>
+          <t>11:58</t>
         </is>
       </c>
       <c r="AD121" t="b">
@@ -13749,10 +13716,10 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>124753606</v>
+        <v>124756770</v>
       </c>
       <c r="B122" t="n">
-        <v>91299</v>
+        <v>74899</v>
       </c>
       <c r="C122" t="inlineStr">
         <is>
@@ -13761,38 +13728,41 @@
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E122" t="n">
-        <v>658</v>
+        <v>6486</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Skuggnål</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Chaenotheca sphaerocephala</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>Nádv.</t>
         </is>
       </c>
       <c r="I122" t="inlineStr"/>
+      <c r="J122" t="inlineStr"/>
+      <c r="K122" t="inlineStr"/>
+      <c r="N122" t="inlineStr"/>
       <c r="P122" t="inlineStr">
         <is>
           <t>Häggsåsen N, Jmt</t>
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>452165</v>
+        <v>452339</v>
       </c>
       <c r="R122" t="n">
-        <v>6990824</v>
+        <v>6990941</v>
       </c>
       <c r="S122" t="n">
         <v>10</v>
@@ -13822,39 +13792,84 @@
           <t>2025-05-03</t>
         </is>
       </c>
+      <c r="Z122" t="inlineStr">
+        <is>
+          <t>10:44</t>
+        </is>
+      </c>
       <c r="AA122" t="inlineStr">
         <is>
           <t>2025-05-03</t>
         </is>
       </c>
+      <c r="AB122" t="inlineStr">
+        <is>
+          <t>10:44</t>
+        </is>
+      </c>
       <c r="AD122" t="b">
         <v>0</v>
       </c>
       <c r="AE122" t="b">
         <v>0</v>
       </c>
+      <c r="AF122" t="inlineStr">
+        <is>
+          <t>mikroskoperad</t>
+        </is>
+      </c>
       <c r="AG122" t="b">
         <v>0</v>
+      </c>
+      <c r="AH122" t="inlineStr">
+        <is>
+          <t>Blåbärsgranskog</t>
+        </is>
+      </c>
+      <c r="AI122" t="inlineStr">
+        <is>
+          <t>I hålighet vid basen av gammal gran i fuktig granskog.</t>
+        </is>
+      </c>
+      <c r="AJ122" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK122" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM122" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO122" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Picea abies</t>
+        </is>
       </c>
       <c r="AT122" t="inlineStr"/>
       <c r="AW122" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX122" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY122" t="inlineStr"/>
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>124753633</v>
+        <v>124753620</v>
       </c>
       <c r="B123" t="n">
-        <v>91008</v>
+        <v>98101</v>
       </c>
       <c r="C123" t="inlineStr">
         <is>
@@ -13863,25 +13878,25 @@
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E123" t="n">
-        <v>1108</v>
+        <v>220787</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I123" t="inlineStr"/>
@@ -13891,10 +13906,10 @@
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>452772</v>
+        <v>452554</v>
       </c>
       <c r="R123" t="n">
-        <v>6990321</v>
+        <v>6990657</v>
       </c>
       <c r="S123" t="n">
         <v>10</v>
@@ -13927,6 +13942,11 @@
       <c r="AA123" t="inlineStr">
         <is>
           <t>2025-05-03</t>
+        </is>
+      </c>
+      <c r="AC123" t="inlineStr">
+        <is>
+          <t>Minst 30</t>
         </is>
       </c>
       <c r="AD123" t="b">
@@ -13953,10 +13973,10 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>124756733</v>
+        <v>124753606</v>
       </c>
       <c r="B124" t="n">
-        <v>79927</v>
+        <v>91299</v>
       </c>
       <c r="C124" t="inlineStr">
         <is>
@@ -13965,25 +13985,25 @@
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E124" t="n">
-        <v>6464</v>
+        <v>658</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I124" t="inlineStr"/>
@@ -13993,10 +14013,10 @@
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>452675</v>
+        <v>452165</v>
       </c>
       <c r="R124" t="n">
-        <v>6990435</v>
+        <v>6990824</v>
       </c>
       <c r="S124" t="n">
         <v>10</v>
@@ -14026,21 +14046,11 @@
           <t>2025-05-03</t>
         </is>
       </c>
-      <c r="Z124" t="inlineStr">
-        <is>
-          <t>14:15</t>
-        </is>
-      </c>
       <c r="AA124" t="inlineStr">
         <is>
           <t>2025-05-03</t>
         </is>
       </c>
-      <c r="AB124" t="inlineStr">
-        <is>
-          <t>14:15</t>
-        </is>
-      </c>
       <c r="AD124" t="b">
         <v>0</v>
       </c>
@@ -14049,41 +14059,26 @@
       </c>
       <c r="AG124" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ124" t="inlineStr">
-        <is>
-          <t>rönn</t>
-        </is>
-      </c>
-      <c r="AK124" t="inlineStr">
-        <is>
-          <t>Sorbus aucuparia</t>
-        </is>
-      </c>
-      <c r="AO124" t="inlineStr">
-        <is>
-          <t>Sorbus aucuparia</t>
-        </is>
       </c>
       <c r="AT124" t="inlineStr"/>
       <c r="AW124" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX124" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY124" t="inlineStr"/>
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>124756755</v>
+        <v>124756764</v>
       </c>
       <c r="B125" t="n">
-        <v>91299</v>
+        <v>78810</v>
       </c>
       <c r="C125" t="inlineStr">
         <is>
@@ -14096,21 +14091,21 @@
         </is>
       </c>
       <c r="E125" t="n">
-        <v>658</v>
+        <v>6425</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I125" t="inlineStr"/>
@@ -14120,10 +14115,10 @@
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>452538</v>
+        <v>452462</v>
       </c>
       <c r="R125" t="n">
-        <v>6990659</v>
+        <v>6990915</v>
       </c>
       <c r="S125" t="n">
         <v>10</v>
@@ -14155,7 +14150,7 @@
       </c>
       <c r="Z125" t="inlineStr">
         <is>
-          <t>11:58</t>
+          <t>11:11</t>
         </is>
       </c>
       <c r="AA125" t="inlineStr">
@@ -14165,7 +14160,7 @@
       </c>
       <c r="AB125" t="inlineStr">
         <is>
-          <t>11:58</t>
+          <t>11:11</t>
         </is>
       </c>
       <c r="AD125" t="b">
@@ -14192,10 +14187,10 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>124753620</v>
+        <v>124756772</v>
       </c>
       <c r="B126" t="n">
-        <v>98101</v>
+        <v>78810</v>
       </c>
       <c r="C126" t="inlineStr">
         <is>
@@ -14204,25 +14199,25 @@
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E126" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I126" t="inlineStr"/>
@@ -14232,10 +14227,10 @@
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>452554</v>
+        <v>452344</v>
       </c>
       <c r="R126" t="n">
-        <v>6990657</v>
+        <v>6990942</v>
       </c>
       <c r="S126" t="n">
         <v>10</v>
@@ -14265,14 +14260,19 @@
           <t>2025-05-03</t>
         </is>
       </c>
+      <c r="Z126" t="inlineStr">
+        <is>
+          <t>10:32</t>
+        </is>
+      </c>
       <c r="AA126" t="inlineStr">
         <is>
           <t>2025-05-03</t>
         </is>
       </c>
-      <c r="AC126" t="inlineStr">
-        <is>
-          <t>Minst 30</t>
+      <c r="AB126" t="inlineStr">
+        <is>
+          <t>10:32</t>
         </is>
       </c>
       <c r="AD126" t="b">
@@ -14287,19 +14287,19 @@
       <c r="AT126" t="inlineStr"/>
       <c r="AW126" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX126" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY126" t="inlineStr"/>
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>124756734</v>
+        <v>124753607</v>
       </c>
       <c r="B127" t="n">
         <v>79891</v>
@@ -14339,10 +14339,10 @@
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>452675</v>
+        <v>452734</v>
       </c>
       <c r="R127" t="n">
-        <v>6990435</v>
+        <v>6990356</v>
       </c>
       <c r="S127" t="n">
         <v>10</v>
@@ -14372,21 +14372,11 @@
           <t>2025-05-03</t>
         </is>
       </c>
-      <c r="Z127" t="inlineStr">
-        <is>
-          <t>14:14</t>
-        </is>
-      </c>
       <c r="AA127" t="inlineStr">
         <is>
           <t>2025-05-03</t>
         </is>
       </c>
-      <c r="AB127" t="inlineStr">
-        <is>
-          <t>14:14</t>
-        </is>
-      </c>
       <c r="AD127" t="b">
         <v>0</v>
       </c>
@@ -14395,38 +14385,23 @@
       </c>
       <c r="AG127" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ127" t="inlineStr">
-        <is>
-          <t>rönn</t>
-        </is>
-      </c>
-      <c r="AK127" t="inlineStr">
-        <is>
-          <t>Sorbus aucuparia</t>
-        </is>
-      </c>
-      <c r="AO127" t="inlineStr">
-        <is>
-          <t>Sorbus aucuparia</t>
-        </is>
       </c>
       <c r="AT127" t="inlineStr"/>
       <c r="AW127" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX127" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY127" t="inlineStr"/>
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>124753607</v>
+        <v>124756734</v>
       </c>
       <c r="B128" t="n">
         <v>79891</v>
@@ -14466,10 +14441,10 @@
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>452734</v>
+        <v>452675</v>
       </c>
       <c r="R128" t="n">
-        <v>6990356</v>
+        <v>6990435</v>
       </c>
       <c r="S128" t="n">
         <v>10</v>
@@ -14499,11 +14474,21 @@
           <t>2025-05-03</t>
         </is>
       </c>
+      <c r="Z128" t="inlineStr">
+        <is>
+          <t>14:14</t>
+        </is>
+      </c>
       <c r="AA128" t="inlineStr">
         <is>
           <t>2025-05-03</t>
         </is>
       </c>
+      <c r="AB128" t="inlineStr">
+        <is>
+          <t>14:14</t>
+        </is>
+      </c>
       <c r="AD128" t="b">
         <v>0</v>
       </c>
@@ -14512,16 +14497,31 @@
       </c>
       <c r="AG128" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ128" t="inlineStr">
+        <is>
+          <t>rönn</t>
+        </is>
+      </c>
+      <c r="AK128" t="inlineStr">
+        <is>
+          <t>Sorbus aucuparia</t>
+        </is>
+      </c>
+      <c r="AO128" t="inlineStr">
+        <is>
+          <t>Sorbus aucuparia</t>
+        </is>
       </c>
       <c r="AT128" t="inlineStr"/>
       <c r="AW128" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX128" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY128" t="inlineStr"/>
@@ -14767,7 +14767,7 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>124756777</v>
+        <v>124756745</v>
       </c>
       <c r="B131" t="n">
         <v>98101</v>
@@ -14802,7 +14802,7 @@
       </c>
       <c r="I131" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J131" t="inlineStr">
@@ -14819,10 +14819,10 @@
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>452146</v>
+        <v>452657</v>
       </c>
       <c r="R131" t="n">
-        <v>6990839</v>
+        <v>6990491</v>
       </c>
       <c r="S131" t="n">
         <v>10</v>
@@ -14854,7 +14854,7 @@
       </c>
       <c r="Z131" t="inlineStr">
         <is>
-          <t>10:06</t>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AA131" t="inlineStr">
@@ -14864,7 +14864,7 @@
       </c>
       <c r="AB131" t="inlineStr">
         <is>
-          <t>10:06</t>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AD131" t="b">
@@ -14892,10 +14892,10 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>124756750</v>
+        <v>124756688</v>
       </c>
       <c r="B132" t="n">
-        <v>98101</v>
+        <v>79891</v>
       </c>
       <c r="C132" t="inlineStr">
         <is>
@@ -14904,50 +14904,38 @@
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E132" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I132" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J132" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K132" t="inlineStr"/>
-      <c r="L132" t="inlineStr"/>
-      <c r="N132" t="inlineStr"/>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I132" t="inlineStr"/>
       <c r="P132" t="inlineStr">
         <is>
           <t>Häggsåsen N, Jmt</t>
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>452617</v>
+        <v>452694</v>
       </c>
       <c r="R132" t="n">
-        <v>6990549</v>
+        <v>6990598</v>
       </c>
       <c r="S132" t="n">
         <v>10</v>
@@ -14979,7 +14967,7 @@
       </c>
       <c r="Z132" t="inlineStr">
         <is>
-          <t>12:28</t>
+          <t>20:19</t>
         </is>
       </c>
       <c r="AA132" t="inlineStr">
@@ -14989,7 +14977,7 @@
       </c>
       <c r="AB132" t="inlineStr">
         <is>
-          <t>12:28</t>
+          <t>20:19</t>
         </is>
       </c>
       <c r="AD132" t="b">
@@ -14998,7 +14986,6 @@
       <c r="AE132" t="b">
         <v>0</v>
       </c>
-      <c r="AF132" t="inlineStr"/>
       <c r="AG132" t="b">
         <v>0</v>
       </c>
@@ -15017,7 +15004,7 @@
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>124756745</v>
+        <v>124756750</v>
       </c>
       <c r="B133" t="n">
         <v>98101</v>
@@ -15052,7 +15039,7 @@
       </c>
       <c r="I133" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J133" t="inlineStr">
@@ -15069,10 +15056,10 @@
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>452657</v>
+        <v>452617</v>
       </c>
       <c r="R133" t="n">
-        <v>6990491</v>
+        <v>6990549</v>
       </c>
       <c r="S133" t="n">
         <v>10</v>
@@ -15104,7 +15091,7 @@
       </c>
       <c r="Z133" t="inlineStr">
         <is>
-          <t>13:44</t>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AA133" t="inlineStr">
@@ -15114,7 +15101,7 @@
       </c>
       <c r="AB133" t="inlineStr">
         <is>
-          <t>13:44</t>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AD133" t="b">
@@ -15142,7 +15129,7 @@
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>124756688</v>
+        <v>124753609</v>
       </c>
       <c r="B134" t="n">
         <v>79891</v>
@@ -15182,10 +15169,10 @@
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>452694</v>
+        <v>452528</v>
       </c>
       <c r="R134" t="n">
-        <v>6990598</v>
+        <v>6990710</v>
       </c>
       <c r="S134" t="n">
         <v>10</v>
@@ -15215,19 +15202,9 @@
           <t>2025-05-03</t>
         </is>
       </c>
-      <c r="Z134" t="inlineStr">
-        <is>
-          <t>20:19</t>
-        </is>
-      </c>
       <c r="AA134" t="inlineStr">
         <is>
           <t>2025-05-03</t>
-        </is>
-      </c>
-      <c r="AB134" t="inlineStr">
-        <is>
-          <t>20:19</t>
         </is>
       </c>
       <c r="AD134" t="b">
@@ -15242,12 +15219,12 @@
       <c r="AT134" t="inlineStr"/>
       <c r="AW134" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX134" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY134" t="inlineStr"/>
@@ -15366,10 +15343,10 @@
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>124753609</v>
+        <v>124756777</v>
       </c>
       <c r="B136" t="n">
-        <v>79891</v>
+        <v>98101</v>
       </c>
       <c r="C136" t="inlineStr">
         <is>
@@ -15378,38 +15355,50 @@
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E136" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I136" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I136" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J136" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K136" t="inlineStr"/>
+      <c r="L136" t="inlineStr"/>
+      <c r="N136" t="inlineStr"/>
       <c r="P136" t="inlineStr">
         <is>
           <t>Häggsåsen N, Jmt</t>
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>452528</v>
+        <v>452146</v>
       </c>
       <c r="R136" t="n">
-        <v>6990710</v>
+        <v>6990839</v>
       </c>
       <c r="S136" t="n">
         <v>10</v>
@@ -15439,29 +15428,40 @@
           <t>2025-05-03</t>
         </is>
       </c>
+      <c r="Z136" t="inlineStr">
+        <is>
+          <t>10:06</t>
+        </is>
+      </c>
       <c r="AA136" t="inlineStr">
         <is>
           <t>2025-05-03</t>
         </is>
       </c>
+      <c r="AB136" t="inlineStr">
+        <is>
+          <t>10:06</t>
+        </is>
+      </c>
       <c r="AD136" t="b">
         <v>0</v>
       </c>
       <c r="AE136" t="b">
         <v>0</v>
       </c>
+      <c r="AF136" t="inlineStr"/>
       <c r="AG136" t="b">
         <v>0</v>
       </c>
       <c r="AT136" t="inlineStr"/>
       <c r="AW136" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX136" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY136" t="inlineStr"/>

--- a/artfynd/A 16493-2025 artfynd.xlsx
+++ b/artfynd/A 16493-2025 artfynd.xlsx
@@ -981,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124701352</v>
+        <v>124706585</v>
       </c>
       <c r="B5" t="n">
-        <v>79892</v>
+        <v>77743</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -997,39 +997,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>2081</v>
+        <v>228579</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Tjärnflon, Tjärnflon, Jmt</t>
+          <t>Häggsåsen, Häggsåsen, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>452657</v>
+        <v>452913</v>
       </c>
       <c r="R5" t="n">
-        <v>6990499</v>
+        <v>6990390</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1062,11 +1057,6 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-05-02</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Rikligt med skrovellav, APOTECHIER på en av bålarna</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1093,10 +1083,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124706585</v>
+        <v>124701352</v>
       </c>
       <c r="B6" t="n">
-        <v>77743</v>
+        <v>79892</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1109,34 +1099,39 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>228579</v>
+        <v>2081</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Häggsåsen, Häggsåsen, Jmt</t>
+          <t>Tjärnflon, Tjärnflon, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>452913</v>
+        <v>452657</v>
       </c>
       <c r="R6" t="n">
-        <v>6990390</v>
+        <v>6990499</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1169,6 +1164,11 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-05-02</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Rikligt med skrovellav, APOTECHIER på en av bålarna</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -3094,7 +3094,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>124721354</v>
+        <v>124689335</v>
       </c>
       <c r="B25" t="n">
         <v>57513</v>
@@ -3139,10 +3139,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>452514</v>
+        <v>452249</v>
       </c>
       <c r="R25" t="n">
-        <v>6990587</v>
+        <v>6990921</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3206,7 +3206,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>124689335</v>
+        <v>124721354</v>
       </c>
       <c r="B26" t="n">
         <v>57513</v>
@@ -3251,10 +3251,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>452249</v>
+        <v>452514</v>
       </c>
       <c r="R26" t="n">
-        <v>6990921</v>
+        <v>6990587</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3643,10 +3643,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>124704726</v>
+        <v>124699728</v>
       </c>
       <c r="B30" t="n">
-        <v>91012</v>
+        <v>79891</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3659,34 +3659,34 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Häggsåsen, Häggsåsen, Jmt</t>
+          <t>Tjärnflon, Tjärnflon, Jmt</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>452828</v>
+        <v>452650</v>
       </c>
       <c r="R30" t="n">
-        <v>6990384</v>
+        <v>6990495</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3745,10 +3745,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>124705215</v>
+        <v>124689574</v>
       </c>
       <c r="B31" t="n">
-        <v>91012</v>
+        <v>57513</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3761,34 +3761,39 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Häggsåsen, Häggsåsen, Jmt</t>
+          <t>Tjärnflon, Tjärnflon, Jmt</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>452850</v>
+        <v>452326</v>
       </c>
       <c r="R31" t="n">
-        <v>6990404</v>
+        <v>6990987</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3821,6 +3826,11 @@
       <c r="AA31" t="inlineStr">
         <is>
           <t>2025-05-02</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3847,10 +3857,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>124699728</v>
+        <v>124704726</v>
       </c>
       <c r="B32" t="n">
-        <v>79891</v>
+        <v>91012</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3863,34 +3873,34 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Tjärnflon, Tjärnflon, Jmt</t>
+          <t>Häggsåsen, Häggsåsen, Jmt</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>452650</v>
+        <v>452828</v>
       </c>
       <c r="R32" t="n">
-        <v>6990495</v>
+        <v>6990384</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3949,10 +3959,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>124689574</v>
+        <v>124705215</v>
       </c>
       <c r="B33" t="n">
-        <v>57513</v>
+        <v>91012</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -3965,39 +3975,34 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Tjärnflon, Tjärnflon, Jmt</t>
+          <t>Häggsåsen, Häggsåsen, Jmt</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>452326</v>
+        <v>452850</v>
       </c>
       <c r="R33" t="n">
-        <v>6990987</v>
+        <v>6990404</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4030,11 +4035,6 @@
       <c r="AA33" t="inlineStr">
         <is>
           <t>2025-05-02</t>
-        </is>
-      </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -5009,10 +5009,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>124753578</v>
+        <v>124756739</v>
       </c>
       <c r="B43" t="n">
-        <v>91012</v>
+        <v>98101</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5021,38 +5021,50 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr"/>
+      <c r="L43" t="inlineStr"/>
+      <c r="N43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
           <t>Häggsåsen N, Jmt</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>452743</v>
+        <v>452711</v>
       </c>
       <c r="R43" t="n">
-        <v>6990405</v>
+        <v>6990473</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5082,29 +5094,40 @@
           <t>2025-05-03</t>
         </is>
       </c>
+      <c r="Z43" t="inlineStr">
+        <is>
+          <t>14:01</t>
+        </is>
+      </c>
       <c r="AA43" t="inlineStr">
         <is>
           <t>2025-05-03</t>
         </is>
       </c>
+      <c r="AB43" t="inlineStr">
+        <is>
+          <t>14:01</t>
+        </is>
+      </c>
       <c r="AD43" t="b">
         <v>0</v>
       </c>
       <c r="AE43" t="b">
         <v>0</v>
       </c>
+      <c r="AF43" t="inlineStr"/>
       <c r="AG43" t="b">
         <v>0</v>
       </c>
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
@@ -5462,10 +5485,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>124756739</v>
+        <v>124753578</v>
       </c>
       <c r="B47" t="n">
-        <v>98101</v>
+        <v>91012</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5474,50 +5497,38 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="J47" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K47" t="inlineStr"/>
-      <c r="L47" t="inlineStr"/>
-      <c r="N47" t="inlineStr"/>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
           <t>Häggsåsen N, Jmt</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>452711</v>
+        <v>452743</v>
       </c>
       <c r="R47" t="n">
-        <v>6990473</v>
+        <v>6990405</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5547,40 +5558,29 @@
           <t>2025-05-03</t>
         </is>
       </c>
-      <c r="Z47" t="inlineStr">
-        <is>
-          <t>14:01</t>
-        </is>
-      </c>
       <c r="AA47" t="inlineStr">
         <is>
           <t>2025-05-03</t>
         </is>
       </c>
-      <c r="AB47" t="inlineStr">
-        <is>
-          <t>14:01</t>
-        </is>
-      </c>
       <c r="AD47" t="b">
         <v>0</v>
       </c>
       <c r="AE47" t="b">
         <v>0</v>
       </c>
-      <c r="AF47" t="inlineStr"/>
       <c r="AG47" t="b">
         <v>0</v>
       </c>
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
@@ -6603,10 +6603,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>124753614</v>
+        <v>124753592</v>
       </c>
       <c r="B57" t="n">
-        <v>98101</v>
+        <v>57513</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6615,25 +6615,25 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6643,10 +6643,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>452751</v>
+        <v>452396</v>
       </c>
       <c r="R57" t="n">
-        <v>6990344</v>
+        <v>6990703</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6683,7 +6683,7 @@
       </c>
       <c r="AC57" t="inlineStr">
         <is>
-          <t>Minst 200</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6822,10 +6822,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>124753592</v>
+        <v>124753614</v>
       </c>
       <c r="B59" t="n">
-        <v>57513</v>
+        <v>98101</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -6834,25 +6834,25 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6862,10 +6862,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>452396</v>
+        <v>452751</v>
       </c>
       <c r="R59" t="n">
-        <v>6990703</v>
+        <v>6990344</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6902,7 +6902,7 @@
       </c>
       <c r="AC59" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Minst 200</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -6929,10 +6929,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>124753632</v>
+        <v>124753604</v>
       </c>
       <c r="B60" t="n">
-        <v>98101</v>
+        <v>79892</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -6941,25 +6941,25 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>220787</v>
+        <v>2081</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6969,10 +6969,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>452455</v>
+        <v>452435</v>
       </c>
       <c r="R60" t="n">
-        <v>6990942</v>
+        <v>6990938</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -7005,11 +7005,6 @@
       <c r="AA60" t="inlineStr">
         <is>
           <t>2025-05-03</t>
-        </is>
-      </c>
-      <c r="AC60" t="inlineStr">
-        <is>
-          <t>Minst 30</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7036,10 +7031,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>124756750</v>
+        <v>124756746</v>
       </c>
       <c r="B61" t="n">
-        <v>98101</v>
+        <v>91012</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -7048,50 +7043,38 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I61" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J61" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K61" t="inlineStr"/>
-      <c r="L61" t="inlineStr"/>
-      <c r="N61" t="inlineStr"/>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
           <t>Häggsåsen N, Jmt</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>452617</v>
+        <v>452639</v>
       </c>
       <c r="R61" t="n">
-        <v>6990549</v>
+        <v>6990537</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7123,7 +7106,7 @@
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>12:28</t>
+          <t>13:36</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -7133,7 +7116,7 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>12:28</t>
+          <t>13:36</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7142,7 +7125,6 @@
       <c r="AE61" t="b">
         <v>0</v>
       </c>
-      <c r="AF61" t="inlineStr"/>
       <c r="AG61" t="b">
         <v>0</v>
       </c>
@@ -7161,10 +7143,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>124753609</v>
+        <v>124756753</v>
       </c>
       <c r="B62" t="n">
-        <v>79891</v>
+        <v>91012</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -7177,21 +7159,21 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -7201,10 +7183,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>452528</v>
+        <v>452608</v>
       </c>
       <c r="R62" t="n">
-        <v>6990710</v>
+        <v>6990625</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7234,9 +7216,19 @@
           <t>2025-05-03</t>
         </is>
       </c>
+      <c r="Z62" t="inlineStr">
+        <is>
+          <t>12:07</t>
+        </is>
+      </c>
       <c r="AA62" t="inlineStr">
         <is>
           <t>2025-05-03</t>
+        </is>
+      </c>
+      <c r="AB62" t="inlineStr">
+        <is>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7251,22 +7243,22 @@
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>124756748</v>
+        <v>124753609</v>
       </c>
       <c r="B63" t="n">
-        <v>78810</v>
+        <v>79891</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -7279,21 +7271,21 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -7303,10 +7295,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>452609</v>
+        <v>452528</v>
       </c>
       <c r="R63" t="n">
-        <v>6990543</v>
+        <v>6990710</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7336,19 +7328,9 @@
           <t>2025-05-03</t>
         </is>
       </c>
-      <c r="Z63" t="inlineStr">
-        <is>
-          <t>12:29</t>
-        </is>
-      </c>
       <c r="AA63" t="inlineStr">
         <is>
           <t>2025-05-03</t>
-        </is>
-      </c>
-      <c r="AB63" t="inlineStr">
-        <is>
-          <t>12:29</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7363,22 +7345,22 @@
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>124753604</v>
+        <v>124756748</v>
       </c>
       <c r="B64" t="n">
-        <v>79892</v>
+        <v>78810</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7391,21 +7373,21 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7415,10 +7397,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>452435</v>
+        <v>452609</v>
       </c>
       <c r="R64" t="n">
-        <v>6990938</v>
+        <v>6990543</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7448,9 +7430,19 @@
           <t>2025-05-03</t>
         </is>
       </c>
+      <c r="Z64" t="inlineStr">
+        <is>
+          <t>12:29</t>
+        </is>
+      </c>
       <c r="AA64" t="inlineStr">
         <is>
           <t>2025-05-03</t>
+        </is>
+      </c>
+      <c r="AB64" t="inlineStr">
+        <is>
+          <t>12:29</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7465,22 +7457,22 @@
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>124756746</v>
+        <v>124753632</v>
       </c>
       <c r="B65" t="n">
-        <v>91012</v>
+        <v>98101</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -7489,25 +7481,25 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7517,10 +7509,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>452639</v>
+        <v>452455</v>
       </c>
       <c r="R65" t="n">
-        <v>6990537</v>
+        <v>6990942</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7550,19 +7542,14 @@
           <t>2025-05-03</t>
         </is>
       </c>
-      <c r="Z65" t="inlineStr">
-        <is>
-          <t>13:36</t>
-        </is>
-      </c>
       <c r="AA65" t="inlineStr">
         <is>
           <t>2025-05-03</t>
         </is>
       </c>
-      <c r="AB65" t="inlineStr">
-        <is>
-          <t>13:36</t>
+      <c r="AC65" t="inlineStr">
+        <is>
+          <t>Minst 30</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7577,22 +7564,22 @@
       <c r="AT65" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>124756753</v>
+        <v>124756750</v>
       </c>
       <c r="B66" t="n">
-        <v>91012</v>
+        <v>98101</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -7601,38 +7588,50 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I66" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J66" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K66" t="inlineStr"/>
+      <c r="L66" t="inlineStr"/>
+      <c r="N66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
           <t>Häggsåsen N, Jmt</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>452608</v>
+        <v>452617</v>
       </c>
       <c r="R66" t="n">
-        <v>6990625</v>
+        <v>6990549</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7664,7 +7663,7 @@
       </c>
       <c r="Z66" t="inlineStr">
         <is>
-          <t>12:07</t>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
@@ -7674,7 +7673,7 @@
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>12:07</t>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7683,6 +7682,7 @@
       <c r="AE66" t="b">
         <v>0</v>
       </c>
+      <c r="AF66" t="inlineStr"/>
       <c r="AG66" t="b">
         <v>0</v>
       </c>
@@ -7701,10 +7701,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>124753629</v>
+        <v>124753584</v>
       </c>
       <c r="B67" t="n">
-        <v>98101</v>
+        <v>91012</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -7713,25 +7713,25 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7741,10 +7741,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>452576</v>
+        <v>452444</v>
       </c>
       <c r="R67" t="n">
-        <v>6990924</v>
+        <v>6990774</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7777,11 +7777,6 @@
       <c r="AA67" t="inlineStr">
         <is>
           <t>2025-05-03</t>
-        </is>
-      </c>
-      <c r="AC67" t="inlineStr">
-        <is>
-          <t>Minst 30</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7808,7 +7803,7 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>124756745</v>
+        <v>124753629</v>
       </c>
       <c r="B68" t="n">
         <v>98101</v>
@@ -7841,29 +7836,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I68" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J68" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K68" t="inlineStr"/>
-      <c r="L68" t="inlineStr"/>
-      <c r="N68" t="inlineStr"/>
+      <c r="I68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
           <t>Häggsåsen N, Jmt</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>452657</v>
+        <v>452576</v>
       </c>
       <c r="R68" t="n">
-        <v>6990491</v>
+        <v>6990924</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7893,19 +7876,14 @@
           <t>2025-05-03</t>
         </is>
       </c>
-      <c r="Z68" t="inlineStr">
-        <is>
-          <t>13:44</t>
-        </is>
-      </c>
       <c r="AA68" t="inlineStr">
         <is>
           <t>2025-05-03</t>
         </is>
       </c>
-      <c r="AB68" t="inlineStr">
-        <is>
-          <t>13:44</t>
+      <c r="AC68" t="inlineStr">
+        <is>
+          <t>Minst 30</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -7914,29 +7892,28 @@
       <c r="AE68" t="b">
         <v>0</v>
       </c>
-      <c r="AF68" t="inlineStr"/>
       <c r="AG68" t="b">
         <v>0</v>
       </c>
       <c r="AT68" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>124753584</v>
+        <v>124756745</v>
       </c>
       <c r="B69" t="n">
-        <v>91012</v>
+        <v>98101</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -7945,38 +7922,50 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I69" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J69" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K69" t="inlineStr"/>
+      <c r="L69" t="inlineStr"/>
+      <c r="N69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
           <t>Häggsåsen N, Jmt</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>452444</v>
+        <v>452657</v>
       </c>
       <c r="R69" t="n">
-        <v>6990774</v>
+        <v>6990491</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -8006,29 +7995,40 @@
           <t>2025-05-03</t>
         </is>
       </c>
+      <c r="Z69" t="inlineStr">
+        <is>
+          <t>13:44</t>
+        </is>
+      </c>
       <c r="AA69" t="inlineStr">
         <is>
           <t>2025-05-03</t>
         </is>
       </c>
+      <c r="AB69" t="inlineStr">
+        <is>
+          <t>13:44</t>
+        </is>
+      </c>
       <c r="AD69" t="b">
         <v>0</v>
       </c>
       <c r="AE69" t="b">
         <v>0</v>
       </c>
+      <c r="AF69" t="inlineStr"/>
       <c r="AG69" t="b">
         <v>0</v>
       </c>
       <c r="AT69" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX69" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
@@ -10597,10 +10597,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>124756740</v>
+        <v>124753622</v>
       </c>
       <c r="B93" t="n">
-        <v>91457</v>
+        <v>98101</v>
       </c>
       <c r="C93" t="inlineStr">
         <is>
@@ -10613,21 +10613,21 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>1209</v>
+        <v>220787</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
@@ -10637,10 +10637,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>452701</v>
+        <v>452472</v>
       </c>
       <c r="R93" t="n">
-        <v>6990475</v>
+        <v>6990821</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -10670,19 +10670,14 @@
           <t>2025-05-03</t>
         </is>
       </c>
-      <c r="Z93" t="inlineStr">
-        <is>
-          <t>13:58</t>
-        </is>
-      </c>
       <c r="AA93" t="inlineStr">
         <is>
           <t>2025-05-03</t>
         </is>
       </c>
-      <c r="AB93" t="inlineStr">
-        <is>
-          <t>13:58</t>
+      <c r="AC93" t="inlineStr">
+        <is>
+          <t>Minst 50</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -10697,22 +10692,22 @@
       <c r="AT93" t="inlineStr"/>
       <c r="AW93" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX93" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY93" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>124753588</v>
+        <v>124756774</v>
       </c>
       <c r="B94" t="n">
-        <v>91012</v>
+        <v>98101</v>
       </c>
       <c r="C94" t="inlineStr">
         <is>
@@ -10721,38 +10716,50 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E94" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I94" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I94" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J94" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K94" t="inlineStr"/>
+      <c r="L94" t="inlineStr"/>
+      <c r="N94" t="inlineStr"/>
       <c r="P94" t="inlineStr">
         <is>
           <t>Häggsåsen N, Jmt</t>
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>452311</v>
+        <v>452308</v>
       </c>
       <c r="R94" t="n">
-        <v>6990887</v>
+        <v>6990943</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -10782,39 +10789,50 @@
           <t>2025-05-03</t>
         </is>
       </c>
+      <c r="Z94" t="inlineStr">
+        <is>
+          <t>10:23</t>
+        </is>
+      </c>
       <c r="AA94" t="inlineStr">
         <is>
           <t>2025-05-03</t>
         </is>
       </c>
+      <c r="AB94" t="inlineStr">
+        <is>
+          <t>10:23</t>
+        </is>
+      </c>
       <c r="AD94" t="b">
         <v>0</v>
       </c>
       <c r="AE94" t="b">
         <v>0</v>
       </c>
+      <c r="AF94" t="inlineStr"/>
       <c r="AG94" t="b">
         <v>0</v>
       </c>
       <c r="AT94" t="inlineStr"/>
       <c r="AW94" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX94" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY94" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>124756756</v>
+        <v>124753630</v>
       </c>
       <c r="B95" t="n">
-        <v>78810</v>
+        <v>98101</v>
       </c>
       <c r="C95" t="inlineStr">
         <is>
@@ -10823,25 +10841,25 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
@@ -10851,10 +10869,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>452545</v>
+        <v>452273</v>
       </c>
       <c r="R95" t="n">
-        <v>6990691</v>
+        <v>6990906</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10884,19 +10902,14 @@
           <t>2025-05-03</t>
         </is>
       </c>
-      <c r="Z95" t="inlineStr">
-        <is>
-          <t>11:54</t>
-        </is>
-      </c>
       <c r="AA95" t="inlineStr">
         <is>
           <t>2025-05-03</t>
         </is>
       </c>
-      <c r="AB95" t="inlineStr">
-        <is>
-          <t>11:54</t>
+      <c r="AC95" t="inlineStr">
+        <is>
+          <t>Minst 10</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -10911,22 +10924,22 @@
       <c r="AT95" t="inlineStr"/>
       <c r="AW95" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX95" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY95" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>124753639</v>
+        <v>124753615</v>
       </c>
       <c r="B96" t="n">
-        <v>78810</v>
+        <v>98101</v>
       </c>
       <c r="C96" t="inlineStr">
         <is>
@@ -10935,25 +10948,25 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E96" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
@@ -10963,10 +10976,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>452511</v>
+        <v>452734</v>
       </c>
       <c r="R96" t="n">
-        <v>6990733</v>
+        <v>6990355</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -10999,6 +11012,11 @@
       <c r="AA96" t="inlineStr">
         <is>
           <t>2025-05-03</t>
+        </is>
+      </c>
+      <c r="AC96" t="inlineStr">
+        <is>
+          <t>Minst 30</t>
         </is>
       </c>
       <c r="AD96" t="b">
@@ -11025,10 +11043,10 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>124753622</v>
+        <v>124756756</v>
       </c>
       <c r="B97" t="n">
-        <v>98101</v>
+        <v>78810</v>
       </c>
       <c r="C97" t="inlineStr">
         <is>
@@ -11037,25 +11055,25 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E97" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
@@ -11065,10 +11083,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>452472</v>
+        <v>452545</v>
       </c>
       <c r="R97" t="n">
-        <v>6990821</v>
+        <v>6990691</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -11098,14 +11116,19 @@
           <t>2025-05-03</t>
         </is>
       </c>
+      <c r="Z97" t="inlineStr">
+        <is>
+          <t>11:54</t>
+        </is>
+      </c>
       <c r="AA97" t="inlineStr">
         <is>
           <t>2025-05-03</t>
         </is>
       </c>
-      <c r="AC97" t="inlineStr">
-        <is>
-          <t>Minst 50</t>
+      <c r="AB97" t="inlineStr">
+        <is>
+          <t>11:54</t>
         </is>
       </c>
       <c r="AD97" t="b">
@@ -11120,22 +11143,22 @@
       <c r="AT97" t="inlineStr"/>
       <c r="AW97" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX97" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY97" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>124756774</v>
+        <v>124753639</v>
       </c>
       <c r="B98" t="n">
-        <v>98101</v>
+        <v>78810</v>
       </c>
       <c r="C98" t="inlineStr">
         <is>
@@ -11144,50 +11167,38 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E98" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I98" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="J98" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K98" t="inlineStr"/>
-      <c r="L98" t="inlineStr"/>
-      <c r="N98" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I98" t="inlineStr"/>
       <c r="P98" t="inlineStr">
         <is>
           <t>Häggsåsen N, Jmt</t>
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>452308</v>
+        <v>452511</v>
       </c>
       <c r="R98" t="n">
-        <v>6990943</v>
+        <v>6990733</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -11217,50 +11228,39 @@
           <t>2025-05-03</t>
         </is>
       </c>
-      <c r="Z98" t="inlineStr">
-        <is>
-          <t>10:23</t>
-        </is>
-      </c>
       <c r="AA98" t="inlineStr">
         <is>
           <t>2025-05-03</t>
         </is>
       </c>
-      <c r="AB98" t="inlineStr">
-        <is>
-          <t>10:23</t>
-        </is>
-      </c>
       <c r="AD98" t="b">
         <v>0</v>
       </c>
       <c r="AE98" t="b">
         <v>0</v>
       </c>
-      <c r="AF98" t="inlineStr"/>
       <c r="AG98" t="b">
         <v>0</v>
       </c>
       <c r="AT98" t="inlineStr"/>
       <c r="AW98" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX98" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY98" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>124753630</v>
+        <v>124756740</v>
       </c>
       <c r="B99" t="n">
-        <v>98101</v>
+        <v>91457</v>
       </c>
       <c r="C99" t="inlineStr">
         <is>
@@ -11273,21 +11273,21 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>220787</v>
+        <v>1209</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
@@ -11297,10 +11297,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>452273</v>
+        <v>452701</v>
       </c>
       <c r="R99" t="n">
-        <v>6990906</v>
+        <v>6990475</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -11330,14 +11330,19 @@
           <t>2025-05-03</t>
         </is>
       </c>
+      <c r="Z99" t="inlineStr">
+        <is>
+          <t>13:58</t>
+        </is>
+      </c>
       <c r="AA99" t="inlineStr">
         <is>
           <t>2025-05-03</t>
         </is>
       </c>
-      <c r="AC99" t="inlineStr">
-        <is>
-          <t>Minst 10</t>
+      <c r="AB99" t="inlineStr">
+        <is>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AD99" t="b">
@@ -11352,22 +11357,22 @@
       <c r="AT99" t="inlineStr"/>
       <c r="AW99" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX99" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY99" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>124753615</v>
+        <v>124753588</v>
       </c>
       <c r="B100" t="n">
-        <v>98101</v>
+        <v>91012</v>
       </c>
       <c r="C100" t="inlineStr">
         <is>
@@ -11376,25 +11381,25 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E100" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
@@ -11404,10 +11409,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>452734</v>
+        <v>452311</v>
       </c>
       <c r="R100" t="n">
-        <v>6990355</v>
+        <v>6990887</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -11440,11 +11445,6 @@
       <c r="AA100" t="inlineStr">
         <is>
           <t>2025-05-03</t>
-        </is>
-      </c>
-      <c r="AC100" t="inlineStr">
-        <is>
-          <t>Minst 30</t>
         </is>
       </c>
       <c r="AD100" t="b">

--- a/artfynd/A 16493-2025 artfynd.xlsx
+++ b/artfynd/A 16493-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124699720</v>
+        <v>124694574</v>
       </c>
       <c r="B2" t="n">
-        <v>79892</v>
+        <v>57513</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,34 +691,39 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>2081</v>
+        <v>100109</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Tjärnflon, Tjärnflon, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>452650</v>
+        <v>452630</v>
       </c>
       <c r="R2" t="n">
-        <v>6990495</v>
+        <v>6990651</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -751,6 +756,11 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-05-02</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -777,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124702530</v>
+        <v>124706864</v>
       </c>
       <c r="B3" t="n">
-        <v>79891</v>
+        <v>57513</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,34 +803,39 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Häggsåsen, Häggsåsen, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>452746</v>
+        <v>453007</v>
       </c>
       <c r="R3" t="n">
-        <v>6990384</v>
+        <v>6990356</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -853,6 +868,11 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-05-02</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -879,10 +899,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124703646</v>
+        <v>124706950</v>
       </c>
       <c r="B4" t="n">
-        <v>91008</v>
+        <v>98101</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -891,38 +911,42 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1108</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Häggsåsen, Häggsåsen, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>452785</v>
+        <v>453007</v>
       </c>
       <c r="R4" t="n">
-        <v>6990307</v>
+        <v>6990356</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -981,10 +1005,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124706585</v>
+        <v>124702902</v>
       </c>
       <c r="B5" t="n">
-        <v>77743</v>
+        <v>79891</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -997,21 +1021,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>228579</v>
+        <v>6458</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1021,10 +1045,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>452913</v>
+        <v>452734</v>
       </c>
       <c r="R5" t="n">
-        <v>6990390</v>
+        <v>6990348</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1083,10 +1107,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124701352</v>
+        <v>124689574</v>
       </c>
       <c r="B6" t="n">
-        <v>79892</v>
+        <v>57513</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1099,27 +1123,27 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>2081</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1128,10 +1152,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>452657</v>
+        <v>452326</v>
       </c>
       <c r="R6" t="n">
-        <v>6990499</v>
+        <v>6990987</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1168,7 +1192,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Rikligt med skrovellav, APOTECHIER på en av bålarna</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1195,10 +1219,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124693950</v>
+        <v>124691533</v>
       </c>
       <c r="B7" t="n">
-        <v>91012</v>
+        <v>79891</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1211,21 +1235,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1235,10 +1259,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>452582</v>
+        <v>452427</v>
       </c>
       <c r="R7" t="n">
-        <v>6990572</v>
+        <v>6990925</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1297,10 +1321,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124688835</v>
+        <v>124695256</v>
       </c>
       <c r="B8" t="n">
-        <v>78810</v>
+        <v>98101</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1309,31 +1333,30 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>24</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -1342,10 +1365,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>452142</v>
+        <v>452624</v>
       </c>
       <c r="R8" t="n">
-        <v>6990800</v>
+        <v>6990535</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1404,10 +1427,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124695424</v>
+        <v>124689335</v>
       </c>
       <c r="B9" t="n">
-        <v>91012</v>
+        <v>57513</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1420,34 +1443,39 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Tjärnflon, Tjärnflon, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>452642</v>
+        <v>452249</v>
       </c>
       <c r="R9" t="n">
-        <v>6990548</v>
+        <v>6990921</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1480,6 +1508,11 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-05-02</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1506,10 +1539,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124704608</v>
+        <v>124703242</v>
       </c>
       <c r="B10" t="n">
-        <v>91012</v>
+        <v>91299</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1522,21 +1555,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1546,10 +1579,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>452839</v>
+        <v>452760</v>
       </c>
       <c r="R10" t="n">
-        <v>6990352</v>
+        <v>6990252</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1608,10 +1641,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124695256</v>
+        <v>124704581</v>
       </c>
       <c r="B11" t="n">
-        <v>98101</v>
+        <v>91299</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1620,42 +1653,38 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Tjärnflon, Tjärnflon, Jmt</t>
+          <t>Häggsåsen, Häggsåsen, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>452624</v>
+        <v>452839</v>
       </c>
       <c r="R11" t="n">
-        <v>6990535</v>
+        <v>6990352</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1714,10 +1743,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124689645</v>
+        <v>124721354</v>
       </c>
       <c r="B12" t="n">
-        <v>91012</v>
+        <v>57513</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1730,34 +1759,39 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Tjärnflon, Tjärnflon, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>452311</v>
+        <v>452514</v>
       </c>
       <c r="R12" t="n">
-        <v>6990960</v>
+        <v>6990587</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1790,6 +1824,11 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-05-02</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1816,7 +1855,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124691378</v>
+        <v>124704608</v>
       </c>
       <c r="B13" t="n">
         <v>91012</v>
@@ -1852,14 +1891,14 @@
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Tjärnflon, Tjärnflon, Jmt</t>
+          <t>Häggsåsen, Häggsåsen, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>452431</v>
+        <v>452839</v>
       </c>
       <c r="R13" t="n">
-        <v>6990946</v>
+        <v>6990352</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1918,10 +1957,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124689546</v>
+        <v>124702770</v>
       </c>
       <c r="B14" t="n">
-        <v>57513</v>
+        <v>79891</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1934,39 +1973,34 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Tjärnflon, Tjärnflon, Jmt</t>
+          <t>Häggsåsen, Häggsåsen, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>452319</v>
+        <v>452731</v>
       </c>
       <c r="R14" t="n">
-        <v>6990963</v>
+        <v>6990355</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1999,11 +2033,6 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-05-02</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2030,10 +2059,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124689528</v>
+        <v>124703646</v>
       </c>
       <c r="B15" t="n">
-        <v>57513</v>
+        <v>91008</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2046,39 +2075,34 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Tjärnflon, Tjärnflon, Jmt</t>
+          <t>Häggsåsen, Häggsåsen, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>452301</v>
+        <v>452785</v>
       </c>
       <c r="R15" t="n">
-        <v>6990964</v>
+        <v>6990307</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2111,11 +2135,6 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-05-02</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2142,10 +2161,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124704581</v>
+        <v>124689504</v>
       </c>
       <c r="B16" t="n">
-        <v>91299</v>
+        <v>57513</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2158,34 +2177,39 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>658</v>
+        <v>100109</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Häggsåsen, Häggsåsen, Jmt</t>
+          <t>Tjärnflon, Tjärnflon, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>452839</v>
+        <v>452322</v>
       </c>
       <c r="R16" t="n">
-        <v>6990352</v>
+        <v>6990950</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2218,6 +2242,11 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-05-02</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2244,10 +2273,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>124705584</v>
+        <v>124699728</v>
       </c>
       <c r="B17" t="n">
-        <v>91030</v>
+        <v>79891</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2260,34 +2289,34 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>5432</v>
+        <v>6458</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Häggsåsen, Häggsåsen, Jmt</t>
+          <t>Tjärnflon, Tjärnflon, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>452865</v>
+        <v>452650</v>
       </c>
       <c r="R17" t="n">
-        <v>6990382</v>
+        <v>6990495</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2346,10 +2375,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>124705813</v>
+        <v>124688930</v>
       </c>
       <c r="B18" t="n">
-        <v>57513</v>
+        <v>79891</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2362,39 +2391,34 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Häggsåsen, Häggsåsen, Jmt</t>
+          <t>Tjärnflon, Tjärnflon, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>452865</v>
+        <v>452168</v>
       </c>
       <c r="R18" t="n">
-        <v>6990385</v>
+        <v>6990824</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2427,11 +2451,6 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-05-02</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Möjligt gammalt bo 3m upp i granstubbe med granticka på</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2458,10 +2477,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>124689504</v>
+        <v>124688835</v>
       </c>
       <c r="B19" t="n">
-        <v>57513</v>
+        <v>78810</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2474,27 +2493,27 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
@@ -2503,10 +2522,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>452322</v>
+        <v>452142</v>
       </c>
       <c r="R19" t="n">
-        <v>6990950</v>
+        <v>6990800</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2539,11 +2558,6 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-05-02</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2672,10 +2686,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>124706950</v>
+        <v>124699720</v>
       </c>
       <c r="B21" t="n">
-        <v>98101</v>
+        <v>79892</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2684,42 +2698,38 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>220787</v>
+        <v>2081</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
-      </c>
+          <t>(Scop.) DC.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Häggsåsen, Häggsåsen, Jmt</t>
+          <t>Tjärnflon, Tjärnflon, Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>453007</v>
+        <v>452650</v>
       </c>
       <c r="R21" t="n">
-        <v>6990356</v>
+        <v>6990495</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2778,10 +2788,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>124688930</v>
+        <v>124689528</v>
       </c>
       <c r="B22" t="n">
-        <v>79891</v>
+        <v>57513</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2794,34 +2804,39 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Tjärnflon, Tjärnflon, Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>452168</v>
+        <v>452301</v>
       </c>
       <c r="R22" t="n">
-        <v>6990824</v>
+        <v>6990964</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2854,6 +2869,11 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-05-02</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2880,10 +2900,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>124691533</v>
+        <v>124704478</v>
       </c>
       <c r="B23" t="n">
-        <v>79891</v>
+        <v>57513</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2896,34 +2916,39 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Tjärnflon, Tjärnflon, Jmt</t>
+          <t>Häggsåsen, Häggsåsen, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>452427</v>
+        <v>452836</v>
       </c>
       <c r="R23" t="n">
-        <v>6990925</v>
+        <v>6990321</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2956,6 +2981,11 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-05-02</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -2982,10 +3012,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>124694574</v>
+        <v>124689645</v>
       </c>
       <c r="B24" t="n">
-        <v>57513</v>
+        <v>91012</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -2998,39 +3028,34 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Tjärnflon, Tjärnflon, Jmt</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>452630</v>
+        <v>452311</v>
       </c>
       <c r="R24" t="n">
-        <v>6990651</v>
+        <v>6990960</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3063,11 +3088,6 @@
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-05-02</t>
-        </is>
-      </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3094,7 +3114,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>124689335</v>
+        <v>124689546</v>
       </c>
       <c r="B25" t="n">
         <v>57513</v>
@@ -3139,10 +3159,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>452249</v>
+        <v>452319</v>
       </c>
       <c r="R25" t="n">
-        <v>6990921</v>
+        <v>6990963</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3206,10 +3226,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>124721354</v>
+        <v>124701516</v>
       </c>
       <c r="B26" t="n">
-        <v>57513</v>
+        <v>91299</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3222,39 +3242,34 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100109</v>
+        <v>658</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Tjärnflon, Tjärnflon, Jmt</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>452514</v>
+        <v>452635</v>
       </c>
       <c r="R26" t="n">
-        <v>6990587</v>
+        <v>6990463</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3287,11 +3302,6 @@
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-05-02</t>
-        </is>
-      </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3318,10 +3328,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>124695367</v>
+        <v>124705584</v>
       </c>
       <c r="B27" t="n">
-        <v>82597</v>
+        <v>91030</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3334,34 +3344,34 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1312</v>
+        <v>5432</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Tjärnflon, Tjärnflon, Jmt</t>
+          <t>Häggsåsen, Häggsåsen, Jmt</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>452617</v>
+        <v>452865</v>
       </c>
       <c r="R27" t="n">
-        <v>6990540</v>
+        <v>6990382</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3420,10 +3430,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>124689475</v>
+        <v>124691814</v>
       </c>
       <c r="B28" t="n">
-        <v>57513</v>
+        <v>56714</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3436,16 +3446,16 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100109</v>
+        <v>102612</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -3453,10 +3463,14 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I28" t="inlineStr"/>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>förbiflygande</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
@@ -3465,10 +3479,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>452291</v>
+        <v>452489</v>
       </c>
       <c r="R28" t="n">
-        <v>6990952</v>
+        <v>6990896</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3501,11 +3515,6 @@
       <c r="AA28" t="inlineStr">
         <is>
           <t>2025-05-02</t>
-        </is>
-      </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3532,10 +3541,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>124691814</v>
+        <v>124693275</v>
       </c>
       <c r="B29" t="n">
-        <v>56714</v>
+        <v>91026</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3548,43 +3557,34 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>102612</v>
+        <v>1204</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>förbiflygande</t>
-        </is>
-      </c>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
           <t>Tjärnflon, Tjärnflon, Jmt</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>452489</v>
+        <v>452523</v>
       </c>
       <c r="R29" t="n">
-        <v>6990896</v>
+        <v>6990595</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3643,10 +3643,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>124699728</v>
+        <v>124701352</v>
       </c>
       <c r="B30" t="n">
-        <v>79891</v>
+        <v>79892</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3659,34 +3659,39 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P30" t="inlineStr">
         <is>
           <t>Tjärnflon, Tjärnflon, Jmt</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>452650</v>
+        <v>452657</v>
       </c>
       <c r="R30" t="n">
-        <v>6990495</v>
+        <v>6990499</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3719,6 +3724,11 @@
       <c r="AA30" t="inlineStr">
         <is>
           <t>2025-05-02</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>Rikligt med skrovellav, APOTECHIER på en av bålarna</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3745,10 +3755,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>124689574</v>
+        <v>124695367</v>
       </c>
       <c r="B31" t="n">
-        <v>57513</v>
+        <v>82597</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3761,39 +3771,34 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>100109</v>
+        <v>1312</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P31" t="inlineStr">
         <is>
           <t>Tjärnflon, Tjärnflon, Jmt</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>452326</v>
+        <v>452617</v>
       </c>
       <c r="R31" t="n">
-        <v>6990987</v>
+        <v>6990540</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3826,11 +3831,6 @@
       <c r="AA31" t="inlineStr">
         <is>
           <t>2025-05-02</t>
-        </is>
-      </c>
-      <c r="AC31" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3857,10 +3857,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>124704726</v>
+        <v>124702530</v>
       </c>
       <c r="B32" t="n">
-        <v>91012</v>
+        <v>79891</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3873,21 +3873,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3897,7 +3897,7 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>452828</v>
+        <v>452746</v>
       </c>
       <c r="R32" t="n">
         <v>6990384</v>
@@ -3959,10 +3959,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>124705215</v>
+        <v>124721401</v>
       </c>
       <c r="B33" t="n">
-        <v>91012</v>
+        <v>57513</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -3975,34 +3975,39 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Häggsåsen, Häggsåsen, Jmt</t>
+          <t>Tjärnflon, Tjärnflon, Jmt</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>452850</v>
+        <v>452415</v>
       </c>
       <c r="R33" t="n">
-        <v>6990404</v>
+        <v>6990714</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4035,6 +4040,11 @@
       <c r="AA33" t="inlineStr">
         <is>
           <t>2025-05-02</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4061,10 +4071,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>124721401</v>
+        <v>124706585</v>
       </c>
       <c r="B34" t="n">
-        <v>57513</v>
+        <v>77743</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4077,39 +4087,34 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>100109</v>
+        <v>228579</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
-      <c r="M34" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Tjärnflon, Tjärnflon, Jmt</t>
+          <t>Häggsåsen, Häggsåsen, Jmt</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>452415</v>
+        <v>452913</v>
       </c>
       <c r="R34" t="n">
-        <v>6990714</v>
+        <v>6990390</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4142,11 +4147,6 @@
       <c r="AA34" t="inlineStr">
         <is>
           <t>2025-05-02</t>
-        </is>
-      </c>
-      <c r="AC34" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4173,10 +4173,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>124706864</v>
+        <v>124693950</v>
       </c>
       <c r="B35" t="n">
-        <v>57513</v>
+        <v>91012</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4189,39 +4189,34 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Häggsåsen, Häggsåsen, Jmt</t>
+          <t>Tjärnflon, Tjärnflon, Jmt</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>453007</v>
+        <v>452582</v>
       </c>
       <c r="R35" t="n">
-        <v>6990356</v>
+        <v>6990572</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4254,11 +4249,6 @@
       <c r="AA35" t="inlineStr">
         <is>
           <t>2025-05-02</t>
-        </is>
-      </c>
-      <c r="AC35" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4285,10 +4275,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>124701516</v>
+        <v>124704726</v>
       </c>
       <c r="B36" t="n">
-        <v>91299</v>
+        <v>91012</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4301,34 +4291,34 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Tjärnflon, Tjärnflon, Jmt</t>
+          <t>Häggsåsen, Häggsåsen, Jmt</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>452635</v>
+        <v>452828</v>
       </c>
       <c r="R36" t="n">
-        <v>6990463</v>
+        <v>6990384</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4387,10 +4377,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>124702902</v>
+        <v>124691378</v>
       </c>
       <c r="B37" t="n">
-        <v>79891</v>
+        <v>91012</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4403,34 +4393,34 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Häggsåsen, Häggsåsen, Jmt</t>
+          <t>Tjärnflon, Tjärnflon, Jmt</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>452734</v>
+        <v>452431</v>
       </c>
       <c r="R37" t="n">
-        <v>6990348</v>
+        <v>6990946</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4489,7 +4479,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>124704478</v>
+        <v>124705813</v>
       </c>
       <c r="B38" t="n">
         <v>57513</v>
@@ -4525,7 +4515,7 @@
       <c r="I38" t="inlineStr"/>
       <c r="M38" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>gammalt bo</t>
         </is>
       </c>
       <c r="P38" t="inlineStr">
@@ -4534,10 +4524,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>452836</v>
+        <v>452865</v>
       </c>
       <c r="R38" t="n">
-        <v>6990321</v>
+        <v>6990385</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4574,7 +4564,7 @@
       </c>
       <c r="AC38" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Möjligt gammalt bo 3m upp i granstubbe med granticka på</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4601,10 +4591,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>124703242</v>
+        <v>124695424</v>
       </c>
       <c r="B39" t="n">
-        <v>91299</v>
+        <v>91012</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4617,34 +4607,34 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Häggsåsen, Häggsåsen, Jmt</t>
+          <t>Tjärnflon, Tjärnflon, Jmt</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>452760</v>
+        <v>452642</v>
       </c>
       <c r="R39" t="n">
-        <v>6990252</v>
+        <v>6990548</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4703,10 +4693,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>124702770</v>
+        <v>124689475</v>
       </c>
       <c r="B40" t="n">
-        <v>79891</v>
+        <v>57513</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4719,34 +4709,39 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Häggsåsen, Häggsåsen, Jmt</t>
+          <t>Tjärnflon, Tjärnflon, Jmt</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>452731</v>
+        <v>452291</v>
       </c>
       <c r="R40" t="n">
-        <v>6990355</v>
+        <v>6990952</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4779,6 +4774,11 @@
       <c r="AA40" t="inlineStr">
         <is>
           <t>2025-05-02</t>
+        </is>
+      </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4805,10 +4805,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>124693275</v>
+        <v>124689655</v>
       </c>
       <c r="B41" t="n">
-        <v>91026</v>
+        <v>91299</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4821,21 +4821,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>1204</v>
+        <v>658</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4845,10 +4845,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>452523</v>
+        <v>452312</v>
       </c>
       <c r="R41" t="n">
-        <v>6990595</v>
+        <v>6990961</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4907,10 +4907,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>124689655</v>
+        <v>124705215</v>
       </c>
       <c r="B42" t="n">
-        <v>91299</v>
+        <v>91012</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -4923,34 +4923,34 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Tjärnflon, Tjärnflon, Jmt</t>
+          <t>Häggsåsen, Häggsåsen, Jmt</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>452312</v>
+        <v>452850</v>
       </c>
       <c r="R42" t="n">
-        <v>6990961</v>
+        <v>6990404</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5009,7 +5009,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>124756739</v>
+        <v>124756750</v>
       </c>
       <c r="B43" t="n">
         <v>98101</v>
@@ -5044,7 +5044,7 @@
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
@@ -5061,10 +5061,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>452711</v>
+        <v>452617</v>
       </c>
       <c r="R43" t="n">
-        <v>6990473</v>
+        <v>6990549</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5096,7 +5096,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5106,7 +5106,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5134,10 +5134,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>124756742</v>
+        <v>124756779</v>
       </c>
       <c r="B44" t="n">
-        <v>79927</v>
+        <v>78810</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5146,25 +5146,25 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6464</v>
+        <v>6425</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5174,10 +5174,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>452682</v>
+        <v>452143</v>
       </c>
       <c r="R44" t="n">
-        <v>6990476</v>
+        <v>6990780</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5209,7 +5209,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>13:53</t>
+          <t>09:51</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5219,7 +5219,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>13:53</t>
+          <t>09:51</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5230,21 +5230,6 @@
       </c>
       <c r="AG44" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ44" t="inlineStr">
-        <is>
-          <t>rönn</t>
-        </is>
-      </c>
-      <c r="AK44" t="inlineStr">
-        <is>
-          <t>Sorbus aucuparia</t>
-        </is>
-      </c>
-      <c r="AO44" t="inlineStr">
-        <is>
-          <t>Sorbus aucuparia</t>
-        </is>
       </c>
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
@@ -5261,7 +5246,7 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>124756754</v>
+        <v>124756725</v>
       </c>
       <c r="B45" t="n">
         <v>78810</v>
@@ -5301,10 +5286,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>452544</v>
+        <v>452762</v>
       </c>
       <c r="R45" t="n">
-        <v>6990646</v>
+        <v>6990327</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5336,7 +5321,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>12:04</t>
+          <t>14:37</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5346,7 +5331,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>12:04</t>
+          <t>14:37</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5373,7 +5358,7 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>124756688</v>
+        <v>124753608</v>
       </c>
       <c r="B46" t="n">
         <v>79891</v>
@@ -5413,10 +5398,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>452694</v>
+        <v>452731</v>
       </c>
       <c r="R46" t="n">
-        <v>6990598</v>
+        <v>6990377</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5446,19 +5431,9 @@
           <t>2025-05-03</t>
         </is>
       </c>
-      <c r="Z46" t="inlineStr">
-        <is>
-          <t>20:19</t>
-        </is>
-      </c>
       <c r="AA46" t="inlineStr">
         <is>
           <t>2025-05-03</t>
-        </is>
-      </c>
-      <c r="AB46" t="inlineStr">
-        <is>
-          <t>20:19</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5473,12 +5448,12 @@
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
@@ -5587,10 +5562,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>124756730</v>
+        <v>124756758</v>
       </c>
       <c r="B48" t="n">
-        <v>98101</v>
+        <v>90962</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5599,50 +5574,38 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>220787</v>
+        <v>112</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Stjärntagging</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Asterodon ferruginosus</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I48" t="inlineStr">
-        <is>
-          <t>200</t>
-        </is>
-      </c>
-      <c r="J48" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K48" t="inlineStr"/>
-      <c r="L48" t="inlineStr"/>
-      <c r="N48" t="inlineStr"/>
+          <t>Pat.</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
           <t>Häggsåsen N, Jmt</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>452675</v>
+        <v>452509</v>
       </c>
       <c r="R48" t="n">
-        <v>6990411</v>
+        <v>6990778</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5674,7 +5637,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>11:40</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -5684,12 +5647,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>14:20</t>
-        </is>
-      </c>
-      <c r="AC48" t="inlineStr">
-        <is>
-          <t>Min antal</t>
+          <t>11:40</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5698,7 +5656,6 @@
       <c r="AE48" t="b">
         <v>0</v>
       </c>
-      <c r="AF48" t="inlineStr"/>
       <c r="AG48" t="b">
         <v>0</v>
       </c>
@@ -5717,10 +5674,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>124756734</v>
+        <v>124756778</v>
       </c>
       <c r="B49" t="n">
-        <v>79891</v>
+        <v>78810</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5733,21 +5690,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5757,10 +5714,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>452675</v>
+        <v>452153</v>
       </c>
       <c r="R49" t="n">
-        <v>6990435</v>
+        <v>6990834</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5792,7 +5749,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>10:03</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -5802,7 +5759,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>10:03</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5813,21 +5770,6 @@
       </c>
       <c r="AG49" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ49" t="inlineStr">
-        <is>
-          <t>rönn</t>
-        </is>
-      </c>
-      <c r="AK49" t="inlineStr">
-        <is>
-          <t>Sorbus aucuparia</t>
-        </is>
-      </c>
-      <c r="AO49" t="inlineStr">
-        <is>
-          <t>Sorbus aucuparia</t>
-        </is>
       </c>
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
@@ -5844,7 +5786,7 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>124753621</v>
+        <v>124756745</v>
       </c>
       <c r="B50" t="n">
         <v>98101</v>
@@ -5877,17 +5819,29 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I50" t="inlineStr"/>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr"/>
+      <c r="L50" t="inlineStr"/>
+      <c r="N50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
           <t>Häggsåsen N, Jmt</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>452506</v>
+        <v>452657</v>
       </c>
       <c r="R50" t="n">
-        <v>6990758</v>
+        <v>6990491</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5917,14 +5871,19 @@
           <t>2025-05-03</t>
         </is>
       </c>
+      <c r="Z50" t="inlineStr">
+        <is>
+          <t>13:44</t>
+        </is>
+      </c>
       <c r="AA50" t="inlineStr">
         <is>
           <t>2025-05-03</t>
         </is>
       </c>
-      <c r="AC50" t="inlineStr">
-        <is>
-          <t>Minst 60</t>
+      <c r="AB50" t="inlineStr">
+        <is>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5933,28 +5892,29 @@
       <c r="AE50" t="b">
         <v>0</v>
       </c>
+      <c r="AF50" t="inlineStr"/>
       <c r="AG50" t="b">
         <v>0</v>
       </c>
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>124753606</v>
+        <v>124756763</v>
       </c>
       <c r="B51" t="n">
-        <v>91299</v>
+        <v>98101</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -5963,38 +5923,50 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>658</v>
+        <v>220787</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
-        </is>
-      </c>
-      <c r="I51" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr"/>
+      <c r="L51" t="inlineStr"/>
+      <c r="N51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
           <t>Häggsåsen N, Jmt</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>452165</v>
+        <v>452478</v>
       </c>
       <c r="R51" t="n">
-        <v>6990824</v>
+        <v>6990887</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6024,39 +5996,50 @@
           <t>2025-05-03</t>
         </is>
       </c>
+      <c r="Z51" t="inlineStr">
+        <is>
+          <t>11:18</t>
+        </is>
+      </c>
       <c r="AA51" t="inlineStr">
         <is>
           <t>2025-05-03</t>
         </is>
       </c>
+      <c r="AB51" t="inlineStr">
+        <is>
+          <t>11:18</t>
+        </is>
+      </c>
       <c r="AD51" t="b">
         <v>0</v>
       </c>
       <c r="AE51" t="b">
         <v>0</v>
       </c>
+      <c r="AF51" t="inlineStr"/>
       <c r="AG51" t="b">
         <v>0</v>
       </c>
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>124753627</v>
+        <v>124756746</v>
       </c>
       <c r="B52" t="n">
-        <v>98101</v>
+        <v>91012</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6065,25 +6048,25 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -6093,10 +6076,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>452608</v>
+        <v>452639</v>
       </c>
       <c r="R52" t="n">
-        <v>6990927</v>
+        <v>6990537</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6126,14 +6109,19 @@
           <t>2025-05-03</t>
         </is>
       </c>
+      <c r="Z52" t="inlineStr">
+        <is>
+          <t>13:36</t>
+        </is>
+      </c>
       <c r="AA52" t="inlineStr">
         <is>
           <t>2025-05-03</t>
         </is>
       </c>
-      <c r="AC52" t="inlineStr">
-        <is>
-          <t>Minst 50</t>
+      <c r="AB52" t="inlineStr">
+        <is>
+          <t>13:36</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6148,22 +6136,22 @@
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>124756733</v>
+        <v>124753580</v>
       </c>
       <c r="B53" t="n">
-        <v>79927</v>
+        <v>91012</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6172,25 +6160,25 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6464</v>
+        <v>1202</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -6200,10 +6188,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>452675</v>
+        <v>452693</v>
       </c>
       <c r="R53" t="n">
-        <v>6990435</v>
+        <v>6990472</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6233,21 +6221,11 @@
           <t>2025-05-03</t>
         </is>
       </c>
-      <c r="Z53" t="inlineStr">
-        <is>
-          <t>14:15</t>
-        </is>
-      </c>
       <c r="AA53" t="inlineStr">
         <is>
           <t>2025-05-03</t>
         </is>
       </c>
-      <c r="AB53" t="inlineStr">
-        <is>
-          <t>14:15</t>
-        </is>
-      </c>
       <c r="AD53" t="b">
         <v>0</v>
       </c>
@@ -6256,41 +6234,26 @@
       </c>
       <c r="AG53" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ53" t="inlineStr">
-        <is>
-          <t>rönn</t>
-        </is>
-      </c>
-      <c r="AK53" t="inlineStr">
-        <is>
-          <t>Sorbus aucuparia</t>
-        </is>
-      </c>
-      <c r="AO53" t="inlineStr">
-        <is>
-          <t>Sorbus aucuparia</t>
-        </is>
       </c>
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>124756766</v>
+        <v>124753638</v>
       </c>
       <c r="B54" t="n">
-        <v>79891</v>
+        <v>78810</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6303,21 +6266,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6327,10 +6290,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>452396</v>
+        <v>452823</v>
       </c>
       <c r="R54" t="n">
-        <v>6990981</v>
+        <v>6990367</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6360,19 +6323,9 @@
           <t>2025-05-03</t>
         </is>
       </c>
-      <c r="Z54" t="inlineStr">
-        <is>
-          <t>10:58</t>
-        </is>
-      </c>
       <c r="AA54" t="inlineStr">
         <is>
           <t>2025-05-03</t>
-        </is>
-      </c>
-      <c r="AB54" t="inlineStr">
-        <is>
-          <t>10:58</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6387,22 +6340,22 @@
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>124753587</v>
+        <v>124756772</v>
       </c>
       <c r="B55" t="n">
-        <v>91012</v>
+        <v>78810</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6415,21 +6368,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6439,10 +6392,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>452331</v>
+        <v>452344</v>
       </c>
       <c r="R55" t="n">
-        <v>6990929</v>
+        <v>6990942</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6472,9 +6425,19 @@
           <t>2025-05-03</t>
         </is>
       </c>
+      <c r="Z55" t="inlineStr">
+        <is>
+          <t>10:32</t>
+        </is>
+      </c>
       <c r="AA55" t="inlineStr">
         <is>
           <t>2025-05-03</t>
+        </is>
+      </c>
+      <c r="AB55" t="inlineStr">
+        <is>
+          <t>10:32</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6489,22 +6452,22 @@
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>124753576</v>
+        <v>124753627</v>
       </c>
       <c r="B56" t="n">
-        <v>91012</v>
+        <v>98101</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6513,25 +6476,25 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6541,10 +6504,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>452837</v>
+        <v>452608</v>
       </c>
       <c r="R56" t="n">
-        <v>6990384</v>
+        <v>6990927</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6577,6 +6540,11 @@
       <c r="AA56" t="inlineStr">
         <is>
           <t>2025-05-03</t>
+        </is>
+      </c>
+      <c r="AC56" t="inlineStr">
+        <is>
+          <t>Minst 50</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6603,10 +6571,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>124753592</v>
+        <v>124753585</v>
       </c>
       <c r="B57" t="n">
-        <v>57513</v>
+        <v>91012</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6619,21 +6587,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6643,10 +6611,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>452396</v>
+        <v>452595</v>
       </c>
       <c r="R57" t="n">
-        <v>6990703</v>
+        <v>6990913</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6679,11 +6647,6 @@
       <c r="AA57" t="inlineStr">
         <is>
           <t>2025-05-03</t>
-        </is>
-      </c>
-      <c r="AC57" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6710,7 +6673,7 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>124756778</v>
+        <v>124756754</v>
       </c>
       <c r="B58" t="n">
         <v>78810</v>
@@ -6750,10 +6713,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>452153</v>
+        <v>452544</v>
       </c>
       <c r="R58" t="n">
-        <v>6990834</v>
+        <v>6990646</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6785,7 +6748,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>10:03</t>
+          <t>12:04</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -6795,7 +6758,7 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>10:03</t>
+          <t>12:04</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6822,10 +6785,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>124753614</v>
+        <v>124753610</v>
       </c>
       <c r="B59" t="n">
-        <v>98101</v>
+        <v>79891</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -6834,25 +6797,25 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6862,10 +6825,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>452751</v>
+        <v>452435</v>
       </c>
       <c r="R59" t="n">
-        <v>6990344</v>
+        <v>6990938</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6898,11 +6861,6 @@
       <c r="AA59" t="inlineStr">
         <is>
           <t>2025-05-03</t>
-        </is>
-      </c>
-      <c r="AC59" t="inlineStr">
-        <is>
-          <t>Minst 200</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -6929,10 +6887,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>124753604</v>
+        <v>124756730</v>
       </c>
       <c r="B60" t="n">
-        <v>79892</v>
+        <v>98101</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -6941,38 +6899,50 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>2081</v>
+        <v>220787</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
-        </is>
-      </c>
-      <c r="I60" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K60" t="inlineStr"/>
+      <c r="L60" t="inlineStr"/>
+      <c r="N60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
           <t>Häggsåsen N, Jmt</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>452435</v>
+        <v>452675</v>
       </c>
       <c r="R60" t="n">
-        <v>6990938</v>
+        <v>6990411</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -7002,39 +6972,55 @@
           <t>2025-05-03</t>
         </is>
       </c>
+      <c r="Z60" t="inlineStr">
+        <is>
+          <t>14:20</t>
+        </is>
+      </c>
       <c r="AA60" t="inlineStr">
         <is>
           <t>2025-05-03</t>
         </is>
       </c>
+      <c r="AB60" t="inlineStr">
+        <is>
+          <t>14:20</t>
+        </is>
+      </c>
+      <c r="AC60" t="inlineStr">
+        <is>
+          <t>Min antal</t>
+        </is>
+      </c>
       <c r="AD60" t="b">
         <v>0</v>
       </c>
       <c r="AE60" t="b">
         <v>0</v>
       </c>
+      <c r="AF60" t="inlineStr"/>
       <c r="AG60" t="b">
         <v>0</v>
       </c>
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>124756746</v>
+        <v>124753625</v>
       </c>
       <c r="B61" t="n">
-        <v>91012</v>
+        <v>98101</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -7043,25 +7029,25 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -7071,10 +7057,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>452639</v>
+        <v>452550</v>
       </c>
       <c r="R61" t="n">
-        <v>6990537</v>
+        <v>6990907</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7104,19 +7090,14 @@
           <t>2025-05-03</t>
         </is>
       </c>
-      <c r="Z61" t="inlineStr">
-        <is>
-          <t>13:36</t>
-        </is>
-      </c>
       <c r="AA61" t="inlineStr">
         <is>
           <t>2025-05-03</t>
         </is>
       </c>
-      <c r="AB61" t="inlineStr">
-        <is>
-          <t>13:36</t>
+      <c r="AC61" t="inlineStr">
+        <is>
+          <t>Minst 50</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7131,22 +7112,22 @@
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>124756753</v>
+        <v>124753617</v>
       </c>
       <c r="B62" t="n">
-        <v>91012</v>
+        <v>98101</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -7155,25 +7136,25 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -7183,10 +7164,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>452608</v>
+        <v>452655</v>
       </c>
       <c r="R62" t="n">
-        <v>6990625</v>
+        <v>6990482</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7216,19 +7197,14 @@
           <t>2025-05-03</t>
         </is>
       </c>
-      <c r="Z62" t="inlineStr">
-        <is>
-          <t>12:07</t>
-        </is>
-      </c>
       <c r="AA62" t="inlineStr">
         <is>
           <t>2025-05-03</t>
         </is>
       </c>
-      <c r="AB62" t="inlineStr">
-        <is>
-          <t>12:07</t>
+      <c r="AC62" t="inlineStr">
+        <is>
+          <t>Minst 50</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7243,22 +7219,22 @@
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>124753609</v>
+        <v>124756777</v>
       </c>
       <c r="B63" t="n">
-        <v>79891</v>
+        <v>98101</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -7267,38 +7243,50 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I63" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J63" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K63" t="inlineStr"/>
+      <c r="L63" t="inlineStr"/>
+      <c r="N63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
           <t>Häggsåsen N, Jmt</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>452528</v>
+        <v>452146</v>
       </c>
       <c r="R63" t="n">
-        <v>6990710</v>
+        <v>6990839</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7328,39 +7316,50 @@
           <t>2025-05-03</t>
         </is>
       </c>
+      <c r="Z63" t="inlineStr">
+        <is>
+          <t>10:06</t>
+        </is>
+      </c>
       <c r="AA63" t="inlineStr">
         <is>
           <t>2025-05-03</t>
         </is>
       </c>
+      <c r="AB63" t="inlineStr">
+        <is>
+          <t>10:06</t>
+        </is>
+      </c>
       <c r="AD63" t="b">
         <v>0</v>
       </c>
       <c r="AE63" t="b">
         <v>0</v>
       </c>
+      <c r="AF63" t="inlineStr"/>
       <c r="AG63" t="b">
         <v>0</v>
       </c>
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>124756748</v>
+        <v>124753586</v>
       </c>
       <c r="B64" t="n">
-        <v>78810</v>
+        <v>91012</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7373,21 +7372,21 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7397,10 +7396,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>452609</v>
+        <v>452500</v>
       </c>
       <c r="R64" t="n">
-        <v>6990543</v>
+        <v>6990950</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7430,19 +7429,9 @@
           <t>2025-05-03</t>
         </is>
       </c>
-      <c r="Z64" t="inlineStr">
-        <is>
-          <t>12:29</t>
-        </is>
-      </c>
       <c r="AA64" t="inlineStr">
         <is>
           <t>2025-05-03</t>
-        </is>
-      </c>
-      <c r="AB64" t="inlineStr">
-        <is>
-          <t>12:29</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7457,22 +7446,22 @@
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>124753632</v>
+        <v>124756734</v>
       </c>
       <c r="B65" t="n">
-        <v>98101</v>
+        <v>79891</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -7481,25 +7470,25 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7509,10 +7498,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>452455</v>
+        <v>452675</v>
       </c>
       <c r="R65" t="n">
-        <v>6990942</v>
+        <v>6990435</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7542,14 +7531,19 @@
           <t>2025-05-03</t>
         </is>
       </c>
+      <c r="Z65" t="inlineStr">
+        <is>
+          <t>14:14</t>
+        </is>
+      </c>
       <c r="AA65" t="inlineStr">
         <is>
           <t>2025-05-03</t>
         </is>
       </c>
-      <c r="AC65" t="inlineStr">
-        <is>
-          <t>Minst 30</t>
+      <c r="AB65" t="inlineStr">
+        <is>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7560,26 +7554,41 @@
       </c>
       <c r="AG65" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ65" t="inlineStr">
+        <is>
+          <t>rönn</t>
+        </is>
+      </c>
+      <c r="AK65" t="inlineStr">
+        <is>
+          <t>Sorbus aucuparia</t>
+        </is>
+      </c>
+      <c r="AO65" t="inlineStr">
+        <is>
+          <t>Sorbus aucuparia</t>
+        </is>
       </c>
       <c r="AT65" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>124756750</v>
+        <v>124753607</v>
       </c>
       <c r="B66" t="n">
-        <v>98101</v>
+        <v>79891</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -7588,50 +7597,38 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I66" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J66" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K66" t="inlineStr"/>
-      <c r="L66" t="inlineStr"/>
-      <c r="N66" t="inlineStr"/>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
           <t>Häggsåsen N, Jmt</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>452617</v>
+        <v>452734</v>
       </c>
       <c r="R66" t="n">
-        <v>6990549</v>
+        <v>6990356</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7661,50 +7658,39 @@
           <t>2025-05-03</t>
         </is>
       </c>
-      <c r="Z66" t="inlineStr">
-        <is>
-          <t>12:28</t>
-        </is>
-      </c>
       <c r="AA66" t="inlineStr">
         <is>
           <t>2025-05-03</t>
         </is>
       </c>
-      <c r="AB66" t="inlineStr">
-        <is>
-          <t>12:28</t>
-        </is>
-      </c>
       <c r="AD66" t="b">
         <v>0</v>
       </c>
       <c r="AE66" t="b">
         <v>0</v>
       </c>
-      <c r="AF66" t="inlineStr"/>
       <c r="AG66" t="b">
         <v>0</v>
       </c>
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>124753584</v>
+        <v>124753629</v>
       </c>
       <c r="B67" t="n">
-        <v>91012</v>
+        <v>98101</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -7713,25 +7699,25 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7741,10 +7727,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>452444</v>
+        <v>452576</v>
       </c>
       <c r="R67" t="n">
-        <v>6990774</v>
+        <v>6990924</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7777,6 +7763,11 @@
       <c r="AA67" t="inlineStr">
         <is>
           <t>2025-05-03</t>
+        </is>
+      </c>
+      <c r="AC67" t="inlineStr">
+        <is>
+          <t>Minst 30</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7803,7 +7794,7 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>124753629</v>
+        <v>124753631</v>
       </c>
       <c r="B68" t="n">
         <v>98101</v>
@@ -7843,10 +7834,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>452576</v>
+        <v>452526</v>
       </c>
       <c r="R68" t="n">
-        <v>6990924</v>
+        <v>6990943</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7883,7 +7874,7 @@
       </c>
       <c r="AC68" t="inlineStr">
         <is>
-          <t>Minst 30</t>
+          <t>Minst 20</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -7910,10 +7901,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>124756745</v>
+        <v>124756755</v>
       </c>
       <c r="B69" t="n">
-        <v>98101</v>
+        <v>91299</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -7922,50 +7913,38 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I69" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J69" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K69" t="inlineStr"/>
-      <c r="L69" t="inlineStr"/>
-      <c r="N69" t="inlineStr"/>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
           <t>Häggsåsen N, Jmt</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>452657</v>
+        <v>452538</v>
       </c>
       <c r="R69" t="n">
-        <v>6990491</v>
+        <v>6990659</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7997,7 +7976,7 @@
       </c>
       <c r="Z69" t="inlineStr">
         <is>
-          <t>13:44</t>
+          <t>11:58</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
@@ -8007,7 +7986,7 @@
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>13:44</t>
+          <t>11:58</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -8016,7 +7995,6 @@
       <c r="AE69" t="b">
         <v>0</v>
       </c>
-      <c r="AF69" t="inlineStr"/>
       <c r="AG69" t="b">
         <v>0</v>
       </c>
@@ -8035,7 +8013,7 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>124756731</v>
+        <v>124753579</v>
       </c>
       <c r="B70" t="n">
         <v>91012</v>
@@ -8075,10 +8053,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>452672</v>
+        <v>452710</v>
       </c>
       <c r="R70" t="n">
-        <v>6990427</v>
+        <v>6990467</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -8108,19 +8086,9 @@
           <t>2025-05-03</t>
         </is>
       </c>
-      <c r="Z70" t="inlineStr">
-        <is>
-          <t>14:19</t>
-        </is>
-      </c>
       <c r="AA70" t="inlineStr">
         <is>
           <t>2025-05-03</t>
-        </is>
-      </c>
-      <c r="AB70" t="inlineStr">
-        <is>
-          <t>14:19</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8135,22 +8103,22 @@
       <c r="AT70" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>124753579</v>
+        <v>124756743</v>
       </c>
       <c r="B71" t="n">
-        <v>91012</v>
+        <v>79891</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -8163,21 +8131,21 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -8187,10 +8155,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>452710</v>
+        <v>452682</v>
       </c>
       <c r="R71" t="n">
-        <v>6990467</v>
+        <v>6990476</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -8220,11 +8188,21 @@
           <t>2025-05-03</t>
         </is>
       </c>
+      <c r="Z71" t="inlineStr">
+        <is>
+          <t>13:53</t>
+        </is>
+      </c>
       <c r="AA71" t="inlineStr">
         <is>
           <t>2025-05-03</t>
         </is>
       </c>
+      <c r="AB71" t="inlineStr">
+        <is>
+          <t>13:53</t>
+        </is>
+      </c>
       <c r="AD71" t="b">
         <v>0</v>
       </c>
@@ -8233,26 +8211,41 @@
       </c>
       <c r="AG71" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ71" t="inlineStr">
+        <is>
+          <t>rönn</t>
+        </is>
+      </c>
+      <c r="AK71" t="inlineStr">
+        <is>
+          <t>Sorbus aucuparia</t>
+        </is>
+      </c>
+      <c r="AO71" t="inlineStr">
+        <is>
+          <t>Sorbus aucuparia</t>
+        </is>
       </c>
       <c r="AT71" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX71" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>124753585</v>
+        <v>124756770</v>
       </c>
       <c r="B72" t="n">
-        <v>91012</v>
+        <v>74899</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -8261,38 +8254,41 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>1202</v>
+        <v>6486</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Skuggnål</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Chaenotheca sphaerocephala</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Nádv.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
+      <c r="J72" t="inlineStr"/>
+      <c r="K72" t="inlineStr"/>
+      <c r="N72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
           <t>Häggsåsen N, Jmt</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>452595</v>
+        <v>452339</v>
       </c>
       <c r="R72" t="n">
-        <v>6990913</v>
+        <v>6990941</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8322,39 +8318,84 @@
           <t>2025-05-03</t>
         </is>
       </c>
+      <c r="Z72" t="inlineStr">
+        <is>
+          <t>10:44</t>
+        </is>
+      </c>
       <c r="AA72" t="inlineStr">
         <is>
           <t>2025-05-03</t>
         </is>
       </c>
+      <c r="AB72" t="inlineStr">
+        <is>
+          <t>10:44</t>
+        </is>
+      </c>
       <c r="AD72" t="b">
         <v>0</v>
       </c>
       <c r="AE72" t="b">
         <v>0</v>
       </c>
+      <c r="AF72" t="inlineStr">
+        <is>
+          <t>mikroskoperad</t>
+        </is>
+      </c>
       <c r="AG72" t="b">
         <v>0</v>
+      </c>
+      <c r="AH72" t="inlineStr">
+        <is>
+          <t>Blåbärsgranskog</t>
+        </is>
+      </c>
+      <c r="AI72" t="inlineStr">
+        <is>
+          <t>I hålighet vid basen av gammal gran i fuktig granskog.</t>
+        </is>
+      </c>
+      <c r="AJ72" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK72" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM72" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO72" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Picea abies</t>
+        </is>
       </c>
       <c r="AT72" t="inlineStr"/>
       <c r="AW72" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX72" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>124753625</v>
+        <v>124756688</v>
       </c>
       <c r="B73" t="n">
-        <v>98101</v>
+        <v>79891</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -8363,25 +8404,25 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -8391,10 +8432,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>452550</v>
+        <v>452694</v>
       </c>
       <c r="R73" t="n">
-        <v>6990907</v>
+        <v>6990598</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8424,14 +8465,19 @@
           <t>2025-05-03</t>
         </is>
       </c>
+      <c r="Z73" t="inlineStr">
+        <is>
+          <t>20:19</t>
+        </is>
+      </c>
       <c r="AA73" t="inlineStr">
         <is>
           <t>2025-05-03</t>
         </is>
       </c>
-      <c r="AC73" t="inlineStr">
-        <is>
-          <t>Minst 50</t>
+      <c r="AB73" t="inlineStr">
+        <is>
+          <t>20:19</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8446,22 +8492,22 @@
       <c r="AT73" t="inlineStr"/>
       <c r="AW73" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>124753612</v>
+        <v>124756766</v>
       </c>
       <c r="B74" t="n">
-        <v>98101</v>
+        <v>79891</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -8470,25 +8516,25 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -8498,10 +8544,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>452924</v>
+        <v>452396</v>
       </c>
       <c r="R74" t="n">
-        <v>6990397</v>
+        <v>6990981</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8531,14 +8577,19 @@
           <t>2025-05-03</t>
         </is>
       </c>
+      <c r="Z74" t="inlineStr">
+        <is>
+          <t>10:58</t>
+        </is>
+      </c>
       <c r="AA74" t="inlineStr">
         <is>
           <t>2025-05-03</t>
         </is>
       </c>
-      <c r="AC74" t="inlineStr">
-        <is>
-          <t>Minst 20</t>
+      <c r="AB74" t="inlineStr">
+        <is>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8553,22 +8604,22 @@
       <c r="AT74" t="inlineStr"/>
       <c r="AW74" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX74" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>124756770</v>
+        <v>124753605</v>
       </c>
       <c r="B75" t="n">
-        <v>74899</v>
+        <v>79892</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -8577,41 +8628,38 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>6486</v>
+        <v>2081</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Skuggnål</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Chaenotheca sphaerocephala</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>Nádv.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
-      <c r="J75" t="inlineStr"/>
-      <c r="K75" t="inlineStr"/>
-      <c r="N75" t="inlineStr"/>
       <c r="P75" t="inlineStr">
         <is>
           <t>Häggsåsen N, Jmt</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>452339</v>
+        <v>452408</v>
       </c>
       <c r="R75" t="n">
-        <v>6990941</v>
+        <v>6990952</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8641,84 +8689,39 @@
           <t>2025-05-03</t>
         </is>
       </c>
-      <c r="Z75" t="inlineStr">
-        <is>
-          <t>10:44</t>
-        </is>
-      </c>
       <c r="AA75" t="inlineStr">
         <is>
           <t>2025-05-03</t>
         </is>
       </c>
-      <c r="AB75" t="inlineStr">
-        <is>
-          <t>10:44</t>
-        </is>
-      </c>
       <c r="AD75" t="b">
         <v>0</v>
       </c>
       <c r="AE75" t="b">
         <v>0</v>
       </c>
-      <c r="AF75" t="inlineStr">
-        <is>
-          <t>mikroskoperad</t>
-        </is>
-      </c>
       <c r="AG75" t="b">
         <v>0</v>
-      </c>
-      <c r="AH75" t="inlineStr">
-        <is>
-          <t>Blåbärsgranskog</t>
-        </is>
-      </c>
-      <c r="AI75" t="inlineStr">
-        <is>
-          <t>I hålighet vid basen av gammal gran i fuktig granskog.</t>
-        </is>
-      </c>
-      <c r="AJ75" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK75" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM75" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO75" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Picea abies</t>
-        </is>
       </c>
       <c r="AT75" t="inlineStr"/>
       <c r="AW75" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX75" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>124756727</v>
+        <v>124753604</v>
       </c>
       <c r="B76" t="n">
-        <v>79920</v>
+        <v>79892</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
@@ -8727,25 +8730,25 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>6462</v>
+        <v>2081</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -8755,10 +8758,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>452745</v>
+        <v>452435</v>
       </c>
       <c r="R76" t="n">
-        <v>6990359</v>
+        <v>6990938</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8788,19 +8791,9 @@
           <t>2025-05-03</t>
         </is>
       </c>
-      <c r="Z76" t="inlineStr">
-        <is>
-          <t>14:31</t>
-        </is>
-      </c>
       <c r="AA76" t="inlineStr">
         <is>
           <t>2025-05-03</t>
-        </is>
-      </c>
-      <c r="AB76" t="inlineStr">
-        <is>
-          <t>14:31</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -8815,22 +8808,22 @@
       <c r="AT76" t="inlineStr"/>
       <c r="AW76" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX76" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>124753607</v>
+        <v>124753639</v>
       </c>
       <c r="B77" t="n">
-        <v>79891</v>
+        <v>78810</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -8843,21 +8836,21 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -8867,10 +8860,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>452734</v>
+        <v>452511</v>
       </c>
       <c r="R77" t="n">
-        <v>6990356</v>
+        <v>6990733</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8929,10 +8922,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>124756764</v>
+        <v>124756721</v>
       </c>
       <c r="B78" t="n">
-        <v>78810</v>
+        <v>79891</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -8945,21 +8938,21 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -8969,10 +8962,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>452462</v>
+        <v>452823</v>
       </c>
       <c r="R78" t="n">
-        <v>6990915</v>
+        <v>6990261</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -9004,7 +8997,7 @@
       </c>
       <c r="Z78" t="inlineStr">
         <is>
-          <t>11:11</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AA78" t="inlineStr">
@@ -9014,7 +9007,7 @@
       </c>
       <c r="AB78" t="inlineStr">
         <is>
-          <t>11:11</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -9025,6 +9018,21 @@
       </c>
       <c r="AG78" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ78" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK78" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO78" t="inlineStr">
+        <is>
+          <t>Omkullfallen grov stam # Salix caprea</t>
+        </is>
       </c>
       <c r="AT78" t="inlineStr"/>
       <c r="AW78" t="inlineStr">
@@ -9041,10 +9049,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>124753623</v>
+        <v>124753635</v>
       </c>
       <c r="B79" t="n">
-        <v>98101</v>
+        <v>91030</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -9053,25 +9061,25 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>220787</v>
+        <v>5432</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -9081,10 +9089,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>452510</v>
+        <v>452732</v>
       </c>
       <c r="R79" t="n">
-        <v>6990873</v>
+        <v>6990486</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -9117,11 +9125,6 @@
       <c r="AA79" t="inlineStr">
         <is>
           <t>2025-05-03</t>
-        </is>
-      </c>
-      <c r="AC79" t="inlineStr">
-        <is>
-          <t>Minst 50</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -9148,7 +9151,7 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>124753634</v>
+        <v>124753633</v>
       </c>
       <c r="B80" t="n">
         <v>91008</v>
@@ -9188,10 +9191,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>452750</v>
+        <v>452772</v>
       </c>
       <c r="R80" t="n">
-        <v>6990344</v>
+        <v>6990321</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -9250,10 +9253,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>124753580</v>
+        <v>124753606</v>
       </c>
       <c r="B81" t="n">
-        <v>91012</v>
+        <v>91299</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
@@ -9266,21 +9269,21 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -9290,10 +9293,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>452693</v>
+        <v>452165</v>
       </c>
       <c r="R81" t="n">
-        <v>6990472</v>
+        <v>6990824</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -9352,10 +9355,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>124753582</v>
+        <v>124753615</v>
       </c>
       <c r="B82" t="n">
-        <v>91012</v>
+        <v>98101</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
@@ -9364,25 +9367,25 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -9392,10 +9395,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>452649</v>
+        <v>452734</v>
       </c>
       <c r="R82" t="n">
-        <v>6990621</v>
+        <v>6990355</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -9428,6 +9431,11 @@
       <c r="AA82" t="inlineStr">
         <is>
           <t>2025-05-03</t>
+        </is>
+      </c>
+      <c r="AC82" t="inlineStr">
+        <is>
+          <t>Minst 30</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -9454,10 +9462,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>124753611</v>
+        <v>124753588</v>
       </c>
       <c r="B83" t="n">
-        <v>98101</v>
+        <v>91012</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
@@ -9466,25 +9474,25 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -9494,10 +9502,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>452997</v>
+        <v>452311</v>
       </c>
       <c r="R83" t="n">
-        <v>6990332</v>
+        <v>6990887</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9530,11 +9538,6 @@
       <c r="AA83" t="inlineStr">
         <is>
           <t>2025-05-03</t>
-        </is>
-      </c>
-      <c r="AC83" t="inlineStr">
-        <is>
-          <t>Minst 100</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -9561,10 +9564,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>124756741</v>
+        <v>124756742</v>
       </c>
       <c r="B84" t="n">
-        <v>79851</v>
+        <v>79927</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
@@ -9577,21 +9580,21 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>229497</v>
+        <v>6464</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -9636,7 +9639,7 @@
       </c>
       <c r="Z84" t="inlineStr">
         <is>
-          <t>13:54</t>
+          <t>13:53</t>
         </is>
       </c>
       <c r="AA84" t="inlineStr">
@@ -9646,7 +9649,7 @@
       </c>
       <c r="AB84" t="inlineStr">
         <is>
-          <t>13:54</t>
+          <t>13:53</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -9688,10 +9691,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>124756757</v>
+        <v>124756733</v>
       </c>
       <c r="B85" t="n">
-        <v>77743</v>
+        <v>79927</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
@@ -9700,25 +9703,25 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>228579</v>
+        <v>6464</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -9728,10 +9731,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>452506</v>
+        <v>452675</v>
       </c>
       <c r="R85" t="n">
-        <v>6990737</v>
+        <v>6990435</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9763,7 +9766,7 @@
       </c>
       <c r="Z85" t="inlineStr">
         <is>
-          <t>11:47</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="AA85" t="inlineStr">
@@ -9773,7 +9776,7 @@
       </c>
       <c r="AB85" t="inlineStr">
         <is>
-          <t>11:47</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -9784,6 +9787,21 @@
       </c>
       <c r="AG85" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ85" t="inlineStr">
+        <is>
+          <t>rönn</t>
+        </is>
+      </c>
+      <c r="AK85" t="inlineStr">
+        <is>
+          <t>Sorbus aucuparia</t>
+        </is>
+      </c>
+      <c r="AO85" t="inlineStr">
+        <is>
+          <t>Sorbus aucuparia</t>
+        </is>
       </c>
       <c r="AT85" t="inlineStr"/>
       <c r="AW85" t="inlineStr">
@@ -9800,10 +9818,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>124753624</v>
+        <v>124756741</v>
       </c>
       <c r="B86" t="n">
-        <v>98101</v>
+        <v>79851</v>
       </c>
       <c r="C86" t="inlineStr">
         <is>
@@ -9812,25 +9830,25 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>220787</v>
+        <v>229497</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -9840,10 +9858,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>452528</v>
+        <v>452682</v>
       </c>
       <c r="R86" t="n">
-        <v>6990882</v>
+        <v>6990476</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9873,14 +9891,19 @@
           <t>2025-05-03</t>
         </is>
       </c>
+      <c r="Z86" t="inlineStr">
+        <is>
+          <t>13:54</t>
+        </is>
+      </c>
       <c r="AA86" t="inlineStr">
         <is>
           <t>2025-05-03</t>
         </is>
       </c>
-      <c r="AC86" t="inlineStr">
-        <is>
-          <t>Minst 30</t>
+      <c r="AB86" t="inlineStr">
+        <is>
+          <t>13:54</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -9891,23 +9914,38 @@
       </c>
       <c r="AG86" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ86" t="inlineStr">
+        <is>
+          <t>rönn</t>
+        </is>
+      </c>
+      <c r="AK86" t="inlineStr">
+        <is>
+          <t>Sorbus aucuparia</t>
+        </is>
+      </c>
+      <c r="AO86" t="inlineStr">
+        <is>
+          <t>Sorbus aucuparia</t>
+        </is>
       </c>
       <c r="AT86" t="inlineStr"/>
       <c r="AW86" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX86" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>124756751</v>
+        <v>124753621</v>
       </c>
       <c r="B87" t="n">
         <v>98101</v>
@@ -9940,29 +9978,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I87" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J87" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K87" t="inlineStr"/>
-      <c r="L87" t="inlineStr"/>
-      <c r="N87" t="inlineStr"/>
+      <c r="I87" t="inlineStr"/>
       <c r="P87" t="inlineStr">
         <is>
           <t>Häggsåsen N, Jmt</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>452638</v>
+        <v>452506</v>
       </c>
       <c r="R87" t="n">
-        <v>6990559</v>
+        <v>6990758</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9992,19 +10018,14 @@
           <t>2025-05-03</t>
         </is>
       </c>
-      <c r="Z87" t="inlineStr">
-        <is>
-          <t>12:23</t>
-        </is>
-      </c>
       <c r="AA87" t="inlineStr">
         <is>
           <t>2025-05-03</t>
         </is>
       </c>
-      <c r="AB87" t="inlineStr">
-        <is>
-          <t>12:23</t>
+      <c r="AC87" t="inlineStr">
+        <is>
+          <t>Minst 60</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -10013,26 +10034,25 @@
       <c r="AE87" t="b">
         <v>0</v>
       </c>
-      <c r="AF87" t="inlineStr"/>
       <c r="AG87" t="b">
         <v>0</v>
       </c>
       <c r="AT87" t="inlineStr"/>
       <c r="AW87" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX87" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>124753581</v>
+        <v>124756759</v>
       </c>
       <c r="B88" t="n">
         <v>91012</v>
@@ -10072,10 +10092,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>452643</v>
+        <v>452509</v>
       </c>
       <c r="R88" t="n">
-        <v>6990504</v>
+        <v>6990778</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -10105,9 +10125,19 @@
           <t>2025-05-03</t>
         </is>
       </c>
+      <c r="Z88" t="inlineStr">
+        <is>
+          <t>11:39</t>
+        </is>
+      </c>
       <c r="AA88" t="inlineStr">
         <is>
           <t>2025-05-03</t>
+        </is>
+      </c>
+      <c r="AB88" t="inlineStr">
+        <is>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -10122,22 +10152,22 @@
       <c r="AT88" t="inlineStr"/>
       <c r="AW88" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX88" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>124756743</v>
+        <v>124753634</v>
       </c>
       <c r="B89" t="n">
-        <v>79891</v>
+        <v>91008</v>
       </c>
       <c r="C89" t="inlineStr">
         <is>
@@ -10150,21 +10180,21 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>6458</v>
+        <v>1108</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
@@ -10174,10 +10204,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>452682</v>
+        <v>452750</v>
       </c>
       <c r="R89" t="n">
-        <v>6990476</v>
+        <v>6990344</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -10207,21 +10237,11 @@
           <t>2025-05-03</t>
         </is>
       </c>
-      <c r="Z89" t="inlineStr">
-        <is>
-          <t>13:53</t>
-        </is>
-      </c>
       <c r="AA89" t="inlineStr">
         <is>
           <t>2025-05-03</t>
         </is>
       </c>
-      <c r="AB89" t="inlineStr">
-        <is>
-          <t>13:53</t>
-        </is>
-      </c>
       <c r="AD89" t="b">
         <v>0</v>
       </c>
@@ -10230,41 +10250,26 @@
       </c>
       <c r="AG89" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ89" t="inlineStr">
-        <is>
-          <t>rönn</t>
-        </is>
-      </c>
-      <c r="AK89" t="inlineStr">
-        <is>
-          <t>Sorbus aucuparia</t>
-        </is>
-      </c>
-      <c r="AO89" t="inlineStr">
-        <is>
-          <t>Sorbus aucuparia</t>
-        </is>
       </c>
       <c r="AT89" t="inlineStr"/>
       <c r="AW89" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX89" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>124756767</v>
+        <v>124756719</v>
       </c>
       <c r="B90" t="n">
-        <v>78810</v>
+        <v>79927</v>
       </c>
       <c r="C90" t="inlineStr">
         <is>
@@ -10273,25 +10278,25 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>6425</v>
+        <v>6464</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
@@ -10301,10 +10306,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>452362</v>
+        <v>452823</v>
       </c>
       <c r="R90" t="n">
-        <v>6991003</v>
+        <v>6990261</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -10336,7 +10341,7 @@
       </c>
       <c r="Z90" t="inlineStr">
         <is>
-          <t>10:55</t>
+          <t>14:59</t>
         </is>
       </c>
       <c r="AA90" t="inlineStr">
@@ -10346,7 +10351,7 @@
       </c>
       <c r="AB90" t="inlineStr">
         <is>
-          <t>10:55</t>
+          <t>14:59</t>
         </is>
       </c>
       <c r="AD90" t="b">
@@ -10373,7 +10378,7 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>124756772</v>
+        <v>124756765</v>
       </c>
       <c r="B91" t="n">
         <v>78810</v>
@@ -10413,7 +10418,7 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>452344</v>
+        <v>452432</v>
       </c>
       <c r="R91" t="n">
         <v>6990942</v>
@@ -10448,7 +10453,7 @@
       </c>
       <c r="Z91" t="inlineStr">
         <is>
-          <t>10:32</t>
+          <t>11:05</t>
         </is>
       </c>
       <c r="AA91" t="inlineStr">
@@ -10458,7 +10463,7 @@
       </c>
       <c r="AB91" t="inlineStr">
         <is>
-          <t>10:32</t>
+          <t>11:05</t>
         </is>
       </c>
       <c r="AD91" t="b">
@@ -10597,7 +10602,7 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>124753622</v>
+        <v>124756751</v>
       </c>
       <c r="B93" t="n">
         <v>98101</v>
@@ -10630,17 +10635,29 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I93" t="inlineStr"/>
+      <c r="I93" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J93" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K93" t="inlineStr"/>
+      <c r="L93" t="inlineStr"/>
+      <c r="N93" t="inlineStr"/>
       <c r="P93" t="inlineStr">
         <is>
           <t>Häggsåsen N, Jmt</t>
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>452472</v>
+        <v>452638</v>
       </c>
       <c r="R93" t="n">
-        <v>6990821</v>
+        <v>6990559</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -10670,14 +10687,19 @@
           <t>2025-05-03</t>
         </is>
       </c>
+      <c r="Z93" t="inlineStr">
+        <is>
+          <t>12:23</t>
+        </is>
+      </c>
       <c r="AA93" t="inlineStr">
         <is>
           <t>2025-05-03</t>
         </is>
       </c>
-      <c r="AC93" t="inlineStr">
-        <is>
-          <t>Minst 50</t>
+      <c r="AB93" t="inlineStr">
+        <is>
+          <t>12:23</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -10686,25 +10708,26 @@
       <c r="AE93" t="b">
         <v>0</v>
       </c>
+      <c r="AF93" t="inlineStr"/>
       <c r="AG93" t="b">
         <v>0</v>
       </c>
       <c r="AT93" t="inlineStr"/>
       <c r="AW93" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX93" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY93" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>124756774</v>
+        <v>124753632</v>
       </c>
       <c r="B94" t="n">
         <v>98101</v>
@@ -10737,29 +10760,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I94" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="J94" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K94" t="inlineStr"/>
-      <c r="L94" t="inlineStr"/>
-      <c r="N94" t="inlineStr"/>
+      <c r="I94" t="inlineStr"/>
       <c r="P94" t="inlineStr">
         <is>
           <t>Häggsåsen N, Jmt</t>
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>452308</v>
+        <v>452455</v>
       </c>
       <c r="R94" t="n">
-        <v>6990943</v>
+        <v>6990942</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -10789,19 +10800,14 @@
           <t>2025-05-03</t>
         </is>
       </c>
-      <c r="Z94" t="inlineStr">
-        <is>
-          <t>10:23</t>
-        </is>
-      </c>
       <c r="AA94" t="inlineStr">
         <is>
           <t>2025-05-03</t>
         </is>
       </c>
-      <c r="AB94" t="inlineStr">
-        <is>
-          <t>10:23</t>
+      <c r="AC94" t="inlineStr">
+        <is>
+          <t>Minst 30</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -10810,26 +10816,25 @@
       <c r="AE94" t="b">
         <v>0</v>
       </c>
-      <c r="AF94" t="inlineStr"/>
       <c r="AG94" t="b">
         <v>0</v>
       </c>
       <c r="AT94" t="inlineStr"/>
       <c r="AW94" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX94" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY94" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>124753630</v>
+        <v>124753622</v>
       </c>
       <c r="B95" t="n">
         <v>98101</v>
@@ -10869,10 +10874,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>452273</v>
+        <v>452472</v>
       </c>
       <c r="R95" t="n">
-        <v>6990906</v>
+        <v>6990821</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10909,7 +10914,7 @@
       </c>
       <c r="AC95" t="inlineStr">
         <is>
-          <t>Minst 10</t>
+          <t>Minst 50</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -10936,7 +10941,7 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>124753615</v>
+        <v>124753623</v>
       </c>
       <c r="B96" t="n">
         <v>98101</v>
@@ -10976,10 +10981,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>452734</v>
+        <v>452510</v>
       </c>
       <c r="R96" t="n">
-        <v>6990355</v>
+        <v>6990873</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -11016,7 +11021,7 @@
       </c>
       <c r="AC96" t="inlineStr">
         <is>
-          <t>Minst 30</t>
+          <t>Minst 50</t>
         </is>
       </c>
       <c r="AD96" t="b">
@@ -11043,10 +11048,10 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>124756756</v>
+        <v>124756727</v>
       </c>
       <c r="B97" t="n">
-        <v>78810</v>
+        <v>79920</v>
       </c>
       <c r="C97" t="inlineStr">
         <is>
@@ -11055,25 +11060,25 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E97" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
@@ -11083,10 +11088,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>452545</v>
+        <v>452745</v>
       </c>
       <c r="R97" t="n">
-        <v>6990691</v>
+        <v>6990359</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -11118,7 +11123,7 @@
       </c>
       <c r="Z97" t="inlineStr">
         <is>
-          <t>11:54</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AA97" t="inlineStr">
@@ -11128,7 +11133,7 @@
       </c>
       <c r="AB97" t="inlineStr">
         <is>
-          <t>11:54</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AD97" t="b">
@@ -11155,10 +11160,10 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>124753639</v>
+        <v>124753614</v>
       </c>
       <c r="B98" t="n">
-        <v>78810</v>
+        <v>98101</v>
       </c>
       <c r="C98" t="inlineStr">
         <is>
@@ -11167,25 +11172,25 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E98" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
@@ -11195,10 +11200,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>452511</v>
+        <v>452751</v>
       </c>
       <c r="R98" t="n">
-        <v>6990733</v>
+        <v>6990344</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -11231,6 +11236,11 @@
       <c r="AA98" t="inlineStr">
         <is>
           <t>2025-05-03</t>
+        </is>
+      </c>
+      <c r="AC98" t="inlineStr">
+        <is>
+          <t>Minst 200</t>
         </is>
       </c>
       <c r="AD98" t="b">
@@ -11257,10 +11267,10 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>124756740</v>
+        <v>124753612</v>
       </c>
       <c r="B99" t="n">
-        <v>91457</v>
+        <v>98101</v>
       </c>
       <c r="C99" t="inlineStr">
         <is>
@@ -11273,21 +11283,21 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>1209</v>
+        <v>220787</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
@@ -11297,10 +11307,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>452701</v>
+        <v>452924</v>
       </c>
       <c r="R99" t="n">
-        <v>6990475</v>
+        <v>6990397</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -11330,19 +11340,14 @@
           <t>2025-05-03</t>
         </is>
       </c>
-      <c r="Z99" t="inlineStr">
-        <is>
-          <t>13:58</t>
-        </is>
-      </c>
       <c r="AA99" t="inlineStr">
         <is>
           <t>2025-05-03</t>
         </is>
       </c>
-      <c r="AB99" t="inlineStr">
-        <is>
-          <t>13:58</t>
+      <c r="AC99" t="inlineStr">
+        <is>
+          <t>Minst 20</t>
         </is>
       </c>
       <c r="AD99" t="b">
@@ -11357,22 +11362,22 @@
       <c r="AT99" t="inlineStr"/>
       <c r="AW99" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX99" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY99" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>124753588</v>
+        <v>124756757</v>
       </c>
       <c r="B100" t="n">
-        <v>91012</v>
+        <v>77743</v>
       </c>
       <c r="C100" t="inlineStr">
         <is>
@@ -11385,21 +11390,21 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>1202</v>
+        <v>228579</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
@@ -11409,10 +11414,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>452311</v>
+        <v>452506</v>
       </c>
       <c r="R100" t="n">
-        <v>6990887</v>
+        <v>6990737</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -11442,9 +11447,19 @@
           <t>2025-05-03</t>
         </is>
       </c>
+      <c r="Z100" t="inlineStr">
+        <is>
+          <t>11:47</t>
+        </is>
+      </c>
       <c r="AA100" t="inlineStr">
         <is>
           <t>2025-05-03</t>
+        </is>
+      </c>
+      <c r="AB100" t="inlineStr">
+        <is>
+          <t>11:47</t>
         </is>
       </c>
       <c r="AD100" t="b">
@@ -11459,22 +11474,22 @@
       <c r="AT100" t="inlineStr"/>
       <c r="AW100" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX100" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY100" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>124756718</v>
+        <v>124756728</v>
       </c>
       <c r="B101" t="n">
-        <v>91030</v>
+        <v>79891</v>
       </c>
       <c r="C101" t="inlineStr">
         <is>
@@ -11487,21 +11502,21 @@
         </is>
       </c>
       <c r="E101" t="n">
-        <v>5432</v>
+        <v>6458</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
@@ -11511,10 +11526,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>452857</v>
+        <v>452745</v>
       </c>
       <c r="R101" t="n">
-        <v>6990267</v>
+        <v>6990359</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -11546,7 +11561,7 @@
       </c>
       <c r="Z101" t="inlineStr">
         <is>
-          <t>15:03</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AA101" t="inlineStr">
@@ -11556,7 +11571,7 @@
       </c>
       <c r="AB101" t="inlineStr">
         <is>
-          <t>15:03</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AD101" t="b">
@@ -11567,6 +11582,21 @@
       </c>
       <c r="AG101" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ101" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK101" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO101" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
       </c>
       <c r="AT101" t="inlineStr"/>
       <c r="AW101" t="inlineStr">
@@ -11583,10 +11613,10 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>124753605</v>
+        <v>124753587</v>
       </c>
       <c r="B102" t="n">
-        <v>79892</v>
+        <v>91012</v>
       </c>
       <c r="C102" t="inlineStr">
         <is>
@@ -11599,21 +11629,21 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>2081</v>
+        <v>1202</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
@@ -11623,10 +11653,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>452408</v>
+        <v>452331</v>
       </c>
       <c r="R102" t="n">
-        <v>6990952</v>
+        <v>6990929</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -11685,10 +11715,10 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>124753631</v>
+        <v>124753584</v>
       </c>
       <c r="B103" t="n">
-        <v>98101</v>
+        <v>91012</v>
       </c>
       <c r="C103" t="inlineStr">
         <is>
@@ -11697,25 +11727,25 @@
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E103" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
@@ -11725,10 +11755,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>452526</v>
+        <v>452444</v>
       </c>
       <c r="R103" t="n">
-        <v>6990943</v>
+        <v>6990774</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -11761,11 +11791,6 @@
       <c r="AA103" t="inlineStr">
         <is>
           <t>2025-05-03</t>
-        </is>
-      </c>
-      <c r="AC103" t="inlineStr">
-        <is>
-          <t>Minst 20</t>
         </is>
       </c>
       <c r="AD103" t="b">
@@ -11792,10 +11817,10 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>124756728</v>
+        <v>124756774</v>
       </c>
       <c r="B104" t="n">
-        <v>79891</v>
+        <v>98101</v>
       </c>
       <c r="C104" t="inlineStr">
         <is>
@@ -11804,38 +11829,50 @@
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E104" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I104" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I104" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J104" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K104" t="inlineStr"/>
+      <c r="L104" t="inlineStr"/>
+      <c r="N104" t="inlineStr"/>
       <c r="P104" t="inlineStr">
         <is>
           <t>Häggsåsen N, Jmt</t>
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>452745</v>
+        <v>452308</v>
       </c>
       <c r="R104" t="n">
-        <v>6990359</v>
+        <v>6990943</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -11867,7 +11904,7 @@
       </c>
       <c r="Z104" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>10:23</t>
         </is>
       </c>
       <c r="AA104" t="inlineStr">
@@ -11877,7 +11914,7 @@
       </c>
       <c r="AB104" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>10:23</t>
         </is>
       </c>
       <c r="AD104" t="b">
@@ -11886,23 +11923,9 @@
       <c r="AE104" t="b">
         <v>0</v>
       </c>
+      <c r="AF104" t="inlineStr"/>
       <c r="AG104" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ104" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK104" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AO104" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
       </c>
       <c r="AT104" t="inlineStr"/>
       <c r="AW104" t="inlineStr">
@@ -11919,10 +11942,10 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>124753610</v>
+        <v>124753620</v>
       </c>
       <c r="B105" t="n">
-        <v>79891</v>
+        <v>98101</v>
       </c>
       <c r="C105" t="inlineStr">
         <is>
@@ -11931,25 +11954,25 @@
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E105" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
@@ -11959,10 +11982,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>452435</v>
+        <v>452554</v>
       </c>
       <c r="R105" t="n">
-        <v>6990938</v>
+        <v>6990657</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -11995,6 +12018,11 @@
       <c r="AA105" t="inlineStr">
         <is>
           <t>2025-05-03</t>
+        </is>
+      </c>
+      <c r="AC105" t="inlineStr">
+        <is>
+          <t>Minst 30</t>
         </is>
       </c>
       <c r="AD105" t="b">
@@ -12021,10 +12049,10 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>124756779</v>
+        <v>124753630</v>
       </c>
       <c r="B106" t="n">
-        <v>78810</v>
+        <v>98101</v>
       </c>
       <c r="C106" t="inlineStr">
         <is>
@@ -12033,25 +12061,25 @@
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E106" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
@@ -12061,10 +12089,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>452143</v>
+        <v>452273</v>
       </c>
       <c r="R106" t="n">
-        <v>6990780</v>
+        <v>6990906</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -12094,19 +12122,14 @@
           <t>2025-05-03</t>
         </is>
       </c>
-      <c r="Z106" t="inlineStr">
-        <is>
-          <t>09:51</t>
-        </is>
-      </c>
       <c r="AA106" t="inlineStr">
         <is>
           <t>2025-05-03</t>
         </is>
       </c>
-      <c r="AB106" t="inlineStr">
-        <is>
-          <t>09:51</t>
+      <c r="AC106" t="inlineStr">
+        <is>
+          <t>Minst 10</t>
         </is>
       </c>
       <c r="AD106" t="b">
@@ -12121,22 +12144,22 @@
       <c r="AT106" t="inlineStr"/>
       <c r="AW106" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX106" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY106" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>124756761</v>
+        <v>124753576</v>
       </c>
       <c r="B107" t="n">
-        <v>78810</v>
+        <v>91012</v>
       </c>
       <c r="C107" t="inlineStr">
         <is>
@@ -12149,21 +12172,21 @@
         </is>
       </c>
       <c r="E107" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
@@ -12173,10 +12196,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>452532</v>
+        <v>452837</v>
       </c>
       <c r="R107" t="n">
-        <v>6990825</v>
+        <v>6990384</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -12206,19 +12229,9 @@
           <t>2025-05-03</t>
         </is>
       </c>
-      <c r="Z107" t="inlineStr">
-        <is>
-          <t>11:26</t>
-        </is>
-      </c>
       <c r="AA107" t="inlineStr">
         <is>
           <t>2025-05-03</t>
-        </is>
-      </c>
-      <c r="AB107" t="inlineStr">
-        <is>
-          <t>11:26</t>
         </is>
       </c>
       <c r="AD107" t="b">
@@ -12233,22 +12246,22 @@
       <c r="AT107" t="inlineStr"/>
       <c r="AW107" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX107" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY107" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>124756765</v>
+        <v>124753637</v>
       </c>
       <c r="B108" t="n">
-        <v>78810</v>
+        <v>91030</v>
       </c>
       <c r="C108" t="inlineStr">
         <is>
@@ -12261,21 +12274,21 @@
         </is>
       </c>
       <c r="E108" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
@@ -12285,10 +12298,10 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>452432</v>
+        <v>452696</v>
       </c>
       <c r="R108" t="n">
-        <v>6990942</v>
+        <v>6990466</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -12318,19 +12331,9 @@
           <t>2025-05-03</t>
         </is>
       </c>
-      <c r="Z108" t="inlineStr">
-        <is>
-          <t>11:05</t>
-        </is>
-      </c>
       <c r="AA108" t="inlineStr">
         <is>
           <t>2025-05-03</t>
-        </is>
-      </c>
-      <c r="AB108" t="inlineStr">
-        <is>
-          <t>11:05</t>
         </is>
       </c>
       <c r="AD108" t="b">
@@ -12345,22 +12348,22 @@
       <c r="AT108" t="inlineStr"/>
       <c r="AW108" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX108" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY108" t="inlineStr"/>
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>124756721</v>
+        <v>124756764</v>
       </c>
       <c r="B109" t="n">
-        <v>79891</v>
+        <v>78810</v>
       </c>
       <c r="C109" t="inlineStr">
         <is>
@@ -12373,21 +12376,21 @@
         </is>
       </c>
       <c r="E109" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
@@ -12397,10 +12400,10 @@
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>452823</v>
+        <v>452462</v>
       </c>
       <c r="R109" t="n">
-        <v>6990261</v>
+        <v>6990915</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -12432,7 +12435,7 @@
       </c>
       <c r="Z109" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>11:11</t>
         </is>
       </c>
       <c r="AA109" t="inlineStr">
@@ -12442,7 +12445,7 @@
       </c>
       <c r="AB109" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>11:11</t>
         </is>
       </c>
       <c r="AD109" t="b">
@@ -12453,21 +12456,6 @@
       </c>
       <c r="AG109" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ109" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK109" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AO109" t="inlineStr">
-        <is>
-          <t>Omkullfallen grov stam # Salix caprea</t>
-        </is>
       </c>
       <c r="AT109" t="inlineStr"/>
       <c r="AW109" t="inlineStr">
@@ -12484,10 +12472,10 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>124756725</v>
+        <v>124756738</v>
       </c>
       <c r="B110" t="n">
-        <v>78810</v>
+        <v>74899</v>
       </c>
       <c r="C110" t="inlineStr">
         <is>
@@ -12496,38 +12484,41 @@
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E110" t="n">
-        <v>6425</v>
+        <v>6486</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skuggnål</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca sphaerocephala</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Nádv.</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
+      <c r="J110" t="inlineStr"/>
+      <c r="K110" t="inlineStr"/>
+      <c r="N110" t="inlineStr"/>
       <c r="P110" t="inlineStr">
         <is>
           <t>Häggsåsen N, Jmt</t>
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>452762</v>
+        <v>452703</v>
       </c>
       <c r="R110" t="n">
-        <v>6990327</v>
+        <v>6990457</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -12559,7 +12550,7 @@
       </c>
       <c r="Z110" t="inlineStr">
         <is>
-          <t>14:37</t>
+          <t>14:09</t>
         </is>
       </c>
       <c r="AA110" t="inlineStr">
@@ -12569,7 +12560,7 @@
       </c>
       <c r="AB110" t="inlineStr">
         <is>
-          <t>14:37</t>
+          <t>14:09</t>
         </is>
       </c>
       <c r="AD110" t="b">
@@ -12577,6 +12568,11 @@
       </c>
       <c r="AE110" t="b">
         <v>0</v>
+      </c>
+      <c r="AF110" t="inlineStr">
+        <is>
+          <t>mikroskoperad</t>
+        </is>
       </c>
       <c r="AG110" t="b">
         <v>0</v>
@@ -12596,10 +12592,10 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>124753583</v>
+        <v>124756740</v>
       </c>
       <c r="B111" t="n">
-        <v>91012</v>
+        <v>91457</v>
       </c>
       <c r="C111" t="inlineStr">
         <is>
@@ -12608,25 +12604,25 @@
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E111" t="n">
-        <v>1202</v>
+        <v>1209</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
@@ -12636,10 +12632,10 @@
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>452606</v>
+        <v>452701</v>
       </c>
       <c r="R111" t="n">
-        <v>6990623</v>
+        <v>6990475</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -12669,9 +12665,19 @@
           <t>2025-05-03</t>
         </is>
       </c>
+      <c r="Z111" t="inlineStr">
+        <is>
+          <t>13:58</t>
+        </is>
+      </c>
       <c r="AA111" t="inlineStr">
         <is>
           <t>2025-05-03</t>
+        </is>
+      </c>
+      <c r="AB111" t="inlineStr">
+        <is>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AD111" t="b">
@@ -12686,19 +12692,19 @@
       <c r="AT111" t="inlineStr"/>
       <c r="AW111" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX111" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY111" t="inlineStr"/>
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>124753637</v>
+        <v>124756718</v>
       </c>
       <c r="B112" t="n">
         <v>91030</v>
@@ -12738,10 +12744,10 @@
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>452696</v>
+        <v>452857</v>
       </c>
       <c r="R112" t="n">
-        <v>6990466</v>
+        <v>6990267</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -12771,9 +12777,19 @@
           <t>2025-05-03</t>
         </is>
       </c>
+      <c r="Z112" t="inlineStr">
+        <is>
+          <t>15:03</t>
+        </is>
+      </c>
       <c r="AA112" t="inlineStr">
         <is>
           <t>2025-05-03</t>
+        </is>
+      </c>
+      <c r="AB112" t="inlineStr">
+        <is>
+          <t>15:03</t>
         </is>
       </c>
       <c r="AD112" t="b">
@@ -12788,22 +12804,22 @@
       <c r="AT112" t="inlineStr"/>
       <c r="AW112" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX112" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY112" t="inlineStr"/>
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>124756719</v>
+        <v>124756752</v>
       </c>
       <c r="B113" t="n">
-        <v>79927</v>
+        <v>98101</v>
       </c>
       <c r="C113" t="inlineStr">
         <is>
@@ -12812,38 +12828,50 @@
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E113" t="n">
-        <v>6464</v>
+        <v>220787</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
-        </is>
-      </c>
-      <c r="I113" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I113" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J113" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K113" t="inlineStr"/>
+      <c r="L113" t="inlineStr"/>
+      <c r="N113" t="inlineStr"/>
       <c r="P113" t="inlineStr">
         <is>
           <t>Häggsåsen N, Jmt</t>
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>452823</v>
+        <v>452608</v>
       </c>
       <c r="R113" t="n">
-        <v>6990261</v>
+        <v>6990625</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -12875,7 +12903,7 @@
       </c>
       <c r="Z113" t="inlineStr">
         <is>
-          <t>14:59</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AA113" t="inlineStr">
@@ -12885,7 +12913,7 @@
       </c>
       <c r="AB113" t="inlineStr">
         <is>
-          <t>14:59</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AD113" t="b">
@@ -12894,6 +12922,7 @@
       <c r="AE113" t="b">
         <v>0</v>
       </c>
+      <c r="AF113" t="inlineStr"/>
       <c r="AG113" t="b">
         <v>0</v>
       </c>
@@ -12912,10 +12941,10 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>124753638</v>
+        <v>124753616</v>
       </c>
       <c r="B114" t="n">
-        <v>78810</v>
+        <v>98101</v>
       </c>
       <c r="C114" t="inlineStr">
         <is>
@@ -12924,25 +12953,25 @@
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E114" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
@@ -12952,10 +12981,10 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>452823</v>
+        <v>452742</v>
       </c>
       <c r="R114" t="n">
-        <v>6990367</v>
+        <v>6990393</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -12988,6 +13017,11 @@
       <c r="AA114" t="inlineStr">
         <is>
           <t>2025-05-03</t>
+        </is>
+      </c>
+      <c r="AC114" t="inlineStr">
+        <is>
+          <t>Minst 60</t>
         </is>
       </c>
       <c r="AD114" t="b">
@@ -13014,10 +13048,10 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>124756724</v>
+        <v>124756739</v>
       </c>
       <c r="B115" t="n">
-        <v>91012</v>
+        <v>98101</v>
       </c>
       <c r="C115" t="inlineStr">
         <is>
@@ -13026,38 +13060,50 @@
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E115" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I115" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I115" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="J115" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K115" t="inlineStr"/>
+      <c r="L115" t="inlineStr"/>
+      <c r="N115" t="inlineStr"/>
       <c r="P115" t="inlineStr">
         <is>
           <t>Häggsåsen N, Jmt</t>
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>452793</v>
+        <v>452711</v>
       </c>
       <c r="R115" t="n">
-        <v>6990262</v>
+        <v>6990473</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -13089,7 +13135,7 @@
       </c>
       <c r="Z115" t="inlineStr">
         <is>
-          <t>14:44</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AA115" t="inlineStr">
@@ -13099,7 +13145,7 @@
       </c>
       <c r="AB115" t="inlineStr">
         <is>
-          <t>14:44</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AD115" t="b">
@@ -13108,6 +13154,7 @@
       <c r="AE115" t="b">
         <v>0</v>
       </c>
+      <c r="AF115" t="inlineStr"/>
       <c r="AG115" t="b">
         <v>0</v>
       </c>
@@ -13126,7 +13173,7 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>124753577</v>
+        <v>124756749</v>
       </c>
       <c r="B116" t="n">
         <v>91012</v>
@@ -13166,10 +13213,10 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>452833</v>
+        <v>452609</v>
       </c>
       <c r="R116" t="n">
-        <v>6990388</v>
+        <v>6990543</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -13199,9 +13246,19 @@
           <t>2025-05-03</t>
         </is>
       </c>
+      <c r="Z116" t="inlineStr">
+        <is>
+          <t>12:29</t>
+        </is>
+      </c>
       <c r="AA116" t="inlineStr">
         <is>
           <t>2025-05-03</t>
+        </is>
+      </c>
+      <c r="AB116" t="inlineStr">
+        <is>
+          <t>12:29</t>
         </is>
       </c>
       <c r="AD116" t="b">
@@ -13216,22 +13273,22 @@
       <c r="AT116" t="inlineStr"/>
       <c r="AW116" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX116" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY116" t="inlineStr"/>
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>124756736</v>
+        <v>124753583</v>
       </c>
       <c r="B117" t="n">
-        <v>98101</v>
+        <v>91012</v>
       </c>
       <c r="C117" t="inlineStr">
         <is>
@@ -13240,50 +13297,38 @@
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E117" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I117" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J117" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K117" t="inlineStr"/>
-      <c r="L117" t="inlineStr"/>
-      <c r="N117" t="inlineStr"/>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I117" t="inlineStr"/>
       <c r="P117" t="inlineStr">
         <is>
           <t>Häggsåsen N, Jmt</t>
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>452691</v>
+        <v>452606</v>
       </c>
       <c r="R117" t="n">
-        <v>6990422</v>
+        <v>6990623</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>
@@ -13313,50 +13358,39 @@
           <t>2025-05-03</t>
         </is>
       </c>
-      <c r="Z117" t="inlineStr">
-        <is>
-          <t>14:13</t>
-        </is>
-      </c>
       <c r="AA117" t="inlineStr">
         <is>
           <t>2025-05-03</t>
         </is>
       </c>
-      <c r="AB117" t="inlineStr">
-        <is>
-          <t>14:13</t>
-        </is>
-      </c>
       <c r="AD117" t="b">
         <v>0</v>
       </c>
       <c r="AE117" t="b">
         <v>0</v>
       </c>
-      <c r="AF117" t="inlineStr"/>
       <c r="AG117" t="b">
         <v>0</v>
       </c>
       <c r="AT117" t="inlineStr"/>
       <c r="AW117" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX117" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY117" t="inlineStr"/>
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>124753616</v>
+        <v>124753577</v>
       </c>
       <c r="B118" t="n">
-        <v>98101</v>
+        <v>91012</v>
       </c>
       <c r="C118" t="inlineStr">
         <is>
@@ -13365,25 +13399,25 @@
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E118" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
@@ -13393,10 +13427,10 @@
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>452742</v>
+        <v>452833</v>
       </c>
       <c r="R118" t="n">
-        <v>6990393</v>
+        <v>6990388</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -13429,11 +13463,6 @@
       <c r="AA118" t="inlineStr">
         <is>
           <t>2025-05-03</t>
-        </is>
-      </c>
-      <c r="AC118" t="inlineStr">
-        <is>
-          <t>Minst 60</t>
         </is>
       </c>
       <c r="AD118" t="b">
@@ -13460,10 +13489,10 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>124753633</v>
+        <v>124756761</v>
       </c>
       <c r="B119" t="n">
-        <v>91008</v>
+        <v>78810</v>
       </c>
       <c r="C119" t="inlineStr">
         <is>
@@ -13476,21 +13505,21 @@
         </is>
       </c>
       <c r="E119" t="n">
-        <v>1108</v>
+        <v>6425</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I119" t="inlineStr"/>
@@ -13500,10 +13529,10 @@
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>452772</v>
+        <v>452532</v>
       </c>
       <c r="R119" t="n">
-        <v>6990321</v>
+        <v>6990825</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -13533,9 +13562,19 @@
           <t>2025-05-03</t>
         </is>
       </c>
+      <c r="Z119" t="inlineStr">
+        <is>
+          <t>11:26</t>
+        </is>
+      </c>
       <c r="AA119" t="inlineStr">
         <is>
           <t>2025-05-03</t>
+        </is>
+      </c>
+      <c r="AB119" t="inlineStr">
+        <is>
+          <t>11:26</t>
         </is>
       </c>
       <c r="AD119" t="b">
@@ -13550,22 +13589,22 @@
       <c r="AT119" t="inlineStr"/>
       <c r="AW119" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX119" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY119" t="inlineStr"/>
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>124753635</v>
+        <v>124756762</v>
       </c>
       <c r="B120" t="n">
-        <v>91030</v>
+        <v>78810</v>
       </c>
       <c r="C120" t="inlineStr">
         <is>
@@ -13578,21 +13617,21 @@
         </is>
       </c>
       <c r="E120" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
@@ -13602,10 +13641,10 @@
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>452732</v>
+        <v>452508</v>
       </c>
       <c r="R120" t="n">
-        <v>6990486</v>
+        <v>6990903</v>
       </c>
       <c r="S120" t="n">
         <v>10</v>
@@ -13635,9 +13674,19 @@
           <t>2025-05-03</t>
         </is>
       </c>
+      <c r="Z120" t="inlineStr">
+        <is>
+          <t>11:20</t>
+        </is>
+      </c>
       <c r="AA120" t="inlineStr">
         <is>
           <t>2025-05-03</t>
+        </is>
+      </c>
+      <c r="AB120" t="inlineStr">
+        <is>
+          <t>11:20</t>
         </is>
       </c>
       <c r="AD120" t="b">
@@ -13652,22 +13701,22 @@
       <c r="AT120" t="inlineStr"/>
       <c r="AW120" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX120" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY120" t="inlineStr"/>
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>124756763</v>
+        <v>124756767</v>
       </c>
       <c r="B121" t="n">
-        <v>98101</v>
+        <v>78810</v>
       </c>
       <c r="C121" t="inlineStr">
         <is>
@@ -13676,50 +13725,38 @@
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E121" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I121" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J121" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K121" t="inlineStr"/>
-      <c r="L121" t="inlineStr"/>
-      <c r="N121" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I121" t="inlineStr"/>
       <c r="P121" t="inlineStr">
         <is>
           <t>Häggsåsen N, Jmt</t>
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>452478</v>
+        <v>452362</v>
       </c>
       <c r="R121" t="n">
-        <v>6990887</v>
+        <v>6991003</v>
       </c>
       <c r="S121" t="n">
         <v>10</v>
@@ -13751,7 +13788,7 @@
       </c>
       <c r="Z121" t="inlineStr">
         <is>
-          <t>11:18</t>
+          <t>10:55</t>
         </is>
       </c>
       <c r="AA121" t="inlineStr">
@@ -13761,7 +13798,7 @@
       </c>
       <c r="AB121" t="inlineStr">
         <is>
-          <t>11:18</t>
+          <t>10:55</t>
         </is>
       </c>
       <c r="AD121" t="b">
@@ -13770,7 +13807,6 @@
       <c r="AE121" t="b">
         <v>0</v>
       </c>
-      <c r="AF121" t="inlineStr"/>
       <c r="AG121" t="b">
         <v>0</v>
       </c>
@@ -13789,7 +13825,7 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>124753620</v>
+        <v>124753611</v>
       </c>
       <c r="B122" t="n">
         <v>98101</v>
@@ -13829,10 +13865,10 @@
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>452554</v>
+        <v>452997</v>
       </c>
       <c r="R122" t="n">
-        <v>6990657</v>
+        <v>6990332</v>
       </c>
       <c r="S122" t="n">
         <v>10</v>
@@ -13869,7 +13905,7 @@
       </c>
       <c r="AC122" t="inlineStr">
         <is>
-          <t>Minst 30</t>
+          <t>Minst 100</t>
         </is>
       </c>
       <c r="AD122" t="b">
@@ -13896,7 +13932,7 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>124756777</v>
+        <v>124756736</v>
       </c>
       <c r="B123" t="n">
         <v>98101</v>
@@ -13931,7 +13967,7 @@
       </c>
       <c r="I123" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J123" t="inlineStr">
@@ -13948,10 +13984,10 @@
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>452146</v>
+        <v>452691</v>
       </c>
       <c r="R123" t="n">
-        <v>6990839</v>
+        <v>6990422</v>
       </c>
       <c r="S123" t="n">
         <v>10</v>
@@ -13983,7 +14019,7 @@
       </c>
       <c r="Z123" t="inlineStr">
         <is>
-          <t>10:06</t>
+          <t>14:13</t>
         </is>
       </c>
       <c r="AA123" t="inlineStr">
@@ -13993,7 +14029,7 @@
       </c>
       <c r="AB123" t="inlineStr">
         <is>
-          <t>10:06</t>
+          <t>14:13</t>
         </is>
       </c>
       <c r="AD123" t="b">
@@ -14021,7 +14057,7 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>124753613</v>
+        <v>124753624</v>
       </c>
       <c r="B124" t="n">
         <v>98101</v>
@@ -14061,10 +14097,10 @@
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>452777</v>
+        <v>452528</v>
       </c>
       <c r="R124" t="n">
-        <v>6990299</v>
+        <v>6990882</v>
       </c>
       <c r="S124" t="n">
         <v>10</v>
@@ -14101,7 +14137,7 @@
       </c>
       <c r="AC124" t="inlineStr">
         <is>
-          <t>Minst 100</t>
+          <t>Minst 30</t>
         </is>
       </c>
       <c r="AD124" t="b">
@@ -14128,10 +14164,10 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>124753617</v>
+        <v>124756724</v>
       </c>
       <c r="B125" t="n">
-        <v>98101</v>
+        <v>91012</v>
       </c>
       <c r="C125" t="inlineStr">
         <is>
@@ -14140,25 +14176,25 @@
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E125" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I125" t="inlineStr"/>
@@ -14168,10 +14204,10 @@
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>452655</v>
+        <v>452793</v>
       </c>
       <c r="R125" t="n">
-        <v>6990482</v>
+        <v>6990262</v>
       </c>
       <c r="S125" t="n">
         <v>10</v>
@@ -14201,14 +14237,19 @@
           <t>2025-05-03</t>
         </is>
       </c>
+      <c r="Z125" t="inlineStr">
+        <is>
+          <t>14:44</t>
+        </is>
+      </c>
       <c r="AA125" t="inlineStr">
         <is>
           <t>2025-05-03</t>
         </is>
       </c>
-      <c r="AC125" t="inlineStr">
-        <is>
-          <t>Minst 50</t>
+      <c r="AB125" t="inlineStr">
+        <is>
+          <t>14:44</t>
         </is>
       </c>
       <c r="AD125" t="b">
@@ -14223,22 +14264,22 @@
       <c r="AT125" t="inlineStr"/>
       <c r="AW125" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX125" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY125" t="inlineStr"/>
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>124756768</v>
+        <v>124756748</v>
       </c>
       <c r="B126" t="n">
-        <v>77743</v>
+        <v>78810</v>
       </c>
       <c r="C126" t="inlineStr">
         <is>
@@ -14251,21 +14292,21 @@
         </is>
       </c>
       <c r="E126" t="n">
-        <v>228579</v>
+        <v>6425</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I126" t="inlineStr"/>
@@ -14275,10 +14316,10 @@
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>452357</v>
+        <v>452609</v>
       </c>
       <c r="R126" t="n">
-        <v>6990970</v>
+        <v>6990543</v>
       </c>
       <c r="S126" t="n">
         <v>10</v>
@@ -14310,7 +14351,7 @@
       </c>
       <c r="Z126" t="inlineStr">
         <is>
-          <t>10:52</t>
+          <t>12:29</t>
         </is>
       </c>
       <c r="AA126" t="inlineStr">
@@ -14320,7 +14361,7 @@
       </c>
       <c r="AB126" t="inlineStr">
         <is>
-          <t>10:52</t>
+          <t>12:29</t>
         </is>
       </c>
       <c r="AD126" t="b">
@@ -14347,10 +14388,10 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>124753586</v>
+        <v>124756775</v>
       </c>
       <c r="B127" t="n">
-        <v>91012</v>
+        <v>79891</v>
       </c>
       <c r="C127" t="inlineStr">
         <is>
@@ -14363,21 +14404,21 @@
         </is>
       </c>
       <c r="E127" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I127" t="inlineStr"/>
@@ -14387,10 +14428,10 @@
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>452500</v>
+        <v>452308</v>
       </c>
       <c r="R127" t="n">
-        <v>6990950</v>
+        <v>6990943</v>
       </c>
       <c r="S127" t="n">
         <v>10</v>
@@ -14420,9 +14461,19 @@
           <t>2025-05-03</t>
         </is>
       </c>
+      <c r="Z127" t="inlineStr">
+        <is>
+          <t>10:22</t>
+        </is>
+      </c>
       <c r="AA127" t="inlineStr">
         <is>
           <t>2025-05-03</t>
+        </is>
+      </c>
+      <c r="AB127" t="inlineStr">
+        <is>
+          <t>10:22</t>
         </is>
       </c>
       <c r="AD127" t="b">
@@ -14437,22 +14488,22 @@
       <c r="AT127" t="inlineStr"/>
       <c r="AW127" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX127" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY127" t="inlineStr"/>
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>124756755</v>
+        <v>124753609</v>
       </c>
       <c r="B128" t="n">
-        <v>91299</v>
+        <v>79891</v>
       </c>
       <c r="C128" t="inlineStr">
         <is>
@@ -14465,21 +14516,21 @@
         </is>
       </c>
       <c r="E128" t="n">
-        <v>658</v>
+        <v>6458</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I128" t="inlineStr"/>
@@ -14489,10 +14540,10 @@
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>452538</v>
+        <v>452528</v>
       </c>
       <c r="R128" t="n">
-        <v>6990659</v>
+        <v>6990710</v>
       </c>
       <c r="S128" t="n">
         <v>10</v>
@@ -14522,19 +14573,9 @@
           <t>2025-05-03</t>
         </is>
       </c>
-      <c r="Z128" t="inlineStr">
-        <is>
-          <t>11:58</t>
-        </is>
-      </c>
       <c r="AA128" t="inlineStr">
         <is>
           <t>2025-05-03</t>
-        </is>
-      </c>
-      <c r="AB128" t="inlineStr">
-        <is>
-          <t>11:58</t>
         </is>
       </c>
       <c r="AD128" t="b">
@@ -14549,22 +14590,22 @@
       <c r="AT128" t="inlineStr"/>
       <c r="AW128" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX128" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY128" t="inlineStr"/>
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>124756758</v>
+        <v>124753613</v>
       </c>
       <c r="B129" t="n">
-        <v>90962</v>
+        <v>98101</v>
       </c>
       <c r="C129" t="inlineStr">
         <is>
@@ -14573,25 +14614,25 @@
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E129" t="n">
-        <v>112</v>
+        <v>220787</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Stjärntagging</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Asterodon ferruginosus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>Pat.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I129" t="inlineStr"/>
@@ -14601,10 +14642,10 @@
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>452509</v>
+        <v>452777</v>
       </c>
       <c r="R129" t="n">
-        <v>6990778</v>
+        <v>6990299</v>
       </c>
       <c r="S129" t="n">
         <v>10</v>
@@ -14634,19 +14675,14 @@
           <t>2025-05-03</t>
         </is>
       </c>
-      <c r="Z129" t="inlineStr">
-        <is>
-          <t>11:40</t>
-        </is>
-      </c>
       <c r="AA129" t="inlineStr">
         <is>
           <t>2025-05-03</t>
         </is>
       </c>
-      <c r="AB129" t="inlineStr">
-        <is>
-          <t>11:40</t>
+      <c r="AC129" t="inlineStr">
+        <is>
+          <t>Minst 100</t>
         </is>
       </c>
       <c r="AD129" t="b">
@@ -14661,22 +14697,22 @@
       <c r="AT129" t="inlineStr"/>
       <c r="AW129" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX129" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY129" t="inlineStr"/>
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>124753608</v>
+        <v>124756731</v>
       </c>
       <c r="B130" t="n">
-        <v>79891</v>
+        <v>91012</v>
       </c>
       <c r="C130" t="inlineStr">
         <is>
@@ -14689,21 +14725,21 @@
         </is>
       </c>
       <c r="E130" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I130" t="inlineStr"/>
@@ -14713,10 +14749,10 @@
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>452731</v>
+        <v>452672</v>
       </c>
       <c r="R130" t="n">
-        <v>6990377</v>
+        <v>6990427</v>
       </c>
       <c r="S130" t="n">
         <v>10</v>
@@ -14746,9 +14782,19 @@
           <t>2025-05-03</t>
         </is>
       </c>
+      <c r="Z130" t="inlineStr">
+        <is>
+          <t>14:19</t>
+        </is>
+      </c>
       <c r="AA130" t="inlineStr">
         <is>
           <t>2025-05-03</t>
+        </is>
+      </c>
+      <c r="AB130" t="inlineStr">
+        <is>
+          <t>14:19</t>
         </is>
       </c>
       <c r="AD130" t="b">
@@ -14763,22 +14809,22 @@
       <c r="AT130" t="inlineStr"/>
       <c r="AW130" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX130" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY130" t="inlineStr"/>
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>124756738</v>
+        <v>124756753</v>
       </c>
       <c r="B131" t="n">
-        <v>74899</v>
+        <v>91012</v>
       </c>
       <c r="C131" t="inlineStr">
         <is>
@@ -14787,41 +14833,38 @@
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E131" t="n">
-        <v>6486</v>
+        <v>1202</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Skuggnål</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Chaenotheca sphaerocephala</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>Nádv.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I131" t="inlineStr"/>
-      <c r="J131" t="inlineStr"/>
-      <c r="K131" t="inlineStr"/>
-      <c r="N131" t="inlineStr"/>
       <c r="P131" t="inlineStr">
         <is>
           <t>Häggsåsen N, Jmt</t>
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>452703</v>
+        <v>452608</v>
       </c>
       <c r="R131" t="n">
-        <v>6990457</v>
+        <v>6990625</v>
       </c>
       <c r="S131" t="n">
         <v>10</v>
@@ -14853,7 +14896,7 @@
       </c>
       <c r="Z131" t="inlineStr">
         <is>
-          <t>14:09</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AA131" t="inlineStr">
@@ -14863,7 +14906,7 @@
       </c>
       <c r="AB131" t="inlineStr">
         <is>
-          <t>14:09</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AD131" t="b">
@@ -14871,11 +14914,6 @@
       </c>
       <c r="AE131" t="b">
         <v>0</v>
-      </c>
-      <c r="AF131" t="inlineStr">
-        <is>
-          <t>mikroskoperad</t>
-        </is>
       </c>
       <c r="AG131" t="b">
         <v>0</v>
@@ -14895,10 +14933,10 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>124756762</v>
+        <v>124753592</v>
       </c>
       <c r="B132" t="n">
-        <v>78810</v>
+        <v>57513</v>
       </c>
       <c r="C132" t="inlineStr">
         <is>
@@ -14911,21 +14949,21 @@
         </is>
       </c>
       <c r="E132" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I132" t="inlineStr"/>
@@ -14935,10 +14973,10 @@
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>452508</v>
+        <v>452396</v>
       </c>
       <c r="R132" t="n">
-        <v>6990903</v>
+        <v>6990703</v>
       </c>
       <c r="S132" t="n">
         <v>10</v>
@@ -14968,19 +15006,14 @@
           <t>2025-05-03</t>
         </is>
       </c>
-      <c r="Z132" t="inlineStr">
-        <is>
-          <t>11:20</t>
-        </is>
-      </c>
       <c r="AA132" t="inlineStr">
         <is>
           <t>2025-05-03</t>
         </is>
       </c>
-      <c r="AB132" t="inlineStr">
-        <is>
-          <t>11:20</t>
+      <c r="AC132" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD132" t="b">
@@ -14995,22 +15028,22 @@
       <c r="AT132" t="inlineStr"/>
       <c r="AW132" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX132" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY132" t="inlineStr"/>
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>124756752</v>
+        <v>124753581</v>
       </c>
       <c r="B133" t="n">
-        <v>98101</v>
+        <v>91012</v>
       </c>
       <c r="C133" t="inlineStr">
         <is>
@@ -15019,50 +15052,38 @@
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E133" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I133" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J133" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K133" t="inlineStr"/>
-      <c r="L133" t="inlineStr"/>
-      <c r="N133" t="inlineStr"/>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I133" t="inlineStr"/>
       <c r="P133" t="inlineStr">
         <is>
           <t>Häggsåsen N, Jmt</t>
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>452608</v>
+        <v>452643</v>
       </c>
       <c r="R133" t="n">
-        <v>6990625</v>
+        <v>6990504</v>
       </c>
       <c r="S133" t="n">
         <v>10</v>
@@ -15092,50 +15113,39 @@
           <t>2025-05-03</t>
         </is>
       </c>
-      <c r="Z133" t="inlineStr">
-        <is>
-          <t>12:07</t>
-        </is>
-      </c>
       <c r="AA133" t="inlineStr">
         <is>
           <t>2025-05-03</t>
         </is>
       </c>
-      <c r="AB133" t="inlineStr">
-        <is>
-          <t>12:07</t>
-        </is>
-      </c>
       <c r="AD133" t="b">
         <v>0</v>
       </c>
       <c r="AE133" t="b">
         <v>0</v>
       </c>
-      <c r="AF133" t="inlineStr"/>
       <c r="AG133" t="b">
         <v>0</v>
       </c>
       <c r="AT133" t="inlineStr"/>
       <c r="AW133" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX133" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY133" t="inlineStr"/>
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>124756775</v>
+        <v>124753582</v>
       </c>
       <c r="B134" t="n">
-        <v>79891</v>
+        <v>91012</v>
       </c>
       <c r="C134" t="inlineStr">
         <is>
@@ -15148,21 +15158,21 @@
         </is>
       </c>
       <c r="E134" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I134" t="inlineStr"/>
@@ -15172,10 +15182,10 @@
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>452308</v>
+        <v>452649</v>
       </c>
       <c r="R134" t="n">
-        <v>6990943</v>
+        <v>6990621</v>
       </c>
       <c r="S134" t="n">
         <v>10</v>
@@ -15205,19 +15215,9 @@
           <t>2025-05-03</t>
         </is>
       </c>
-      <c r="Z134" t="inlineStr">
-        <is>
-          <t>10:22</t>
-        </is>
-      </c>
       <c r="AA134" t="inlineStr">
         <is>
           <t>2025-05-03</t>
-        </is>
-      </c>
-      <c r="AB134" t="inlineStr">
-        <is>
-          <t>10:22</t>
         </is>
       </c>
       <c r="AD134" t="b">
@@ -15232,22 +15232,22 @@
       <c r="AT134" t="inlineStr"/>
       <c r="AW134" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX134" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY134" t="inlineStr"/>
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>124756749</v>
+        <v>124756768</v>
       </c>
       <c r="B135" t="n">
-        <v>91012</v>
+        <v>77743</v>
       </c>
       <c r="C135" t="inlineStr">
         <is>
@@ -15260,21 +15260,21 @@
         </is>
       </c>
       <c r="E135" t="n">
-        <v>1202</v>
+        <v>228579</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I135" t="inlineStr"/>
@@ -15284,10 +15284,10 @@
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>452609</v>
+        <v>452357</v>
       </c>
       <c r="R135" t="n">
-        <v>6990543</v>
+        <v>6990970</v>
       </c>
       <c r="S135" t="n">
         <v>10</v>
@@ -15319,7 +15319,7 @@
       </c>
       <c r="Z135" t="inlineStr">
         <is>
-          <t>12:29</t>
+          <t>10:52</t>
         </is>
       </c>
       <c r="AA135" t="inlineStr">
@@ -15329,7 +15329,7 @@
       </c>
       <c r="AB135" t="inlineStr">
         <is>
-          <t>12:29</t>
+          <t>10:52</t>
         </is>
       </c>
       <c r="AD135" t="b">
@@ -15356,10 +15356,10 @@
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>124756759</v>
+        <v>124756756</v>
       </c>
       <c r="B136" t="n">
-        <v>91012</v>
+        <v>78810</v>
       </c>
       <c r="C136" t="inlineStr">
         <is>
@@ -15372,21 +15372,21 @@
         </is>
       </c>
       <c r="E136" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I136" t="inlineStr"/>
@@ -15396,10 +15396,10 @@
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>452509</v>
+        <v>452545</v>
       </c>
       <c r="R136" t="n">
-        <v>6990778</v>
+        <v>6990691</v>
       </c>
       <c r="S136" t="n">
         <v>10</v>
@@ -15431,7 +15431,7 @@
       </c>
       <c r="Z136" t="inlineStr">
         <is>
-          <t>11:39</t>
+          <t>11:54</t>
         </is>
       </c>
       <c r="AA136" t="inlineStr">
@@ -15441,7 +15441,7 @@
       </c>
       <c r="AB136" t="inlineStr">
         <is>
-          <t>11:39</t>
+          <t>11:54</t>
         </is>
       </c>
       <c r="AD136" t="b">

--- a/artfynd/A 16493-2025 artfynd.xlsx
+++ b/artfynd/A 16493-2025 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124694574</v>
+        <v>124689504</v>
       </c>
       <c r="B2" t="n">
         <v>57513</v>
@@ -711,7 +711,7 @@
       <c r="I2" t="inlineStr"/>
       <c r="M2" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -720,10 +720,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>452630</v>
+        <v>452322</v>
       </c>
       <c r="R2" t="n">
-        <v>6990651</v>
+        <v>6990950</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -760,7 +760,7 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Färska ringhack på tall</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124706864</v>
+        <v>124705584</v>
       </c>
       <c r="B3" t="n">
-        <v>57513</v>
+        <v>91030</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -803,39 +803,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Häggsåsen, Häggsåsen, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>453007</v>
+        <v>452865</v>
       </c>
       <c r="R3" t="n">
-        <v>6990356</v>
+        <v>6990382</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -868,11 +863,6 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-05-02</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -899,10 +889,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124706950</v>
+        <v>124721401</v>
       </c>
       <c r="B4" t="n">
-        <v>98101</v>
+        <v>57513</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -911,42 +901,43 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>21</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Häggsåsen, Häggsåsen, Jmt</t>
+          <t>Tjärnflon, Tjärnflon, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>453007</v>
+        <v>452415</v>
       </c>
       <c r="R4" t="n">
-        <v>6990356</v>
+        <v>6990714</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -979,6 +970,11 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-05-02</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1005,10 +1001,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124702902</v>
+        <v>124695367</v>
       </c>
       <c r="B5" t="n">
-        <v>79891</v>
+        <v>82597</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1021,34 +1017,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6458</v>
+        <v>1312</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Häggsåsen, Häggsåsen, Jmt</t>
+          <t>Tjärnflon, Tjärnflon, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>452734</v>
+        <v>452617</v>
       </c>
       <c r="R5" t="n">
-        <v>6990348</v>
+        <v>6990540</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1219,10 +1215,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124691533</v>
+        <v>124694574</v>
       </c>
       <c r="B7" t="n">
-        <v>79891</v>
+        <v>57513</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1235,34 +1231,39 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Tjärnflon, Tjärnflon, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>452427</v>
+        <v>452630</v>
       </c>
       <c r="R7" t="n">
-        <v>6990925</v>
+        <v>6990651</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1295,6 +1296,11 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-05-02</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1321,10 +1327,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124695256</v>
+        <v>124691533</v>
       </c>
       <c r="B8" t="n">
-        <v>98101</v>
+        <v>79891</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1333,42 +1339,38 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Tjärnflon, Tjärnflon, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>452624</v>
+        <v>452427</v>
       </c>
       <c r="R8" t="n">
-        <v>6990535</v>
+        <v>6990925</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1427,7 +1429,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124689335</v>
+        <v>124704478</v>
       </c>
       <c r="B9" t="n">
         <v>57513</v>
@@ -1463,19 +1465,19 @@
       <c r="I9" t="inlineStr"/>
       <c r="M9" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Tjärnflon, Tjärnflon, Jmt</t>
+          <t>Häggsåsen, Häggsåsen, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>452249</v>
+        <v>452836</v>
       </c>
       <c r="R9" t="n">
-        <v>6990921</v>
+        <v>6990321</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1539,7 +1541,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124703242</v>
+        <v>124704581</v>
       </c>
       <c r="B10" t="n">
         <v>91299</v>
@@ -1579,10 +1581,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>452760</v>
+        <v>452839</v>
       </c>
       <c r="R10" t="n">
-        <v>6990252</v>
+        <v>6990352</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1641,10 +1643,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124704581</v>
+        <v>124688835</v>
       </c>
       <c r="B11" t="n">
-        <v>91299</v>
+        <v>78810</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1657,34 +1659,39 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>658</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Häggsåsen, Häggsåsen, Jmt</t>
+          <t>Tjärnflon, Tjärnflon, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>452839</v>
+        <v>452142</v>
       </c>
       <c r="R11" t="n">
-        <v>6990352</v>
+        <v>6990800</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1743,10 +1750,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124721354</v>
+        <v>124702902</v>
       </c>
       <c r="B12" t="n">
-        <v>57513</v>
+        <v>79891</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1759,39 +1766,34 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Tjärnflon, Tjärnflon, Jmt</t>
+          <t>Häggsåsen, Häggsåsen, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>452514</v>
+        <v>452734</v>
       </c>
       <c r="R12" t="n">
-        <v>6990587</v>
+        <v>6990348</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1824,11 +1826,6 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-05-02</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1855,7 +1852,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124704608</v>
+        <v>124693950</v>
       </c>
       <c r="B13" t="n">
         <v>91012</v>
@@ -1891,14 +1888,14 @@
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Häggsåsen, Häggsåsen, Jmt</t>
+          <t>Tjärnflon, Tjärnflon, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>452839</v>
+        <v>452582</v>
       </c>
       <c r="R13" t="n">
-        <v>6990352</v>
+        <v>6990572</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1957,10 +1954,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124702770</v>
+        <v>124701516</v>
       </c>
       <c r="B14" t="n">
-        <v>79891</v>
+        <v>91299</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1973,34 +1970,34 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6458</v>
+        <v>658</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Häggsåsen, Häggsåsen, Jmt</t>
+          <t>Tjärnflon, Tjärnflon, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>452731</v>
+        <v>452635</v>
       </c>
       <c r="R14" t="n">
-        <v>6990355</v>
+        <v>6990463</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2059,10 +2056,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124703646</v>
+        <v>124688930</v>
       </c>
       <c r="B15" t="n">
-        <v>91008</v>
+        <v>79891</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2075,34 +2072,34 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1108</v>
+        <v>6458</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Häggsåsen, Häggsåsen, Jmt</t>
+          <t>Tjärnflon, Tjärnflon, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>452785</v>
+        <v>452168</v>
       </c>
       <c r="R15" t="n">
-        <v>6990307</v>
+        <v>6990824</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2161,10 +2158,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124689504</v>
+        <v>124691528</v>
       </c>
       <c r="B16" t="n">
-        <v>57513</v>
+        <v>79892</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2177,39 +2174,34 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100109</v>
+        <v>2081</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Tjärnflon, Tjärnflon, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>452322</v>
+        <v>452427</v>
       </c>
       <c r="R16" t="n">
-        <v>6990950</v>
+        <v>6990925</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2242,11 +2234,6 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-05-02</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2273,10 +2260,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>124699728</v>
+        <v>124689528</v>
       </c>
       <c r="B17" t="n">
-        <v>79891</v>
+        <v>57513</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2289,34 +2276,39 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Tjärnflon, Tjärnflon, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>452650</v>
+        <v>452301</v>
       </c>
       <c r="R17" t="n">
-        <v>6990495</v>
+        <v>6990964</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2349,6 +2341,11 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-05-02</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2375,10 +2372,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>124688930</v>
+        <v>124689645</v>
       </c>
       <c r="B18" t="n">
-        <v>79891</v>
+        <v>91012</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2391,21 +2388,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2415,10 +2412,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>452168</v>
+        <v>452311</v>
       </c>
       <c r="R18" t="n">
-        <v>6990824</v>
+        <v>6990960</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2477,10 +2474,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>124688835</v>
+        <v>124691814</v>
       </c>
       <c r="B19" t="n">
-        <v>78810</v>
+        <v>56714</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2493,27 +2490,31 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>102612</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr"/>
-      <c r="K19" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>förbiflygande</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
@@ -2522,10 +2523,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>452142</v>
+        <v>452489</v>
       </c>
       <c r="R19" t="n">
-        <v>6990800</v>
+        <v>6990896</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2584,10 +2585,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>124691528</v>
+        <v>124706950</v>
       </c>
       <c r="B20" t="n">
-        <v>79892</v>
+        <v>98101</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2596,38 +2597,42 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>2081</v>
+        <v>220787</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Tjärnflon, Tjärnflon, Jmt</t>
+          <t>Häggsåsen, Häggsåsen, Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>452427</v>
+        <v>453007</v>
       </c>
       <c r="R20" t="n">
-        <v>6990925</v>
+        <v>6990356</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2686,10 +2691,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>124699720</v>
+        <v>124699728</v>
       </c>
       <c r="B21" t="n">
-        <v>79892</v>
+        <v>79891</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2702,21 +2707,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>2081</v>
+        <v>6458</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2788,10 +2793,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>124689528</v>
+        <v>124702530</v>
       </c>
       <c r="B22" t="n">
-        <v>57513</v>
+        <v>79891</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2804,39 +2809,34 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Tjärnflon, Tjärnflon, Jmt</t>
+          <t>Häggsåsen, Häggsåsen, Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>452301</v>
+        <v>452746</v>
       </c>
       <c r="R22" t="n">
-        <v>6990964</v>
+        <v>6990384</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2869,11 +2869,6 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-05-02</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2900,7 +2895,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>124704478</v>
+        <v>124689546</v>
       </c>
       <c r="B23" t="n">
         <v>57513</v>
@@ -2936,19 +2931,19 @@
       <c r="I23" t="inlineStr"/>
       <c r="M23" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Häggsåsen, Häggsåsen, Jmt</t>
+          <t>Tjärnflon, Tjärnflon, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>452836</v>
+        <v>452319</v>
       </c>
       <c r="R23" t="n">
-        <v>6990321</v>
+        <v>6990963</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3012,10 +3007,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>124689645</v>
+        <v>124721354</v>
       </c>
       <c r="B24" t="n">
-        <v>91012</v>
+        <v>57513</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3028,34 +3023,39 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Tjärnflon, Tjärnflon, Jmt</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>452311</v>
+        <v>452514</v>
       </c>
       <c r="R24" t="n">
-        <v>6990960</v>
+        <v>6990587</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3088,6 +3088,11 @@
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-05-02</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3114,10 +3119,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>124689546</v>
+        <v>124704726</v>
       </c>
       <c r="B25" t="n">
-        <v>57513</v>
+        <v>91012</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3130,39 +3135,34 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Tjärnflon, Tjärnflon, Jmt</t>
+          <t>Häggsåsen, Häggsåsen, Jmt</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>452319</v>
+        <v>452828</v>
       </c>
       <c r="R25" t="n">
-        <v>6990963</v>
+        <v>6990384</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3195,11 +3195,6 @@
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-05-02</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3226,10 +3221,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>124701516</v>
+        <v>124704608</v>
       </c>
       <c r="B26" t="n">
-        <v>91299</v>
+        <v>91012</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3242,34 +3237,34 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Tjärnflon, Tjärnflon, Jmt</t>
+          <t>Häggsåsen, Häggsåsen, Jmt</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>452635</v>
+        <v>452839</v>
       </c>
       <c r="R26" t="n">
-        <v>6990463</v>
+        <v>6990352</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3328,10 +3323,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>124705584</v>
+        <v>124706585</v>
       </c>
       <c r="B27" t="n">
-        <v>91030</v>
+        <v>77743</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3344,21 +3339,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>5432</v>
+        <v>228579</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3368,10 +3363,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>452865</v>
+        <v>452913</v>
       </c>
       <c r="R27" t="n">
-        <v>6990382</v>
+        <v>6990390</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3430,10 +3425,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>124691814</v>
+        <v>124703646</v>
       </c>
       <c r="B28" t="n">
-        <v>56714</v>
+        <v>91008</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3446,43 +3441,34 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>102612</v>
+        <v>1108</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>förbiflygande</t>
-        </is>
-      </c>
+          <t>(Fr.) Krieglst.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Tjärnflon, Tjärnflon, Jmt</t>
+          <t>Häggsåsen, Häggsåsen, Jmt</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>452489</v>
+        <v>452785</v>
       </c>
       <c r="R28" t="n">
-        <v>6990896</v>
+        <v>6990307</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3541,10 +3527,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>124693275</v>
+        <v>124689475</v>
       </c>
       <c r="B29" t="n">
-        <v>91026</v>
+        <v>57513</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3557,34 +3543,39 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1204</v>
+        <v>100109</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P29" t="inlineStr">
         <is>
           <t>Tjärnflon, Tjärnflon, Jmt</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>452523</v>
+        <v>452291</v>
       </c>
       <c r="R29" t="n">
-        <v>6990595</v>
+        <v>6990952</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3617,6 +3608,11 @@
       <c r="AA29" t="inlineStr">
         <is>
           <t>2025-05-02</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3643,10 +3639,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>124701352</v>
+        <v>124705813</v>
       </c>
       <c r="B30" t="n">
-        <v>79892</v>
+        <v>57513</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3659,39 +3655,39 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>2081</v>
+        <v>100109</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
-      <c r="K30" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Tjärnflon, Tjärnflon, Jmt</t>
+          <t>Häggsåsen, Häggsåsen, Jmt</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>452657</v>
+        <v>452865</v>
       </c>
       <c r="R30" t="n">
-        <v>6990499</v>
+        <v>6990385</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3728,7 +3724,7 @@
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>Rikligt med skrovellav, APOTECHIER på en av bålarna</t>
+          <t>Möjligt gammalt bo 3m upp i granstubbe med granticka på</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3755,10 +3751,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>124695367</v>
+        <v>124695424</v>
       </c>
       <c r="B31" t="n">
-        <v>82597</v>
+        <v>91012</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3771,21 +3767,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>1312</v>
+        <v>1202</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3795,10 +3791,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>452617</v>
+        <v>452642</v>
       </c>
       <c r="R31" t="n">
-        <v>6990540</v>
+        <v>6990548</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3857,10 +3853,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>124702530</v>
+        <v>124705215</v>
       </c>
       <c r="B32" t="n">
-        <v>79891</v>
+        <v>91012</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3873,21 +3869,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3897,10 +3893,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>452746</v>
+        <v>452850</v>
       </c>
       <c r="R32" t="n">
-        <v>6990384</v>
+        <v>6990404</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3959,7 +3955,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>124721401</v>
+        <v>124706864</v>
       </c>
       <c r="B33" t="n">
         <v>57513</v>
@@ -3995,19 +3991,19 @@
       <c r="I33" t="inlineStr"/>
       <c r="M33" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Tjärnflon, Tjärnflon, Jmt</t>
+          <t>Häggsåsen, Häggsåsen, Jmt</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>452415</v>
+        <v>453007</v>
       </c>
       <c r="R33" t="n">
-        <v>6990714</v>
+        <v>6990356</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4071,10 +4067,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>124706585</v>
+        <v>124695256</v>
       </c>
       <c r="B34" t="n">
-        <v>77743</v>
+        <v>98101</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4083,38 +4079,42 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>228579</v>
+        <v>220787</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>Tibell</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Häggsåsen, Häggsåsen, Jmt</t>
+          <t>Tjärnflon, Tjärnflon, Jmt</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>452913</v>
+        <v>452624</v>
       </c>
       <c r="R34" t="n">
-        <v>6990390</v>
+        <v>6990535</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4173,10 +4173,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>124693950</v>
+        <v>124703242</v>
       </c>
       <c r="B35" t="n">
-        <v>91012</v>
+        <v>91299</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4189,34 +4189,34 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Tjärnflon, Tjärnflon, Jmt</t>
+          <t>Häggsåsen, Häggsåsen, Jmt</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>452582</v>
+        <v>452760</v>
       </c>
       <c r="R35" t="n">
-        <v>6990572</v>
+        <v>6990252</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4275,10 +4275,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>124704726</v>
+        <v>124702770</v>
       </c>
       <c r="B36" t="n">
-        <v>91012</v>
+        <v>79891</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4291,21 +4291,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4315,10 +4315,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>452828</v>
+        <v>452731</v>
       </c>
       <c r="R36" t="n">
-        <v>6990384</v>
+        <v>6990355</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4377,10 +4377,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>124691378</v>
+        <v>124689335</v>
       </c>
       <c r="B37" t="n">
-        <v>91012</v>
+        <v>57513</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4393,34 +4393,39 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P37" t="inlineStr">
         <is>
           <t>Tjärnflon, Tjärnflon, Jmt</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>452431</v>
+        <v>452249</v>
       </c>
       <c r="R37" t="n">
-        <v>6990946</v>
+        <v>6990921</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4453,6 +4458,11 @@
       <c r="AA37" t="inlineStr">
         <is>
           <t>2025-05-02</t>
+        </is>
+      </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4479,10 +4489,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>124705813</v>
+        <v>124701352</v>
       </c>
       <c r="B38" t="n">
-        <v>57513</v>
+        <v>79892</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4495,39 +4505,39 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>100109</v>
+        <v>2081</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
-      <c r="M38" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Häggsåsen, Häggsåsen, Jmt</t>
+          <t>Tjärnflon, Tjärnflon, Jmt</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>452865</v>
+        <v>452657</v>
       </c>
       <c r="R38" t="n">
-        <v>6990385</v>
+        <v>6990499</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4564,7 +4574,7 @@
       </c>
       <c r="AC38" t="inlineStr">
         <is>
-          <t>Möjligt gammalt bo 3m upp i granstubbe med granticka på</t>
+          <t>Rikligt med skrovellav, APOTECHIER på en av bålarna</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4591,10 +4601,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>124695424</v>
+        <v>124689655</v>
       </c>
       <c r="B39" t="n">
-        <v>91012</v>
+        <v>91299</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4607,21 +4617,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4631,10 +4641,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>452642</v>
+        <v>452312</v>
       </c>
       <c r="R39" t="n">
-        <v>6990548</v>
+        <v>6990961</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4693,10 +4703,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>124689475</v>
+        <v>124699720</v>
       </c>
       <c r="B40" t="n">
-        <v>57513</v>
+        <v>79892</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4709,39 +4719,34 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>100109</v>
+        <v>2081</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
-      <c r="M40" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P40" t="inlineStr">
         <is>
           <t>Tjärnflon, Tjärnflon, Jmt</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>452291</v>
+        <v>452650</v>
       </c>
       <c r="R40" t="n">
-        <v>6990952</v>
+        <v>6990495</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4774,11 +4779,6 @@
       <c r="AA40" t="inlineStr">
         <is>
           <t>2025-05-02</t>
-        </is>
-      </c>
-      <c r="AC40" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4805,10 +4805,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>124689655</v>
+        <v>124693275</v>
       </c>
       <c r="B41" t="n">
-        <v>91299</v>
+        <v>91026</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4821,21 +4821,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>658</v>
+        <v>1204</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4845,10 +4845,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>452312</v>
+        <v>452523</v>
       </c>
       <c r="R41" t="n">
-        <v>6990961</v>
+        <v>6990595</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4907,7 +4907,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>124705215</v>
+        <v>124691378</v>
       </c>
       <c r="B42" t="n">
         <v>91012</v>
@@ -4943,14 +4943,14 @@
       <c r="I42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Häggsåsen, Häggsåsen, Jmt</t>
+          <t>Tjärnflon, Tjärnflon, Jmt</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>452850</v>
+        <v>452431</v>
       </c>
       <c r="R42" t="n">
-        <v>6990404</v>
+        <v>6990946</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5009,10 +5009,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>124756750</v>
+        <v>124756728</v>
       </c>
       <c r="B43" t="n">
-        <v>98101</v>
+        <v>79891</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5021,50 +5021,38 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J43" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K43" t="inlineStr"/>
-      <c r="L43" t="inlineStr"/>
-      <c r="N43" t="inlineStr"/>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
           <t>Häggsåsen N, Jmt</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>452617</v>
+        <v>452745</v>
       </c>
       <c r="R43" t="n">
-        <v>6990549</v>
+        <v>6990359</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5096,7 +5084,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>12:28</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5106,7 +5094,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>12:28</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5115,9 +5103,23 @@
       <c r="AE43" t="b">
         <v>0</v>
       </c>
-      <c r="AF43" t="inlineStr"/>
       <c r="AG43" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ43" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK43" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO43" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
       </c>
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
@@ -5134,10 +5136,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>124756779</v>
+        <v>124756724</v>
       </c>
       <c r="B44" t="n">
-        <v>78810</v>
+        <v>91012</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5150,21 +5152,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5174,10 +5176,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>452143</v>
+        <v>452793</v>
       </c>
       <c r="R44" t="n">
-        <v>6990780</v>
+        <v>6990262</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5209,7 +5211,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>09:51</t>
+          <t>14:44</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5219,7 +5221,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>09:51</t>
+          <t>14:44</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5246,10 +5248,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>124756725</v>
+        <v>124756759</v>
       </c>
       <c r="B45" t="n">
-        <v>78810</v>
+        <v>91012</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5262,21 +5264,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5286,10 +5288,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>452762</v>
+        <v>452509</v>
       </c>
       <c r="R45" t="n">
-        <v>6990327</v>
+        <v>6990778</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5321,7 +5323,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>14:37</t>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5331,7 +5333,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>14:37</t>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5358,10 +5360,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>124753608</v>
+        <v>124753620</v>
       </c>
       <c r="B46" t="n">
-        <v>79891</v>
+        <v>98101</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5370,25 +5372,25 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5398,10 +5400,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>452731</v>
+        <v>452554</v>
       </c>
       <c r="R46" t="n">
-        <v>6990377</v>
+        <v>6990657</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5434,6 +5436,11 @@
       <c r="AA46" t="inlineStr">
         <is>
           <t>2025-05-03</t>
+        </is>
+      </c>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>Minst 30</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5460,10 +5467,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>124753578</v>
+        <v>124756740</v>
       </c>
       <c r="B47" t="n">
-        <v>91012</v>
+        <v>91457</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5472,25 +5479,25 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>1202</v>
+        <v>1209</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5500,10 +5507,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>452743</v>
+        <v>452701</v>
       </c>
       <c r="R47" t="n">
-        <v>6990405</v>
+        <v>6990475</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5533,9 +5540,19 @@
           <t>2025-05-03</t>
         </is>
       </c>
+      <c r="Z47" t="inlineStr">
+        <is>
+          <t>13:58</t>
+        </is>
+      </c>
       <c r="AA47" t="inlineStr">
         <is>
           <t>2025-05-03</t>
+        </is>
+      </c>
+      <c r="AB47" t="inlineStr">
+        <is>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5550,22 +5567,22 @@
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>124756758</v>
+        <v>124753587</v>
       </c>
       <c r="B48" t="n">
-        <v>90962</v>
+        <v>91012</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5578,21 +5595,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>112</v>
+        <v>1202</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Stjärntagging</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Asterodon ferruginosus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>Pat.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5602,10 +5619,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>452509</v>
+        <v>452331</v>
       </c>
       <c r="R48" t="n">
-        <v>6990778</v>
+        <v>6990929</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5635,19 +5652,9 @@
           <t>2025-05-03</t>
         </is>
       </c>
-      <c r="Z48" t="inlineStr">
-        <is>
-          <t>11:40</t>
-        </is>
-      </c>
       <c r="AA48" t="inlineStr">
         <is>
           <t>2025-05-03</t>
-        </is>
-      </c>
-      <c r="AB48" t="inlineStr">
-        <is>
-          <t>11:40</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5662,12 +5669,12 @@
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
@@ -5786,10 +5793,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>124756745</v>
+        <v>124756765</v>
       </c>
       <c r="B50" t="n">
-        <v>98101</v>
+        <v>78810</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -5798,50 +5805,38 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I50" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J50" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K50" t="inlineStr"/>
-      <c r="L50" t="inlineStr"/>
-      <c r="N50" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
           <t>Häggsåsen N, Jmt</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>452657</v>
+        <v>452432</v>
       </c>
       <c r="R50" t="n">
-        <v>6990491</v>
+        <v>6990942</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5873,7 +5868,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>13:44</t>
+          <t>11:05</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -5883,7 +5878,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>13:44</t>
+          <t>11:05</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5892,7 +5887,6 @@
       <c r="AE50" t="b">
         <v>0</v>
       </c>
-      <c r="AF50" t="inlineStr"/>
       <c r="AG50" t="b">
         <v>0</v>
       </c>
@@ -5911,7 +5905,7 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>124756763</v>
+        <v>124753630</v>
       </c>
       <c r="B51" t="n">
         <v>98101</v>
@@ -5944,29 +5938,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I51" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J51" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K51" t="inlineStr"/>
-      <c r="L51" t="inlineStr"/>
-      <c r="N51" t="inlineStr"/>
+      <c r="I51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
           <t>Häggsåsen N, Jmt</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>452478</v>
+        <v>452273</v>
       </c>
       <c r="R51" t="n">
-        <v>6990887</v>
+        <v>6990906</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5996,19 +5978,14 @@
           <t>2025-05-03</t>
         </is>
       </c>
-      <c r="Z51" t="inlineStr">
-        <is>
-          <t>11:18</t>
-        </is>
-      </c>
       <c r="AA51" t="inlineStr">
         <is>
           <t>2025-05-03</t>
         </is>
       </c>
-      <c r="AB51" t="inlineStr">
-        <is>
-          <t>11:18</t>
+      <c r="AC51" t="inlineStr">
+        <is>
+          <t>Minst 10</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6017,29 +5994,28 @@
       <c r="AE51" t="b">
         <v>0</v>
       </c>
-      <c r="AF51" t="inlineStr"/>
       <c r="AG51" t="b">
         <v>0</v>
       </c>
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>124756746</v>
+        <v>124756752</v>
       </c>
       <c r="B52" t="n">
-        <v>91012</v>
+        <v>98101</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6048,38 +6024,50 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr"/>
+      <c r="L52" t="inlineStr"/>
+      <c r="N52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
           <t>Häggsåsen N, Jmt</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>452639</v>
+        <v>452608</v>
       </c>
       <c r="R52" t="n">
-        <v>6990537</v>
+        <v>6990625</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6111,7 +6099,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>13:36</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6121,7 +6109,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>13:36</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6130,6 +6118,7 @@
       <c r="AE52" t="b">
         <v>0</v>
       </c>
+      <c r="AF52" t="inlineStr"/>
       <c r="AG52" t="b">
         <v>0</v>
       </c>
@@ -6148,7 +6137,7 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>124753580</v>
+        <v>124753577</v>
       </c>
       <c r="B53" t="n">
         <v>91012</v>
@@ -6188,10 +6177,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>452693</v>
+        <v>452833</v>
       </c>
       <c r="R53" t="n">
-        <v>6990472</v>
+        <v>6990388</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6250,10 +6239,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>124753638</v>
+        <v>124753634</v>
       </c>
       <c r="B54" t="n">
-        <v>78810</v>
+        <v>91008</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6266,21 +6255,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6425</v>
+        <v>1108</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6290,10 +6279,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>452823</v>
+        <v>452750</v>
       </c>
       <c r="R54" t="n">
-        <v>6990367</v>
+        <v>6990344</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6352,10 +6341,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>124756772</v>
+        <v>124756770</v>
       </c>
       <c r="B55" t="n">
-        <v>78810</v>
+        <v>74899</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6364,38 +6353,41 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6425</v>
+        <v>6486</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skuggnål</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca sphaerocephala</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Nádv.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
+      <c r="J55" t="inlineStr"/>
+      <c r="K55" t="inlineStr"/>
+      <c r="N55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
           <t>Häggsåsen N, Jmt</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>452344</v>
+        <v>452339</v>
       </c>
       <c r="R55" t="n">
-        <v>6990942</v>
+        <v>6990941</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6427,7 +6419,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>10:32</t>
+          <t>10:44</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -6437,7 +6429,7 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>10:32</t>
+          <t>10:44</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6446,8 +6438,43 @@
       <c r="AE55" t="b">
         <v>0</v>
       </c>
+      <c r="AF55" t="inlineStr">
+        <is>
+          <t>mikroskoperad</t>
+        </is>
+      </c>
       <c r="AG55" t="b">
         <v>0</v>
+      </c>
+      <c r="AH55" t="inlineStr">
+        <is>
+          <t>Blåbärsgranskog</t>
+        </is>
+      </c>
+      <c r="AI55" t="inlineStr">
+        <is>
+          <t>I hålighet vid basen av gammal gran i fuktig granskog.</t>
+        </is>
+      </c>
+      <c r="AJ55" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK55" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM55" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO55" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Picea abies</t>
+        </is>
       </c>
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
@@ -6464,10 +6491,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>124753627</v>
+        <v>124756742</v>
       </c>
       <c r="B56" t="n">
-        <v>98101</v>
+        <v>79927</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6476,25 +6503,25 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>220787</v>
+        <v>6464</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6504,10 +6531,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>452608</v>
+        <v>452682</v>
       </c>
       <c r="R56" t="n">
-        <v>6990927</v>
+        <v>6990476</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6537,14 +6564,19 @@
           <t>2025-05-03</t>
         </is>
       </c>
+      <c r="Z56" t="inlineStr">
+        <is>
+          <t>13:53</t>
+        </is>
+      </c>
       <c r="AA56" t="inlineStr">
         <is>
           <t>2025-05-03</t>
         </is>
       </c>
-      <c r="AC56" t="inlineStr">
-        <is>
-          <t>Minst 50</t>
+      <c r="AB56" t="inlineStr">
+        <is>
+          <t>13:53</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6555,23 +6587,38 @@
       </c>
       <c r="AG56" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ56" t="inlineStr">
+        <is>
+          <t>rönn</t>
+        </is>
+      </c>
+      <c r="AK56" t="inlineStr">
+        <is>
+          <t>Sorbus aucuparia</t>
+        </is>
+      </c>
+      <c r="AO56" t="inlineStr">
+        <is>
+          <t>Sorbus aucuparia</t>
+        </is>
       </c>
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>124753585</v>
+        <v>124753588</v>
       </c>
       <c r="B57" t="n">
         <v>91012</v>
@@ -6611,10 +6658,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>452595</v>
+        <v>452311</v>
       </c>
       <c r="R57" t="n">
-        <v>6990913</v>
+        <v>6990887</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6673,7 +6720,7 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>124756754</v>
+        <v>124756761</v>
       </c>
       <c r="B58" t="n">
         <v>78810</v>
@@ -6713,10 +6760,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>452544</v>
+        <v>452532</v>
       </c>
       <c r="R58" t="n">
-        <v>6990646</v>
+        <v>6990825</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6748,7 +6795,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>12:04</t>
+          <t>11:26</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -6758,7 +6805,7 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>12:04</t>
+          <t>11:26</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6785,10 +6832,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>124753610</v>
+        <v>124756776</v>
       </c>
       <c r="B59" t="n">
-        <v>79891</v>
+        <v>78810</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -6801,21 +6848,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6825,10 +6872,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>452435</v>
+        <v>452308</v>
       </c>
       <c r="R59" t="n">
-        <v>6990938</v>
+        <v>6990943</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6858,9 +6905,19 @@
           <t>2025-05-03</t>
         </is>
       </c>
+      <c r="Z59" t="inlineStr">
+        <is>
+          <t>10:21</t>
+        </is>
+      </c>
       <c r="AA59" t="inlineStr">
         <is>
           <t>2025-05-03</t>
+        </is>
+      </c>
+      <c r="AB59" t="inlineStr">
+        <is>
+          <t>10:21</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -6875,19 +6932,19 @@
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>124756730</v>
+        <v>124753612</v>
       </c>
       <c r="B60" t="n">
         <v>98101</v>
@@ -6920,29 +6977,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I60" t="inlineStr">
-        <is>
-          <t>200</t>
-        </is>
-      </c>
-      <c r="J60" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K60" t="inlineStr"/>
-      <c r="L60" t="inlineStr"/>
-      <c r="N60" t="inlineStr"/>
+      <c r="I60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
           <t>Häggsåsen N, Jmt</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>452675</v>
+        <v>452924</v>
       </c>
       <c r="R60" t="n">
-        <v>6990411</v>
+        <v>6990397</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6972,24 +7017,14 @@
           <t>2025-05-03</t>
         </is>
       </c>
-      <c r="Z60" t="inlineStr">
-        <is>
-          <t>14:20</t>
-        </is>
-      </c>
       <c r="AA60" t="inlineStr">
         <is>
           <t>2025-05-03</t>
         </is>
       </c>
-      <c r="AB60" t="inlineStr">
-        <is>
-          <t>14:20</t>
-        </is>
-      </c>
       <c r="AC60" t="inlineStr">
         <is>
-          <t>Min antal</t>
+          <t>Minst 20</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -6998,26 +7033,25 @@
       <c r="AE60" t="b">
         <v>0</v>
       </c>
-      <c r="AF60" t="inlineStr"/>
       <c r="AG60" t="b">
         <v>0</v>
       </c>
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>124753625</v>
+        <v>124753629</v>
       </c>
       <c r="B61" t="n">
         <v>98101</v>
@@ -7057,10 +7091,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>452550</v>
+        <v>452576</v>
       </c>
       <c r="R61" t="n">
-        <v>6990907</v>
+        <v>6990924</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7097,7 +7131,7 @@
       </c>
       <c r="AC61" t="inlineStr">
         <is>
-          <t>Minst 50</t>
+          <t>Minst 30</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7124,7 +7158,7 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>124753617</v>
+        <v>124756751</v>
       </c>
       <c r="B62" t="n">
         <v>98101</v>
@@ -7157,17 +7191,29 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I62" t="inlineStr"/>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K62" t="inlineStr"/>
+      <c r="L62" t="inlineStr"/>
+      <c r="N62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
           <t>Häggsåsen N, Jmt</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>452655</v>
+        <v>452638</v>
       </c>
       <c r="R62" t="n">
-        <v>6990482</v>
+        <v>6990559</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7197,14 +7243,19 @@
           <t>2025-05-03</t>
         </is>
       </c>
+      <c r="Z62" t="inlineStr">
+        <is>
+          <t>12:23</t>
+        </is>
+      </c>
       <c r="AA62" t="inlineStr">
         <is>
           <t>2025-05-03</t>
         </is>
       </c>
-      <c r="AC62" t="inlineStr">
-        <is>
-          <t>Minst 50</t>
+      <c r="AB62" t="inlineStr">
+        <is>
+          <t>12:23</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7213,28 +7264,29 @@
       <c r="AE62" t="b">
         <v>0</v>
       </c>
+      <c r="AF62" t="inlineStr"/>
       <c r="AG62" t="b">
         <v>0</v>
       </c>
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>124756777</v>
+        <v>124753583</v>
       </c>
       <c r="B63" t="n">
-        <v>98101</v>
+        <v>91012</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -7243,50 +7295,38 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I63" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J63" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K63" t="inlineStr"/>
-      <c r="L63" t="inlineStr"/>
-      <c r="N63" t="inlineStr"/>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
           <t>Häggsåsen N, Jmt</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>452146</v>
+        <v>452606</v>
       </c>
       <c r="R63" t="n">
-        <v>6990839</v>
+        <v>6990623</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7316,50 +7356,39 @@
           <t>2025-05-03</t>
         </is>
       </c>
-      <c r="Z63" t="inlineStr">
-        <is>
-          <t>10:06</t>
-        </is>
-      </c>
       <c r="AA63" t="inlineStr">
         <is>
           <t>2025-05-03</t>
         </is>
       </c>
-      <c r="AB63" t="inlineStr">
-        <is>
-          <t>10:06</t>
-        </is>
-      </c>
       <c r="AD63" t="b">
         <v>0</v>
       </c>
       <c r="AE63" t="b">
         <v>0</v>
       </c>
-      <c r="AF63" t="inlineStr"/>
       <c r="AG63" t="b">
         <v>0</v>
       </c>
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>124753586</v>
+        <v>124753604</v>
       </c>
       <c r="B64" t="n">
-        <v>91012</v>
+        <v>79892</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7372,21 +7401,21 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>1202</v>
+        <v>2081</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7396,10 +7425,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>452500</v>
+        <v>452435</v>
       </c>
       <c r="R64" t="n">
-        <v>6990950</v>
+        <v>6990938</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7458,10 +7487,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>124756734</v>
+        <v>124753635</v>
       </c>
       <c r="B65" t="n">
-        <v>79891</v>
+        <v>91030</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -7474,21 +7503,21 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6458</v>
+        <v>5432</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7498,10 +7527,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>452675</v>
+        <v>452732</v>
       </c>
       <c r="R65" t="n">
-        <v>6990435</v>
+        <v>6990486</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7531,21 +7560,11 @@
           <t>2025-05-03</t>
         </is>
       </c>
-      <c r="Z65" t="inlineStr">
-        <is>
-          <t>14:14</t>
-        </is>
-      </c>
       <c r="AA65" t="inlineStr">
         <is>
           <t>2025-05-03</t>
         </is>
       </c>
-      <c r="AB65" t="inlineStr">
-        <is>
-          <t>14:14</t>
-        </is>
-      </c>
       <c r="AD65" t="b">
         <v>0</v>
       </c>
@@ -7554,41 +7573,26 @@
       </c>
       <c r="AG65" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ65" t="inlineStr">
-        <is>
-          <t>rönn</t>
-        </is>
-      </c>
-      <c r="AK65" t="inlineStr">
-        <is>
-          <t>Sorbus aucuparia</t>
-        </is>
-      </c>
-      <c r="AO65" t="inlineStr">
-        <is>
-          <t>Sorbus aucuparia</t>
-        </is>
       </c>
       <c r="AT65" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>124753607</v>
+        <v>124753638</v>
       </c>
       <c r="B66" t="n">
-        <v>79891</v>
+        <v>78810</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -7601,21 +7605,21 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7625,10 +7629,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>452734</v>
+        <v>452823</v>
       </c>
       <c r="R66" t="n">
-        <v>6990356</v>
+        <v>6990367</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7687,10 +7691,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>124753629</v>
+        <v>124756767</v>
       </c>
       <c r="B67" t="n">
-        <v>98101</v>
+        <v>78810</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -7699,25 +7703,25 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7727,10 +7731,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>452576</v>
+        <v>452362</v>
       </c>
       <c r="R67" t="n">
-        <v>6990924</v>
+        <v>6991003</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7760,14 +7764,19 @@
           <t>2025-05-03</t>
         </is>
       </c>
+      <c r="Z67" t="inlineStr">
+        <is>
+          <t>10:55</t>
+        </is>
+      </c>
       <c r="AA67" t="inlineStr">
         <is>
           <t>2025-05-03</t>
         </is>
       </c>
-      <c r="AC67" t="inlineStr">
-        <is>
-          <t>Minst 30</t>
+      <c r="AB67" t="inlineStr">
+        <is>
+          <t>10:55</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7782,22 +7791,22 @@
       <c r="AT67" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>124753631</v>
+        <v>124753592</v>
       </c>
       <c r="B68" t="n">
-        <v>98101</v>
+        <v>57513</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -7806,25 +7815,25 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7834,10 +7843,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>452526</v>
+        <v>452396</v>
       </c>
       <c r="R68" t="n">
-        <v>6990943</v>
+        <v>6990703</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7874,7 +7883,7 @@
       </c>
       <c r="AC68" t="inlineStr">
         <is>
-          <t>Minst 20</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -7901,10 +7910,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>124756755</v>
+        <v>124756741</v>
       </c>
       <c r="B69" t="n">
-        <v>91299</v>
+        <v>79851</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -7913,25 +7922,25 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>658</v>
+        <v>229497</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7941,10 +7950,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>452538</v>
+        <v>452682</v>
       </c>
       <c r="R69" t="n">
-        <v>6990659</v>
+        <v>6990476</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7976,7 +7985,7 @@
       </c>
       <c r="Z69" t="inlineStr">
         <is>
-          <t>11:58</t>
+          <t>13:54</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
@@ -7986,7 +7995,7 @@
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>11:58</t>
+          <t>13:54</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -7997,6 +8006,21 @@
       </c>
       <c r="AG69" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ69" t="inlineStr">
+        <is>
+          <t>rönn</t>
+        </is>
+      </c>
+      <c r="AK69" t="inlineStr">
+        <is>
+          <t>Sorbus aucuparia</t>
+        </is>
+      </c>
+      <c r="AO69" t="inlineStr">
+        <is>
+          <t>Sorbus aucuparia</t>
+        </is>
       </c>
       <c r="AT69" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
@@ -8013,10 +8037,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>124753579</v>
+        <v>124756758</v>
       </c>
       <c r="B70" t="n">
-        <v>91012</v>
+        <v>90962</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -8029,21 +8053,21 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>1202</v>
+        <v>112</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Stjärntagging</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Asterodon ferruginosus</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Pat.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -8053,10 +8077,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>452710</v>
+        <v>452509</v>
       </c>
       <c r="R70" t="n">
-        <v>6990467</v>
+        <v>6990778</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -8086,9 +8110,19 @@
           <t>2025-05-03</t>
         </is>
       </c>
+      <c r="Z70" t="inlineStr">
+        <is>
+          <t>11:40</t>
+        </is>
+      </c>
       <c r="AA70" t="inlineStr">
         <is>
           <t>2025-05-03</t>
+        </is>
+      </c>
+      <c r="AB70" t="inlineStr">
+        <is>
+          <t>11:40</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8103,22 +8137,22 @@
       <c r="AT70" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>124756743</v>
+        <v>124753623</v>
       </c>
       <c r="B71" t="n">
-        <v>79891</v>
+        <v>98101</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -8127,25 +8161,25 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -8155,10 +8189,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>452682</v>
+        <v>452510</v>
       </c>
       <c r="R71" t="n">
-        <v>6990476</v>
+        <v>6990873</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -8188,19 +8222,14 @@
           <t>2025-05-03</t>
         </is>
       </c>
-      <c r="Z71" t="inlineStr">
-        <is>
-          <t>13:53</t>
-        </is>
-      </c>
       <c r="AA71" t="inlineStr">
         <is>
           <t>2025-05-03</t>
         </is>
       </c>
-      <c r="AB71" t="inlineStr">
-        <is>
-          <t>13:53</t>
+      <c r="AC71" t="inlineStr">
+        <is>
+          <t>Minst 50</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -8211,41 +8240,26 @@
       </c>
       <c r="AG71" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ71" t="inlineStr">
-        <is>
-          <t>rönn</t>
-        </is>
-      </c>
-      <c r="AK71" t="inlineStr">
-        <is>
-          <t>Sorbus aucuparia</t>
-        </is>
-      </c>
-      <c r="AO71" t="inlineStr">
-        <is>
-          <t>Sorbus aucuparia</t>
-        </is>
       </c>
       <c r="AT71" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX71" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>124756770</v>
+        <v>124756777</v>
       </c>
       <c r="B72" t="n">
-        <v>74899</v>
+        <v>98101</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -8258,26 +8272,35 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>6486</v>
+        <v>220787</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Skuggnål</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Chaenotheca sphaerocephala</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>Nádv.</t>
-        </is>
-      </c>
-      <c r="I72" t="inlineStr"/>
-      <c r="J72" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J72" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="K72" t="inlineStr"/>
+      <c r="L72" t="inlineStr"/>
       <c r="N72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
@@ -8285,10 +8308,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>452339</v>
+        <v>452146</v>
       </c>
       <c r="R72" t="n">
-        <v>6990941</v>
+        <v>6990839</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8320,7 +8343,7 @@
       </c>
       <c r="Z72" t="inlineStr">
         <is>
-          <t>10:44</t>
+          <t>10:06</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
@@ -8330,7 +8353,7 @@
       </c>
       <c r="AB72" t="inlineStr">
         <is>
-          <t>10:44</t>
+          <t>10:06</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8339,43 +8362,9 @@
       <c r="AE72" t="b">
         <v>0</v>
       </c>
-      <c r="AF72" t="inlineStr">
-        <is>
-          <t>mikroskoperad</t>
-        </is>
-      </c>
+      <c r="AF72" t="inlineStr"/>
       <c r="AG72" t="b">
         <v>0</v>
-      </c>
-      <c r="AH72" t="inlineStr">
-        <is>
-          <t>Blåbärsgranskog</t>
-        </is>
-      </c>
-      <c r="AI72" t="inlineStr">
-        <is>
-          <t>I hålighet vid basen av gammal gran i fuktig granskog.</t>
-        </is>
-      </c>
-      <c r="AJ72" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK72" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM72" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO72" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Picea abies</t>
-        </is>
       </c>
       <c r="AT72" t="inlineStr"/>
       <c r="AW72" t="inlineStr">
@@ -8392,10 +8381,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>124756688</v>
+        <v>124756719</v>
       </c>
       <c r="B73" t="n">
-        <v>79891</v>
+        <v>79927</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -8404,25 +8393,25 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>6458</v>
+        <v>6464</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -8432,10 +8421,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>452694</v>
+        <v>452823</v>
       </c>
       <c r="R73" t="n">
-        <v>6990598</v>
+        <v>6990261</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8467,7 +8456,7 @@
       </c>
       <c r="Z73" t="inlineStr">
         <is>
-          <t>20:19</t>
+          <t>14:59</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
@@ -8477,7 +8466,7 @@
       </c>
       <c r="AB73" t="inlineStr">
         <is>
-          <t>20:19</t>
+          <t>14:59</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8504,10 +8493,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>124756766</v>
+        <v>124756779</v>
       </c>
       <c r="B74" t="n">
-        <v>79891</v>
+        <v>78810</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -8520,21 +8509,21 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -8544,10 +8533,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>452396</v>
+        <v>452143</v>
       </c>
       <c r="R74" t="n">
-        <v>6990981</v>
+        <v>6990780</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8579,7 +8568,7 @@
       </c>
       <c r="Z74" t="inlineStr">
         <is>
-          <t>10:58</t>
+          <t>09:51</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
@@ -8589,7 +8578,7 @@
       </c>
       <c r="AB74" t="inlineStr">
         <is>
-          <t>10:58</t>
+          <t>09:51</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8616,10 +8605,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>124753605</v>
+        <v>124756725</v>
       </c>
       <c r="B75" t="n">
-        <v>79892</v>
+        <v>78810</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -8632,21 +8621,21 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8656,10 +8645,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>452408</v>
+        <v>452762</v>
       </c>
       <c r="R75" t="n">
-        <v>6990952</v>
+        <v>6990327</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8689,9 +8678,19 @@
           <t>2025-05-03</t>
         </is>
       </c>
+      <c r="Z75" t="inlineStr">
+        <is>
+          <t>14:37</t>
+        </is>
+      </c>
       <c r="AA75" t="inlineStr">
         <is>
           <t>2025-05-03</t>
+        </is>
+      </c>
+      <c r="AB75" t="inlineStr">
+        <is>
+          <t>14:37</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -8706,22 +8705,22 @@
       <c r="AT75" t="inlineStr"/>
       <c r="AW75" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX75" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>124753604</v>
+        <v>124753607</v>
       </c>
       <c r="B76" t="n">
-        <v>79892</v>
+        <v>79891</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
@@ -8734,21 +8733,21 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>2081</v>
+        <v>6458</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -8758,10 +8757,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>452435</v>
+        <v>452734</v>
       </c>
       <c r="R76" t="n">
-        <v>6990938</v>
+        <v>6990356</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8820,10 +8819,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>124753639</v>
+        <v>124753621</v>
       </c>
       <c r="B77" t="n">
-        <v>78810</v>
+        <v>98101</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -8832,25 +8831,25 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -8860,10 +8859,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>452511</v>
+        <v>452506</v>
       </c>
       <c r="R77" t="n">
-        <v>6990733</v>
+        <v>6990758</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8896,6 +8895,11 @@
       <c r="AA77" t="inlineStr">
         <is>
           <t>2025-05-03</t>
+        </is>
+      </c>
+      <c r="AC77" t="inlineStr">
+        <is>
+          <t>Minst 60</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -8922,10 +8926,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>124756721</v>
+        <v>124756745</v>
       </c>
       <c r="B78" t="n">
-        <v>79891</v>
+        <v>98101</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -8934,38 +8938,50 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I78" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J78" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K78" t="inlineStr"/>
+      <c r="L78" t="inlineStr"/>
+      <c r="N78" t="inlineStr"/>
       <c r="P78" t="inlineStr">
         <is>
           <t>Häggsåsen N, Jmt</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>452823</v>
+        <v>452657</v>
       </c>
       <c r="R78" t="n">
-        <v>6990261</v>
+        <v>6990491</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8997,7 +9013,7 @@
       </c>
       <c r="Z78" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AA78" t="inlineStr">
@@ -9007,7 +9023,7 @@
       </c>
       <c r="AB78" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -9016,23 +9032,9 @@
       <c r="AE78" t="b">
         <v>0</v>
       </c>
+      <c r="AF78" t="inlineStr"/>
       <c r="AG78" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ78" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK78" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AO78" t="inlineStr">
-        <is>
-          <t>Omkullfallen grov stam # Salix caprea</t>
-        </is>
       </c>
       <c r="AT78" t="inlineStr"/>
       <c r="AW78" t="inlineStr">
@@ -9049,10 +9051,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>124753635</v>
+        <v>124753614</v>
       </c>
       <c r="B79" t="n">
-        <v>91030</v>
+        <v>98101</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -9061,25 +9063,25 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>5432</v>
+        <v>220787</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -9089,10 +9091,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>452732</v>
+        <v>452751</v>
       </c>
       <c r="R79" t="n">
-        <v>6990486</v>
+        <v>6990344</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -9125,6 +9127,11 @@
       <c r="AA79" t="inlineStr">
         <is>
           <t>2025-05-03</t>
+        </is>
+      </c>
+      <c r="AC79" t="inlineStr">
+        <is>
+          <t>Minst 200</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -9151,10 +9158,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>124753633</v>
+        <v>124753624</v>
       </c>
       <c r="B80" t="n">
-        <v>91008</v>
+        <v>98101</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
@@ -9163,25 +9170,25 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>1108</v>
+        <v>220787</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -9191,10 +9198,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>452772</v>
+        <v>452528</v>
       </c>
       <c r="R80" t="n">
-        <v>6990321</v>
+        <v>6990882</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -9227,6 +9234,11 @@
       <c r="AA80" t="inlineStr">
         <is>
           <t>2025-05-03</t>
+        </is>
+      </c>
+      <c r="AC80" t="inlineStr">
+        <is>
+          <t>Minst 30</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -9253,10 +9265,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>124753606</v>
+        <v>124756749</v>
       </c>
       <c r="B81" t="n">
-        <v>91299</v>
+        <v>91012</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
@@ -9269,21 +9281,21 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -9293,10 +9305,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>452165</v>
+        <v>452609</v>
       </c>
       <c r="R81" t="n">
-        <v>6990824</v>
+        <v>6990543</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -9326,9 +9338,19 @@
           <t>2025-05-03</t>
         </is>
       </c>
+      <c r="Z81" t="inlineStr">
+        <is>
+          <t>12:29</t>
+        </is>
+      </c>
       <c r="AA81" t="inlineStr">
         <is>
           <t>2025-05-03</t>
+        </is>
+      </c>
+      <c r="AB81" t="inlineStr">
+        <is>
+          <t>12:29</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -9343,22 +9365,22 @@
       <c r="AT81" t="inlineStr"/>
       <c r="AW81" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX81" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>124753615</v>
+        <v>124756755</v>
       </c>
       <c r="B82" t="n">
-        <v>98101</v>
+        <v>91299</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
@@ -9367,25 +9389,25 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -9395,10 +9417,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>452734</v>
+        <v>452538</v>
       </c>
       <c r="R82" t="n">
-        <v>6990355</v>
+        <v>6990659</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -9428,14 +9450,19 @@
           <t>2025-05-03</t>
         </is>
       </c>
+      <c r="Z82" t="inlineStr">
+        <is>
+          <t>11:58</t>
+        </is>
+      </c>
       <c r="AA82" t="inlineStr">
         <is>
           <t>2025-05-03</t>
         </is>
       </c>
-      <c r="AC82" t="inlineStr">
-        <is>
-          <t>Minst 30</t>
+      <c r="AB82" t="inlineStr">
+        <is>
+          <t>11:58</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -9450,19 +9477,19 @@
       <c r="AT82" t="inlineStr"/>
       <c r="AW82" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX82" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>124753588</v>
+        <v>124753584</v>
       </c>
       <c r="B83" t="n">
         <v>91012</v>
@@ -9502,10 +9529,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>452311</v>
+        <v>452444</v>
       </c>
       <c r="R83" t="n">
-        <v>6990887</v>
+        <v>6990774</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9564,10 +9591,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>124756742</v>
+        <v>124753610</v>
       </c>
       <c r="B84" t="n">
-        <v>79927</v>
+        <v>79891</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
@@ -9576,25 +9603,25 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>6464</v>
+        <v>6458</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -9604,10 +9631,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>452682</v>
+        <v>452435</v>
       </c>
       <c r="R84" t="n">
-        <v>6990476</v>
+        <v>6990938</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9637,21 +9664,11 @@
           <t>2025-05-03</t>
         </is>
       </c>
-      <c r="Z84" t="inlineStr">
-        <is>
-          <t>13:53</t>
-        </is>
-      </c>
       <c r="AA84" t="inlineStr">
         <is>
           <t>2025-05-03</t>
         </is>
       </c>
-      <c r="AB84" t="inlineStr">
-        <is>
-          <t>13:53</t>
-        </is>
-      </c>
       <c r="AD84" t="b">
         <v>0</v>
       </c>
@@ -9660,41 +9677,26 @@
       </c>
       <c r="AG84" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ84" t="inlineStr">
-        <is>
-          <t>rönn</t>
-        </is>
-      </c>
-      <c r="AK84" t="inlineStr">
-        <is>
-          <t>Sorbus aucuparia</t>
-        </is>
-      </c>
-      <c r="AO84" t="inlineStr">
-        <is>
-          <t>Sorbus aucuparia</t>
-        </is>
       </c>
       <c r="AT84" t="inlineStr"/>
       <c r="AW84" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX84" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>124756733</v>
+        <v>124753637</v>
       </c>
       <c r="B85" t="n">
-        <v>79927</v>
+        <v>91030</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
@@ -9703,25 +9705,25 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>6464</v>
+        <v>5432</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -9731,10 +9733,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>452675</v>
+        <v>452696</v>
       </c>
       <c r="R85" t="n">
-        <v>6990435</v>
+        <v>6990466</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9764,21 +9766,11 @@
           <t>2025-05-03</t>
         </is>
       </c>
-      <c r="Z85" t="inlineStr">
-        <is>
-          <t>14:15</t>
-        </is>
-      </c>
       <c r="AA85" t="inlineStr">
         <is>
           <t>2025-05-03</t>
         </is>
       </c>
-      <c r="AB85" t="inlineStr">
-        <is>
-          <t>14:15</t>
-        </is>
-      </c>
       <c r="AD85" t="b">
         <v>0</v>
       </c>
@@ -9787,41 +9779,26 @@
       </c>
       <c r="AG85" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ85" t="inlineStr">
-        <is>
-          <t>rönn</t>
-        </is>
-      </c>
-      <c r="AK85" t="inlineStr">
-        <is>
-          <t>Sorbus aucuparia</t>
-        </is>
-      </c>
-      <c r="AO85" t="inlineStr">
-        <is>
-          <t>Sorbus aucuparia</t>
-        </is>
       </c>
       <c r="AT85" t="inlineStr"/>
       <c r="AW85" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX85" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>124756741</v>
+        <v>124756756</v>
       </c>
       <c r="B86" t="n">
-        <v>79851</v>
+        <v>78810</v>
       </c>
       <c r="C86" t="inlineStr">
         <is>
@@ -9830,25 +9807,25 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>229497</v>
+        <v>6425</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -9858,10 +9835,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>452682</v>
+        <v>452545</v>
       </c>
       <c r="R86" t="n">
-        <v>6990476</v>
+        <v>6990691</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9893,7 +9870,7 @@
       </c>
       <c r="Z86" t="inlineStr">
         <is>
-          <t>13:54</t>
+          <t>11:54</t>
         </is>
       </c>
       <c r="AA86" t="inlineStr">
@@ -9903,7 +9880,7 @@
       </c>
       <c r="AB86" t="inlineStr">
         <is>
-          <t>13:54</t>
+          <t>11:54</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -9914,21 +9891,6 @@
       </c>
       <c r="AG86" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ86" t="inlineStr">
-        <is>
-          <t>rönn</t>
-        </is>
-      </c>
-      <c r="AK86" t="inlineStr">
-        <is>
-          <t>Sorbus aucuparia</t>
-        </is>
-      </c>
-      <c r="AO86" t="inlineStr">
-        <is>
-          <t>Sorbus aucuparia</t>
-        </is>
       </c>
       <c r="AT86" t="inlineStr"/>
       <c r="AW86" t="inlineStr">
@@ -9945,10 +9907,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>124753621</v>
+        <v>124756718</v>
       </c>
       <c r="B87" t="n">
-        <v>98101</v>
+        <v>91030</v>
       </c>
       <c r="C87" t="inlineStr">
         <is>
@@ -9957,25 +9919,25 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>220787</v>
+        <v>5432</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
@@ -9985,10 +9947,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>452506</v>
+        <v>452857</v>
       </c>
       <c r="R87" t="n">
-        <v>6990758</v>
+        <v>6990267</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -10018,14 +9980,19 @@
           <t>2025-05-03</t>
         </is>
       </c>
+      <c r="Z87" t="inlineStr">
+        <is>
+          <t>15:03</t>
+        </is>
+      </c>
       <c r="AA87" t="inlineStr">
         <is>
           <t>2025-05-03</t>
         </is>
       </c>
-      <c r="AC87" t="inlineStr">
-        <is>
-          <t>Minst 60</t>
+      <c r="AB87" t="inlineStr">
+        <is>
+          <t>15:03</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -10040,22 +10007,22 @@
       <c r="AT87" t="inlineStr"/>
       <c r="AW87" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX87" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>124756759</v>
+        <v>124753609</v>
       </c>
       <c r="B88" t="n">
-        <v>91012</v>
+        <v>79891</v>
       </c>
       <c r="C88" t="inlineStr">
         <is>
@@ -10068,21 +10035,21 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
@@ -10092,10 +10059,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>452509</v>
+        <v>452528</v>
       </c>
       <c r="R88" t="n">
-        <v>6990778</v>
+        <v>6990710</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -10125,19 +10092,9 @@
           <t>2025-05-03</t>
         </is>
       </c>
-      <c r="Z88" t="inlineStr">
-        <is>
-          <t>11:39</t>
-        </is>
-      </c>
       <c r="AA88" t="inlineStr">
         <is>
           <t>2025-05-03</t>
-        </is>
-      </c>
-      <c r="AB88" t="inlineStr">
-        <is>
-          <t>11:39</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -10152,22 +10109,22 @@
       <c r="AT88" t="inlineStr"/>
       <c r="AW88" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX88" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>124753634</v>
+        <v>124756739</v>
       </c>
       <c r="B89" t="n">
-        <v>91008</v>
+        <v>98101</v>
       </c>
       <c r="C89" t="inlineStr">
         <is>
@@ -10176,38 +10133,50 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>1108</v>
+        <v>220787</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
-        </is>
-      </c>
-      <c r="I89" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I89" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="J89" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K89" t="inlineStr"/>
+      <c r="L89" t="inlineStr"/>
+      <c r="N89" t="inlineStr"/>
       <c r="P89" t="inlineStr">
         <is>
           <t>Häggsåsen N, Jmt</t>
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>452750</v>
+        <v>452711</v>
       </c>
       <c r="R89" t="n">
-        <v>6990344</v>
+        <v>6990473</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -10237,39 +10206,50 @@
           <t>2025-05-03</t>
         </is>
       </c>
+      <c r="Z89" t="inlineStr">
+        <is>
+          <t>14:01</t>
+        </is>
+      </c>
       <c r="AA89" t="inlineStr">
         <is>
           <t>2025-05-03</t>
         </is>
       </c>
+      <c r="AB89" t="inlineStr">
+        <is>
+          <t>14:01</t>
+        </is>
+      </c>
       <c r="AD89" t="b">
         <v>0</v>
       </c>
       <c r="AE89" t="b">
         <v>0</v>
       </c>
+      <c r="AF89" t="inlineStr"/>
       <c r="AG89" t="b">
         <v>0</v>
       </c>
       <c r="AT89" t="inlineStr"/>
       <c r="AW89" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX89" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>124756719</v>
+        <v>124753611</v>
       </c>
       <c r="B90" t="n">
-        <v>79927</v>
+        <v>98101</v>
       </c>
       <c r="C90" t="inlineStr">
         <is>
@@ -10278,25 +10258,25 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>6464</v>
+        <v>220787</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
@@ -10306,10 +10286,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>452823</v>
+        <v>452997</v>
       </c>
       <c r="R90" t="n">
-        <v>6990261</v>
+        <v>6990332</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -10339,19 +10319,14 @@
           <t>2025-05-03</t>
         </is>
       </c>
-      <c r="Z90" t="inlineStr">
-        <is>
-          <t>14:59</t>
-        </is>
-      </c>
       <c r="AA90" t="inlineStr">
         <is>
           <t>2025-05-03</t>
         </is>
       </c>
-      <c r="AB90" t="inlineStr">
-        <is>
-          <t>14:59</t>
+      <c r="AC90" t="inlineStr">
+        <is>
+          <t>Minst 100</t>
         </is>
       </c>
       <c r="AD90" t="b">
@@ -10366,22 +10341,22 @@
       <c r="AT90" t="inlineStr"/>
       <c r="AW90" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX90" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>124756765</v>
+        <v>124753613</v>
       </c>
       <c r="B91" t="n">
-        <v>78810</v>
+        <v>98101</v>
       </c>
       <c r="C91" t="inlineStr">
         <is>
@@ -10390,25 +10365,25 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
@@ -10418,10 +10393,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>452432</v>
+        <v>452777</v>
       </c>
       <c r="R91" t="n">
-        <v>6990942</v>
+        <v>6990299</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -10451,19 +10426,14 @@
           <t>2025-05-03</t>
         </is>
       </c>
-      <c r="Z91" t="inlineStr">
-        <is>
-          <t>11:05</t>
-        </is>
-      </c>
       <c r="AA91" t="inlineStr">
         <is>
           <t>2025-05-03</t>
         </is>
       </c>
-      <c r="AB91" t="inlineStr">
-        <is>
-          <t>11:05</t>
+      <c r="AC91" t="inlineStr">
+        <is>
+          <t>Minst 100</t>
         </is>
       </c>
       <c r="AD91" t="b">
@@ -10478,22 +10448,22 @@
       <c r="AT91" t="inlineStr"/>
       <c r="AW91" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX91" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>124756776</v>
+        <v>124756731</v>
       </c>
       <c r="B92" t="n">
-        <v>78810</v>
+        <v>91012</v>
       </c>
       <c r="C92" t="inlineStr">
         <is>
@@ -10506,21 +10476,21 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
@@ -10530,10 +10500,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>452308</v>
+        <v>452672</v>
       </c>
       <c r="R92" t="n">
-        <v>6990943</v>
+        <v>6990427</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -10565,7 +10535,7 @@
       </c>
       <c r="Z92" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>14:19</t>
         </is>
       </c>
       <c r="AA92" t="inlineStr">
@@ -10575,7 +10545,7 @@
       </c>
       <c r="AB92" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>14:19</t>
         </is>
       </c>
       <c r="AD92" t="b">
@@ -10602,10 +10572,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>124756751</v>
+        <v>124753578</v>
       </c>
       <c r="B93" t="n">
-        <v>98101</v>
+        <v>91012</v>
       </c>
       <c r="C93" t="inlineStr">
         <is>
@@ -10614,50 +10584,38 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I93" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J93" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K93" t="inlineStr"/>
-      <c r="L93" t="inlineStr"/>
-      <c r="N93" t="inlineStr"/>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I93" t="inlineStr"/>
       <c r="P93" t="inlineStr">
         <is>
           <t>Häggsåsen N, Jmt</t>
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>452638</v>
+        <v>452743</v>
       </c>
       <c r="R93" t="n">
-        <v>6990559</v>
+        <v>6990405</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -10687,50 +10645,39 @@
           <t>2025-05-03</t>
         </is>
       </c>
-      <c r="Z93" t="inlineStr">
-        <is>
-          <t>12:23</t>
-        </is>
-      </c>
       <c r="AA93" t="inlineStr">
         <is>
           <t>2025-05-03</t>
         </is>
       </c>
-      <c r="AB93" t="inlineStr">
-        <is>
-          <t>12:23</t>
-        </is>
-      </c>
       <c r="AD93" t="b">
         <v>0</v>
       </c>
       <c r="AE93" t="b">
         <v>0</v>
       </c>
-      <c r="AF93" t="inlineStr"/>
       <c r="AG93" t="b">
         <v>0</v>
       </c>
       <c r="AT93" t="inlineStr"/>
       <c r="AW93" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX93" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY93" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>124753632</v>
+        <v>124753582</v>
       </c>
       <c r="B94" t="n">
-        <v>98101</v>
+        <v>91012</v>
       </c>
       <c r="C94" t="inlineStr">
         <is>
@@ -10739,25 +10686,25 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E94" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
@@ -10767,10 +10714,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>452455</v>
+        <v>452649</v>
       </c>
       <c r="R94" t="n">
-        <v>6990942</v>
+        <v>6990621</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -10803,11 +10750,6 @@
       <c r="AA94" t="inlineStr">
         <is>
           <t>2025-05-03</t>
-        </is>
-      </c>
-      <c r="AC94" t="inlineStr">
-        <is>
-          <t>Minst 30</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -10834,10 +10776,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>124753622</v>
+        <v>124756753</v>
       </c>
       <c r="B95" t="n">
-        <v>98101</v>
+        <v>91012</v>
       </c>
       <c r="C95" t="inlineStr">
         <is>
@@ -10846,25 +10788,25 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
@@ -10874,10 +10816,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>452472</v>
+        <v>452608</v>
       </c>
       <c r="R95" t="n">
-        <v>6990821</v>
+        <v>6990625</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10907,14 +10849,19 @@
           <t>2025-05-03</t>
         </is>
       </c>
+      <c r="Z95" t="inlineStr">
+        <is>
+          <t>12:07</t>
+        </is>
+      </c>
       <c r="AA95" t="inlineStr">
         <is>
           <t>2025-05-03</t>
         </is>
       </c>
-      <c r="AC95" t="inlineStr">
-        <is>
-          <t>Minst 50</t>
+      <c r="AB95" t="inlineStr">
+        <is>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -10929,22 +10876,22 @@
       <c r="AT95" t="inlineStr"/>
       <c r="AW95" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX95" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY95" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>124753623</v>
+        <v>124756772</v>
       </c>
       <c r="B96" t="n">
-        <v>98101</v>
+        <v>78810</v>
       </c>
       <c r="C96" t="inlineStr">
         <is>
@@ -10953,25 +10900,25 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E96" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
@@ -10981,10 +10928,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>452510</v>
+        <v>452344</v>
       </c>
       <c r="R96" t="n">
-        <v>6990873</v>
+        <v>6990942</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -11014,14 +10961,19 @@
           <t>2025-05-03</t>
         </is>
       </c>
+      <c r="Z96" t="inlineStr">
+        <is>
+          <t>10:32</t>
+        </is>
+      </c>
       <c r="AA96" t="inlineStr">
         <is>
           <t>2025-05-03</t>
         </is>
       </c>
-      <c r="AC96" t="inlineStr">
-        <is>
-          <t>Minst 50</t>
+      <c r="AB96" t="inlineStr">
+        <is>
+          <t>10:32</t>
         </is>
       </c>
       <c r="AD96" t="b">
@@ -11036,22 +10988,22 @@
       <c r="AT96" t="inlineStr"/>
       <c r="AW96" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX96" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY96" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>124756727</v>
+        <v>124753576</v>
       </c>
       <c r="B97" t="n">
-        <v>79920</v>
+        <v>91012</v>
       </c>
       <c r="C97" t="inlineStr">
         <is>
@@ -11060,25 +11012,25 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E97" t="n">
-        <v>6462</v>
+        <v>1202</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
@@ -11088,10 +11040,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>452745</v>
+        <v>452837</v>
       </c>
       <c r="R97" t="n">
-        <v>6990359</v>
+        <v>6990384</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -11121,19 +11073,9 @@
           <t>2025-05-03</t>
         </is>
       </c>
-      <c r="Z97" t="inlineStr">
-        <is>
-          <t>14:31</t>
-        </is>
-      </c>
       <c r="AA97" t="inlineStr">
         <is>
           <t>2025-05-03</t>
-        </is>
-      </c>
-      <c r="AB97" t="inlineStr">
-        <is>
-          <t>14:31</t>
         </is>
       </c>
       <c r="AD97" t="b">
@@ -11148,22 +11090,22 @@
       <c r="AT97" t="inlineStr"/>
       <c r="AW97" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX97" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY97" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>124753614</v>
+        <v>124756754</v>
       </c>
       <c r="B98" t="n">
-        <v>98101</v>
+        <v>78810</v>
       </c>
       <c r="C98" t="inlineStr">
         <is>
@@ -11172,25 +11114,25 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E98" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
@@ -11200,10 +11142,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>452751</v>
+        <v>452544</v>
       </c>
       <c r="R98" t="n">
-        <v>6990344</v>
+        <v>6990646</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -11233,14 +11175,19 @@
           <t>2025-05-03</t>
         </is>
       </c>
+      <c r="Z98" t="inlineStr">
+        <is>
+          <t>12:04</t>
+        </is>
+      </c>
       <c r="AA98" t="inlineStr">
         <is>
           <t>2025-05-03</t>
         </is>
       </c>
-      <c r="AC98" t="inlineStr">
-        <is>
-          <t>Minst 200</t>
+      <c r="AB98" t="inlineStr">
+        <is>
+          <t>12:04</t>
         </is>
       </c>
       <c r="AD98" t="b">
@@ -11255,19 +11202,19 @@
       <c r="AT98" t="inlineStr"/>
       <c r="AW98" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX98" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY98" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>124753612</v>
+        <v>124753622</v>
       </c>
       <c r="B99" t="n">
         <v>98101</v>
@@ -11307,10 +11254,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>452924</v>
+        <v>452472</v>
       </c>
       <c r="R99" t="n">
-        <v>6990397</v>
+        <v>6990821</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -11347,7 +11294,7 @@
       </c>
       <c r="AC99" t="inlineStr">
         <is>
-          <t>Minst 20</t>
+          <t>Minst 50</t>
         </is>
       </c>
       <c r="AD99" t="b">
@@ -11374,10 +11321,10 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>124756757</v>
+        <v>124753631</v>
       </c>
       <c r="B100" t="n">
-        <v>77743</v>
+        <v>98101</v>
       </c>
       <c r="C100" t="inlineStr">
         <is>
@@ -11386,25 +11333,25 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E100" t="n">
-        <v>228579</v>
+        <v>220787</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
@@ -11414,10 +11361,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>452506</v>
+        <v>452526</v>
       </c>
       <c r="R100" t="n">
-        <v>6990737</v>
+        <v>6990943</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -11447,19 +11394,14 @@
           <t>2025-05-03</t>
         </is>
       </c>
-      <c r="Z100" t="inlineStr">
-        <is>
-          <t>11:47</t>
-        </is>
-      </c>
       <c r="AA100" t="inlineStr">
         <is>
           <t>2025-05-03</t>
         </is>
       </c>
-      <c r="AB100" t="inlineStr">
-        <is>
-          <t>11:47</t>
+      <c r="AC100" t="inlineStr">
+        <is>
+          <t>Minst 20</t>
         </is>
       </c>
       <c r="AD100" t="b">
@@ -11474,22 +11416,22 @@
       <c r="AT100" t="inlineStr"/>
       <c r="AW100" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX100" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY100" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>124756728</v>
+        <v>124753625</v>
       </c>
       <c r="B101" t="n">
-        <v>79891</v>
+        <v>98101</v>
       </c>
       <c r="C101" t="inlineStr">
         <is>
@@ -11498,25 +11440,25 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E101" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
@@ -11526,10 +11468,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>452745</v>
+        <v>452550</v>
       </c>
       <c r="R101" t="n">
-        <v>6990359</v>
+        <v>6990907</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -11559,19 +11501,14 @@
           <t>2025-05-03</t>
         </is>
       </c>
-      <c r="Z101" t="inlineStr">
-        <is>
-          <t>14:30</t>
-        </is>
-      </c>
       <c r="AA101" t="inlineStr">
         <is>
           <t>2025-05-03</t>
         </is>
       </c>
-      <c r="AB101" t="inlineStr">
-        <is>
-          <t>14:30</t>
+      <c r="AC101" t="inlineStr">
+        <is>
+          <t>Minst 50</t>
         </is>
       </c>
       <c r="AD101" t="b">
@@ -11582,41 +11519,26 @@
       </c>
       <c r="AG101" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ101" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK101" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AO101" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
       </c>
       <c r="AT101" t="inlineStr"/>
       <c r="AW101" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX101" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY101" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>124753587</v>
+        <v>124756748</v>
       </c>
       <c r="B102" t="n">
-        <v>91012</v>
+        <v>78810</v>
       </c>
       <c r="C102" t="inlineStr">
         <is>
@@ -11629,21 +11551,21 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
@@ -11653,10 +11575,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>452331</v>
+        <v>452609</v>
       </c>
       <c r="R102" t="n">
-        <v>6990929</v>
+        <v>6990543</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -11686,9 +11608,19 @@
           <t>2025-05-03</t>
         </is>
       </c>
+      <c r="Z102" t="inlineStr">
+        <is>
+          <t>12:29</t>
+        </is>
+      </c>
       <c r="AA102" t="inlineStr">
         <is>
           <t>2025-05-03</t>
+        </is>
+      </c>
+      <c r="AB102" t="inlineStr">
+        <is>
+          <t>12:29</t>
         </is>
       </c>
       <c r="AD102" t="b">
@@ -11703,19 +11635,19 @@
       <c r="AT102" t="inlineStr"/>
       <c r="AW102" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX102" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY102" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>124753584</v>
+        <v>124753579</v>
       </c>
       <c r="B103" t="n">
         <v>91012</v>
@@ -11755,10 +11687,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>452444</v>
+        <v>452710</v>
       </c>
       <c r="R103" t="n">
-        <v>6990774</v>
+        <v>6990467</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -11817,10 +11749,10 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>124756774</v>
+        <v>124753580</v>
       </c>
       <c r="B104" t="n">
-        <v>98101</v>
+        <v>91012</v>
       </c>
       <c r="C104" t="inlineStr">
         <is>
@@ -11829,50 +11761,38 @@
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E104" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I104" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="J104" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K104" t="inlineStr"/>
-      <c r="L104" t="inlineStr"/>
-      <c r="N104" t="inlineStr"/>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I104" t="inlineStr"/>
       <c r="P104" t="inlineStr">
         <is>
           <t>Häggsåsen N, Jmt</t>
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>452308</v>
+        <v>452693</v>
       </c>
       <c r="R104" t="n">
-        <v>6990943</v>
+        <v>6990472</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -11902,50 +11822,39 @@
           <t>2025-05-03</t>
         </is>
       </c>
-      <c r="Z104" t="inlineStr">
-        <is>
-          <t>10:23</t>
-        </is>
-      </c>
       <c r="AA104" t="inlineStr">
         <is>
           <t>2025-05-03</t>
         </is>
       </c>
-      <c r="AB104" t="inlineStr">
-        <is>
-          <t>10:23</t>
-        </is>
-      </c>
       <c r="AD104" t="b">
         <v>0</v>
       </c>
       <c r="AE104" t="b">
         <v>0</v>
       </c>
-      <c r="AF104" t="inlineStr"/>
       <c r="AG104" t="b">
         <v>0</v>
       </c>
       <c r="AT104" t="inlineStr"/>
       <c r="AW104" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX104" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY104" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>124753620</v>
+        <v>124753585</v>
       </c>
       <c r="B105" t="n">
-        <v>98101</v>
+        <v>91012</v>
       </c>
       <c r="C105" t="inlineStr">
         <is>
@@ -11954,25 +11863,25 @@
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E105" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
@@ -11982,10 +11891,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>452554</v>
+        <v>452595</v>
       </c>
       <c r="R105" t="n">
-        <v>6990657</v>
+        <v>6990913</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -12018,11 +11927,6 @@
       <c r="AA105" t="inlineStr">
         <is>
           <t>2025-05-03</t>
-        </is>
-      </c>
-      <c r="AC105" t="inlineStr">
-        <is>
-          <t>Minst 30</t>
         </is>
       </c>
       <c r="AD105" t="b">
@@ -12049,10 +11953,10 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>124753630</v>
+        <v>124753606</v>
       </c>
       <c r="B106" t="n">
-        <v>98101</v>
+        <v>91299</v>
       </c>
       <c r="C106" t="inlineStr">
         <is>
@@ -12061,25 +11965,25 @@
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E106" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
@@ -12089,10 +11993,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>452273</v>
+        <v>452165</v>
       </c>
       <c r="R106" t="n">
-        <v>6990906</v>
+        <v>6990824</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -12125,11 +12029,6 @@
       <c r="AA106" t="inlineStr">
         <is>
           <t>2025-05-03</t>
-        </is>
-      </c>
-      <c r="AC106" t="inlineStr">
-        <is>
-          <t>Minst 10</t>
         </is>
       </c>
       <c r="AD106" t="b">
@@ -12156,10 +12055,10 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>124753576</v>
+        <v>124753608</v>
       </c>
       <c r="B107" t="n">
-        <v>91012</v>
+        <v>79891</v>
       </c>
       <c r="C107" t="inlineStr">
         <is>
@@ -12172,21 +12071,21 @@
         </is>
       </c>
       <c r="E107" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
@@ -12196,10 +12095,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>452837</v>
+        <v>452731</v>
       </c>
       <c r="R107" t="n">
-        <v>6990384</v>
+        <v>6990377</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -12258,10 +12157,10 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>124753637</v>
+        <v>124756688</v>
       </c>
       <c r="B108" t="n">
-        <v>91030</v>
+        <v>79891</v>
       </c>
       <c r="C108" t="inlineStr">
         <is>
@@ -12274,21 +12173,21 @@
         </is>
       </c>
       <c r="E108" t="n">
-        <v>5432</v>
+        <v>6458</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
@@ -12298,10 +12197,10 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>452696</v>
+        <v>452694</v>
       </c>
       <c r="R108" t="n">
-        <v>6990466</v>
+        <v>6990598</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -12331,9 +12230,19 @@
           <t>2025-05-03</t>
         </is>
       </c>
+      <c r="Z108" t="inlineStr">
+        <is>
+          <t>20:19</t>
+        </is>
+      </c>
       <c r="AA108" t="inlineStr">
         <is>
           <t>2025-05-03</t>
+        </is>
+      </c>
+      <c r="AB108" t="inlineStr">
+        <is>
+          <t>20:19</t>
         </is>
       </c>
       <c r="AD108" t="b">
@@ -12348,22 +12257,22 @@
       <c r="AT108" t="inlineStr"/>
       <c r="AW108" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX108" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY108" t="inlineStr"/>
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>124756764</v>
+        <v>124756736</v>
       </c>
       <c r="B109" t="n">
-        <v>78810</v>
+        <v>98101</v>
       </c>
       <c r="C109" t="inlineStr">
         <is>
@@ -12372,38 +12281,50 @@
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E109" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I109" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I109" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J109" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K109" t="inlineStr"/>
+      <c r="L109" t="inlineStr"/>
+      <c r="N109" t="inlineStr"/>
       <c r="P109" t="inlineStr">
         <is>
           <t>Häggsåsen N, Jmt</t>
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>452462</v>
+        <v>452691</v>
       </c>
       <c r="R109" t="n">
-        <v>6990915</v>
+        <v>6990422</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -12435,7 +12356,7 @@
       </c>
       <c r="Z109" t="inlineStr">
         <is>
-          <t>11:11</t>
+          <t>14:13</t>
         </is>
       </c>
       <c r="AA109" t="inlineStr">
@@ -12445,7 +12366,7 @@
       </c>
       <c r="AB109" t="inlineStr">
         <is>
-          <t>11:11</t>
+          <t>14:13</t>
         </is>
       </c>
       <c r="AD109" t="b">
@@ -12454,6 +12375,7 @@
       <c r="AE109" t="b">
         <v>0</v>
       </c>
+      <c r="AF109" t="inlineStr"/>
       <c r="AG109" t="b">
         <v>0</v>
       </c>
@@ -12472,10 +12394,10 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>124756738</v>
+        <v>124753617</v>
       </c>
       <c r="B110" t="n">
-        <v>74899</v>
+        <v>98101</v>
       </c>
       <c r="C110" t="inlineStr">
         <is>
@@ -12488,37 +12410,34 @@
         </is>
       </c>
       <c r="E110" t="n">
-        <v>6486</v>
+        <v>220787</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Skuggnål</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Chaenotheca sphaerocephala</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>Nádv.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
-      <c r="J110" t="inlineStr"/>
-      <c r="K110" t="inlineStr"/>
-      <c r="N110" t="inlineStr"/>
       <c r="P110" t="inlineStr">
         <is>
           <t>Häggsåsen N, Jmt</t>
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>452703</v>
+        <v>452655</v>
       </c>
       <c r="R110" t="n">
-        <v>6990457</v>
+        <v>6990482</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -12548,19 +12467,14 @@
           <t>2025-05-03</t>
         </is>
       </c>
-      <c r="Z110" t="inlineStr">
-        <is>
-          <t>14:09</t>
-        </is>
-      </c>
       <c r="AA110" t="inlineStr">
         <is>
           <t>2025-05-03</t>
         </is>
       </c>
-      <c r="AB110" t="inlineStr">
-        <is>
-          <t>14:09</t>
+      <c r="AC110" t="inlineStr">
+        <is>
+          <t>Minst 50</t>
         </is>
       </c>
       <c r="AD110" t="b">
@@ -12568,11 +12482,6 @@
       </c>
       <c r="AE110" t="b">
         <v>0</v>
-      </c>
-      <c r="AF110" t="inlineStr">
-        <is>
-          <t>mikroskoperad</t>
-        </is>
       </c>
       <c r="AG110" t="b">
         <v>0</v>
@@ -12580,22 +12489,22 @@
       <c r="AT110" t="inlineStr"/>
       <c r="AW110" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX110" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY110" t="inlineStr"/>
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>124756740</v>
+        <v>124756768</v>
       </c>
       <c r="B111" t="n">
-        <v>91457</v>
+        <v>77743</v>
       </c>
       <c r="C111" t="inlineStr">
         <is>
@@ -12604,25 +12513,25 @@
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E111" t="n">
-        <v>1209</v>
+        <v>228579</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
@@ -12632,10 +12541,10 @@
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>452701</v>
+        <v>452357</v>
       </c>
       <c r="R111" t="n">
-        <v>6990475</v>
+        <v>6990970</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -12667,7 +12576,7 @@
       </c>
       <c r="Z111" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>10:52</t>
         </is>
       </c>
       <c r="AA111" t="inlineStr">
@@ -12677,7 +12586,7 @@
       </c>
       <c r="AB111" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>10:52</t>
         </is>
       </c>
       <c r="AD111" t="b">
@@ -12704,10 +12613,10 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>124756718</v>
+        <v>124753581</v>
       </c>
       <c r="B112" t="n">
-        <v>91030</v>
+        <v>91012</v>
       </c>
       <c r="C112" t="inlineStr">
         <is>
@@ -12720,21 +12629,21 @@
         </is>
       </c>
       <c r="E112" t="n">
-        <v>5432</v>
+        <v>1202</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I112" t="inlineStr"/>
@@ -12744,10 +12653,10 @@
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>452857</v>
+        <v>452643</v>
       </c>
       <c r="R112" t="n">
-        <v>6990267</v>
+        <v>6990504</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -12777,19 +12686,9 @@
           <t>2025-05-03</t>
         </is>
       </c>
-      <c r="Z112" t="inlineStr">
-        <is>
-          <t>15:03</t>
-        </is>
-      </c>
       <c r="AA112" t="inlineStr">
         <is>
           <t>2025-05-03</t>
-        </is>
-      </c>
-      <c r="AB112" t="inlineStr">
-        <is>
-          <t>15:03</t>
         </is>
       </c>
       <c r="AD112" t="b">
@@ -12804,22 +12703,22 @@
       <c r="AT112" t="inlineStr"/>
       <c r="AW112" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX112" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY112" t="inlineStr"/>
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>124756752</v>
+        <v>124756764</v>
       </c>
       <c r="B113" t="n">
-        <v>98101</v>
+        <v>78810</v>
       </c>
       <c r="C113" t="inlineStr">
         <is>
@@ -12828,50 +12727,38 @@
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E113" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I113" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J113" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K113" t="inlineStr"/>
-      <c r="L113" t="inlineStr"/>
-      <c r="N113" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I113" t="inlineStr"/>
       <c r="P113" t="inlineStr">
         <is>
           <t>Häggsåsen N, Jmt</t>
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>452608</v>
+        <v>452462</v>
       </c>
       <c r="R113" t="n">
-        <v>6990625</v>
+        <v>6990915</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -12903,7 +12790,7 @@
       </c>
       <c r="Z113" t="inlineStr">
         <is>
-          <t>12:07</t>
+          <t>11:11</t>
         </is>
       </c>
       <c r="AA113" t="inlineStr">
@@ -12913,7 +12800,7 @@
       </c>
       <c r="AB113" t="inlineStr">
         <is>
-          <t>12:07</t>
+          <t>11:11</t>
         </is>
       </c>
       <c r="AD113" t="b">
@@ -12922,7 +12809,6 @@
       <c r="AE113" t="b">
         <v>0</v>
       </c>
-      <c r="AF113" t="inlineStr"/>
       <c r="AG113" t="b">
         <v>0</v>
       </c>
@@ -12941,10 +12827,10 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>124753616</v>
+        <v>124756727</v>
       </c>
       <c r="B114" t="n">
-        <v>98101</v>
+        <v>79920</v>
       </c>
       <c r="C114" t="inlineStr">
         <is>
@@ -12953,25 +12839,25 @@
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E114" t="n">
-        <v>220787</v>
+        <v>6462</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
@@ -12981,10 +12867,10 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>452742</v>
+        <v>452745</v>
       </c>
       <c r="R114" t="n">
-        <v>6990393</v>
+        <v>6990359</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -13014,14 +12900,19 @@
           <t>2025-05-03</t>
         </is>
       </c>
+      <c r="Z114" t="inlineStr">
+        <is>
+          <t>14:31</t>
+        </is>
+      </c>
       <c r="AA114" t="inlineStr">
         <is>
           <t>2025-05-03</t>
         </is>
       </c>
-      <c r="AC114" t="inlineStr">
-        <is>
-          <t>Minst 60</t>
+      <c r="AB114" t="inlineStr">
+        <is>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AD114" t="b">
@@ -13036,19 +12927,19 @@
       <c r="AT114" t="inlineStr"/>
       <c r="AW114" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX114" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY114" t="inlineStr"/>
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>124756739</v>
+        <v>124756774</v>
       </c>
       <c r="B115" t="n">
         <v>98101</v>
@@ -13083,7 +12974,7 @@
       </c>
       <c r="I115" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>6</t>
         </is>
       </c>
       <c r="J115" t="inlineStr">
@@ -13100,10 +12991,10 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>452711</v>
+        <v>452308</v>
       </c>
       <c r="R115" t="n">
-        <v>6990473</v>
+        <v>6990943</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -13135,7 +13026,7 @@
       </c>
       <c r="Z115" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>10:23</t>
         </is>
       </c>
       <c r="AA115" t="inlineStr">
@@ -13145,7 +13036,7 @@
       </c>
       <c r="AB115" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>10:23</t>
         </is>
       </c>
       <c r="AD115" t="b">
@@ -13173,10 +13064,10 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>124756749</v>
+        <v>124753615</v>
       </c>
       <c r="B116" t="n">
-        <v>91012</v>
+        <v>98101</v>
       </c>
       <c r="C116" t="inlineStr">
         <is>
@@ -13185,25 +13076,25 @@
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E116" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
@@ -13213,10 +13104,10 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>452609</v>
+        <v>452734</v>
       </c>
       <c r="R116" t="n">
-        <v>6990543</v>
+        <v>6990355</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -13246,19 +13137,14 @@
           <t>2025-05-03</t>
         </is>
       </c>
-      <c r="Z116" t="inlineStr">
-        <is>
-          <t>12:29</t>
-        </is>
-      </c>
       <c r="AA116" t="inlineStr">
         <is>
           <t>2025-05-03</t>
         </is>
       </c>
-      <c r="AB116" t="inlineStr">
-        <is>
-          <t>12:29</t>
+      <c r="AC116" t="inlineStr">
+        <is>
+          <t>Minst 30</t>
         </is>
       </c>
       <c r="AD116" t="b">
@@ -13273,22 +13159,22 @@
       <c r="AT116" t="inlineStr"/>
       <c r="AW116" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX116" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY116" t="inlineStr"/>
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>124753583</v>
+        <v>124756743</v>
       </c>
       <c r="B117" t="n">
-        <v>91012</v>
+        <v>79891</v>
       </c>
       <c r="C117" t="inlineStr">
         <is>
@@ -13301,21 +13187,21 @@
         </is>
       </c>
       <c r="E117" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
@@ -13325,10 +13211,10 @@
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>452606</v>
+        <v>452682</v>
       </c>
       <c r="R117" t="n">
-        <v>6990623</v>
+        <v>6990476</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>
@@ -13358,11 +13244,21 @@
           <t>2025-05-03</t>
         </is>
       </c>
+      <c r="Z117" t="inlineStr">
+        <is>
+          <t>13:53</t>
+        </is>
+      </c>
       <c r="AA117" t="inlineStr">
         <is>
           <t>2025-05-03</t>
         </is>
       </c>
+      <c r="AB117" t="inlineStr">
+        <is>
+          <t>13:53</t>
+        </is>
+      </c>
       <c r="AD117" t="b">
         <v>0</v>
       </c>
@@ -13371,23 +13267,38 @@
       </c>
       <c r="AG117" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ117" t="inlineStr">
+        <is>
+          <t>rönn</t>
+        </is>
+      </c>
+      <c r="AK117" t="inlineStr">
+        <is>
+          <t>Sorbus aucuparia</t>
+        </is>
+      </c>
+      <c r="AO117" t="inlineStr">
+        <is>
+          <t>Sorbus aucuparia</t>
+        </is>
       </c>
       <c r="AT117" t="inlineStr"/>
       <c r="AW117" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX117" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY117" t="inlineStr"/>
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>124753577</v>
+        <v>124756746</v>
       </c>
       <c r="B118" t="n">
         <v>91012</v>
@@ -13427,10 +13338,10 @@
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>452833</v>
+        <v>452639</v>
       </c>
       <c r="R118" t="n">
-        <v>6990388</v>
+        <v>6990537</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -13460,9 +13371,19 @@
           <t>2025-05-03</t>
         </is>
       </c>
+      <c r="Z118" t="inlineStr">
+        <is>
+          <t>13:36</t>
+        </is>
+      </c>
       <c r="AA118" t="inlineStr">
         <is>
           <t>2025-05-03</t>
+        </is>
+      </c>
+      <c r="AB118" t="inlineStr">
+        <is>
+          <t>13:36</t>
         </is>
       </c>
       <c r="AD118" t="b">
@@ -13477,22 +13398,22 @@
       <c r="AT118" t="inlineStr"/>
       <c r="AW118" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX118" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY118" t="inlineStr"/>
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>124756761</v>
+        <v>124756721</v>
       </c>
       <c r="B119" t="n">
-        <v>78810</v>
+        <v>79891</v>
       </c>
       <c r="C119" t="inlineStr">
         <is>
@@ -13505,21 +13426,21 @@
         </is>
       </c>
       <c r="E119" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I119" t="inlineStr"/>
@@ -13529,10 +13450,10 @@
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>452532</v>
+        <v>452823</v>
       </c>
       <c r="R119" t="n">
-        <v>6990825</v>
+        <v>6990261</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -13564,7 +13485,7 @@
       </c>
       <c r="Z119" t="inlineStr">
         <is>
-          <t>11:26</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AA119" t="inlineStr">
@@ -13574,7 +13495,7 @@
       </c>
       <c r="AB119" t="inlineStr">
         <is>
-          <t>11:26</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AD119" t="b">
@@ -13585,6 +13506,21 @@
       </c>
       <c r="AG119" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ119" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK119" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO119" t="inlineStr">
+        <is>
+          <t>Omkullfallen grov stam # Salix caprea</t>
+        </is>
       </c>
       <c r="AT119" t="inlineStr"/>
       <c r="AW119" t="inlineStr">
@@ -13601,10 +13537,10 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>124756762</v>
+        <v>124756766</v>
       </c>
       <c r="B120" t="n">
-        <v>78810</v>
+        <v>79891</v>
       </c>
       <c r="C120" t="inlineStr">
         <is>
@@ -13617,21 +13553,21 @@
         </is>
       </c>
       <c r="E120" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
@@ -13641,10 +13577,10 @@
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>452508</v>
+        <v>452396</v>
       </c>
       <c r="R120" t="n">
-        <v>6990903</v>
+        <v>6990981</v>
       </c>
       <c r="S120" t="n">
         <v>10</v>
@@ -13676,7 +13612,7 @@
       </c>
       <c r="Z120" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AA120" t="inlineStr">
@@ -13686,7 +13622,7 @@
       </c>
       <c r="AB120" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AD120" t="b">
@@ -13713,10 +13649,10 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>124756767</v>
+        <v>124753627</v>
       </c>
       <c r="B121" t="n">
-        <v>78810</v>
+        <v>98101</v>
       </c>
       <c r="C121" t="inlineStr">
         <is>
@@ -13725,25 +13661,25 @@
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E121" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
@@ -13753,10 +13689,10 @@
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>452362</v>
+        <v>452608</v>
       </c>
       <c r="R121" t="n">
-        <v>6991003</v>
+        <v>6990927</v>
       </c>
       <c r="S121" t="n">
         <v>10</v>
@@ -13786,19 +13722,14 @@
           <t>2025-05-03</t>
         </is>
       </c>
-      <c r="Z121" t="inlineStr">
-        <is>
-          <t>10:55</t>
-        </is>
-      </c>
       <c r="AA121" t="inlineStr">
         <is>
           <t>2025-05-03</t>
         </is>
       </c>
-      <c r="AB121" t="inlineStr">
-        <is>
-          <t>10:55</t>
+      <c r="AC121" t="inlineStr">
+        <is>
+          <t>Minst 50</t>
         </is>
       </c>
       <c r="AD121" t="b">
@@ -13813,19 +13744,19 @@
       <c r="AT121" t="inlineStr"/>
       <c r="AW121" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX121" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY121" t="inlineStr"/>
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>124753611</v>
+        <v>124753616</v>
       </c>
       <c r="B122" t="n">
         <v>98101</v>
@@ -13865,10 +13796,10 @@
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>452997</v>
+        <v>452742</v>
       </c>
       <c r="R122" t="n">
-        <v>6990332</v>
+        <v>6990393</v>
       </c>
       <c r="S122" t="n">
         <v>10</v>
@@ -13905,7 +13836,7 @@
       </c>
       <c r="AC122" t="inlineStr">
         <is>
-          <t>Minst 100</t>
+          <t>Minst 60</t>
         </is>
       </c>
       <c r="AD122" t="b">
@@ -13932,7 +13863,7 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>124756736</v>
+        <v>124756763</v>
       </c>
       <c r="B123" t="n">
         <v>98101</v>
@@ -13967,7 +13898,7 @@
       </c>
       <c r="I123" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J123" t="inlineStr">
@@ -13984,10 +13915,10 @@
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>452691</v>
+        <v>452478</v>
       </c>
       <c r="R123" t="n">
-        <v>6990422</v>
+        <v>6990887</v>
       </c>
       <c r="S123" t="n">
         <v>10</v>
@@ -14019,7 +13950,7 @@
       </c>
       <c r="Z123" t="inlineStr">
         <is>
-          <t>14:13</t>
+          <t>11:18</t>
         </is>
       </c>
       <c r="AA123" t="inlineStr">
@@ -14029,7 +13960,7 @@
       </c>
       <c r="AB123" t="inlineStr">
         <is>
-          <t>14:13</t>
+          <t>11:18</t>
         </is>
       </c>
       <c r="AD123" t="b">
@@ -14057,10 +13988,10 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>124753624</v>
+        <v>124756733</v>
       </c>
       <c r="B124" t="n">
-        <v>98101</v>
+        <v>79927</v>
       </c>
       <c r="C124" t="inlineStr">
         <is>
@@ -14069,25 +14000,25 @@
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E124" t="n">
-        <v>220787</v>
+        <v>6464</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I124" t="inlineStr"/>
@@ -14097,10 +14028,10 @@
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>452528</v>
+        <v>452675</v>
       </c>
       <c r="R124" t="n">
-        <v>6990882</v>
+        <v>6990435</v>
       </c>
       <c r="S124" t="n">
         <v>10</v>
@@ -14130,14 +14061,19 @@
           <t>2025-05-03</t>
         </is>
       </c>
+      <c r="Z124" t="inlineStr">
+        <is>
+          <t>14:15</t>
+        </is>
+      </c>
       <c r="AA124" t="inlineStr">
         <is>
           <t>2025-05-03</t>
         </is>
       </c>
-      <c r="AC124" t="inlineStr">
-        <is>
-          <t>Minst 30</t>
+      <c r="AB124" t="inlineStr">
+        <is>
+          <t>14:15</t>
         </is>
       </c>
       <c r="AD124" t="b">
@@ -14148,26 +14084,41 @@
       </c>
       <c r="AG124" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ124" t="inlineStr">
+        <is>
+          <t>rönn</t>
+        </is>
+      </c>
+      <c r="AK124" t="inlineStr">
+        <is>
+          <t>Sorbus aucuparia</t>
+        </is>
+      </c>
+      <c r="AO124" t="inlineStr">
+        <is>
+          <t>Sorbus aucuparia</t>
+        </is>
       </c>
       <c r="AT124" t="inlineStr"/>
       <c r="AW124" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX124" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY124" t="inlineStr"/>
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>124756724</v>
+        <v>124756762</v>
       </c>
       <c r="B125" t="n">
-        <v>91012</v>
+        <v>78810</v>
       </c>
       <c r="C125" t="inlineStr">
         <is>
@@ -14180,21 +14131,21 @@
         </is>
       </c>
       <c r="E125" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I125" t="inlineStr"/>
@@ -14204,10 +14155,10 @@
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>452793</v>
+        <v>452508</v>
       </c>
       <c r="R125" t="n">
-        <v>6990262</v>
+        <v>6990903</v>
       </c>
       <c r="S125" t="n">
         <v>10</v>
@@ -14239,7 +14190,7 @@
       </c>
       <c r="Z125" t="inlineStr">
         <is>
-          <t>14:44</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="AA125" t="inlineStr">
@@ -14249,7 +14200,7 @@
       </c>
       <c r="AB125" t="inlineStr">
         <is>
-          <t>14:44</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="AD125" t="b">
@@ -14276,10 +14227,10 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>124756748</v>
+        <v>124756757</v>
       </c>
       <c r="B126" t="n">
-        <v>78810</v>
+        <v>77743</v>
       </c>
       <c r="C126" t="inlineStr">
         <is>
@@ -14292,21 +14243,21 @@
         </is>
       </c>
       <c r="E126" t="n">
-        <v>6425</v>
+        <v>228579</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I126" t="inlineStr"/>
@@ -14316,10 +14267,10 @@
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>452609</v>
+        <v>452506</v>
       </c>
       <c r="R126" t="n">
-        <v>6990543</v>
+        <v>6990737</v>
       </c>
       <c r="S126" t="n">
         <v>10</v>
@@ -14351,7 +14302,7 @@
       </c>
       <c r="Z126" t="inlineStr">
         <is>
-          <t>12:29</t>
+          <t>11:47</t>
         </is>
       </c>
       <c r="AA126" t="inlineStr">
@@ -14361,7 +14312,7 @@
       </c>
       <c r="AB126" t="inlineStr">
         <is>
-          <t>12:29</t>
+          <t>11:47</t>
         </is>
       </c>
       <c r="AD126" t="b">
@@ -14388,10 +14339,10 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>124756775</v>
+        <v>124753605</v>
       </c>
       <c r="B127" t="n">
-        <v>79891</v>
+        <v>79892</v>
       </c>
       <c r="C127" t="inlineStr">
         <is>
@@ -14404,21 +14355,21 @@
         </is>
       </c>
       <c r="E127" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I127" t="inlineStr"/>
@@ -14428,10 +14379,10 @@
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>452308</v>
+        <v>452408</v>
       </c>
       <c r="R127" t="n">
-        <v>6990943</v>
+        <v>6990952</v>
       </c>
       <c r="S127" t="n">
         <v>10</v>
@@ -14461,19 +14412,9 @@
           <t>2025-05-03</t>
         </is>
       </c>
-      <c r="Z127" t="inlineStr">
-        <is>
-          <t>10:22</t>
-        </is>
-      </c>
       <c r="AA127" t="inlineStr">
         <is>
           <t>2025-05-03</t>
-        </is>
-      </c>
-      <c r="AB127" t="inlineStr">
-        <is>
-          <t>10:22</t>
         </is>
       </c>
       <c r="AD127" t="b">
@@ -14488,22 +14429,22 @@
       <c r="AT127" t="inlineStr"/>
       <c r="AW127" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX127" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY127" t="inlineStr"/>
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>124753609</v>
+        <v>124753632</v>
       </c>
       <c r="B128" t="n">
-        <v>79891</v>
+        <v>98101</v>
       </c>
       <c r="C128" t="inlineStr">
         <is>
@@ -14512,25 +14453,25 @@
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E128" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I128" t="inlineStr"/>
@@ -14540,10 +14481,10 @@
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>452528</v>
+        <v>452455</v>
       </c>
       <c r="R128" t="n">
-        <v>6990710</v>
+        <v>6990942</v>
       </c>
       <c r="S128" t="n">
         <v>10</v>
@@ -14576,6 +14517,11 @@
       <c r="AA128" t="inlineStr">
         <is>
           <t>2025-05-03</t>
+        </is>
+      </c>
+      <c r="AC128" t="inlineStr">
+        <is>
+          <t>Minst 30</t>
         </is>
       </c>
       <c r="AD128" t="b">
@@ -14602,7 +14548,7 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>124753613</v>
+        <v>124756750</v>
       </c>
       <c r="B129" t="n">
         <v>98101</v>
@@ -14635,17 +14581,29 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I129" t="inlineStr"/>
+      <c r="I129" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J129" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K129" t="inlineStr"/>
+      <c r="L129" t="inlineStr"/>
+      <c r="N129" t="inlineStr"/>
       <c r="P129" t="inlineStr">
         <is>
           <t>Häggsåsen N, Jmt</t>
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>452777</v>
+        <v>452617</v>
       </c>
       <c r="R129" t="n">
-        <v>6990299</v>
+        <v>6990549</v>
       </c>
       <c r="S129" t="n">
         <v>10</v>
@@ -14675,14 +14633,19 @@
           <t>2025-05-03</t>
         </is>
       </c>
+      <c r="Z129" t="inlineStr">
+        <is>
+          <t>12:28</t>
+        </is>
+      </c>
       <c r="AA129" t="inlineStr">
         <is>
           <t>2025-05-03</t>
         </is>
       </c>
-      <c r="AC129" t="inlineStr">
-        <is>
-          <t>Minst 100</t>
+      <c r="AB129" t="inlineStr">
+        <is>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AD129" t="b">
@@ -14691,28 +14654,29 @@
       <c r="AE129" t="b">
         <v>0</v>
       </c>
+      <c r="AF129" t="inlineStr"/>
       <c r="AG129" t="b">
         <v>0</v>
       </c>
       <c r="AT129" t="inlineStr"/>
       <c r="AW129" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX129" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY129" t="inlineStr"/>
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>124756731</v>
+        <v>124756738</v>
       </c>
       <c r="B130" t="n">
-        <v>91012</v>
+        <v>74899</v>
       </c>
       <c r="C130" t="inlineStr">
         <is>
@@ -14721,38 +14685,41 @@
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E130" t="n">
-        <v>1202</v>
+        <v>6486</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Skuggnål</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Chaenotheca sphaerocephala</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Nádv.</t>
         </is>
       </c>
       <c r="I130" t="inlineStr"/>
+      <c r="J130" t="inlineStr"/>
+      <c r="K130" t="inlineStr"/>
+      <c r="N130" t="inlineStr"/>
       <c r="P130" t="inlineStr">
         <is>
           <t>Häggsåsen N, Jmt</t>
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>452672</v>
+        <v>452703</v>
       </c>
       <c r="R130" t="n">
-        <v>6990427</v>
+        <v>6990457</v>
       </c>
       <c r="S130" t="n">
         <v>10</v>
@@ -14784,7 +14751,7 @@
       </c>
       <c r="Z130" t="inlineStr">
         <is>
-          <t>14:19</t>
+          <t>14:09</t>
         </is>
       </c>
       <c r="AA130" t="inlineStr">
@@ -14794,7 +14761,7 @@
       </c>
       <c r="AB130" t="inlineStr">
         <is>
-          <t>14:19</t>
+          <t>14:09</t>
         </is>
       </c>
       <c r="AD130" t="b">
@@ -14802,6 +14769,11 @@
       </c>
       <c r="AE130" t="b">
         <v>0</v>
+      </c>
+      <c r="AF130" t="inlineStr">
+        <is>
+          <t>mikroskoperad</t>
+        </is>
       </c>
       <c r="AG130" t="b">
         <v>0</v>
@@ -14821,10 +14793,10 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>124756753</v>
+        <v>124756734</v>
       </c>
       <c r="B131" t="n">
-        <v>91012</v>
+        <v>79891</v>
       </c>
       <c r="C131" t="inlineStr">
         <is>
@@ -14837,21 +14809,21 @@
         </is>
       </c>
       <c r="E131" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I131" t="inlineStr"/>
@@ -14861,10 +14833,10 @@
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>452608</v>
+        <v>452675</v>
       </c>
       <c r="R131" t="n">
-        <v>6990625</v>
+        <v>6990435</v>
       </c>
       <c r="S131" t="n">
         <v>10</v>
@@ -14896,7 +14868,7 @@
       </c>
       <c r="Z131" t="inlineStr">
         <is>
-          <t>12:07</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AA131" t="inlineStr">
@@ -14906,7 +14878,7 @@
       </c>
       <c r="AB131" t="inlineStr">
         <is>
-          <t>12:07</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AD131" t="b">
@@ -14917,6 +14889,21 @@
       </c>
       <c r="AG131" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ131" t="inlineStr">
+        <is>
+          <t>rönn</t>
+        </is>
+      </c>
+      <c r="AK131" t="inlineStr">
+        <is>
+          <t>Sorbus aucuparia</t>
+        </is>
+      </c>
+      <c r="AO131" t="inlineStr">
+        <is>
+          <t>Sorbus aucuparia</t>
+        </is>
       </c>
       <c r="AT131" t="inlineStr"/>
       <c r="AW131" t="inlineStr">
@@ -14933,10 +14920,10 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>124753592</v>
+        <v>124756730</v>
       </c>
       <c r="B132" t="n">
-        <v>57513</v>
+        <v>98101</v>
       </c>
       <c r="C132" t="inlineStr">
         <is>
@@ -14945,38 +14932,50 @@
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E132" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I132" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I132" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="J132" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K132" t="inlineStr"/>
+      <c r="L132" t="inlineStr"/>
+      <c r="N132" t="inlineStr"/>
       <c r="P132" t="inlineStr">
         <is>
           <t>Häggsåsen N, Jmt</t>
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>452396</v>
+        <v>452675</v>
       </c>
       <c r="R132" t="n">
-        <v>6990703</v>
+        <v>6990411</v>
       </c>
       <c r="S132" t="n">
         <v>10</v>
@@ -15006,14 +15005,24 @@
           <t>2025-05-03</t>
         </is>
       </c>
+      <c r="Z132" t="inlineStr">
+        <is>
+          <t>14:20</t>
+        </is>
+      </c>
       <c r="AA132" t="inlineStr">
         <is>
           <t>2025-05-03</t>
         </is>
       </c>
+      <c r="AB132" t="inlineStr">
+        <is>
+          <t>14:20</t>
+        </is>
+      </c>
       <c r="AC132" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Min antal</t>
         </is>
       </c>
       <c r="AD132" t="b">
@@ -15022,25 +15031,26 @@
       <c r="AE132" t="b">
         <v>0</v>
       </c>
+      <c r="AF132" t="inlineStr"/>
       <c r="AG132" t="b">
         <v>0</v>
       </c>
       <c r="AT132" t="inlineStr"/>
       <c r="AW132" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX132" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY132" t="inlineStr"/>
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>124753581</v>
+        <v>124753586</v>
       </c>
       <c r="B133" t="n">
         <v>91012</v>
@@ -15080,10 +15090,10 @@
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>452643</v>
+        <v>452500</v>
       </c>
       <c r="R133" t="n">
-        <v>6990504</v>
+        <v>6990950</v>
       </c>
       <c r="S133" t="n">
         <v>10</v>
@@ -15142,10 +15152,10 @@
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>124753582</v>
+        <v>124753633</v>
       </c>
       <c r="B134" t="n">
-        <v>91012</v>
+        <v>91008</v>
       </c>
       <c r="C134" t="inlineStr">
         <is>
@@ -15158,21 +15168,21 @@
         </is>
       </c>
       <c r="E134" t="n">
-        <v>1202</v>
+        <v>1108</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I134" t="inlineStr"/>
@@ -15182,10 +15192,10 @@
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>452649</v>
+        <v>452772</v>
       </c>
       <c r="R134" t="n">
-        <v>6990621</v>
+        <v>6990321</v>
       </c>
       <c r="S134" t="n">
         <v>10</v>
@@ -15244,10 +15254,10 @@
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>124756768</v>
+        <v>124753639</v>
       </c>
       <c r="B135" t="n">
-        <v>77743</v>
+        <v>78810</v>
       </c>
       <c r="C135" t="inlineStr">
         <is>
@@ -15260,21 +15270,21 @@
         </is>
       </c>
       <c r="E135" t="n">
-        <v>228579</v>
+        <v>6425</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I135" t="inlineStr"/>
@@ -15284,10 +15294,10 @@
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>452357</v>
+        <v>452511</v>
       </c>
       <c r="R135" t="n">
-        <v>6990970</v>
+        <v>6990733</v>
       </c>
       <c r="S135" t="n">
         <v>10</v>
@@ -15317,19 +15327,9 @@
           <t>2025-05-03</t>
         </is>
       </c>
-      <c r="Z135" t="inlineStr">
-        <is>
-          <t>10:52</t>
-        </is>
-      </c>
       <c r="AA135" t="inlineStr">
         <is>
           <t>2025-05-03</t>
-        </is>
-      </c>
-      <c r="AB135" t="inlineStr">
-        <is>
-          <t>10:52</t>
         </is>
       </c>
       <c r="AD135" t="b">
@@ -15344,22 +15344,22 @@
       <c r="AT135" t="inlineStr"/>
       <c r="AW135" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX135" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY135" t="inlineStr"/>
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>124756756</v>
+        <v>124756775</v>
       </c>
       <c r="B136" t="n">
-        <v>78810</v>
+        <v>79891</v>
       </c>
       <c r="C136" t="inlineStr">
         <is>
@@ -15372,21 +15372,21 @@
         </is>
       </c>
       <c r="E136" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I136" t="inlineStr"/>
@@ -15396,10 +15396,10 @@
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>452545</v>
+        <v>452308</v>
       </c>
       <c r="R136" t="n">
-        <v>6990691</v>
+        <v>6990943</v>
       </c>
       <c r="S136" t="n">
         <v>10</v>
@@ -15431,7 +15431,7 @@
       </c>
       <c r="Z136" t="inlineStr">
         <is>
-          <t>11:54</t>
+          <t>10:22</t>
         </is>
       </c>
       <c r="AA136" t="inlineStr">
@@ -15441,7 +15441,7 @@
       </c>
       <c r="AB136" t="inlineStr">
         <is>
-          <t>11:54</t>
+          <t>10:22</t>
         </is>
       </c>
       <c r="AD136" t="b">

--- a/artfynd/A 16493-2025 artfynd.xlsx
+++ b/artfynd/A 16493-2025 artfynd.xlsx
@@ -787,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124705584</v>
+        <v>124695367</v>
       </c>
       <c r="B3" t="n">
-        <v>91030</v>
+        <v>82597</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -803,34 +803,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5432</v>
+        <v>1312</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Häggsåsen, Häggsåsen, Jmt</t>
+          <t>Tjärnflon, Tjärnflon, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>452865</v>
+        <v>452617</v>
       </c>
       <c r="R3" t="n">
-        <v>6990382</v>
+        <v>6990540</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -889,7 +889,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124721401</v>
+        <v>124689574</v>
       </c>
       <c r="B4" t="n">
         <v>57513</v>
@@ -934,10 +934,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>452415</v>
+        <v>452326</v>
       </c>
       <c r="R4" t="n">
-        <v>6990714</v>
+        <v>6990987</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1001,10 +1001,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124695367</v>
+        <v>124694574</v>
       </c>
       <c r="B5" t="n">
-        <v>82597</v>
+        <v>57513</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1017,34 +1017,39 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1312</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Tjärnflon, Tjärnflon, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>452617</v>
+        <v>452630</v>
       </c>
       <c r="R5" t="n">
-        <v>6990540</v>
+        <v>6990651</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1077,6 +1082,11 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-05-02</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1103,10 +1113,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124689574</v>
+        <v>124705584</v>
       </c>
       <c r="B6" t="n">
-        <v>57513</v>
+        <v>91030</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1119,39 +1129,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Tjärnflon, Tjärnflon, Jmt</t>
+          <t>Häggsåsen, Häggsåsen, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>452326</v>
+        <v>452865</v>
       </c>
       <c r="R6" t="n">
-        <v>6990987</v>
+        <v>6990382</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1184,11 +1189,6 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-05-02</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1215,7 +1215,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124694574</v>
+        <v>124721401</v>
       </c>
       <c r="B7" t="n">
         <v>57513</v>
@@ -1251,7 +1251,7 @@
       <c r="I7" t="inlineStr"/>
       <c r="M7" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1260,10 +1260,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>452630</v>
+        <v>452415</v>
       </c>
       <c r="R7" t="n">
-        <v>6990651</v>
+        <v>6990714</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1300,7 +1300,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Färska ringhack på tall</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1327,10 +1327,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124691533</v>
+        <v>124704478</v>
       </c>
       <c r="B8" t="n">
-        <v>79891</v>
+        <v>57513</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1343,34 +1343,39 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Tjärnflon, Tjärnflon, Jmt</t>
+          <t>Häggsåsen, Häggsåsen, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>452427</v>
+        <v>452836</v>
       </c>
       <c r="R8" t="n">
-        <v>6990925</v>
+        <v>6990321</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1403,6 +1408,11 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-05-02</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1429,10 +1439,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124704478</v>
+        <v>124691533</v>
       </c>
       <c r="B9" t="n">
-        <v>57513</v>
+        <v>79891</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1445,39 +1455,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Häggsåsen, Häggsåsen, Jmt</t>
+          <t>Tjärnflon, Tjärnflon, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>452836</v>
+        <v>452427</v>
       </c>
       <c r="R9" t="n">
-        <v>6990321</v>
+        <v>6990925</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1510,11 +1515,6 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-05-02</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -2372,10 +2372,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>124689645</v>
+        <v>124691814</v>
       </c>
       <c r="B18" t="n">
-        <v>91012</v>
+        <v>56714</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2388,34 +2388,43 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1202</v>
+        <v>102612</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>förbiflygande</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Tjärnflon, Tjärnflon, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>452311</v>
+        <v>452489</v>
       </c>
       <c r="R18" t="n">
-        <v>6990960</v>
+        <v>6990896</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2474,10 +2483,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>124691814</v>
+        <v>124689645</v>
       </c>
       <c r="B19" t="n">
-        <v>56714</v>
+        <v>91012</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2490,43 +2499,34 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>102612</v>
+        <v>1202</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>förbiflygande</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
           <t>Tjärnflon, Tjärnflon, Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>452489</v>
+        <v>452311</v>
       </c>
       <c r="R19" t="n">
-        <v>6990896</v>
+        <v>6990960</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -3007,10 +3007,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>124721354</v>
+        <v>124704726</v>
       </c>
       <c r="B24" t="n">
-        <v>57513</v>
+        <v>91012</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3023,39 +3023,34 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Tjärnflon, Tjärnflon, Jmt</t>
+          <t>Häggsåsen, Häggsåsen, Jmt</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>452514</v>
+        <v>452828</v>
       </c>
       <c r="R24" t="n">
-        <v>6990587</v>
+        <v>6990384</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3088,11 +3083,6 @@
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-05-02</t>
-        </is>
-      </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3119,7 +3109,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>124704726</v>
+        <v>124704608</v>
       </c>
       <c r="B25" t="n">
         <v>91012</v>
@@ -3159,10 +3149,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>452828</v>
+        <v>452839</v>
       </c>
       <c r="R25" t="n">
-        <v>6990384</v>
+        <v>6990352</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3221,10 +3211,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>124704608</v>
+        <v>124721354</v>
       </c>
       <c r="B26" t="n">
-        <v>91012</v>
+        <v>57513</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3237,34 +3227,39 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Häggsåsen, Häggsåsen, Jmt</t>
+          <t>Tjärnflon, Tjärnflon, Jmt</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>452839</v>
+        <v>452514</v>
       </c>
       <c r="R26" t="n">
-        <v>6990352</v>
+        <v>6990587</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3297,6 +3292,11 @@
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-05-02</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3323,10 +3323,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>124706585</v>
+        <v>124703646</v>
       </c>
       <c r="B27" t="n">
-        <v>77743</v>
+        <v>91008</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3339,21 +3339,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>228579</v>
+        <v>1108</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3363,10 +3363,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>452913</v>
+        <v>452785</v>
       </c>
       <c r="R27" t="n">
-        <v>6990390</v>
+        <v>6990307</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3425,10 +3425,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>124703646</v>
+        <v>124706585</v>
       </c>
       <c r="B28" t="n">
-        <v>91008</v>
+        <v>77743</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3441,21 +3441,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1108</v>
+        <v>228579</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3465,10 +3465,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>452785</v>
+        <v>452913</v>
       </c>
       <c r="R28" t="n">
-        <v>6990307</v>
+        <v>6990390</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3639,10 +3639,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>124705813</v>
+        <v>124695424</v>
       </c>
       <c r="B30" t="n">
-        <v>57513</v>
+        <v>91012</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3655,39 +3655,34 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Häggsåsen, Häggsåsen, Jmt</t>
+          <t>Tjärnflon, Tjärnflon, Jmt</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>452865</v>
+        <v>452642</v>
       </c>
       <c r="R30" t="n">
-        <v>6990385</v>
+        <v>6990548</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3720,11 +3715,6 @@
       <c r="AA30" t="inlineStr">
         <is>
           <t>2025-05-02</t>
-        </is>
-      </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>Möjligt gammalt bo 3m upp i granstubbe med granticka på</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3751,10 +3741,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>124695424</v>
+        <v>124705813</v>
       </c>
       <c r="B31" t="n">
-        <v>91012</v>
+        <v>57513</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3767,34 +3757,39 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Tjärnflon, Tjärnflon, Jmt</t>
+          <t>Häggsåsen, Häggsåsen, Jmt</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>452642</v>
+        <v>452865</v>
       </c>
       <c r="R31" t="n">
-        <v>6990548</v>
+        <v>6990385</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3827,6 +3822,11 @@
       <c r="AA31" t="inlineStr">
         <is>
           <t>2025-05-02</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>Möjligt gammalt bo 3m upp i granstubbe med granticka på</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4173,10 +4173,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>124703242</v>
+        <v>124702770</v>
       </c>
       <c r="B35" t="n">
-        <v>91299</v>
+        <v>79891</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4189,21 +4189,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>658</v>
+        <v>6458</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4213,10 +4213,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>452760</v>
+        <v>452731</v>
       </c>
       <c r="R35" t="n">
-        <v>6990252</v>
+        <v>6990355</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4275,10 +4275,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>124702770</v>
+        <v>124703242</v>
       </c>
       <c r="B36" t="n">
-        <v>79891</v>
+        <v>91299</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4291,21 +4291,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6458</v>
+        <v>658</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4315,10 +4315,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>452731</v>
+        <v>452760</v>
       </c>
       <c r="R36" t="n">
-        <v>6990355</v>
+        <v>6990252</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4377,10 +4377,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>124689335</v>
+        <v>124689655</v>
       </c>
       <c r="B37" t="n">
-        <v>57513</v>
+        <v>91299</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4393,39 +4393,34 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>100109</v>
+        <v>658</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
-      <c r="M37" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P37" t="inlineStr">
         <is>
           <t>Tjärnflon, Tjärnflon, Jmt</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>452249</v>
+        <v>452312</v>
       </c>
       <c r="R37" t="n">
-        <v>6990921</v>
+        <v>6990961</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4458,11 +4453,6 @@
       <c r="AA37" t="inlineStr">
         <is>
           <t>2025-05-02</t>
-        </is>
-      </c>
-      <c r="AC37" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4601,10 +4591,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>124689655</v>
+        <v>124689335</v>
       </c>
       <c r="B39" t="n">
-        <v>91299</v>
+        <v>57513</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4617,34 +4607,39 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>658</v>
+        <v>100109</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P39" t="inlineStr">
         <is>
           <t>Tjärnflon, Tjärnflon, Jmt</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>452312</v>
+        <v>452249</v>
       </c>
       <c r="R39" t="n">
-        <v>6990961</v>
+        <v>6990921</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4677,6 +4672,11 @@
       <c r="AA39" t="inlineStr">
         <is>
           <t>2025-05-02</t>
+        </is>
+      </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5009,10 +5009,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>124756728</v>
+        <v>124756724</v>
       </c>
       <c r="B43" t="n">
-        <v>79891</v>
+        <v>91012</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5025,21 +5025,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5049,10 +5049,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>452745</v>
+        <v>452793</v>
       </c>
       <c r="R43" t="n">
-        <v>6990359</v>
+        <v>6990262</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5084,7 +5084,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:44</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5094,7 +5094,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:44</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5105,21 +5105,6 @@
       </c>
       <c r="AG43" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ43" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK43" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AO43" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
       </c>
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
@@ -5136,7 +5121,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>124756724</v>
+        <v>124756759</v>
       </c>
       <c r="B44" t="n">
         <v>91012</v>
@@ -5176,10 +5161,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>452793</v>
+        <v>452509</v>
       </c>
       <c r="R44" t="n">
-        <v>6990262</v>
+        <v>6990778</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5211,7 +5196,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>14:44</t>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5221,7 +5206,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>14:44</t>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5248,10 +5233,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>124756759</v>
+        <v>124753620</v>
       </c>
       <c r="B45" t="n">
-        <v>91012</v>
+        <v>98101</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5260,25 +5245,25 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5288,10 +5273,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>452509</v>
+        <v>452554</v>
       </c>
       <c r="R45" t="n">
-        <v>6990778</v>
+        <v>6990657</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5321,19 +5306,14 @@
           <t>2025-05-03</t>
         </is>
       </c>
-      <c r="Z45" t="inlineStr">
-        <is>
-          <t>11:39</t>
-        </is>
-      </c>
       <c r="AA45" t="inlineStr">
         <is>
           <t>2025-05-03</t>
         </is>
       </c>
-      <c r="AB45" t="inlineStr">
-        <is>
-          <t>11:39</t>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>Minst 30</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5348,22 +5328,22 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>124753620</v>
+        <v>124756728</v>
       </c>
       <c r="B46" t="n">
-        <v>98101</v>
+        <v>79891</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5372,25 +5352,25 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5400,10 +5380,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>452554</v>
+        <v>452745</v>
       </c>
       <c r="R46" t="n">
-        <v>6990657</v>
+        <v>6990359</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5433,14 +5413,19 @@
           <t>2025-05-03</t>
         </is>
       </c>
+      <c r="Z46" t="inlineStr">
+        <is>
+          <t>14:30</t>
+        </is>
+      </c>
       <c r="AA46" t="inlineStr">
         <is>
           <t>2025-05-03</t>
         </is>
       </c>
-      <c r="AC46" t="inlineStr">
-        <is>
-          <t>Minst 30</t>
+      <c r="AB46" t="inlineStr">
+        <is>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5451,16 +5436,31 @@
       </c>
       <c r="AG46" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ46" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK46" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO46" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
       </c>
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
@@ -7803,10 +7803,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>124753592</v>
+        <v>124756741</v>
       </c>
       <c r="B68" t="n">
-        <v>57513</v>
+        <v>79851</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -7815,25 +7815,25 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>100109</v>
+        <v>229497</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7843,10 +7843,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>452396</v>
+        <v>452682</v>
       </c>
       <c r="R68" t="n">
-        <v>6990703</v>
+        <v>6990476</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7876,14 +7876,19 @@
           <t>2025-05-03</t>
         </is>
       </c>
+      <c r="Z68" t="inlineStr">
+        <is>
+          <t>13:54</t>
+        </is>
+      </c>
       <c r="AA68" t="inlineStr">
         <is>
           <t>2025-05-03</t>
         </is>
       </c>
-      <c r="AC68" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
+      <c r="AB68" t="inlineStr">
+        <is>
+          <t>13:54</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -7894,26 +7899,41 @@
       </c>
       <c r="AG68" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ68" t="inlineStr">
+        <is>
+          <t>rönn</t>
+        </is>
+      </c>
+      <c r="AK68" t="inlineStr">
+        <is>
+          <t>Sorbus aucuparia</t>
+        </is>
+      </c>
+      <c r="AO68" t="inlineStr">
+        <is>
+          <t>Sorbus aucuparia</t>
+        </is>
       </c>
       <c r="AT68" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>124756741</v>
+        <v>124753592</v>
       </c>
       <c r="B69" t="n">
-        <v>79851</v>
+        <v>57513</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -7922,25 +7942,25 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>229497</v>
+        <v>100109</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7950,10 +7970,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>452682</v>
+        <v>452396</v>
       </c>
       <c r="R69" t="n">
-        <v>6990476</v>
+        <v>6990703</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7983,19 +8003,14 @@
           <t>2025-05-03</t>
         </is>
       </c>
-      <c r="Z69" t="inlineStr">
-        <is>
-          <t>13:54</t>
-        </is>
-      </c>
       <c r="AA69" t="inlineStr">
         <is>
           <t>2025-05-03</t>
         </is>
       </c>
-      <c r="AB69" t="inlineStr">
-        <is>
-          <t>13:54</t>
+      <c r="AC69" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -8006,41 +8021,26 @@
       </c>
       <c r="AG69" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ69" t="inlineStr">
-        <is>
-          <t>rönn</t>
-        </is>
-      </c>
-      <c r="AK69" t="inlineStr">
-        <is>
-          <t>Sorbus aucuparia</t>
-        </is>
-      </c>
-      <c r="AO69" t="inlineStr">
-        <is>
-          <t>Sorbus aucuparia</t>
-        </is>
       </c>
       <c r="AT69" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX69" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>124756758</v>
+        <v>124753623</v>
       </c>
       <c r="B70" t="n">
-        <v>90962</v>
+        <v>98101</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -8049,25 +8049,25 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>112</v>
+        <v>220787</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Stjärntagging</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Asterodon ferruginosus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>Pat.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -8077,10 +8077,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>452509</v>
+        <v>452510</v>
       </c>
       <c r="R70" t="n">
-        <v>6990778</v>
+        <v>6990873</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -8110,19 +8110,14 @@
           <t>2025-05-03</t>
         </is>
       </c>
-      <c r="Z70" t="inlineStr">
-        <is>
-          <t>11:40</t>
-        </is>
-      </c>
       <c r="AA70" t="inlineStr">
         <is>
           <t>2025-05-03</t>
         </is>
       </c>
-      <c r="AB70" t="inlineStr">
-        <is>
-          <t>11:40</t>
+      <c r="AC70" t="inlineStr">
+        <is>
+          <t>Minst 50</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8137,19 +8132,19 @@
       <c r="AT70" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>124753623</v>
+        <v>124756777</v>
       </c>
       <c r="B71" t="n">
         <v>98101</v>
@@ -8182,17 +8177,29 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I71" t="inlineStr"/>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J71" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K71" t="inlineStr"/>
+      <c r="L71" t="inlineStr"/>
+      <c r="N71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
           <t>Häggsåsen N, Jmt</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>452510</v>
+        <v>452146</v>
       </c>
       <c r="R71" t="n">
-        <v>6990873</v>
+        <v>6990839</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -8222,14 +8229,19 @@
           <t>2025-05-03</t>
         </is>
       </c>
+      <c r="Z71" t="inlineStr">
+        <is>
+          <t>10:06</t>
+        </is>
+      </c>
       <c r="AA71" t="inlineStr">
         <is>
           <t>2025-05-03</t>
         </is>
       </c>
-      <c r="AC71" t="inlineStr">
-        <is>
-          <t>Minst 50</t>
+      <c r="AB71" t="inlineStr">
+        <is>
+          <t>10:06</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -8238,28 +8250,29 @@
       <c r="AE71" t="b">
         <v>0</v>
       </c>
+      <c r="AF71" t="inlineStr"/>
       <c r="AG71" t="b">
         <v>0</v>
       </c>
       <c r="AT71" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX71" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>124756777</v>
+        <v>124756758</v>
       </c>
       <c r="B72" t="n">
-        <v>98101</v>
+        <v>90962</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -8268,50 +8281,38 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>220787</v>
+        <v>112</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Stjärntagging</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Asterodon ferruginosus</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I72" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J72" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K72" t="inlineStr"/>
-      <c r="L72" t="inlineStr"/>
-      <c r="N72" t="inlineStr"/>
+          <t>Pat.</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
           <t>Häggsåsen N, Jmt</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>452146</v>
+        <v>452509</v>
       </c>
       <c r="R72" t="n">
-        <v>6990839</v>
+        <v>6990778</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8343,7 +8344,7 @@
       </c>
       <c r="Z72" t="inlineStr">
         <is>
-          <t>10:06</t>
+          <t>11:40</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
@@ -8353,7 +8354,7 @@
       </c>
       <c r="AB72" t="inlineStr">
         <is>
-          <t>10:06</t>
+          <t>11:40</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8362,7 +8363,6 @@
       <c r="AE72" t="b">
         <v>0</v>
       </c>
-      <c r="AF72" t="inlineStr"/>
       <c r="AG72" t="b">
         <v>0</v>
       </c>
@@ -11000,10 +11000,10 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>124753576</v>
+        <v>124756754</v>
       </c>
       <c r="B97" t="n">
-        <v>91012</v>
+        <v>78810</v>
       </c>
       <c r="C97" t="inlineStr">
         <is>
@@ -11016,21 +11016,21 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
@@ -11040,10 +11040,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>452837</v>
+        <v>452544</v>
       </c>
       <c r="R97" t="n">
-        <v>6990384</v>
+        <v>6990646</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -11073,9 +11073,19 @@
           <t>2025-05-03</t>
         </is>
       </c>
+      <c r="Z97" t="inlineStr">
+        <is>
+          <t>12:04</t>
+        </is>
+      </c>
       <c r="AA97" t="inlineStr">
         <is>
           <t>2025-05-03</t>
+        </is>
+      </c>
+      <c r="AB97" t="inlineStr">
+        <is>
+          <t>12:04</t>
         </is>
       </c>
       <c r="AD97" t="b">
@@ -11090,22 +11100,22 @@
       <c r="AT97" t="inlineStr"/>
       <c r="AW97" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX97" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY97" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>124756754</v>
+        <v>124753576</v>
       </c>
       <c r="B98" t="n">
-        <v>78810</v>
+        <v>91012</v>
       </c>
       <c r="C98" t="inlineStr">
         <is>
@@ -11118,21 +11128,21 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
@@ -11142,10 +11152,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>452544</v>
+        <v>452837</v>
       </c>
       <c r="R98" t="n">
-        <v>6990646</v>
+        <v>6990384</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -11175,19 +11185,9 @@
           <t>2025-05-03</t>
         </is>
       </c>
-      <c r="Z98" t="inlineStr">
-        <is>
-          <t>12:04</t>
-        </is>
-      </c>
       <c r="AA98" t="inlineStr">
         <is>
           <t>2025-05-03</t>
-        </is>
-      </c>
-      <c r="AB98" t="inlineStr">
-        <is>
-          <t>12:04</t>
         </is>
       </c>
       <c r="AD98" t="b">
@@ -11202,12 +11202,12 @@
       <c r="AT98" t="inlineStr"/>
       <c r="AW98" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX98" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY98" t="inlineStr"/>
@@ -11321,10 +11321,10 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>124753631</v>
+        <v>124756748</v>
       </c>
       <c r="B100" t="n">
-        <v>98101</v>
+        <v>78810</v>
       </c>
       <c r="C100" t="inlineStr">
         <is>
@@ -11333,25 +11333,25 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E100" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
@@ -11361,10 +11361,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>452526</v>
+        <v>452609</v>
       </c>
       <c r="R100" t="n">
-        <v>6990943</v>
+        <v>6990543</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -11394,14 +11394,19 @@
           <t>2025-05-03</t>
         </is>
       </c>
+      <c r="Z100" t="inlineStr">
+        <is>
+          <t>12:29</t>
+        </is>
+      </c>
       <c r="AA100" t="inlineStr">
         <is>
           <t>2025-05-03</t>
         </is>
       </c>
-      <c r="AC100" t="inlineStr">
-        <is>
-          <t>Minst 20</t>
+      <c r="AB100" t="inlineStr">
+        <is>
+          <t>12:29</t>
         </is>
       </c>
       <c r="AD100" t="b">
@@ -11416,19 +11421,19 @@
       <c r="AT100" t="inlineStr"/>
       <c r="AW100" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX100" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY100" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>124753625</v>
+        <v>124753631</v>
       </c>
       <c r="B101" t="n">
         <v>98101</v>
@@ -11468,10 +11473,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>452550</v>
+        <v>452526</v>
       </c>
       <c r="R101" t="n">
-        <v>6990907</v>
+        <v>6990943</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -11508,7 +11513,7 @@
       </c>
       <c r="AC101" t="inlineStr">
         <is>
-          <t>Minst 50</t>
+          <t>Minst 20</t>
         </is>
       </c>
       <c r="AD101" t="b">
@@ -11535,10 +11540,10 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>124756748</v>
+        <v>124753625</v>
       </c>
       <c r="B102" t="n">
-        <v>78810</v>
+        <v>98101</v>
       </c>
       <c r="C102" t="inlineStr">
         <is>
@@ -11547,25 +11552,25 @@
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E102" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
@@ -11575,10 +11580,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>452609</v>
+        <v>452550</v>
       </c>
       <c r="R102" t="n">
-        <v>6990543</v>
+        <v>6990907</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -11608,19 +11613,14 @@
           <t>2025-05-03</t>
         </is>
       </c>
-      <c r="Z102" t="inlineStr">
-        <is>
-          <t>12:29</t>
-        </is>
-      </c>
       <c r="AA102" t="inlineStr">
         <is>
           <t>2025-05-03</t>
         </is>
       </c>
-      <c r="AB102" t="inlineStr">
-        <is>
-          <t>12:29</t>
+      <c r="AC102" t="inlineStr">
+        <is>
+          <t>Minst 50</t>
         </is>
       </c>
       <c r="AD102" t="b">
@@ -11635,12 +11635,12 @@
       <c r="AT102" t="inlineStr"/>
       <c r="AW102" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX102" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY102" t="inlineStr"/>
@@ -12613,10 +12613,10 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>124753581</v>
+        <v>124756764</v>
       </c>
       <c r="B112" t="n">
-        <v>91012</v>
+        <v>78810</v>
       </c>
       <c r="C112" t="inlineStr">
         <is>
@@ -12629,21 +12629,21 @@
         </is>
       </c>
       <c r="E112" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I112" t="inlineStr"/>
@@ -12653,10 +12653,10 @@
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>452643</v>
+        <v>452462</v>
       </c>
       <c r="R112" t="n">
-        <v>6990504</v>
+        <v>6990915</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -12686,9 +12686,19 @@
           <t>2025-05-03</t>
         </is>
       </c>
+      <c r="Z112" t="inlineStr">
+        <is>
+          <t>11:11</t>
+        </is>
+      </c>
       <c r="AA112" t="inlineStr">
         <is>
           <t>2025-05-03</t>
+        </is>
+      </c>
+      <c r="AB112" t="inlineStr">
+        <is>
+          <t>11:11</t>
         </is>
       </c>
       <c r="AD112" t="b">
@@ -12703,22 +12713,22 @@
       <c r="AT112" t="inlineStr"/>
       <c r="AW112" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX112" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY112" t="inlineStr"/>
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>124756764</v>
+        <v>124756727</v>
       </c>
       <c r="B113" t="n">
-        <v>78810</v>
+        <v>79920</v>
       </c>
       <c r="C113" t="inlineStr">
         <is>
@@ -12727,25 +12737,25 @@
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E113" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
@@ -12755,10 +12765,10 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>452462</v>
+        <v>452745</v>
       </c>
       <c r="R113" t="n">
-        <v>6990915</v>
+        <v>6990359</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -12790,7 +12800,7 @@
       </c>
       <c r="Z113" t="inlineStr">
         <is>
-          <t>11:11</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AA113" t="inlineStr">
@@ -12800,7 +12810,7 @@
       </c>
       <c r="AB113" t="inlineStr">
         <is>
-          <t>11:11</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AD113" t="b">
@@ -12827,10 +12837,10 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>124756727</v>
+        <v>124756774</v>
       </c>
       <c r="B114" t="n">
-        <v>79920</v>
+        <v>98101</v>
       </c>
       <c r="C114" t="inlineStr">
         <is>
@@ -12839,38 +12849,50 @@
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E114" t="n">
-        <v>6462</v>
+        <v>220787</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
-        </is>
-      </c>
-      <c r="I114" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I114" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J114" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K114" t="inlineStr"/>
+      <c r="L114" t="inlineStr"/>
+      <c r="N114" t="inlineStr"/>
       <c r="P114" t="inlineStr">
         <is>
           <t>Häggsåsen N, Jmt</t>
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>452745</v>
+        <v>452308</v>
       </c>
       <c r="R114" t="n">
-        <v>6990359</v>
+        <v>6990943</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -12902,7 +12924,7 @@
       </c>
       <c r="Z114" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>10:23</t>
         </is>
       </c>
       <c r="AA114" t="inlineStr">
@@ -12912,7 +12934,7 @@
       </c>
       <c r="AB114" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>10:23</t>
         </is>
       </c>
       <c r="AD114" t="b">
@@ -12921,6 +12943,7 @@
       <c r="AE114" t="b">
         <v>0</v>
       </c>
+      <c r="AF114" t="inlineStr"/>
       <c r="AG114" t="b">
         <v>0</v>
       </c>
@@ -12939,10 +12962,10 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>124756774</v>
+        <v>124753581</v>
       </c>
       <c r="B115" t="n">
-        <v>98101</v>
+        <v>91012</v>
       </c>
       <c r="C115" t="inlineStr">
         <is>
@@ -12951,50 +12974,38 @@
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E115" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I115" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="J115" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K115" t="inlineStr"/>
-      <c r="L115" t="inlineStr"/>
-      <c r="N115" t="inlineStr"/>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I115" t="inlineStr"/>
       <c r="P115" t="inlineStr">
         <is>
           <t>Häggsåsen N, Jmt</t>
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>452308</v>
+        <v>452643</v>
       </c>
       <c r="R115" t="n">
-        <v>6990943</v>
+        <v>6990504</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -13024,50 +13035,39 @@
           <t>2025-05-03</t>
         </is>
       </c>
-      <c r="Z115" t="inlineStr">
-        <is>
-          <t>10:23</t>
-        </is>
-      </c>
       <c r="AA115" t="inlineStr">
         <is>
           <t>2025-05-03</t>
         </is>
       </c>
-      <c r="AB115" t="inlineStr">
-        <is>
-          <t>10:23</t>
-        </is>
-      </c>
       <c r="AD115" t="b">
         <v>0</v>
       </c>
       <c r="AE115" t="b">
         <v>0</v>
       </c>
-      <c r="AF115" t="inlineStr"/>
       <c r="AG115" t="b">
         <v>0</v>
       </c>
       <c r="AT115" t="inlineStr"/>
       <c r="AW115" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX115" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY115" t="inlineStr"/>
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>124753615</v>
+        <v>124756743</v>
       </c>
       <c r="B116" t="n">
-        <v>98101</v>
+        <v>79891</v>
       </c>
       <c r="C116" t="inlineStr">
         <is>
@@ -13076,25 +13076,25 @@
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E116" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
@@ -13104,10 +13104,10 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>452734</v>
+        <v>452682</v>
       </c>
       <c r="R116" t="n">
-        <v>6990355</v>
+        <v>6990476</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -13137,14 +13137,19 @@
           <t>2025-05-03</t>
         </is>
       </c>
+      <c r="Z116" t="inlineStr">
+        <is>
+          <t>13:53</t>
+        </is>
+      </c>
       <c r="AA116" t="inlineStr">
         <is>
           <t>2025-05-03</t>
         </is>
       </c>
-      <c r="AC116" t="inlineStr">
-        <is>
-          <t>Minst 30</t>
+      <c r="AB116" t="inlineStr">
+        <is>
+          <t>13:53</t>
         </is>
       </c>
       <c r="AD116" t="b">
@@ -13155,26 +13160,41 @@
       </c>
       <c r="AG116" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ116" t="inlineStr">
+        <is>
+          <t>rönn</t>
+        </is>
+      </c>
+      <c r="AK116" t="inlineStr">
+        <is>
+          <t>Sorbus aucuparia</t>
+        </is>
+      </c>
+      <c r="AO116" t="inlineStr">
+        <is>
+          <t>Sorbus aucuparia</t>
+        </is>
       </c>
       <c r="AT116" t="inlineStr"/>
       <c r="AW116" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX116" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY116" t="inlineStr"/>
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>124756743</v>
+        <v>124753615</v>
       </c>
       <c r="B117" t="n">
-        <v>79891</v>
+        <v>98101</v>
       </c>
       <c r="C117" t="inlineStr">
         <is>
@@ -13183,25 +13203,25 @@
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E117" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
@@ -13211,10 +13231,10 @@
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>452682</v>
+        <v>452734</v>
       </c>
       <c r="R117" t="n">
-        <v>6990476</v>
+        <v>6990355</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>
@@ -13244,19 +13264,14 @@
           <t>2025-05-03</t>
         </is>
       </c>
-      <c r="Z117" t="inlineStr">
-        <is>
-          <t>13:53</t>
-        </is>
-      </c>
       <c r="AA117" t="inlineStr">
         <is>
           <t>2025-05-03</t>
         </is>
       </c>
-      <c r="AB117" t="inlineStr">
-        <is>
-          <t>13:53</t>
+      <c r="AC117" t="inlineStr">
+        <is>
+          <t>Minst 30</t>
         </is>
       </c>
       <c r="AD117" t="b">
@@ -13267,41 +13282,26 @@
       </c>
       <c r="AG117" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ117" t="inlineStr">
-        <is>
-          <t>rönn</t>
-        </is>
-      </c>
-      <c r="AK117" t="inlineStr">
-        <is>
-          <t>Sorbus aucuparia</t>
-        </is>
-      </c>
-      <c r="AO117" t="inlineStr">
-        <is>
-          <t>Sorbus aucuparia</t>
-        </is>
       </c>
       <c r="AT117" t="inlineStr"/>
       <c r="AW117" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX117" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY117" t="inlineStr"/>
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>124756746</v>
+        <v>124753627</v>
       </c>
       <c r="B118" t="n">
-        <v>91012</v>
+        <v>98101</v>
       </c>
       <c r="C118" t="inlineStr">
         <is>
@@ -13310,25 +13310,25 @@
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E118" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
@@ -13338,10 +13338,10 @@
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>452639</v>
+        <v>452608</v>
       </c>
       <c r="R118" t="n">
-        <v>6990537</v>
+        <v>6990927</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -13371,19 +13371,14 @@
           <t>2025-05-03</t>
         </is>
       </c>
-      <c r="Z118" t="inlineStr">
-        <is>
-          <t>13:36</t>
-        </is>
-      </c>
       <c r="AA118" t="inlineStr">
         <is>
           <t>2025-05-03</t>
         </is>
       </c>
-      <c r="AB118" t="inlineStr">
-        <is>
-          <t>13:36</t>
+      <c r="AC118" t="inlineStr">
+        <is>
+          <t>Minst 50</t>
         </is>
       </c>
       <c r="AD118" t="b">
@@ -13398,22 +13393,22 @@
       <c r="AT118" t="inlineStr"/>
       <c r="AW118" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX118" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY118" t="inlineStr"/>
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>124756721</v>
+        <v>124753616</v>
       </c>
       <c r="B119" t="n">
-        <v>79891</v>
+        <v>98101</v>
       </c>
       <c r="C119" t="inlineStr">
         <is>
@@ -13422,25 +13417,25 @@
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E119" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I119" t="inlineStr"/>
@@ -13450,10 +13445,10 @@
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>452823</v>
+        <v>452742</v>
       </c>
       <c r="R119" t="n">
-        <v>6990261</v>
+        <v>6990393</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -13483,19 +13478,14 @@
           <t>2025-05-03</t>
         </is>
       </c>
-      <c r="Z119" t="inlineStr">
-        <is>
-          <t>14:51</t>
-        </is>
-      </c>
       <c r="AA119" t="inlineStr">
         <is>
           <t>2025-05-03</t>
         </is>
       </c>
-      <c r="AB119" t="inlineStr">
-        <is>
-          <t>14:51</t>
+      <c r="AC119" t="inlineStr">
+        <is>
+          <t>Minst 60</t>
         </is>
       </c>
       <c r="AD119" t="b">
@@ -13506,41 +13496,26 @@
       </c>
       <c r="AG119" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ119" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK119" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AO119" t="inlineStr">
-        <is>
-          <t>Omkullfallen grov stam # Salix caprea</t>
-        </is>
       </c>
       <c r="AT119" t="inlineStr"/>
       <c r="AW119" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX119" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY119" t="inlineStr"/>
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>124756766</v>
+        <v>124756763</v>
       </c>
       <c r="B120" t="n">
-        <v>79891</v>
+        <v>98101</v>
       </c>
       <c r="C120" t="inlineStr">
         <is>
@@ -13549,38 +13524,50 @@
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E120" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I120" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I120" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J120" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K120" t="inlineStr"/>
+      <c r="L120" t="inlineStr"/>
+      <c r="N120" t="inlineStr"/>
       <c r="P120" t="inlineStr">
         <is>
           <t>Häggsåsen N, Jmt</t>
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>452396</v>
+        <v>452478</v>
       </c>
       <c r="R120" t="n">
-        <v>6990981</v>
+        <v>6990887</v>
       </c>
       <c r="S120" t="n">
         <v>10</v>
@@ -13612,7 +13599,7 @@
       </c>
       <c r="Z120" t="inlineStr">
         <is>
-          <t>10:58</t>
+          <t>11:18</t>
         </is>
       </c>
       <c r="AA120" t="inlineStr">
@@ -13622,7 +13609,7 @@
       </c>
       <c r="AB120" t="inlineStr">
         <is>
-          <t>10:58</t>
+          <t>11:18</t>
         </is>
       </c>
       <c r="AD120" t="b">
@@ -13631,6 +13618,7 @@
       <c r="AE120" t="b">
         <v>0</v>
       </c>
+      <c r="AF120" t="inlineStr"/>
       <c r="AG120" t="b">
         <v>0</v>
       </c>
@@ -13649,10 +13637,10 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>124753627</v>
+        <v>124756746</v>
       </c>
       <c r="B121" t="n">
-        <v>98101</v>
+        <v>91012</v>
       </c>
       <c r="C121" t="inlineStr">
         <is>
@@ -13661,25 +13649,25 @@
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E121" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
@@ -13689,10 +13677,10 @@
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>452608</v>
+        <v>452639</v>
       </c>
       <c r="R121" t="n">
-        <v>6990927</v>
+        <v>6990537</v>
       </c>
       <c r="S121" t="n">
         <v>10</v>
@@ -13722,14 +13710,19 @@
           <t>2025-05-03</t>
         </is>
       </c>
+      <c r="Z121" t="inlineStr">
+        <is>
+          <t>13:36</t>
+        </is>
+      </c>
       <c r="AA121" t="inlineStr">
         <is>
           <t>2025-05-03</t>
         </is>
       </c>
-      <c r="AC121" t="inlineStr">
-        <is>
-          <t>Minst 50</t>
+      <c r="AB121" t="inlineStr">
+        <is>
+          <t>13:36</t>
         </is>
       </c>
       <c r="AD121" t="b">
@@ -13744,22 +13737,22 @@
       <c r="AT121" t="inlineStr"/>
       <c r="AW121" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX121" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY121" t="inlineStr"/>
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>124753616</v>
+        <v>124756721</v>
       </c>
       <c r="B122" t="n">
-        <v>98101</v>
+        <v>79891</v>
       </c>
       <c r="C122" t="inlineStr">
         <is>
@@ -13768,25 +13761,25 @@
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E122" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I122" t="inlineStr"/>
@@ -13796,10 +13789,10 @@
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>452742</v>
+        <v>452823</v>
       </c>
       <c r="R122" t="n">
-        <v>6990393</v>
+        <v>6990261</v>
       </c>
       <c r="S122" t="n">
         <v>10</v>
@@ -13829,14 +13822,19 @@
           <t>2025-05-03</t>
         </is>
       </c>
+      <c r="Z122" t="inlineStr">
+        <is>
+          <t>14:51</t>
+        </is>
+      </c>
       <c r="AA122" t="inlineStr">
         <is>
           <t>2025-05-03</t>
         </is>
       </c>
-      <c r="AC122" t="inlineStr">
-        <is>
-          <t>Minst 60</t>
+      <c r="AB122" t="inlineStr">
+        <is>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AD122" t="b">
@@ -13847,26 +13845,41 @@
       </c>
       <c r="AG122" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ122" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK122" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO122" t="inlineStr">
+        <is>
+          <t>Omkullfallen grov stam # Salix caprea</t>
+        </is>
       </c>
       <c r="AT122" t="inlineStr"/>
       <c r="AW122" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX122" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY122" t="inlineStr"/>
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>124756763</v>
+        <v>124756766</v>
       </c>
       <c r="B123" t="n">
-        <v>98101</v>
+        <v>79891</v>
       </c>
       <c r="C123" t="inlineStr">
         <is>
@@ -13875,50 +13888,38 @@
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E123" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I123" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J123" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K123" t="inlineStr"/>
-      <c r="L123" t="inlineStr"/>
-      <c r="N123" t="inlineStr"/>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I123" t="inlineStr"/>
       <c r="P123" t="inlineStr">
         <is>
           <t>Häggsåsen N, Jmt</t>
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>452478</v>
+        <v>452396</v>
       </c>
       <c r="R123" t="n">
-        <v>6990887</v>
+        <v>6990981</v>
       </c>
       <c r="S123" t="n">
         <v>10</v>
@@ -13950,7 +13951,7 @@
       </c>
       <c r="Z123" t="inlineStr">
         <is>
-          <t>11:18</t>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AA123" t="inlineStr">
@@ -13960,7 +13961,7 @@
       </c>
       <c r="AB123" t="inlineStr">
         <is>
-          <t>11:18</t>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AD123" t="b">
@@ -13969,7 +13970,6 @@
       <c r="AE123" t="b">
         <v>0</v>
       </c>
-      <c r="AF123" t="inlineStr"/>
       <c r="AG123" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 16493-2025 artfynd.xlsx
+++ b/artfynd/A 16493-2025 artfynd.xlsx
@@ -787,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124695367</v>
+        <v>124705584</v>
       </c>
       <c r="B3" t="n">
-        <v>82597</v>
+        <v>91030</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -803,34 +803,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1312</v>
+        <v>5432</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Tjärnflon, Tjärnflon, Jmt</t>
+          <t>Häggsåsen, Häggsåsen, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>452617</v>
+        <v>452865</v>
       </c>
       <c r="R3" t="n">
-        <v>6990540</v>
+        <v>6990382</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -889,7 +889,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124689574</v>
+        <v>124721401</v>
       </c>
       <c r="B4" t="n">
         <v>57513</v>
@@ -934,10 +934,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>452326</v>
+        <v>452415</v>
       </c>
       <c r="R4" t="n">
-        <v>6990987</v>
+        <v>6990714</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1001,10 +1001,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124694574</v>
+        <v>124695367</v>
       </c>
       <c r="B5" t="n">
-        <v>57513</v>
+        <v>82597</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1017,39 +1017,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>1312</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Tjärnflon, Tjärnflon, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>452630</v>
+        <v>452617</v>
       </c>
       <c r="R5" t="n">
-        <v>6990651</v>
+        <v>6990540</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1082,11 +1077,6 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-05-02</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1113,10 +1103,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124705584</v>
+        <v>124689574</v>
       </c>
       <c r="B6" t="n">
-        <v>91030</v>
+        <v>57513</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1129,34 +1119,39 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Häggsåsen, Häggsåsen, Jmt</t>
+          <t>Tjärnflon, Tjärnflon, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>452865</v>
+        <v>452326</v>
       </c>
       <c r="R6" t="n">
-        <v>6990382</v>
+        <v>6990987</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1189,6 +1184,11 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-05-02</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1215,7 +1215,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124721401</v>
+        <v>124694574</v>
       </c>
       <c r="B7" t="n">
         <v>57513</v>
@@ -1251,7 +1251,7 @@
       <c r="I7" t="inlineStr"/>
       <c r="M7" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1260,10 +1260,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>452415</v>
+        <v>452630</v>
       </c>
       <c r="R7" t="n">
-        <v>6990714</v>
+        <v>6990651</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1300,7 +1300,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -2056,10 +2056,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124688930</v>
+        <v>124689528</v>
       </c>
       <c r="B15" t="n">
-        <v>79891</v>
+        <v>57513</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2072,34 +2072,39 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Tjärnflon, Tjärnflon, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>452168</v>
+        <v>452301</v>
       </c>
       <c r="R15" t="n">
-        <v>6990824</v>
+        <v>6990964</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2132,6 +2137,11 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-05-02</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2158,10 +2168,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124691528</v>
+        <v>124688930</v>
       </c>
       <c r="B16" t="n">
-        <v>79892</v>
+        <v>79891</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2174,21 +2184,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>2081</v>
+        <v>6458</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2198,10 +2208,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>452427</v>
+        <v>452168</v>
       </c>
       <c r="R16" t="n">
-        <v>6990925</v>
+        <v>6990824</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2260,10 +2270,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>124689528</v>
+        <v>124691528</v>
       </c>
       <c r="B17" t="n">
-        <v>57513</v>
+        <v>79892</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2276,39 +2286,34 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100109</v>
+        <v>2081</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Tjärnflon, Tjärnflon, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>452301</v>
+        <v>452427</v>
       </c>
       <c r="R17" t="n">
-        <v>6990964</v>
+        <v>6990925</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2341,11 +2346,6 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-05-02</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2372,10 +2372,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>124691814</v>
+        <v>124689645</v>
       </c>
       <c r="B18" t="n">
-        <v>56714</v>
+        <v>91012</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2388,43 +2388,34 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>102612</v>
+        <v>1202</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>förbiflygande</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Tjärnflon, Tjärnflon, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>452489</v>
+        <v>452311</v>
       </c>
       <c r="R18" t="n">
-        <v>6990896</v>
+        <v>6990960</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2483,10 +2474,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>124689645</v>
+        <v>124691814</v>
       </c>
       <c r="B19" t="n">
-        <v>91012</v>
+        <v>56714</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2499,34 +2490,43 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1202</v>
+        <v>102612</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>förbiflygande</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Tjärnflon, Tjärnflon, Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>452311</v>
+        <v>452489</v>
       </c>
       <c r="R19" t="n">
-        <v>6990960</v>
+        <v>6990896</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -3007,10 +3007,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>124704726</v>
+        <v>124721354</v>
       </c>
       <c r="B24" t="n">
-        <v>91012</v>
+        <v>57513</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3023,34 +3023,39 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Häggsåsen, Häggsåsen, Jmt</t>
+          <t>Tjärnflon, Tjärnflon, Jmt</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>452828</v>
+        <v>452514</v>
       </c>
       <c r="R24" t="n">
-        <v>6990384</v>
+        <v>6990587</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3083,6 +3088,11 @@
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-05-02</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3109,7 +3119,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>124704608</v>
+        <v>124704726</v>
       </c>
       <c r="B25" t="n">
         <v>91012</v>
@@ -3149,10 +3159,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>452839</v>
+        <v>452828</v>
       </c>
       <c r="R25" t="n">
-        <v>6990352</v>
+        <v>6990384</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3211,10 +3221,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>124721354</v>
+        <v>124704608</v>
       </c>
       <c r="B26" t="n">
-        <v>57513</v>
+        <v>91012</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3227,39 +3237,34 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Tjärnflon, Tjärnflon, Jmt</t>
+          <t>Häggsåsen, Häggsåsen, Jmt</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>452514</v>
+        <v>452839</v>
       </c>
       <c r="R26" t="n">
-        <v>6990587</v>
+        <v>6990352</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3292,11 +3297,6 @@
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-05-02</t>
-        </is>
-      </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3323,10 +3323,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>124703646</v>
+        <v>124706585</v>
       </c>
       <c r="B27" t="n">
-        <v>91008</v>
+        <v>77743</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3339,21 +3339,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1108</v>
+        <v>228579</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3363,10 +3363,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>452785</v>
+        <v>452913</v>
       </c>
       <c r="R27" t="n">
-        <v>6990307</v>
+        <v>6990390</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3425,10 +3425,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>124706585</v>
+        <v>124703646</v>
       </c>
       <c r="B28" t="n">
-        <v>77743</v>
+        <v>91008</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3441,21 +3441,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>228579</v>
+        <v>1108</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3465,10 +3465,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>452913</v>
+        <v>452785</v>
       </c>
       <c r="R28" t="n">
-        <v>6990390</v>
+        <v>6990307</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -4173,10 +4173,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>124702770</v>
+        <v>124703242</v>
       </c>
       <c r="B35" t="n">
-        <v>79891</v>
+        <v>91299</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4189,21 +4189,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6458</v>
+        <v>658</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4213,10 +4213,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>452731</v>
+        <v>452760</v>
       </c>
       <c r="R35" t="n">
-        <v>6990355</v>
+        <v>6990252</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4275,10 +4275,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>124703242</v>
+        <v>124702770</v>
       </c>
       <c r="B36" t="n">
-        <v>91299</v>
+        <v>79891</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4291,21 +4291,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>658</v>
+        <v>6458</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4315,10 +4315,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>452760</v>
+        <v>452731</v>
       </c>
       <c r="R36" t="n">
-        <v>6990252</v>
+        <v>6990355</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4377,10 +4377,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>124689655</v>
+        <v>124689335</v>
       </c>
       <c r="B37" t="n">
-        <v>91299</v>
+        <v>57513</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4393,34 +4393,39 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>658</v>
+        <v>100109</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P37" t="inlineStr">
         <is>
           <t>Tjärnflon, Tjärnflon, Jmt</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>452312</v>
+        <v>452249</v>
       </c>
       <c r="R37" t="n">
-        <v>6990961</v>
+        <v>6990921</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4453,6 +4458,11 @@
       <c r="AA37" t="inlineStr">
         <is>
           <t>2025-05-02</t>
+        </is>
+      </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4591,10 +4601,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>124689335</v>
+        <v>124689655</v>
       </c>
       <c r="B39" t="n">
-        <v>57513</v>
+        <v>91299</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4607,39 +4617,34 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>100109</v>
+        <v>658</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
-      <c r="M39" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P39" t="inlineStr">
         <is>
           <t>Tjärnflon, Tjärnflon, Jmt</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>452249</v>
+        <v>452312</v>
       </c>
       <c r="R39" t="n">
-        <v>6990921</v>
+        <v>6990961</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4672,11 +4677,6 @@
       <c r="AA39" t="inlineStr">
         <is>
           <t>2025-05-02</t>
-        </is>
-      </c>
-      <c r="AC39" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5233,10 +5233,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>124753620</v>
+        <v>124756728</v>
       </c>
       <c r="B45" t="n">
-        <v>98101</v>
+        <v>79891</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5245,25 +5245,25 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5273,10 +5273,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>452554</v>
+        <v>452745</v>
       </c>
       <c r="R45" t="n">
-        <v>6990657</v>
+        <v>6990359</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5306,14 +5306,19 @@
           <t>2025-05-03</t>
         </is>
       </c>
+      <c r="Z45" t="inlineStr">
+        <is>
+          <t>14:30</t>
+        </is>
+      </c>
       <c r="AA45" t="inlineStr">
         <is>
           <t>2025-05-03</t>
         </is>
       </c>
-      <c r="AC45" t="inlineStr">
-        <is>
-          <t>Minst 30</t>
+      <c r="AB45" t="inlineStr">
+        <is>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5324,26 +5329,41 @@
       </c>
       <c r="AG45" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ45" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK45" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO45" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
       </c>
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>124756728</v>
+        <v>124753620</v>
       </c>
       <c r="B46" t="n">
-        <v>79891</v>
+        <v>98101</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5352,25 +5372,25 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5380,10 +5400,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>452745</v>
+        <v>452554</v>
       </c>
       <c r="R46" t="n">
-        <v>6990359</v>
+        <v>6990657</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5413,19 +5433,14 @@
           <t>2025-05-03</t>
         </is>
       </c>
-      <c r="Z46" t="inlineStr">
-        <is>
-          <t>14:30</t>
-        </is>
-      </c>
       <c r="AA46" t="inlineStr">
         <is>
           <t>2025-05-03</t>
         </is>
       </c>
-      <c r="AB46" t="inlineStr">
-        <is>
-          <t>14:30</t>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>Minst 30</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5436,31 +5451,16 @@
       </c>
       <c r="AG46" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ46" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK46" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AO46" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
       </c>
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
@@ -7803,10 +7803,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>124756741</v>
+        <v>124753592</v>
       </c>
       <c r="B68" t="n">
-        <v>79851</v>
+        <v>57513</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -7815,25 +7815,25 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>229497</v>
+        <v>100109</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7843,10 +7843,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>452682</v>
+        <v>452396</v>
       </c>
       <c r="R68" t="n">
-        <v>6990476</v>
+        <v>6990703</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7876,19 +7876,14 @@
           <t>2025-05-03</t>
         </is>
       </c>
-      <c r="Z68" t="inlineStr">
-        <is>
-          <t>13:54</t>
-        </is>
-      </c>
       <c r="AA68" t="inlineStr">
         <is>
           <t>2025-05-03</t>
         </is>
       </c>
-      <c r="AB68" t="inlineStr">
-        <is>
-          <t>13:54</t>
+      <c r="AC68" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -7899,41 +7894,26 @@
       </c>
       <c r="AG68" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ68" t="inlineStr">
-        <is>
-          <t>rönn</t>
-        </is>
-      </c>
-      <c r="AK68" t="inlineStr">
-        <is>
-          <t>Sorbus aucuparia</t>
-        </is>
-      </c>
-      <c r="AO68" t="inlineStr">
-        <is>
-          <t>Sorbus aucuparia</t>
-        </is>
       </c>
       <c r="AT68" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>124753592</v>
+        <v>124756741</v>
       </c>
       <c r="B69" t="n">
-        <v>57513</v>
+        <v>79851</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -7942,25 +7922,25 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>100109</v>
+        <v>229497</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7970,10 +7950,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>452396</v>
+        <v>452682</v>
       </c>
       <c r="R69" t="n">
-        <v>6990703</v>
+        <v>6990476</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -8003,14 +7983,19 @@
           <t>2025-05-03</t>
         </is>
       </c>
+      <c r="Z69" t="inlineStr">
+        <is>
+          <t>13:54</t>
+        </is>
+      </c>
       <c r="AA69" t="inlineStr">
         <is>
           <t>2025-05-03</t>
         </is>
       </c>
-      <c r="AC69" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
+      <c r="AB69" t="inlineStr">
+        <is>
+          <t>13:54</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -8021,16 +8006,31 @@
       </c>
       <c r="AG69" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ69" t="inlineStr">
+        <is>
+          <t>rönn</t>
+        </is>
+      </c>
+      <c r="AK69" t="inlineStr">
+        <is>
+          <t>Sorbus aucuparia</t>
+        </is>
+      </c>
+      <c r="AO69" t="inlineStr">
+        <is>
+          <t>Sorbus aucuparia</t>
+        </is>
       </c>
       <c r="AT69" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX69" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
@@ -12613,10 +12613,10 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>124756764</v>
+        <v>124753581</v>
       </c>
       <c r="B112" t="n">
-        <v>78810</v>
+        <v>91012</v>
       </c>
       <c r="C112" t="inlineStr">
         <is>
@@ -12629,21 +12629,21 @@
         </is>
       </c>
       <c r="E112" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I112" t="inlineStr"/>
@@ -12653,10 +12653,10 @@
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>452462</v>
+        <v>452643</v>
       </c>
       <c r="R112" t="n">
-        <v>6990915</v>
+        <v>6990504</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -12686,19 +12686,9 @@
           <t>2025-05-03</t>
         </is>
       </c>
-      <c r="Z112" t="inlineStr">
-        <is>
-          <t>11:11</t>
-        </is>
-      </c>
       <c r="AA112" t="inlineStr">
         <is>
           <t>2025-05-03</t>
-        </is>
-      </c>
-      <c r="AB112" t="inlineStr">
-        <is>
-          <t>11:11</t>
         </is>
       </c>
       <c r="AD112" t="b">
@@ -12713,22 +12703,22 @@
       <c r="AT112" t="inlineStr"/>
       <c r="AW112" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX112" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY112" t="inlineStr"/>
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>124756727</v>
+        <v>124756764</v>
       </c>
       <c r="B113" t="n">
-        <v>79920</v>
+        <v>78810</v>
       </c>
       <c r="C113" t="inlineStr">
         <is>
@@ -12737,25 +12727,25 @@
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E113" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
@@ -12765,10 +12755,10 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>452745</v>
+        <v>452462</v>
       </c>
       <c r="R113" t="n">
-        <v>6990359</v>
+        <v>6990915</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -12800,7 +12790,7 @@
       </c>
       <c r="Z113" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>11:11</t>
         </is>
       </c>
       <c r="AA113" t="inlineStr">
@@ -12810,7 +12800,7 @@
       </c>
       <c r="AB113" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>11:11</t>
         </is>
       </c>
       <c r="AD113" t="b">
@@ -12837,10 +12827,10 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>124756774</v>
+        <v>124756727</v>
       </c>
       <c r="B114" t="n">
-        <v>98101</v>
+        <v>79920</v>
       </c>
       <c r="C114" t="inlineStr">
         <is>
@@ -12849,50 +12839,38 @@
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E114" t="n">
-        <v>220787</v>
+        <v>6462</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I114" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="J114" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K114" t="inlineStr"/>
-      <c r="L114" t="inlineStr"/>
-      <c r="N114" t="inlineStr"/>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
+      <c r="I114" t="inlineStr"/>
       <c r="P114" t="inlineStr">
         <is>
           <t>Häggsåsen N, Jmt</t>
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>452308</v>
+        <v>452745</v>
       </c>
       <c r="R114" t="n">
-        <v>6990943</v>
+        <v>6990359</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -12924,7 +12902,7 @@
       </c>
       <c r="Z114" t="inlineStr">
         <is>
-          <t>10:23</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AA114" t="inlineStr">
@@ -12934,7 +12912,7 @@
       </c>
       <c r="AB114" t="inlineStr">
         <is>
-          <t>10:23</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AD114" t="b">
@@ -12943,7 +12921,6 @@
       <c r="AE114" t="b">
         <v>0</v>
       </c>
-      <c r="AF114" t="inlineStr"/>
       <c r="AG114" t="b">
         <v>0</v>
       </c>
@@ -12962,10 +12939,10 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>124753581</v>
+        <v>124756774</v>
       </c>
       <c r="B115" t="n">
-        <v>91012</v>
+        <v>98101</v>
       </c>
       <c r="C115" t="inlineStr">
         <is>
@@ -12974,38 +12951,50 @@
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E115" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I115" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I115" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J115" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K115" t="inlineStr"/>
+      <c r="L115" t="inlineStr"/>
+      <c r="N115" t="inlineStr"/>
       <c r="P115" t="inlineStr">
         <is>
           <t>Häggsåsen N, Jmt</t>
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>452643</v>
+        <v>452308</v>
       </c>
       <c r="R115" t="n">
-        <v>6990504</v>
+        <v>6990943</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -13035,29 +13024,40 @@
           <t>2025-05-03</t>
         </is>
       </c>
+      <c r="Z115" t="inlineStr">
+        <is>
+          <t>10:23</t>
+        </is>
+      </c>
       <c r="AA115" t="inlineStr">
         <is>
           <t>2025-05-03</t>
         </is>
       </c>
+      <c r="AB115" t="inlineStr">
+        <is>
+          <t>10:23</t>
+        </is>
+      </c>
       <c r="AD115" t="b">
         <v>0</v>
       </c>
       <c r="AE115" t="b">
         <v>0</v>
       </c>
+      <c r="AF115" t="inlineStr"/>
       <c r="AG115" t="b">
         <v>0</v>
       </c>
       <c r="AT115" t="inlineStr"/>
       <c r="AW115" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX115" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY115" t="inlineStr"/>

--- a/artfynd/A 16493-2025 artfynd.xlsx
+++ b/artfynd/A 16493-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124695367</v>
+        <v>124704478</v>
       </c>
       <c r="B2" t="n">
-        <v>82597</v>
+        <v>57513</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,34 +691,39 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1312</v>
+        <v>100109</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Tjärnflon, Tjärnflon, Jmt</t>
+          <t>Häggsåsen, Häggsåsen, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>452617</v>
+        <v>452836</v>
       </c>
       <c r="R2" t="n">
-        <v>6990540</v>
+        <v>6990321</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -751,6 +756,11 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-05-02</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -777,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124691533</v>
+        <v>124701352</v>
       </c>
       <c r="B3" t="n">
-        <v>79891</v>
+        <v>79892</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,34 +803,39 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Tjärnflon, Tjärnflon, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>452427</v>
+        <v>452657</v>
       </c>
       <c r="R3" t="n">
-        <v>6990925</v>
+        <v>6990499</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -853,6 +868,11 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-05-02</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Rikligt med skrovellav, APOTECHIER på en av bålarna</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -879,10 +899,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124703242</v>
+        <v>124706864</v>
       </c>
       <c r="B4" t="n">
-        <v>91299</v>
+        <v>57513</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -895,34 +915,39 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>658</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Häggsåsen, Häggsåsen, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>452760</v>
+        <v>453007</v>
       </c>
       <c r="R4" t="n">
-        <v>6990252</v>
+        <v>6990356</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -955,6 +980,11 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-05-02</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -981,10 +1011,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124704608</v>
+        <v>124688930</v>
       </c>
       <c r="B5" t="n">
-        <v>91012</v>
+        <v>79891</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -997,34 +1027,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Häggsåsen, Häggsåsen, Jmt</t>
+          <t>Tjärnflon, Tjärnflon, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>452839</v>
+        <v>452168</v>
       </c>
       <c r="R5" t="n">
-        <v>6990352</v>
+        <v>6990824</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1083,10 +1113,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124702530</v>
+        <v>124704726</v>
       </c>
       <c r="B6" t="n">
-        <v>79891</v>
+        <v>91012</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1099,21 +1129,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1123,7 +1153,7 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>452746</v>
+        <v>452828</v>
       </c>
       <c r="R6" t="n">
         <v>6990384</v>
@@ -1185,10 +1215,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124689335</v>
+        <v>124689645</v>
       </c>
       <c r="B7" t="n">
-        <v>57513</v>
+        <v>91012</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1201,39 +1231,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Tjärnflon, Tjärnflon, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>452249</v>
+        <v>452311</v>
       </c>
       <c r="R7" t="n">
-        <v>6990921</v>
+        <v>6990960</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1266,11 +1291,6 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-05-02</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1399,10 +1419,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124705813</v>
+        <v>124699720</v>
       </c>
       <c r="B9" t="n">
-        <v>57513</v>
+        <v>79892</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1415,39 +1435,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>2081</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Häggsåsen, Häggsåsen, Jmt</t>
+          <t>Tjärnflon, Tjärnflon, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>452865</v>
+        <v>452650</v>
       </c>
       <c r="R9" t="n">
-        <v>6990385</v>
+        <v>6990495</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1480,11 +1495,6 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-05-02</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Möjligt gammalt bo 3m upp i granstubbe med granticka på</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1511,10 +1521,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124689546</v>
+        <v>124691814</v>
       </c>
       <c r="B10" t="n">
-        <v>57513</v>
+        <v>56714</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1527,16 +1537,16 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>102612</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1544,10 +1554,14 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I10" t="inlineStr"/>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>förbiflygande</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
@@ -1556,10 +1570,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>452319</v>
+        <v>452489</v>
       </c>
       <c r="R10" t="n">
-        <v>6990963</v>
+        <v>6990896</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1592,11 +1606,6 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-05-02</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1623,10 +1632,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124689645</v>
+        <v>124689655</v>
       </c>
       <c r="B11" t="n">
-        <v>91012</v>
+        <v>91299</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1639,21 +1648,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1663,10 +1672,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>452311</v>
+        <v>452312</v>
       </c>
       <c r="R11" t="n">
-        <v>6990960</v>
+        <v>6990961</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1725,7 +1734,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124689574</v>
+        <v>124689528</v>
       </c>
       <c r="B12" t="n">
         <v>57513</v>
@@ -1770,10 +1779,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>452326</v>
+        <v>452301</v>
       </c>
       <c r="R12" t="n">
-        <v>6990987</v>
+        <v>6990964</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1837,10 +1846,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124691814</v>
+        <v>124704608</v>
       </c>
       <c r="B13" t="n">
-        <v>56714</v>
+        <v>91012</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1853,43 +1862,34 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>102612</v>
+        <v>1202</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>förbiflygande</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Tjärnflon, Tjärnflon, Jmt</t>
+          <t>Häggsåsen, Häggsåsen, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>452489</v>
+        <v>452839</v>
       </c>
       <c r="R13" t="n">
-        <v>6990896</v>
+        <v>6990352</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1948,10 +1948,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124688835</v>
+        <v>124702770</v>
       </c>
       <c r="B14" t="n">
-        <v>78810</v>
+        <v>79891</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1964,39 +1964,34 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="K14" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Tjärnflon, Tjärnflon, Jmt</t>
+          <t>Häggsåsen, Häggsåsen, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>452142</v>
+        <v>452731</v>
       </c>
       <c r="R14" t="n">
-        <v>6990800</v>
+        <v>6990355</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2055,10 +2050,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124695256</v>
+        <v>124703242</v>
       </c>
       <c r="B15" t="n">
-        <v>98101</v>
+        <v>91299</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2067,42 +2062,38 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Tjärnflon, Tjärnflon, Jmt</t>
+          <t>Häggsåsen, Häggsåsen, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>452624</v>
+        <v>452760</v>
       </c>
       <c r="R15" t="n">
-        <v>6990535</v>
+        <v>6990252</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2161,7 +2152,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124704581</v>
+        <v>124701516</v>
       </c>
       <c r="B16" t="n">
         <v>91299</v>
@@ -2197,14 +2188,14 @@
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Häggsåsen, Häggsåsen, Jmt</t>
+          <t>Tjärnflon, Tjärnflon, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>452839</v>
+        <v>452635</v>
       </c>
       <c r="R16" t="n">
-        <v>6990352</v>
+        <v>6990463</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2263,10 +2254,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>124706950</v>
+        <v>124721354</v>
       </c>
       <c r="B17" t="n">
-        <v>98101</v>
+        <v>57513</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2275,42 +2266,43 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>21</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Häggsåsen, Häggsåsen, Jmt</t>
+          <t>Tjärnflon, Tjärnflon, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>453007</v>
+        <v>452514</v>
       </c>
       <c r="R17" t="n">
-        <v>6990356</v>
+        <v>6990587</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2343,6 +2335,11 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-05-02</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2369,10 +2366,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>124704478</v>
+        <v>124702530</v>
       </c>
       <c r="B18" t="n">
-        <v>57513</v>
+        <v>79891</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2385,39 +2382,34 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Häggsåsen, Häggsåsen, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>452836</v>
+        <v>452746</v>
       </c>
       <c r="R18" t="n">
-        <v>6990321</v>
+        <v>6990384</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2450,11 +2442,6 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-05-02</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2481,7 +2468,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>124694574</v>
+        <v>124721401</v>
       </c>
       <c r="B19" t="n">
         <v>57513</v>
@@ -2517,7 +2504,7 @@
       <c r="I19" t="inlineStr"/>
       <c r="M19" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
@@ -2526,10 +2513,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>452630</v>
+        <v>452415</v>
       </c>
       <c r="R19" t="n">
-        <v>6990651</v>
+        <v>6990714</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2566,7 +2553,7 @@
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>Färska ringhack på tall</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2593,10 +2580,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>124689475</v>
+        <v>124695367</v>
       </c>
       <c r="B20" t="n">
-        <v>57513</v>
+        <v>82597</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2609,39 +2596,34 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100109</v>
+        <v>1312</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Tjärnflon, Tjärnflon, Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>452291</v>
+        <v>452617</v>
       </c>
       <c r="R20" t="n">
-        <v>6990952</v>
+        <v>6990540</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2674,11 +2656,6 @@
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-05-02</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2705,10 +2682,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>124701352</v>
+        <v>124691378</v>
       </c>
       <c r="B21" t="n">
-        <v>79892</v>
+        <v>91012</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2721,39 +2698,34 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>2081</v>
+        <v>1202</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="K21" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Tjärnflon, Tjärnflon, Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>452657</v>
+        <v>452431</v>
       </c>
       <c r="R21" t="n">
-        <v>6990499</v>
+        <v>6990946</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2786,11 +2758,6 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-05-02</t>
-        </is>
-      </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>Rikligt med skrovellav, APOTECHIER på en av bålarna</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2817,10 +2784,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>124702770</v>
+        <v>124706950</v>
       </c>
       <c r="B22" t="n">
-        <v>79891</v>
+        <v>98101</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2829,38 +2796,42 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Häggsåsen, Häggsåsen, Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>452731</v>
+        <v>453007</v>
       </c>
       <c r="R22" t="n">
-        <v>6990355</v>
+        <v>6990356</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2919,10 +2890,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>124691528</v>
+        <v>124689574</v>
       </c>
       <c r="B23" t="n">
-        <v>79892</v>
+        <v>57513</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2935,34 +2906,39 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>2081</v>
+        <v>100109</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Tjärnflon, Tjärnflon, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>452427</v>
+        <v>452326</v>
       </c>
       <c r="R23" t="n">
-        <v>6990925</v>
+        <v>6990987</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2995,6 +2971,11 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-05-02</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3021,10 +3002,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>124704726</v>
+        <v>124689546</v>
       </c>
       <c r="B24" t="n">
-        <v>91012</v>
+        <v>57513</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3037,34 +3018,39 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Häggsåsen, Häggsåsen, Jmt</t>
+          <t>Tjärnflon, Tjärnflon, Jmt</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>452828</v>
+        <v>452319</v>
       </c>
       <c r="R24" t="n">
-        <v>6990384</v>
+        <v>6990963</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3097,6 +3083,11 @@
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-05-02</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3123,10 +3114,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>124703646</v>
+        <v>124705813</v>
       </c>
       <c r="B25" t="n">
-        <v>91008</v>
+        <v>57513</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3139,34 +3130,39 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Häggsåsen, Häggsåsen, Jmt</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>452785</v>
+        <v>452865</v>
       </c>
       <c r="R25" t="n">
-        <v>6990307</v>
+        <v>6990385</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3199,6 +3195,11 @@
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-05-02</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Möjligt gammalt bo 3m upp i granstubbe med granticka på</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3225,7 +3226,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>124689504</v>
+        <v>124694574</v>
       </c>
       <c r="B26" t="n">
         <v>57513</v>
@@ -3261,7 +3262,7 @@
       <c r="I26" t="inlineStr"/>
       <c r="M26" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
@@ -3270,10 +3271,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>452322</v>
+        <v>452630</v>
       </c>
       <c r="R26" t="n">
-        <v>6990950</v>
+        <v>6990651</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3310,7 +3311,7 @@
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3337,10 +3338,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>124702902</v>
+        <v>124705215</v>
       </c>
       <c r="B27" t="n">
-        <v>79891</v>
+        <v>91012</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3353,21 +3354,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3377,10 +3378,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>452734</v>
+        <v>452850</v>
       </c>
       <c r="R27" t="n">
-        <v>6990348</v>
+        <v>6990404</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3439,10 +3440,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>124701516</v>
+        <v>124705584</v>
       </c>
       <c r="B28" t="n">
-        <v>91299</v>
+        <v>91030</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3455,34 +3456,34 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>658</v>
+        <v>5432</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Tjärnflon, Tjärnflon, Jmt</t>
+          <t>Häggsåsen, Häggsåsen, Jmt</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>452635</v>
+        <v>452865</v>
       </c>
       <c r="R28" t="n">
-        <v>6990463</v>
+        <v>6990382</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3541,10 +3542,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>124695424</v>
+        <v>124695256</v>
       </c>
       <c r="B29" t="n">
-        <v>91012</v>
+        <v>98101</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3553,38 +3554,42 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
       <c r="P29" t="inlineStr">
         <is>
           <t>Tjärnflon, Tjärnflon, Jmt</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>452642</v>
+        <v>452624</v>
       </c>
       <c r="R29" t="n">
-        <v>6990548</v>
+        <v>6990535</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3643,10 +3648,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>124721401</v>
+        <v>124699728</v>
       </c>
       <c r="B30" t="n">
-        <v>57513</v>
+        <v>79891</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3659,39 +3664,34 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P30" t="inlineStr">
         <is>
           <t>Tjärnflon, Tjärnflon, Jmt</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>452415</v>
+        <v>452650</v>
       </c>
       <c r="R30" t="n">
-        <v>6990714</v>
+        <v>6990495</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3724,11 +3724,6 @@
       <c r="AA30" t="inlineStr">
         <is>
           <t>2025-05-02</t>
-        </is>
-      </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3755,10 +3750,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>124688930</v>
+        <v>124693950</v>
       </c>
       <c r="B31" t="n">
-        <v>79891</v>
+        <v>91012</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3771,21 +3766,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3795,10 +3790,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>452168</v>
+        <v>452582</v>
       </c>
       <c r="R31" t="n">
-        <v>6990824</v>
+        <v>6990572</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3857,10 +3852,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>124699728</v>
+        <v>124689504</v>
       </c>
       <c r="B32" t="n">
-        <v>79891</v>
+        <v>57513</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3873,34 +3868,39 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P32" t="inlineStr">
         <is>
           <t>Tjärnflon, Tjärnflon, Jmt</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>452650</v>
+        <v>452322</v>
       </c>
       <c r="R32" t="n">
-        <v>6990495</v>
+        <v>6990950</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3933,6 +3933,11 @@
       <c r="AA32" t="inlineStr">
         <is>
           <t>2025-05-02</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3959,10 +3964,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>124705215</v>
+        <v>124689335</v>
       </c>
       <c r="B33" t="n">
-        <v>91012</v>
+        <v>57513</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -3975,34 +3980,39 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Häggsåsen, Häggsåsen, Jmt</t>
+          <t>Tjärnflon, Tjärnflon, Jmt</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>452850</v>
+        <v>452249</v>
       </c>
       <c r="R33" t="n">
-        <v>6990404</v>
+        <v>6990921</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4035,6 +4045,11 @@
       <c r="AA33" t="inlineStr">
         <is>
           <t>2025-05-02</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4061,10 +4076,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>124721354</v>
+        <v>124703646</v>
       </c>
       <c r="B34" t="n">
-        <v>57513</v>
+        <v>91008</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4077,39 +4092,34 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
-      <c r="M34" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Tjärnflon, Tjärnflon, Jmt</t>
+          <t>Häggsåsen, Häggsåsen, Jmt</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>452514</v>
+        <v>452785</v>
       </c>
       <c r="R34" t="n">
-        <v>6990587</v>
+        <v>6990307</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4142,11 +4152,6 @@
       <c r="AA34" t="inlineStr">
         <is>
           <t>2025-05-02</t>
-        </is>
-      </c>
-      <c r="AC34" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4173,10 +4178,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>124689528</v>
+        <v>124691533</v>
       </c>
       <c r="B35" t="n">
-        <v>57513</v>
+        <v>79891</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4189,39 +4194,34 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P35" t="inlineStr">
         <is>
           <t>Tjärnflon, Tjärnflon, Jmt</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>452301</v>
+        <v>452427</v>
       </c>
       <c r="R35" t="n">
-        <v>6990964</v>
+        <v>6990925</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4254,11 +4254,6 @@
       <c r="AA35" t="inlineStr">
         <is>
           <t>2025-05-02</t>
-        </is>
-      </c>
-      <c r="AC35" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4285,10 +4280,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>124705584</v>
+        <v>124695424</v>
       </c>
       <c r="B36" t="n">
-        <v>91030</v>
+        <v>91012</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4301,34 +4296,34 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>5432</v>
+        <v>1202</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Häggsåsen, Häggsåsen, Jmt</t>
+          <t>Tjärnflon, Tjärnflon, Jmt</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>452865</v>
+        <v>452642</v>
       </c>
       <c r="R36" t="n">
-        <v>6990382</v>
+        <v>6990548</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4387,10 +4382,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>124706864</v>
+        <v>124702902</v>
       </c>
       <c r="B37" t="n">
-        <v>57513</v>
+        <v>79891</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4403,39 +4398,34 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
-      <c r="M37" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P37" t="inlineStr">
         <is>
           <t>Häggsåsen, Häggsåsen, Jmt</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>453007</v>
+        <v>452734</v>
       </c>
       <c r="R37" t="n">
-        <v>6990356</v>
+        <v>6990348</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4468,11 +4458,6 @@
       <c r="AA37" t="inlineStr">
         <is>
           <t>2025-05-02</t>
-        </is>
-      </c>
-      <c r="AC37" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4499,10 +4484,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>124693275</v>
+        <v>124689475</v>
       </c>
       <c r="B38" t="n">
-        <v>91026</v>
+        <v>57513</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4515,34 +4500,39 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>1204</v>
+        <v>100109</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P38" t="inlineStr">
         <is>
           <t>Tjärnflon, Tjärnflon, Jmt</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>452523</v>
+        <v>452291</v>
       </c>
       <c r="R38" t="n">
-        <v>6990595</v>
+        <v>6990952</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4575,6 +4565,11 @@
       <c r="AA38" t="inlineStr">
         <is>
           <t>2025-05-02</t>
+        </is>
+      </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4601,10 +4596,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>124689655</v>
+        <v>124693275</v>
       </c>
       <c r="B39" t="n">
-        <v>91299</v>
+        <v>91026</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4617,21 +4612,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>658</v>
+        <v>1204</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4641,10 +4636,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>452312</v>
+        <v>452523</v>
       </c>
       <c r="R39" t="n">
-        <v>6990961</v>
+        <v>6990595</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4703,10 +4698,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>124699720</v>
+        <v>124704581</v>
       </c>
       <c r="B40" t="n">
-        <v>79892</v>
+        <v>91299</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4719,34 +4714,34 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>2081</v>
+        <v>658</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Tjärnflon, Tjärnflon, Jmt</t>
+          <t>Häggsåsen, Häggsåsen, Jmt</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>452650</v>
+        <v>452839</v>
       </c>
       <c r="R40" t="n">
-        <v>6990495</v>
+        <v>6990352</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4805,10 +4800,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>124691378</v>
+        <v>124688835</v>
       </c>
       <c r="B41" t="n">
-        <v>91012</v>
+        <v>78810</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4821,34 +4816,39 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P41" t="inlineStr">
         <is>
           <t>Tjärnflon, Tjärnflon, Jmt</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>452431</v>
+        <v>452142</v>
       </c>
       <c r="R41" t="n">
-        <v>6990946</v>
+        <v>6990800</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4907,10 +4907,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>124693950</v>
+        <v>124691528</v>
       </c>
       <c r="B42" t="n">
-        <v>91012</v>
+        <v>79892</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -4923,21 +4923,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>1202</v>
+        <v>2081</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4947,10 +4947,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>452582</v>
+        <v>452427</v>
       </c>
       <c r="R42" t="n">
-        <v>6990572</v>
+        <v>6990925</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5009,10 +5009,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>124756761</v>
+        <v>124756755</v>
       </c>
       <c r="B43" t="n">
-        <v>78810</v>
+        <v>91299</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5025,21 +5025,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6425</v>
+        <v>658</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5049,10 +5049,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>452532</v>
+        <v>452538</v>
       </c>
       <c r="R43" t="n">
-        <v>6990825</v>
+        <v>6990659</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5084,7 +5084,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>11:26</t>
+          <t>11:58</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5094,7 +5094,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>11:26</t>
+          <t>11:58</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5121,10 +5121,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>124756736</v>
+        <v>124756740</v>
       </c>
       <c r="B44" t="n">
-        <v>98101</v>
+        <v>91457</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5137,46 +5137,34 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>220787</v>
+        <v>1209</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J44" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K44" t="inlineStr"/>
-      <c r="L44" t="inlineStr"/>
-      <c r="N44" t="inlineStr"/>
+          <t>P.Karst.</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
           <t>Häggsåsen N, Jmt</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>452691</v>
+        <v>452701</v>
       </c>
       <c r="R44" t="n">
-        <v>6990422</v>
+        <v>6990475</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5208,7 +5196,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>14:13</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5218,7 +5206,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>14:13</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5227,7 +5215,6 @@
       <c r="AE44" t="b">
         <v>0</v>
       </c>
-      <c r="AF44" t="inlineStr"/>
       <c r="AG44" t="b">
         <v>0</v>
       </c>
@@ -5246,10 +5233,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>124756755</v>
+        <v>124756753</v>
       </c>
       <c r="B45" t="n">
-        <v>91299</v>
+        <v>91012</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5262,21 +5249,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5286,10 +5273,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>452538</v>
+        <v>452608</v>
       </c>
       <c r="R45" t="n">
-        <v>6990659</v>
+        <v>6990625</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5321,7 +5308,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>11:58</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5331,7 +5318,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>11:58</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5358,10 +5345,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>124756740</v>
+        <v>124756761</v>
       </c>
       <c r="B46" t="n">
-        <v>91457</v>
+        <v>78810</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5370,25 +5357,25 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>1209</v>
+        <v>6425</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5398,10 +5385,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>452701</v>
+        <v>452532</v>
       </c>
       <c r="R46" t="n">
-        <v>6990475</v>
+        <v>6990825</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5433,7 +5420,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>11:26</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5443,7 +5430,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>11:26</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5470,10 +5457,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>124756753</v>
+        <v>124756736</v>
       </c>
       <c r="B47" t="n">
-        <v>91012</v>
+        <v>98101</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5482,38 +5469,50 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr"/>
+      <c r="L47" t="inlineStr"/>
+      <c r="N47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
           <t>Häggsåsen N, Jmt</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>452608</v>
+        <v>452691</v>
       </c>
       <c r="R47" t="n">
-        <v>6990625</v>
+        <v>6990422</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5545,7 +5544,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>12:07</t>
+          <t>14:13</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5555,7 +5554,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>12:07</t>
+          <t>14:13</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5564,6 +5563,7 @@
       <c r="AE47" t="b">
         <v>0</v>
       </c>
+      <c r="AF47" t="inlineStr"/>
       <c r="AG47" t="b">
         <v>0</v>
       </c>
@@ -6667,10 +6667,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>124753632</v>
+        <v>124756762</v>
       </c>
       <c r="B58" t="n">
-        <v>98101</v>
+        <v>78810</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -6679,25 +6679,25 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6707,10 +6707,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>452455</v>
+        <v>452508</v>
       </c>
       <c r="R58" t="n">
-        <v>6990942</v>
+        <v>6990903</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6740,14 +6740,19 @@
           <t>2025-05-03</t>
         </is>
       </c>
+      <c r="Z58" t="inlineStr">
+        <is>
+          <t>11:20</t>
+        </is>
+      </c>
       <c r="AA58" t="inlineStr">
         <is>
           <t>2025-05-03</t>
         </is>
       </c>
-      <c r="AC58" t="inlineStr">
-        <is>
-          <t>Minst 30</t>
+      <c r="AB58" t="inlineStr">
+        <is>
+          <t>11:20</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6762,22 +6767,22 @@
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>124756745</v>
+        <v>124756719</v>
       </c>
       <c r="B59" t="n">
-        <v>98101</v>
+        <v>79927</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -6786,50 +6791,38 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>220787</v>
+        <v>6464</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I59" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J59" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K59" t="inlineStr"/>
-      <c r="L59" t="inlineStr"/>
-      <c r="N59" t="inlineStr"/>
+          <t>(L.) Ach.</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
           <t>Häggsåsen N, Jmt</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>452657</v>
+        <v>452823</v>
       </c>
       <c r="R59" t="n">
-        <v>6990491</v>
+        <v>6990261</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6861,7 +6854,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>13:44</t>
+          <t>14:59</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -6871,7 +6864,7 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>13:44</t>
+          <t>14:59</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -6880,7 +6873,6 @@
       <c r="AE59" t="b">
         <v>0</v>
       </c>
-      <c r="AF59" t="inlineStr"/>
       <c r="AG59" t="b">
         <v>0</v>
       </c>
@@ -6899,10 +6891,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>124753627</v>
+        <v>124756743</v>
       </c>
       <c r="B60" t="n">
-        <v>98101</v>
+        <v>79891</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -6911,25 +6903,25 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6939,10 +6931,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>452608</v>
+        <v>452682</v>
       </c>
       <c r="R60" t="n">
-        <v>6990927</v>
+        <v>6990476</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6972,14 +6964,19 @@
           <t>2025-05-03</t>
         </is>
       </c>
+      <c r="Z60" t="inlineStr">
+        <is>
+          <t>13:53</t>
+        </is>
+      </c>
       <c r="AA60" t="inlineStr">
         <is>
           <t>2025-05-03</t>
         </is>
       </c>
-      <c r="AC60" t="inlineStr">
-        <is>
-          <t>Minst 50</t>
+      <c r="AB60" t="inlineStr">
+        <is>
+          <t>13:53</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -6990,16 +6987,31 @@
       </c>
       <c r="AG60" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ60" t="inlineStr">
+        <is>
+          <t>rönn</t>
+        </is>
+      </c>
+      <c r="AK60" t="inlineStr">
+        <is>
+          <t>Sorbus aucuparia</t>
+        </is>
+      </c>
+      <c r="AO60" t="inlineStr">
+        <is>
+          <t>Sorbus aucuparia</t>
+        </is>
       </c>
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
@@ -7108,10 +7120,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>124756762</v>
+        <v>124753632</v>
       </c>
       <c r="B62" t="n">
-        <v>78810</v>
+        <v>98101</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -7120,25 +7132,25 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -7148,10 +7160,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>452508</v>
+        <v>452455</v>
       </c>
       <c r="R62" t="n">
-        <v>6990903</v>
+        <v>6990942</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7181,19 +7193,14 @@
           <t>2025-05-03</t>
         </is>
       </c>
-      <c r="Z62" t="inlineStr">
-        <is>
-          <t>11:20</t>
-        </is>
-      </c>
       <c r="AA62" t="inlineStr">
         <is>
           <t>2025-05-03</t>
         </is>
       </c>
-      <c r="AB62" t="inlineStr">
-        <is>
-          <t>11:20</t>
+      <c r="AC62" t="inlineStr">
+        <is>
+          <t>Minst 30</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7208,22 +7215,22 @@
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>124756719</v>
+        <v>124756745</v>
       </c>
       <c r="B63" t="n">
-        <v>79927</v>
+        <v>98101</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -7232,38 +7239,50 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6464</v>
+        <v>220787</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
-        </is>
-      </c>
-      <c r="I63" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J63" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K63" t="inlineStr"/>
+      <c r="L63" t="inlineStr"/>
+      <c r="N63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
           <t>Häggsåsen N, Jmt</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>452823</v>
+        <v>452657</v>
       </c>
       <c r="R63" t="n">
-        <v>6990261</v>
+        <v>6990491</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7295,7 +7314,7 @@
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>14:59</t>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
@@ -7305,7 +7324,7 @@
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>14:59</t>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7314,6 +7333,7 @@
       <c r="AE63" t="b">
         <v>0</v>
       </c>
+      <c r="AF63" t="inlineStr"/>
       <c r="AG63" t="b">
         <v>0</v>
       </c>
@@ -7332,10 +7352,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>124756743</v>
+        <v>124753627</v>
       </c>
       <c r="B64" t="n">
-        <v>79891</v>
+        <v>98101</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7344,25 +7364,25 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7372,10 +7392,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>452682</v>
+        <v>452608</v>
       </c>
       <c r="R64" t="n">
-        <v>6990476</v>
+        <v>6990927</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7405,19 +7425,14 @@
           <t>2025-05-03</t>
         </is>
       </c>
-      <c r="Z64" t="inlineStr">
-        <is>
-          <t>13:53</t>
-        </is>
-      </c>
       <c r="AA64" t="inlineStr">
         <is>
           <t>2025-05-03</t>
         </is>
       </c>
-      <c r="AB64" t="inlineStr">
-        <is>
-          <t>13:53</t>
+      <c r="AC64" t="inlineStr">
+        <is>
+          <t>Minst 50</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7428,31 +7443,16 @@
       </c>
       <c r="AG64" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ64" t="inlineStr">
-        <is>
-          <t>rönn</t>
-        </is>
-      </c>
-      <c r="AK64" t="inlineStr">
-        <is>
-          <t>Sorbus aucuparia</t>
-        </is>
-      </c>
-      <c r="AO64" t="inlineStr">
-        <is>
-          <t>Sorbus aucuparia</t>
-        </is>
       </c>
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
@@ -8691,10 +8691,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>124756718</v>
+        <v>124753604</v>
       </c>
       <c r="B76" t="n">
-        <v>91030</v>
+        <v>79892</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
@@ -8707,21 +8707,21 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>5432</v>
+        <v>2081</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -8731,10 +8731,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>452857</v>
+        <v>452435</v>
       </c>
       <c r="R76" t="n">
-        <v>6990267</v>
+        <v>6990938</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8764,19 +8764,9 @@
           <t>2025-05-03</t>
         </is>
       </c>
-      <c r="Z76" t="inlineStr">
-        <is>
-          <t>15:03</t>
-        </is>
-      </c>
       <c r="AA76" t="inlineStr">
         <is>
           <t>2025-05-03</t>
-        </is>
-      </c>
-      <c r="AB76" t="inlineStr">
-        <is>
-          <t>15:03</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -8791,22 +8781,22 @@
       <c r="AT76" t="inlineStr"/>
       <c r="AW76" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX76" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>124753604</v>
+        <v>124753608</v>
       </c>
       <c r="B77" t="n">
-        <v>79892</v>
+        <v>79891</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -8819,21 +8809,21 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>2081</v>
+        <v>6458</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -8843,10 +8833,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>452435</v>
+        <v>452731</v>
       </c>
       <c r="R77" t="n">
-        <v>6990938</v>
+        <v>6990377</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -9017,10 +9007,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>124753608</v>
+        <v>124756718</v>
       </c>
       <c r="B79" t="n">
-        <v>79891</v>
+        <v>91030</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -9033,21 +9023,21 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>6458</v>
+        <v>5432</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -9057,10 +9047,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>452731</v>
+        <v>452857</v>
       </c>
       <c r="R79" t="n">
-        <v>6990377</v>
+        <v>6990267</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -9090,9 +9080,19 @@
           <t>2025-05-03</t>
         </is>
       </c>
+      <c r="Z79" t="inlineStr">
+        <is>
+          <t>15:03</t>
+        </is>
+      </c>
       <c r="AA79" t="inlineStr">
         <is>
           <t>2025-05-03</t>
+        </is>
+      </c>
+      <c r="AB79" t="inlineStr">
+        <is>
+          <t>15:03</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -9107,12 +9107,12 @@
       <c r="AT79" t="inlineStr"/>
       <c r="AW79" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX79" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
@@ -9476,10 +9476,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>124756764</v>
+        <v>124756757</v>
       </c>
       <c r="B83" t="n">
-        <v>78810</v>
+        <v>77743</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
@@ -9492,21 +9492,21 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>6425</v>
+        <v>228579</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -9516,10 +9516,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>452462</v>
+        <v>452506</v>
       </c>
       <c r="R83" t="n">
-        <v>6990915</v>
+        <v>6990737</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9551,7 +9551,7 @@
       </c>
       <c r="Z83" t="inlineStr">
         <is>
-          <t>11:11</t>
+          <t>11:47</t>
         </is>
       </c>
       <c r="AA83" t="inlineStr">
@@ -9561,7 +9561,7 @@
       </c>
       <c r="AB83" t="inlineStr">
         <is>
-          <t>11:11</t>
+          <t>11:47</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -9588,10 +9588,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>124756754</v>
+        <v>124756768</v>
       </c>
       <c r="B84" t="n">
-        <v>78810</v>
+        <v>77743</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
@@ -9604,21 +9604,21 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>6425</v>
+        <v>228579</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -9628,10 +9628,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>452544</v>
+        <v>452357</v>
       </c>
       <c r="R84" t="n">
-        <v>6990646</v>
+        <v>6990970</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9663,7 +9663,7 @@
       </c>
       <c r="Z84" t="inlineStr">
         <is>
-          <t>12:04</t>
+          <t>10:52</t>
         </is>
       </c>
       <c r="AA84" t="inlineStr">
@@ -9673,7 +9673,7 @@
       </c>
       <c r="AB84" t="inlineStr">
         <is>
-          <t>12:04</t>
+          <t>10:52</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -9700,7 +9700,7 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>124756776</v>
+        <v>124756764</v>
       </c>
       <c r="B85" t="n">
         <v>78810</v>
@@ -9740,10 +9740,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>452308</v>
+        <v>452462</v>
       </c>
       <c r="R85" t="n">
-        <v>6990943</v>
+        <v>6990915</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9775,7 +9775,7 @@
       </c>
       <c r="Z85" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:11</t>
         </is>
       </c>
       <c r="AA85" t="inlineStr">
@@ -9785,7 +9785,7 @@
       </c>
       <c r="AB85" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:11</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -9812,10 +9812,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>124756734</v>
+        <v>124756754</v>
       </c>
       <c r="B86" t="n">
-        <v>79891</v>
+        <v>78810</v>
       </c>
       <c r="C86" t="inlineStr">
         <is>
@@ -9828,21 +9828,21 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -9852,10 +9852,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>452675</v>
+        <v>452544</v>
       </c>
       <c r="R86" t="n">
-        <v>6990435</v>
+        <v>6990646</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9887,7 +9887,7 @@
       </c>
       <c r="Z86" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>12:04</t>
         </is>
       </c>
       <c r="AA86" t="inlineStr">
@@ -9897,7 +9897,7 @@
       </c>
       <c r="AB86" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>12:04</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -9908,21 +9908,6 @@
       </c>
       <c r="AG86" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ86" t="inlineStr">
-        <is>
-          <t>rönn</t>
-        </is>
-      </c>
-      <c r="AK86" t="inlineStr">
-        <is>
-          <t>Sorbus aucuparia</t>
-        </is>
-      </c>
-      <c r="AO86" t="inlineStr">
-        <is>
-          <t>Sorbus aucuparia</t>
-        </is>
       </c>
       <c r="AT86" t="inlineStr"/>
       <c r="AW86" t="inlineStr">
@@ -9939,10 +9924,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>124756757</v>
+        <v>124756776</v>
       </c>
       <c r="B87" t="n">
-        <v>77743</v>
+        <v>78810</v>
       </c>
       <c r="C87" t="inlineStr">
         <is>
@@ -9955,21 +9940,21 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>228579</v>
+        <v>6425</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
@@ -9979,10 +9964,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>452506</v>
+        <v>452308</v>
       </c>
       <c r="R87" t="n">
-        <v>6990737</v>
+        <v>6990943</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -10014,7 +9999,7 @@
       </c>
       <c r="Z87" t="inlineStr">
         <is>
-          <t>11:47</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="AA87" t="inlineStr">
@@ -10024,7 +10009,7 @@
       </c>
       <c r="AB87" t="inlineStr">
         <is>
-          <t>11:47</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -10051,10 +10036,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>124756768</v>
+        <v>124756734</v>
       </c>
       <c r="B88" t="n">
-        <v>77743</v>
+        <v>79891</v>
       </c>
       <c r="C88" t="inlineStr">
         <is>
@@ -10067,21 +10052,21 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>228579</v>
+        <v>6458</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
@@ -10091,10 +10076,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>452357</v>
+        <v>452675</v>
       </c>
       <c r="R88" t="n">
-        <v>6990970</v>
+        <v>6990435</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -10126,7 +10111,7 @@
       </c>
       <c r="Z88" t="inlineStr">
         <is>
-          <t>10:52</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AA88" t="inlineStr">
@@ -10136,7 +10121,7 @@
       </c>
       <c r="AB88" t="inlineStr">
         <is>
-          <t>10:52</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -10147,6 +10132,21 @@
       </c>
       <c r="AG88" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ88" t="inlineStr">
+        <is>
+          <t>rönn</t>
+        </is>
+      </c>
+      <c r="AK88" t="inlineStr">
+        <is>
+          <t>Sorbus aucuparia</t>
+        </is>
+      </c>
+      <c r="AO88" t="inlineStr">
+        <is>
+          <t>Sorbus aucuparia</t>
+        </is>
       </c>
       <c r="AT88" t="inlineStr"/>
       <c r="AW88" t="inlineStr">
@@ -11126,10 +11126,10 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>124753577</v>
+        <v>124753623</v>
       </c>
       <c r="B98" t="n">
-        <v>91012</v>
+        <v>98101</v>
       </c>
       <c r="C98" t="inlineStr">
         <is>
@@ -11138,25 +11138,25 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E98" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
@@ -11166,10 +11166,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>452833</v>
+        <v>452510</v>
       </c>
       <c r="R98" t="n">
-        <v>6990388</v>
+        <v>6990873</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -11202,6 +11202,11 @@
       <c r="AA98" t="inlineStr">
         <is>
           <t>2025-05-03</t>
+        </is>
+      </c>
+      <c r="AC98" t="inlineStr">
+        <is>
+          <t>Minst 50</t>
         </is>
       </c>
       <c r="AD98" t="b">
@@ -11228,10 +11233,10 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>124756765</v>
+        <v>124753577</v>
       </c>
       <c r="B99" t="n">
-        <v>78810</v>
+        <v>91012</v>
       </c>
       <c r="C99" t="inlineStr">
         <is>
@@ -11244,21 +11249,21 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
@@ -11268,10 +11273,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>452432</v>
+        <v>452833</v>
       </c>
       <c r="R99" t="n">
-        <v>6990942</v>
+        <v>6990388</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -11301,19 +11306,9 @@
           <t>2025-05-03</t>
         </is>
       </c>
-      <c r="Z99" t="inlineStr">
-        <is>
-          <t>11:05</t>
-        </is>
-      </c>
       <c r="AA99" t="inlineStr">
         <is>
           <t>2025-05-03</t>
-        </is>
-      </c>
-      <c r="AB99" t="inlineStr">
-        <is>
-          <t>11:05</t>
         </is>
       </c>
       <c r="AD99" t="b">
@@ -11328,22 +11323,22 @@
       <c r="AT99" t="inlineStr"/>
       <c r="AW99" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX99" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY99" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>124756721</v>
+        <v>124756765</v>
       </c>
       <c r="B100" t="n">
-        <v>79891</v>
+        <v>78810</v>
       </c>
       <c r="C100" t="inlineStr">
         <is>
@@ -11356,21 +11351,21 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
@@ -11380,10 +11375,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>452823</v>
+        <v>452432</v>
       </c>
       <c r="R100" t="n">
-        <v>6990261</v>
+        <v>6990942</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -11415,7 +11410,7 @@
       </c>
       <c r="Z100" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>11:05</t>
         </is>
       </c>
       <c r="AA100" t="inlineStr">
@@ -11425,7 +11420,7 @@
       </c>
       <c r="AB100" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>11:05</t>
         </is>
       </c>
       <c r="AD100" t="b">
@@ -11436,21 +11431,6 @@
       </c>
       <c r="AG100" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ100" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK100" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AO100" t="inlineStr">
-        <is>
-          <t>Omkullfallen grov stam # Salix caprea</t>
-        </is>
       </c>
       <c r="AT100" t="inlineStr"/>
       <c r="AW100" t="inlineStr">
@@ -11467,10 +11447,10 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>124753623</v>
+        <v>124756721</v>
       </c>
       <c r="B101" t="n">
-        <v>98101</v>
+        <v>79891</v>
       </c>
       <c r="C101" t="inlineStr">
         <is>
@@ -11479,25 +11459,25 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E101" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
@@ -11507,10 +11487,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>452510</v>
+        <v>452823</v>
       </c>
       <c r="R101" t="n">
-        <v>6990873</v>
+        <v>6990261</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -11540,14 +11520,19 @@
           <t>2025-05-03</t>
         </is>
       </c>
+      <c r="Z101" t="inlineStr">
+        <is>
+          <t>14:51</t>
+        </is>
+      </c>
       <c r="AA101" t="inlineStr">
         <is>
           <t>2025-05-03</t>
         </is>
       </c>
-      <c r="AC101" t="inlineStr">
-        <is>
-          <t>Minst 50</t>
+      <c r="AB101" t="inlineStr">
+        <is>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AD101" t="b">
@@ -11558,16 +11543,31 @@
       </c>
       <c r="AG101" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ101" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK101" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO101" t="inlineStr">
+        <is>
+          <t>Omkullfallen grov stam # Salix caprea</t>
+        </is>
       </c>
       <c r="AT101" t="inlineStr"/>
       <c r="AW101" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX101" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY101" t="inlineStr"/>
@@ -12787,10 +12787,10 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>124753638</v>
+        <v>124753634</v>
       </c>
       <c r="B113" t="n">
-        <v>78810</v>
+        <v>91008</v>
       </c>
       <c r="C113" t="inlineStr">
         <is>
@@ -12803,21 +12803,21 @@
         </is>
       </c>
       <c r="E113" t="n">
-        <v>6425</v>
+        <v>1108</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
@@ -12827,10 +12827,10 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>452823</v>
+        <v>452750</v>
       </c>
       <c r="R113" t="n">
-        <v>6990367</v>
+        <v>6990344</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -12889,10 +12889,10 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>124753634</v>
+        <v>124753638</v>
       </c>
       <c r="B114" t="n">
-        <v>91008</v>
+        <v>78810</v>
       </c>
       <c r="C114" t="inlineStr">
         <is>
@@ -12905,21 +12905,21 @@
         </is>
       </c>
       <c r="E114" t="n">
-        <v>1108</v>
+        <v>6425</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
@@ -12929,10 +12929,10 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>452750</v>
+        <v>452823</v>
       </c>
       <c r="R114" t="n">
-        <v>6990344</v>
+        <v>6990367</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -13689,7 +13689,7 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>124753579</v>
+        <v>124753588</v>
       </c>
       <c r="B121" t="n">
         <v>91012</v>
@@ -13729,10 +13729,10 @@
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>452710</v>
+        <v>452311</v>
       </c>
       <c r="R121" t="n">
-        <v>6990467</v>
+        <v>6990887</v>
       </c>
       <c r="S121" t="n">
         <v>10</v>
@@ -13791,7 +13791,7 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>124753588</v>
+        <v>124753587</v>
       </c>
       <c r="B122" t="n">
         <v>91012</v>
@@ -13831,10 +13831,10 @@
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>452311</v>
+        <v>452331</v>
       </c>
       <c r="R122" t="n">
-        <v>6990887</v>
+        <v>6990929</v>
       </c>
       <c r="S122" t="n">
         <v>10</v>
@@ -13893,10 +13893,10 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>124753587</v>
+        <v>124756751</v>
       </c>
       <c r="B123" t="n">
-        <v>91012</v>
+        <v>98101</v>
       </c>
       <c r="C123" t="inlineStr">
         <is>
@@ -13905,38 +13905,50 @@
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E123" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I123" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I123" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J123" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K123" t="inlineStr"/>
+      <c r="L123" t="inlineStr"/>
+      <c r="N123" t="inlineStr"/>
       <c r="P123" t="inlineStr">
         <is>
           <t>Häggsåsen N, Jmt</t>
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>452331</v>
+        <v>452638</v>
       </c>
       <c r="R123" t="n">
-        <v>6990929</v>
+        <v>6990559</v>
       </c>
       <c r="S123" t="n">
         <v>10</v>
@@ -13966,39 +13978,50 @@
           <t>2025-05-03</t>
         </is>
       </c>
+      <c r="Z123" t="inlineStr">
+        <is>
+          <t>12:23</t>
+        </is>
+      </c>
       <c r="AA123" t="inlineStr">
         <is>
           <t>2025-05-03</t>
         </is>
       </c>
+      <c r="AB123" t="inlineStr">
+        <is>
+          <t>12:23</t>
+        </is>
+      </c>
       <c r="AD123" t="b">
         <v>0</v>
       </c>
       <c r="AE123" t="b">
         <v>0</v>
       </c>
+      <c r="AF123" t="inlineStr"/>
       <c r="AG123" t="b">
         <v>0</v>
       </c>
       <c r="AT123" t="inlineStr"/>
       <c r="AW123" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX123" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY123" t="inlineStr"/>
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>124756748</v>
+        <v>124753579</v>
       </c>
       <c r="B124" t="n">
-        <v>78810</v>
+        <v>91012</v>
       </c>
       <c r="C124" t="inlineStr">
         <is>
@@ -14011,21 +14034,21 @@
         </is>
       </c>
       <c r="E124" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I124" t="inlineStr"/>
@@ -14035,10 +14058,10 @@
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>452609</v>
+        <v>452710</v>
       </c>
       <c r="R124" t="n">
-        <v>6990543</v>
+        <v>6990467</v>
       </c>
       <c r="S124" t="n">
         <v>10</v>
@@ -14068,19 +14091,9 @@
           <t>2025-05-03</t>
         </is>
       </c>
-      <c r="Z124" t="inlineStr">
-        <is>
-          <t>12:29</t>
-        </is>
-      </c>
       <c r="AA124" t="inlineStr">
         <is>
           <t>2025-05-03</t>
-        </is>
-      </c>
-      <c r="AB124" t="inlineStr">
-        <is>
-          <t>12:29</t>
         </is>
       </c>
       <c r="AD124" t="b">
@@ -14095,22 +14108,22 @@
       <c r="AT124" t="inlineStr"/>
       <c r="AW124" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX124" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY124" t="inlineStr"/>
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>124756751</v>
+        <v>124756748</v>
       </c>
       <c r="B125" t="n">
-        <v>98101</v>
+        <v>78810</v>
       </c>
       <c r="C125" t="inlineStr">
         <is>
@@ -14119,50 +14132,38 @@
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E125" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I125" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J125" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K125" t="inlineStr"/>
-      <c r="L125" t="inlineStr"/>
-      <c r="N125" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I125" t="inlineStr"/>
       <c r="P125" t="inlineStr">
         <is>
           <t>Häggsåsen N, Jmt</t>
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>452638</v>
+        <v>452609</v>
       </c>
       <c r="R125" t="n">
-        <v>6990559</v>
+        <v>6990543</v>
       </c>
       <c r="S125" t="n">
         <v>10</v>
@@ -14194,7 +14195,7 @@
       </c>
       <c r="Z125" t="inlineStr">
         <is>
-          <t>12:23</t>
+          <t>12:29</t>
         </is>
       </c>
       <c r="AA125" t="inlineStr">
@@ -14204,7 +14205,7 @@
       </c>
       <c r="AB125" t="inlineStr">
         <is>
-          <t>12:23</t>
+          <t>12:29</t>
         </is>
       </c>
       <c r="AD125" t="b">
@@ -14213,7 +14214,6 @@
       <c r="AE125" t="b">
         <v>0</v>
       </c>
-      <c r="AF125" t="inlineStr"/>
       <c r="AG125" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 16493-2025 artfynd.xlsx
+++ b/artfynd/A 16493-2025 artfynd.xlsx
@@ -985,10 +985,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124704581</v>
+        <v>124693275</v>
       </c>
       <c r="B5" t="n">
-        <v>91299</v>
+        <v>91026</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1001,34 +1001,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>658</v>
+        <v>1204</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Häggsåsen, Häggsåsen, Jmt</t>
+          <t>Tjärnflon, Tjärnflon, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>452839</v>
+        <v>452523</v>
       </c>
       <c r="R5" t="n">
-        <v>6990352</v>
+        <v>6990595</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1087,10 +1087,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124693275</v>
+        <v>124701352</v>
       </c>
       <c r="B6" t="n">
-        <v>91026</v>
+        <v>79892</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1103,34 +1103,39 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1204</v>
+        <v>2081</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Tjärnflon, Tjärnflon, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>452523</v>
+        <v>452657</v>
       </c>
       <c r="R6" t="n">
-        <v>6990595</v>
+        <v>6990499</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1163,6 +1168,11 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-05-02</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Rikligt med skrovellav, APOTECHIER på en av bålarna</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1189,10 +1199,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124701352</v>
+        <v>124704581</v>
       </c>
       <c r="B7" t="n">
-        <v>79892</v>
+        <v>91299</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1205,39 +1215,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>2081</v>
+        <v>658</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Tjärnflon, Tjärnflon, Jmt</t>
+          <t>Häggsåsen, Häggsåsen, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>452657</v>
+        <v>452839</v>
       </c>
       <c r="R7" t="n">
-        <v>6990499</v>
+        <v>6990352</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1270,11 +1275,6 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-05-02</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Rikligt med skrovellav, APOTECHIER på en av bålarna</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1616,10 +1616,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124689335</v>
+        <v>124703242</v>
       </c>
       <c r="B11" t="n">
-        <v>57513</v>
+        <v>91299</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1632,39 +1632,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>658</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Tjärnflon, Tjärnflon, Jmt</t>
+          <t>Häggsåsen, Häggsåsen, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>452249</v>
+        <v>452760</v>
       </c>
       <c r="R11" t="n">
-        <v>6990921</v>
+        <v>6990252</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1697,11 +1692,6 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-05-02</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1728,10 +1718,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124703242</v>
+        <v>124689335</v>
       </c>
       <c r="B12" t="n">
-        <v>91299</v>
+        <v>57513</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1744,34 +1734,39 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>658</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Häggsåsen, Häggsåsen, Jmt</t>
+          <t>Tjärnflon, Tjärnflon, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>452760</v>
+        <v>452249</v>
       </c>
       <c r="R12" t="n">
-        <v>6990252</v>
+        <v>6990921</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1804,6 +1799,11 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-05-02</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -5888,10 +5888,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>124753605</v>
+        <v>124753639</v>
       </c>
       <c r="B51" t="n">
-        <v>79892</v>
+        <v>78810</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -5904,21 +5904,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5928,10 +5928,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>452408</v>
+        <v>452511</v>
       </c>
       <c r="R51" t="n">
-        <v>6990952</v>
+        <v>6990733</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5990,10 +5990,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>124753587</v>
+        <v>124753607</v>
       </c>
       <c r="B52" t="n">
-        <v>91012</v>
+        <v>79891</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6006,21 +6006,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -6030,10 +6030,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>452331</v>
+        <v>452734</v>
       </c>
       <c r="R52" t="n">
-        <v>6990929</v>
+        <v>6990356</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6092,10 +6092,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>124753639</v>
+        <v>124753605</v>
       </c>
       <c r="B53" t="n">
-        <v>78810</v>
+        <v>79892</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6108,21 +6108,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -6132,10 +6132,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>452511</v>
+        <v>452408</v>
       </c>
       <c r="R53" t="n">
-        <v>6990733</v>
+        <v>6990952</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6194,10 +6194,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>124753607</v>
+        <v>124753587</v>
       </c>
       <c r="B54" t="n">
-        <v>79891</v>
+        <v>91012</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6210,21 +6210,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6234,10 +6234,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>452734</v>
+        <v>452331</v>
       </c>
       <c r="R54" t="n">
-        <v>6990356</v>
+        <v>6990929</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -7784,10 +7784,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>124756768</v>
+        <v>124753622</v>
       </c>
       <c r="B68" t="n">
-        <v>77743</v>
+        <v>98101</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -7796,25 +7796,25 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>228579</v>
+        <v>220787</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7824,10 +7824,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>452357</v>
+        <v>452472</v>
       </c>
       <c r="R68" t="n">
-        <v>6990970</v>
+        <v>6990821</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7857,19 +7857,14 @@
           <t>2025-05-03</t>
         </is>
       </c>
-      <c r="Z68" t="inlineStr">
-        <is>
-          <t>10:52</t>
-        </is>
-      </c>
       <c r="AA68" t="inlineStr">
         <is>
           <t>2025-05-03</t>
         </is>
       </c>
-      <c r="AB68" t="inlineStr">
-        <is>
-          <t>10:52</t>
+      <c r="AC68" t="inlineStr">
+        <is>
+          <t>Minst 50</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -7884,19 +7879,19 @@
       <c r="AT68" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>124753622</v>
+        <v>124756777</v>
       </c>
       <c r="B69" t="n">
         <v>98101</v>
@@ -7929,17 +7924,29 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I69" t="inlineStr"/>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J69" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K69" t="inlineStr"/>
+      <c r="L69" t="inlineStr"/>
+      <c r="N69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
           <t>Häggsåsen N, Jmt</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>452472</v>
+        <v>452146</v>
       </c>
       <c r="R69" t="n">
-        <v>6990821</v>
+        <v>6990839</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7969,14 +7976,19 @@
           <t>2025-05-03</t>
         </is>
       </c>
+      <c r="Z69" t="inlineStr">
+        <is>
+          <t>10:06</t>
+        </is>
+      </c>
       <c r="AA69" t="inlineStr">
         <is>
           <t>2025-05-03</t>
         </is>
       </c>
-      <c r="AC69" t="inlineStr">
-        <is>
-          <t>Minst 50</t>
+      <c r="AB69" t="inlineStr">
+        <is>
+          <t>10:06</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -7985,28 +7997,29 @@
       <c r="AE69" t="b">
         <v>0</v>
       </c>
+      <c r="AF69" t="inlineStr"/>
       <c r="AG69" t="b">
         <v>0</v>
       </c>
       <c r="AT69" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX69" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>124756777</v>
+        <v>124756768</v>
       </c>
       <c r="B70" t="n">
-        <v>98101</v>
+        <v>77743</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -8015,50 +8028,38 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>220787</v>
+        <v>228579</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I70" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J70" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K70" t="inlineStr"/>
-      <c r="L70" t="inlineStr"/>
-      <c r="N70" t="inlineStr"/>
+          <t>Tibell</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
           <t>Häggsåsen N, Jmt</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>452146</v>
+        <v>452357</v>
       </c>
       <c r="R70" t="n">
-        <v>6990839</v>
+        <v>6990970</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -8090,7 +8091,7 @@
       </c>
       <c r="Z70" t="inlineStr">
         <is>
-          <t>10:06</t>
+          <t>10:52</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
@@ -8100,7 +8101,7 @@
       </c>
       <c r="AB70" t="inlineStr">
         <is>
-          <t>10:06</t>
+          <t>10:52</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8109,7 +8110,6 @@
       <c r="AE70" t="b">
         <v>0</v>
       </c>
-      <c r="AF70" t="inlineStr"/>
       <c r="AG70" t="b">
         <v>0</v>
       </c>
@@ -10124,10 +10124,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>124753612</v>
+        <v>124756779</v>
       </c>
       <c r="B89" t="n">
-        <v>98101</v>
+        <v>78810</v>
       </c>
       <c r="C89" t="inlineStr">
         <is>
@@ -10136,25 +10136,25 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
@@ -10164,10 +10164,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>452924</v>
+        <v>452143</v>
       </c>
       <c r="R89" t="n">
-        <v>6990397</v>
+        <v>6990780</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -10197,14 +10197,19 @@
           <t>2025-05-03</t>
         </is>
       </c>
+      <c r="Z89" t="inlineStr">
+        <is>
+          <t>09:51</t>
+        </is>
+      </c>
       <c r="AA89" t="inlineStr">
         <is>
           <t>2025-05-03</t>
         </is>
       </c>
-      <c r="AC89" t="inlineStr">
-        <is>
-          <t>Minst 20</t>
+      <c r="AB89" t="inlineStr">
+        <is>
+          <t>09:51</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -10219,22 +10224,22 @@
       <c r="AT89" t="inlineStr"/>
       <c r="AW89" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX89" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>124756779</v>
+        <v>124756775</v>
       </c>
       <c r="B90" t="n">
-        <v>78810</v>
+        <v>79891</v>
       </c>
       <c r="C90" t="inlineStr">
         <is>
@@ -10247,21 +10252,21 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
@@ -10271,10 +10276,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>452143</v>
+        <v>452308</v>
       </c>
       <c r="R90" t="n">
-        <v>6990780</v>
+        <v>6990943</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -10306,7 +10311,7 @@
       </c>
       <c r="Z90" t="inlineStr">
         <is>
-          <t>09:51</t>
+          <t>10:22</t>
         </is>
       </c>
       <c r="AA90" t="inlineStr">
@@ -10316,7 +10321,7 @@
       </c>
       <c r="AB90" t="inlineStr">
         <is>
-          <t>09:51</t>
+          <t>10:22</t>
         </is>
       </c>
       <c r="AD90" t="b">
@@ -10343,7 +10348,7 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>124756775</v>
+        <v>124753610</v>
       </c>
       <c r="B91" t="n">
         <v>79891</v>
@@ -10383,10 +10388,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>452308</v>
+        <v>452435</v>
       </c>
       <c r="R91" t="n">
-        <v>6990943</v>
+        <v>6990938</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -10416,19 +10421,9 @@
           <t>2025-05-03</t>
         </is>
       </c>
-      <c r="Z91" t="inlineStr">
-        <is>
-          <t>10:22</t>
-        </is>
-      </c>
       <c r="AA91" t="inlineStr">
         <is>
           <t>2025-05-03</t>
-        </is>
-      </c>
-      <c r="AB91" t="inlineStr">
-        <is>
-          <t>10:22</t>
         </is>
       </c>
       <c r="AD91" t="b">
@@ -10443,22 +10438,22 @@
       <c r="AT91" t="inlineStr"/>
       <c r="AW91" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX91" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>124753610</v>
+        <v>124753612</v>
       </c>
       <c r="B92" t="n">
-        <v>79891</v>
+        <v>98101</v>
       </c>
       <c r="C92" t="inlineStr">
         <is>
@@ -10467,25 +10462,25 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
@@ -10495,10 +10490,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>452435</v>
+        <v>452924</v>
       </c>
       <c r="R92" t="n">
-        <v>6990938</v>
+        <v>6990397</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -10531,6 +10526,11 @@
       <c r="AA92" t="inlineStr">
         <is>
           <t>2025-05-03</t>
+        </is>
+      </c>
+      <c r="AC92" t="inlineStr">
+        <is>
+          <t>Minst 20</t>
         </is>
       </c>
       <c r="AD92" t="b">
@@ -10557,10 +10557,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>124753578</v>
+        <v>124756742</v>
       </c>
       <c r="B93" t="n">
-        <v>91012</v>
+        <v>79927</v>
       </c>
       <c r="C93" t="inlineStr">
         <is>
@@ -10569,25 +10569,25 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>1202</v>
+        <v>6464</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
@@ -10597,10 +10597,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>452743</v>
+        <v>452682</v>
       </c>
       <c r="R93" t="n">
-        <v>6990405</v>
+        <v>6990476</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -10630,11 +10630,21 @@
           <t>2025-05-03</t>
         </is>
       </c>
+      <c r="Z93" t="inlineStr">
+        <is>
+          <t>13:53</t>
+        </is>
+      </c>
       <c r="AA93" t="inlineStr">
         <is>
           <t>2025-05-03</t>
         </is>
       </c>
+      <c r="AB93" t="inlineStr">
+        <is>
+          <t>13:53</t>
+        </is>
+      </c>
       <c r="AD93" t="b">
         <v>0</v>
       </c>
@@ -10643,26 +10653,41 @@
       </c>
       <c r="AG93" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ93" t="inlineStr">
+        <is>
+          <t>rönn</t>
+        </is>
+      </c>
+      <c r="AK93" t="inlineStr">
+        <is>
+          <t>Sorbus aucuparia</t>
+        </is>
+      </c>
+      <c r="AO93" t="inlineStr">
+        <is>
+          <t>Sorbus aucuparia</t>
+        </is>
       </c>
       <c r="AT93" t="inlineStr"/>
       <c r="AW93" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX93" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY93" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>124756758</v>
+        <v>124756767</v>
       </c>
       <c r="B94" t="n">
-        <v>90962</v>
+        <v>78810</v>
       </c>
       <c r="C94" t="inlineStr">
         <is>
@@ -10675,21 +10700,21 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>112</v>
+        <v>6425</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Stjärntagging</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Asterodon ferruginosus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>Pat.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
@@ -10699,10 +10724,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>452509</v>
+        <v>452362</v>
       </c>
       <c r="R94" t="n">
-        <v>6990778</v>
+        <v>6991003</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -10734,7 +10759,7 @@
       </c>
       <c r="Z94" t="inlineStr">
         <is>
-          <t>11:40</t>
+          <t>10:55</t>
         </is>
       </c>
       <c r="AA94" t="inlineStr">
@@ -10744,7 +10769,7 @@
       </c>
       <c r="AB94" t="inlineStr">
         <is>
-          <t>11:40</t>
+          <t>10:55</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -10771,10 +10796,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>124756718</v>
+        <v>124753578</v>
       </c>
       <c r="B95" t="n">
-        <v>91030</v>
+        <v>91012</v>
       </c>
       <c r="C95" t="inlineStr">
         <is>
@@ -10787,21 +10812,21 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>5432</v>
+        <v>1202</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
@@ -10811,10 +10836,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>452857</v>
+        <v>452743</v>
       </c>
       <c r="R95" t="n">
-        <v>6990267</v>
+        <v>6990405</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10844,19 +10869,9 @@
           <t>2025-05-03</t>
         </is>
       </c>
-      <c r="Z95" t="inlineStr">
-        <is>
-          <t>15:03</t>
-        </is>
-      </c>
       <c r="AA95" t="inlineStr">
         <is>
           <t>2025-05-03</t>
-        </is>
-      </c>
-      <c r="AB95" t="inlineStr">
-        <is>
-          <t>15:03</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -10871,22 +10886,22 @@
       <c r="AT95" t="inlineStr"/>
       <c r="AW95" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX95" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY95" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>124756742</v>
+        <v>124756758</v>
       </c>
       <c r="B96" t="n">
-        <v>79927</v>
+        <v>90962</v>
       </c>
       <c r="C96" t="inlineStr">
         <is>
@@ -10895,25 +10910,25 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E96" t="n">
-        <v>6464</v>
+        <v>112</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Stjärntagging</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Asterodon ferruginosus</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>Pat.</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
@@ -10923,10 +10938,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>452682</v>
+        <v>452509</v>
       </c>
       <c r="R96" t="n">
-        <v>6990476</v>
+        <v>6990778</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -10958,7 +10973,7 @@
       </c>
       <c r="Z96" t="inlineStr">
         <is>
-          <t>13:53</t>
+          <t>11:40</t>
         </is>
       </c>
       <c r="AA96" t="inlineStr">
@@ -10968,7 +10983,7 @@
       </c>
       <c r="AB96" t="inlineStr">
         <is>
-          <t>13:53</t>
+          <t>11:40</t>
         </is>
       </c>
       <c r="AD96" t="b">
@@ -10979,21 +10994,6 @@
       </c>
       <c r="AG96" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ96" t="inlineStr">
-        <is>
-          <t>rönn</t>
-        </is>
-      </c>
-      <c r="AK96" t="inlineStr">
-        <is>
-          <t>Sorbus aucuparia</t>
-        </is>
-      </c>
-      <c r="AO96" t="inlineStr">
-        <is>
-          <t>Sorbus aucuparia</t>
-        </is>
       </c>
       <c r="AT96" t="inlineStr"/>
       <c r="AW96" t="inlineStr">
@@ -11010,10 +11010,10 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>124756767</v>
+        <v>124756718</v>
       </c>
       <c r="B97" t="n">
-        <v>78810</v>
+        <v>91030</v>
       </c>
       <c r="C97" t="inlineStr">
         <is>
@@ -11026,21 +11026,21 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
@@ -11050,10 +11050,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>452362</v>
+        <v>452857</v>
       </c>
       <c r="R97" t="n">
-        <v>6991003</v>
+        <v>6990267</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -11085,7 +11085,7 @@
       </c>
       <c r="Z97" t="inlineStr">
         <is>
-          <t>10:55</t>
+          <t>15:03</t>
         </is>
       </c>
       <c r="AA97" t="inlineStr">
@@ -11095,7 +11095,7 @@
       </c>
       <c r="AB97" t="inlineStr">
         <is>
-          <t>10:55</t>
+          <t>15:03</t>
         </is>
       </c>
       <c r="AD97" t="b">
@@ -12898,10 +12898,10 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>124756748</v>
+        <v>124753609</v>
       </c>
       <c r="B114" t="n">
-        <v>78810</v>
+        <v>79891</v>
       </c>
       <c r="C114" t="inlineStr">
         <is>
@@ -12914,21 +12914,21 @@
         </is>
       </c>
       <c r="E114" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
@@ -12938,10 +12938,10 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>452609</v>
+        <v>452528</v>
       </c>
       <c r="R114" t="n">
-        <v>6990543</v>
+        <v>6990710</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -12971,19 +12971,9 @@
           <t>2025-05-03</t>
         </is>
       </c>
-      <c r="Z114" t="inlineStr">
-        <is>
-          <t>12:29</t>
-        </is>
-      </c>
       <c r="AA114" t="inlineStr">
         <is>
           <t>2025-05-03</t>
-        </is>
-      </c>
-      <c r="AB114" t="inlineStr">
-        <is>
-          <t>12:29</t>
         </is>
       </c>
       <c r="AD114" t="b">
@@ -12998,22 +12988,22 @@
       <c r="AT114" t="inlineStr"/>
       <c r="AW114" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX114" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY114" t="inlineStr"/>
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>124756743</v>
+        <v>124753635</v>
       </c>
       <c r="B115" t="n">
-        <v>79891</v>
+        <v>91030</v>
       </c>
       <c r="C115" t="inlineStr">
         <is>
@@ -13026,21 +13016,21 @@
         </is>
       </c>
       <c r="E115" t="n">
-        <v>6458</v>
+        <v>5432</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
@@ -13050,10 +13040,10 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>452682</v>
+        <v>452732</v>
       </c>
       <c r="R115" t="n">
-        <v>6990476</v>
+        <v>6990486</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -13083,21 +13073,11 @@
           <t>2025-05-03</t>
         </is>
       </c>
-      <c r="Z115" t="inlineStr">
-        <is>
-          <t>13:53</t>
-        </is>
-      </c>
       <c r="AA115" t="inlineStr">
         <is>
           <t>2025-05-03</t>
         </is>
       </c>
-      <c r="AB115" t="inlineStr">
-        <is>
-          <t>13:53</t>
-        </is>
-      </c>
       <c r="AD115" t="b">
         <v>0</v>
       </c>
@@ -13106,41 +13086,26 @@
       </c>
       <c r="AG115" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ115" t="inlineStr">
-        <is>
-          <t>rönn</t>
-        </is>
-      </c>
-      <c r="AK115" t="inlineStr">
-        <is>
-          <t>Sorbus aucuparia</t>
-        </is>
-      </c>
-      <c r="AO115" t="inlineStr">
-        <is>
-          <t>Sorbus aucuparia</t>
-        </is>
       </c>
       <c r="AT115" t="inlineStr"/>
       <c r="AW115" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX115" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY115" t="inlineStr"/>
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>124753609</v>
+        <v>124756748</v>
       </c>
       <c r="B116" t="n">
-        <v>79891</v>
+        <v>78810</v>
       </c>
       <c r="C116" t="inlineStr">
         <is>
@@ -13153,21 +13118,21 @@
         </is>
       </c>
       <c r="E116" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
@@ -13177,10 +13142,10 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>452528</v>
+        <v>452609</v>
       </c>
       <c r="R116" t="n">
-        <v>6990710</v>
+        <v>6990543</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -13210,9 +13175,19 @@
           <t>2025-05-03</t>
         </is>
       </c>
+      <c r="Z116" t="inlineStr">
+        <is>
+          <t>12:29</t>
+        </is>
+      </c>
       <c r="AA116" t="inlineStr">
         <is>
           <t>2025-05-03</t>
+        </is>
+      </c>
+      <c r="AB116" t="inlineStr">
+        <is>
+          <t>12:29</t>
         </is>
       </c>
       <c r="AD116" t="b">
@@ -13227,22 +13202,22 @@
       <c r="AT116" t="inlineStr"/>
       <c r="AW116" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX116" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY116" t="inlineStr"/>
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>124753635</v>
+        <v>124756743</v>
       </c>
       <c r="B117" t="n">
-        <v>91030</v>
+        <v>79891</v>
       </c>
       <c r="C117" t="inlineStr">
         <is>
@@ -13255,21 +13230,21 @@
         </is>
       </c>
       <c r="E117" t="n">
-        <v>5432</v>
+        <v>6458</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
@@ -13279,10 +13254,10 @@
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>452732</v>
+        <v>452682</v>
       </c>
       <c r="R117" t="n">
-        <v>6990486</v>
+        <v>6990476</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>
@@ -13312,11 +13287,21 @@
           <t>2025-05-03</t>
         </is>
       </c>
+      <c r="Z117" t="inlineStr">
+        <is>
+          <t>13:53</t>
+        </is>
+      </c>
       <c r="AA117" t="inlineStr">
         <is>
           <t>2025-05-03</t>
         </is>
       </c>
+      <c r="AB117" t="inlineStr">
+        <is>
+          <t>13:53</t>
+        </is>
+      </c>
       <c r="AD117" t="b">
         <v>0</v>
       </c>
@@ -13325,16 +13310,31 @@
       </c>
       <c r="AG117" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ117" t="inlineStr">
+        <is>
+          <t>rönn</t>
+        </is>
+      </c>
+      <c r="AK117" t="inlineStr">
+        <is>
+          <t>Sorbus aucuparia</t>
+        </is>
+      </c>
+      <c r="AO117" t="inlineStr">
+        <is>
+          <t>Sorbus aucuparia</t>
+        </is>
       </c>
       <c r="AT117" t="inlineStr"/>
       <c r="AW117" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX117" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY117" t="inlineStr"/>
@@ -14344,10 +14344,10 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>124753584</v>
+        <v>124753604</v>
       </c>
       <c r="B127" t="n">
-        <v>91012</v>
+        <v>79892</v>
       </c>
       <c r="C127" t="inlineStr">
         <is>
@@ -14360,21 +14360,21 @@
         </is>
       </c>
       <c r="E127" t="n">
-        <v>1202</v>
+        <v>2081</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I127" t="inlineStr"/>
@@ -14384,10 +14384,10 @@
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>452444</v>
+        <v>452435</v>
       </c>
       <c r="R127" t="n">
-        <v>6990774</v>
+        <v>6990938</v>
       </c>
       <c r="S127" t="n">
         <v>10</v>
@@ -14446,10 +14446,10 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>124753592</v>
+        <v>124753584</v>
       </c>
       <c r="B128" t="n">
-        <v>57513</v>
+        <v>91012</v>
       </c>
       <c r="C128" t="inlineStr">
         <is>
@@ -14462,21 +14462,21 @@
         </is>
       </c>
       <c r="E128" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I128" t="inlineStr"/>
@@ -14486,10 +14486,10 @@
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>452396</v>
+        <v>452444</v>
       </c>
       <c r="R128" t="n">
-        <v>6990703</v>
+        <v>6990774</v>
       </c>
       <c r="S128" t="n">
         <v>10</v>
@@ -14522,11 +14522,6 @@
       <c r="AA128" t="inlineStr">
         <is>
           <t>2025-05-03</t>
-        </is>
-      </c>
-      <c r="AC128" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD128" t="b">
@@ -14553,10 +14548,10 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>124753604</v>
+        <v>124753592</v>
       </c>
       <c r="B129" t="n">
-        <v>79892</v>
+        <v>57513</v>
       </c>
       <c r="C129" t="inlineStr">
         <is>
@@ -14569,21 +14564,21 @@
         </is>
       </c>
       <c r="E129" t="n">
-        <v>2081</v>
+        <v>100109</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I129" t="inlineStr"/>
@@ -14593,10 +14588,10 @@
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>452435</v>
+        <v>452396</v>
       </c>
       <c r="R129" t="n">
-        <v>6990938</v>
+        <v>6990703</v>
       </c>
       <c r="S129" t="n">
         <v>10</v>
@@ -14629,6 +14624,11 @@
       <c r="AA129" t="inlineStr">
         <is>
           <t>2025-05-03</t>
+        </is>
+      </c>
+      <c r="AC129" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD129" t="b">

--- a/artfynd/A 16493-2025 artfynd.xlsx
+++ b/artfynd/A 16493-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124702770</v>
+        <v>124694574</v>
       </c>
       <c r="B2" t="n">
-        <v>79891</v>
+        <v>57635</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,34 +691,39 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Häggsåsen, Häggsåsen, Jmt</t>
+          <t>Tjärnflon, Tjärnflon, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>452731</v>
+        <v>452630</v>
       </c>
       <c r="R2" t="n">
-        <v>6990355</v>
+        <v>6990651</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -751,6 +756,11 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-05-02</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -777,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124705584</v>
+        <v>124689546</v>
       </c>
       <c r="B3" t="n">
-        <v>91030</v>
+        <v>57635</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,34 +803,39 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Häggsåsen, Häggsåsen, Jmt</t>
+          <t>Tjärnflon, Tjärnflon, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>452865</v>
+        <v>452319</v>
       </c>
       <c r="R3" t="n">
-        <v>6990382</v>
+        <v>6990963</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -853,6 +868,11 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-05-02</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -879,10 +899,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124689528</v>
+        <v>124721354</v>
       </c>
       <c r="B4" t="n">
-        <v>57513</v>
+        <v>57635</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -924,10 +944,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>452301</v>
+        <v>452514</v>
       </c>
       <c r="R4" t="n">
-        <v>6990964</v>
+        <v>6990587</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -991,10 +1011,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124721354</v>
+        <v>124705813</v>
       </c>
       <c r="B5" t="n">
-        <v>57513</v>
+        <v>57635</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1027,19 +1047,19 @@
       <c r="I5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>gammalt bo</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Tjärnflon, Tjärnflon, Jmt</t>
+          <t>Häggsåsen, Häggsåsen, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>452514</v>
+        <v>452865</v>
       </c>
       <c r="R5" t="n">
-        <v>6990587</v>
+        <v>6990385</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1076,7 +1096,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Möjligt gammalt bo 3m upp i granstubbe med granticka på</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1103,10 +1123,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124693275</v>
+        <v>124701516</v>
       </c>
       <c r="B6" t="n">
-        <v>91026</v>
+        <v>91459</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1119,21 +1139,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1204</v>
+        <v>658</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1143,10 +1163,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>452523</v>
+        <v>452635</v>
       </c>
       <c r="R6" t="n">
-        <v>6990595</v>
+        <v>6990463</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1205,10 +1225,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124706950</v>
+        <v>124703646</v>
       </c>
       <c r="B7" t="n">
-        <v>98101</v>
+        <v>91162</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1217,42 +1237,38 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>1108</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
-      </c>
+          <t>(Fr.) Krieglst.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Häggsåsen, Häggsåsen, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>453007</v>
+        <v>452785</v>
       </c>
       <c r="R7" t="n">
-        <v>6990356</v>
+        <v>6990307</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1311,10 +1327,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124704608</v>
+        <v>124693950</v>
       </c>
       <c r="B8" t="n">
-        <v>91012</v>
+        <v>91166</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1347,14 +1363,14 @@
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Häggsåsen, Häggsåsen, Jmt</t>
+          <t>Tjärnflon, Tjärnflon, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>452839</v>
+        <v>452582</v>
       </c>
       <c r="R8" t="n">
-        <v>6990352</v>
+        <v>6990572</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1413,10 +1429,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124702530</v>
+        <v>124691814</v>
       </c>
       <c r="B9" t="n">
-        <v>79891</v>
+        <v>56828</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1429,34 +1445,43 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6458</v>
+        <v>102612</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>förbiflygande</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Häggsåsen, Häggsåsen, Jmt</t>
+          <t>Tjärnflon, Tjärnflon, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>452746</v>
+        <v>452489</v>
       </c>
       <c r="R9" t="n">
-        <v>6990384</v>
+        <v>6990896</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1515,10 +1540,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124701352</v>
+        <v>124695256</v>
       </c>
       <c r="B10" t="n">
-        <v>79892</v>
+        <v>98269</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1527,31 +1552,30 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>2081</v>
+        <v>220787</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>24</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
@@ -1560,10 +1584,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>452657</v>
+        <v>452624</v>
       </c>
       <c r="R10" t="n">
-        <v>6990499</v>
+        <v>6990535</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1596,11 +1620,6 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-05-02</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Rikligt med skrovellav, APOTECHIER på en av bålarna</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1627,10 +1646,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124691814</v>
+        <v>124689655</v>
       </c>
       <c r="B11" t="n">
-        <v>56714</v>
+        <v>91459</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1643,43 +1662,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>102612</v>
+        <v>658</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>förbiflygande</t>
-        </is>
-      </c>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Tjärnflon, Tjärnflon, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>452489</v>
+        <v>452312</v>
       </c>
       <c r="R11" t="n">
-        <v>6990896</v>
+        <v>6990961</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1738,10 +1748,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124695424</v>
+        <v>124705215</v>
       </c>
       <c r="B12" t="n">
-        <v>91012</v>
+        <v>91166</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1774,14 +1784,14 @@
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Tjärnflon, Tjärnflon, Jmt</t>
+          <t>Häggsåsen, Häggsåsen, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>452642</v>
+        <v>452850</v>
       </c>
       <c r="R12" t="n">
-        <v>6990548</v>
+        <v>6990404</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1840,10 +1850,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124695367</v>
+        <v>124695424</v>
       </c>
       <c r="B13" t="n">
-        <v>82597</v>
+        <v>91166</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1856,21 +1866,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1312</v>
+        <v>1202</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1880,10 +1890,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>452617</v>
+        <v>452642</v>
       </c>
       <c r="R13" t="n">
-        <v>6990540</v>
+        <v>6990548</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1942,10 +1952,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124688930</v>
+        <v>124705584</v>
       </c>
       <c r="B14" t="n">
-        <v>79891</v>
+        <v>91184</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1958,34 +1968,34 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6458</v>
+        <v>5432</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Tjärnflon, Tjärnflon, Jmt</t>
+          <t>Häggsåsen, Häggsåsen, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>452168</v>
+        <v>452865</v>
       </c>
       <c r="R14" t="n">
-        <v>6990824</v>
+        <v>6990382</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2044,10 +2054,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124689335</v>
+        <v>124689475</v>
       </c>
       <c r="B15" t="n">
-        <v>57513</v>
+        <v>57635</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2089,10 +2099,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>452249</v>
+        <v>452291</v>
       </c>
       <c r="R15" t="n">
-        <v>6990921</v>
+        <v>6990952</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2156,10 +2166,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124704726</v>
+        <v>124699720</v>
       </c>
       <c r="B16" t="n">
-        <v>91012</v>
+        <v>80029</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2172,34 +2182,34 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1202</v>
+        <v>2081</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Häggsåsen, Häggsåsen, Jmt</t>
+          <t>Tjärnflon, Tjärnflon, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>452828</v>
+        <v>452650</v>
       </c>
       <c r="R16" t="n">
-        <v>6990384</v>
+        <v>6990495</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2258,10 +2268,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>124689574</v>
+        <v>124706864</v>
       </c>
       <c r="B17" t="n">
-        <v>57513</v>
+        <v>57635</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2294,19 +2304,19 @@
       <c r="I17" t="inlineStr"/>
       <c r="M17" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Tjärnflon, Tjärnflon, Jmt</t>
+          <t>Häggsåsen, Häggsåsen, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>452326</v>
+        <v>453007</v>
       </c>
       <c r="R17" t="n">
-        <v>6990987</v>
+        <v>6990356</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2370,10 +2380,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>124703646</v>
+        <v>124706950</v>
       </c>
       <c r="B18" t="n">
-        <v>91008</v>
+        <v>98269</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2382,38 +2392,42 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1108</v>
+        <v>220787</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Häggsåsen, Häggsåsen, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>452785</v>
+        <v>453007</v>
       </c>
       <c r="R18" t="n">
-        <v>6990307</v>
+        <v>6990356</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2472,10 +2486,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>124705215</v>
+        <v>124691378</v>
       </c>
       <c r="B19" t="n">
-        <v>91012</v>
+        <v>91166</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2508,14 +2522,14 @@
       <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Häggsåsen, Häggsåsen, Jmt</t>
+          <t>Tjärnflon, Tjärnflon, Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>452850</v>
+        <v>452431</v>
       </c>
       <c r="R19" t="n">
-        <v>6990404</v>
+        <v>6990946</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2574,10 +2588,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>124721401</v>
+        <v>124703242</v>
       </c>
       <c r="B20" t="n">
-        <v>57513</v>
+        <v>91459</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2590,39 +2604,34 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100109</v>
+        <v>658</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Tjärnflon, Tjärnflon, Jmt</t>
+          <t>Häggsåsen, Häggsåsen, Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>452415</v>
+        <v>452760</v>
       </c>
       <c r="R20" t="n">
-        <v>6990714</v>
+        <v>6990252</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2655,11 +2664,6 @@
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-05-02</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2686,10 +2690,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>124689504</v>
+        <v>124699728</v>
       </c>
       <c r="B21" t="n">
-        <v>57513</v>
+        <v>80028</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2702,39 +2706,34 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Tjärnflon, Tjärnflon, Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>452322</v>
+        <v>452650</v>
       </c>
       <c r="R21" t="n">
-        <v>6990950</v>
+        <v>6990495</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2767,11 +2766,6 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-05-02</t>
-        </is>
-      </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2798,10 +2792,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>124689475</v>
+        <v>124721401</v>
       </c>
       <c r="B22" t="n">
-        <v>57513</v>
+        <v>57635</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2843,10 +2837,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>452291</v>
+        <v>452415</v>
       </c>
       <c r="R22" t="n">
-        <v>6990952</v>
+        <v>6990714</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2910,10 +2904,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>124691378</v>
+        <v>124689335</v>
       </c>
       <c r="B23" t="n">
-        <v>91012</v>
+        <v>57635</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2926,34 +2920,39 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Tjärnflon, Tjärnflon, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>452431</v>
+        <v>452249</v>
       </c>
       <c r="R23" t="n">
-        <v>6990946</v>
+        <v>6990921</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2986,6 +2985,11 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-05-02</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3012,10 +3016,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>124689546</v>
+        <v>124688835</v>
       </c>
       <c r="B24" t="n">
-        <v>57513</v>
+        <v>78947</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3028,27 +3032,27 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
@@ -3057,10 +3061,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>452319</v>
+        <v>452142</v>
       </c>
       <c r="R24" t="n">
-        <v>6990963</v>
+        <v>6990800</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3093,11 +3097,6 @@
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-05-02</t>
-        </is>
-      </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3124,10 +3123,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>124689655</v>
+        <v>124693275</v>
       </c>
       <c r="B25" t="n">
-        <v>91299</v>
+        <v>91180</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3140,21 +3139,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>658</v>
+        <v>1204</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3164,10 +3163,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>452312</v>
+        <v>452523</v>
       </c>
       <c r="R25" t="n">
-        <v>6990961</v>
+        <v>6990595</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3226,10 +3225,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>124701516</v>
+        <v>124691533</v>
       </c>
       <c r="B26" t="n">
-        <v>91299</v>
+        <v>80028</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3242,21 +3241,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>658</v>
+        <v>6458</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3266,10 +3265,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>452635</v>
+        <v>452427</v>
       </c>
       <c r="R26" t="n">
-        <v>6990463</v>
+        <v>6990925</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3328,10 +3327,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>124703242</v>
+        <v>124689528</v>
       </c>
       <c r="B27" t="n">
-        <v>91299</v>
+        <v>57635</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3344,34 +3343,39 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>658</v>
+        <v>100109</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Häggsåsen, Häggsåsen, Jmt</t>
+          <t>Tjärnflon, Tjärnflon, Jmt</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>452760</v>
+        <v>452301</v>
       </c>
       <c r="R27" t="n">
-        <v>6990252</v>
+        <v>6990964</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3404,6 +3408,11 @@
       <c r="AA27" t="inlineStr">
         <is>
           <t>2025-05-02</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3430,10 +3439,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>124699728</v>
+        <v>124689504</v>
       </c>
       <c r="B28" t="n">
-        <v>79891</v>
+        <v>57635</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3446,34 +3455,39 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P28" t="inlineStr">
         <is>
           <t>Tjärnflon, Tjärnflon, Jmt</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>452650</v>
+        <v>452322</v>
       </c>
       <c r="R28" t="n">
-        <v>6990495</v>
+        <v>6990950</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3506,6 +3520,11 @@
       <c r="AA28" t="inlineStr">
         <is>
           <t>2025-05-02</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3535,7 +3554,7 @@
         <v>124704478</v>
       </c>
       <c r="B29" t="n">
-        <v>57513</v>
+        <v>57635</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3644,10 +3663,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>124688835</v>
+        <v>124702770</v>
       </c>
       <c r="B30" t="n">
-        <v>78810</v>
+        <v>80028</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3660,39 +3679,34 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
-      <c r="K30" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Tjärnflon, Tjärnflon, Jmt</t>
+          <t>Häggsåsen, Häggsåsen, Jmt</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>452142</v>
+        <v>452731</v>
       </c>
       <c r="R30" t="n">
-        <v>6990800</v>
+        <v>6990355</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3751,10 +3765,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>124695256</v>
+        <v>124704726</v>
       </c>
       <c r="B31" t="n">
-        <v>98101</v>
+        <v>91166</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3763,42 +3777,38 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Tjärnflon, Tjärnflon, Jmt</t>
+          <t>Häggsåsen, Häggsåsen, Jmt</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>452624</v>
+        <v>452828</v>
       </c>
       <c r="R31" t="n">
-        <v>6990535</v>
+        <v>6990384</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3857,10 +3867,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>124704581</v>
+        <v>124691528</v>
       </c>
       <c r="B32" t="n">
-        <v>91299</v>
+        <v>80029</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3873,34 +3883,34 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>658</v>
+        <v>2081</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Häggsåsen, Häggsåsen, Jmt</t>
+          <t>Tjärnflon, Tjärnflon, Jmt</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>452839</v>
+        <v>452427</v>
       </c>
       <c r="R32" t="n">
-        <v>6990352</v>
+        <v>6990925</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3959,10 +3969,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>124693950</v>
+        <v>124702902</v>
       </c>
       <c r="B33" t="n">
-        <v>91012</v>
+        <v>80028</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -3975,34 +3985,34 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Tjärnflon, Tjärnflon, Jmt</t>
+          <t>Häggsåsen, Häggsåsen, Jmt</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>452582</v>
+        <v>452734</v>
       </c>
       <c r="R33" t="n">
-        <v>6990572</v>
+        <v>6990348</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4061,10 +4071,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>124694574</v>
+        <v>124701352</v>
       </c>
       <c r="B34" t="n">
-        <v>57513</v>
+        <v>80029</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4077,27 +4087,27 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>100109</v>
+        <v>2081</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
-      <c r="M34" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
@@ -4106,10 +4116,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>452630</v>
+        <v>452657</v>
       </c>
       <c r="R34" t="n">
-        <v>6990651</v>
+        <v>6990499</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4146,7 +4156,7 @@
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>Färska ringhack på tall</t>
+          <t>Rikligt med skrovellav, APOTECHIER på en av bålarna</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4173,10 +4183,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>124699720</v>
+        <v>124688930</v>
       </c>
       <c r="B35" t="n">
-        <v>79892</v>
+        <v>80028</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4189,21 +4199,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>2081</v>
+        <v>6458</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4213,10 +4223,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>452650</v>
+        <v>452168</v>
       </c>
       <c r="R35" t="n">
-        <v>6990495</v>
+        <v>6990824</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4275,10 +4285,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>124689645</v>
+        <v>124704608</v>
       </c>
       <c r="B36" t="n">
-        <v>91012</v>
+        <v>91166</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4311,14 +4321,14 @@
       <c r="I36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Tjärnflon, Tjärnflon, Jmt</t>
+          <t>Häggsåsen, Häggsåsen, Jmt</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>452311</v>
+        <v>452839</v>
       </c>
       <c r="R36" t="n">
-        <v>6990960</v>
+        <v>6990352</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4377,10 +4387,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>124705813</v>
+        <v>124706585</v>
       </c>
       <c r="B37" t="n">
-        <v>57513</v>
+        <v>77879</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4393,39 +4403,34 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>100109</v>
+        <v>228579</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
-      <c r="M37" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
       <c r="P37" t="inlineStr">
         <is>
           <t>Häggsåsen, Häggsåsen, Jmt</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>452865</v>
+        <v>452913</v>
       </c>
       <c r="R37" t="n">
-        <v>6990385</v>
+        <v>6990390</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4458,11 +4463,6 @@
       <c r="AA37" t="inlineStr">
         <is>
           <t>2025-05-02</t>
-        </is>
-      </c>
-      <c r="AC37" t="inlineStr">
-        <is>
-          <t>Möjligt gammalt bo 3m upp i granstubbe med granticka på</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4489,10 +4489,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>124702902</v>
+        <v>124704581</v>
       </c>
       <c r="B38" t="n">
-        <v>79891</v>
+        <v>91459</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4505,21 +4505,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6458</v>
+        <v>658</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4529,10 +4529,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>452734</v>
+        <v>452839</v>
       </c>
       <c r="R38" t="n">
-        <v>6990348</v>
+        <v>6990352</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4591,10 +4591,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>124691533</v>
+        <v>124689645</v>
       </c>
       <c r="B39" t="n">
-        <v>79891</v>
+        <v>91166</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4607,21 +4607,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4631,10 +4631,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>452427</v>
+        <v>452311</v>
       </c>
       <c r="R39" t="n">
-        <v>6990925</v>
+        <v>6990960</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4693,10 +4693,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>124706864</v>
+        <v>124689574</v>
       </c>
       <c r="B40" t="n">
-        <v>57513</v>
+        <v>57635</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4729,19 +4729,19 @@
       <c r="I40" t="inlineStr"/>
       <c r="M40" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Häggsåsen, Häggsåsen, Jmt</t>
+          <t>Tjärnflon, Tjärnflon, Jmt</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>453007</v>
+        <v>452326</v>
       </c>
       <c r="R40" t="n">
-        <v>6990356</v>
+        <v>6990987</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4805,10 +4805,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>124691528</v>
+        <v>124695367</v>
       </c>
       <c r="B41" t="n">
-        <v>79892</v>
+        <v>82737</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4821,21 +4821,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>2081</v>
+        <v>1312</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4845,10 +4845,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>452427</v>
+        <v>452617</v>
       </c>
       <c r="R41" t="n">
-        <v>6990925</v>
+        <v>6990540</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4907,10 +4907,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>124706585</v>
+        <v>124702530</v>
       </c>
       <c r="B42" t="n">
-        <v>77743</v>
+        <v>80028</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -4923,21 +4923,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>228579</v>
+        <v>6458</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4947,10 +4947,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>452913</v>
+        <v>452746</v>
       </c>
       <c r="R42" t="n">
-        <v>6990390</v>
+        <v>6990384</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5009,10 +5009,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>124756741</v>
+        <v>124756757</v>
       </c>
       <c r="B43" t="n">
-        <v>79851</v>
+        <v>77879</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5021,25 +5021,25 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>229497</v>
+        <v>228579</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5049,10 +5049,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>452682</v>
+        <v>452506</v>
       </c>
       <c r="R43" t="n">
-        <v>6990476</v>
+        <v>6990737</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5084,7 +5084,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>13:54</t>
+          <t>11:47</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5094,7 +5094,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>13:54</t>
+          <t>11:47</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5105,21 +5105,6 @@
       </c>
       <c r="AG43" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ43" t="inlineStr">
-        <is>
-          <t>rönn</t>
-        </is>
-      </c>
-      <c r="AK43" t="inlineStr">
-        <is>
-          <t>Sorbus aucuparia</t>
-        </is>
-      </c>
-      <c r="AO43" t="inlineStr">
-        <is>
-          <t>Sorbus aucuparia</t>
-        </is>
       </c>
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
@@ -5136,10 +5121,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>124753629</v>
+        <v>124756755</v>
       </c>
       <c r="B44" t="n">
-        <v>98101</v>
+        <v>91459</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5148,25 +5133,25 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5176,10 +5161,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>452576</v>
+        <v>452538</v>
       </c>
       <c r="R44" t="n">
-        <v>6990924</v>
+        <v>6990659</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5209,14 +5194,19 @@
           <t>2025-05-03</t>
         </is>
       </c>
+      <c r="Z44" t="inlineStr">
+        <is>
+          <t>11:58</t>
+        </is>
+      </c>
       <c r="AA44" t="inlineStr">
         <is>
           <t>2025-05-03</t>
         </is>
       </c>
-      <c r="AC44" t="inlineStr">
-        <is>
-          <t>Minst 30</t>
+      <c r="AB44" t="inlineStr">
+        <is>
+          <t>11:58</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5231,22 +5221,22 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>124753624</v>
+        <v>124753609</v>
       </c>
       <c r="B45" t="n">
-        <v>98101</v>
+        <v>80028</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5255,25 +5245,25 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5286,7 +5276,7 @@
         <v>452528</v>
       </c>
       <c r="R45" t="n">
-        <v>6990882</v>
+        <v>6990710</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5319,11 +5309,6 @@
       <c r="AA45" t="inlineStr">
         <is>
           <t>2025-05-03</t>
-        </is>
-      </c>
-      <c r="AC45" t="inlineStr">
-        <is>
-          <t>Minst 30</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5350,10 +5335,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>124753611</v>
+        <v>124753622</v>
       </c>
       <c r="B46" t="n">
-        <v>98101</v>
+        <v>98269</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5390,10 +5375,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>452997</v>
+        <v>452472</v>
       </c>
       <c r="R46" t="n">
-        <v>6990332</v>
+        <v>6990821</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5430,7 +5415,7 @@
       </c>
       <c r="AC46" t="inlineStr">
         <is>
-          <t>Minst 100</t>
+          <t>Minst 50</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5457,10 +5442,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>124756752</v>
+        <v>124756776</v>
       </c>
       <c r="B47" t="n">
-        <v>98101</v>
+        <v>78947</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5469,50 +5454,38 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J47" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K47" t="inlineStr"/>
-      <c r="L47" t="inlineStr"/>
-      <c r="N47" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
           <t>Häggsåsen N, Jmt</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>452608</v>
+        <v>452308</v>
       </c>
       <c r="R47" t="n">
-        <v>6990625</v>
+        <v>6990943</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5544,7 +5517,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>12:07</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5554,7 +5527,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>12:07</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5563,7 +5536,6 @@
       <c r="AE47" t="b">
         <v>0</v>
       </c>
-      <c r="AF47" t="inlineStr"/>
       <c r="AG47" t="b">
         <v>0</v>
       </c>
@@ -5582,10 +5554,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>124753615</v>
+        <v>124756779</v>
       </c>
       <c r="B48" t="n">
-        <v>98101</v>
+        <v>78947</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5594,25 +5566,25 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5622,10 +5594,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>452734</v>
+        <v>452143</v>
       </c>
       <c r="R48" t="n">
-        <v>6990355</v>
+        <v>6990780</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5655,14 +5627,19 @@
           <t>2025-05-03</t>
         </is>
       </c>
+      <c r="Z48" t="inlineStr">
+        <is>
+          <t>09:51</t>
+        </is>
+      </c>
       <c r="AA48" t="inlineStr">
         <is>
           <t>2025-05-03</t>
         </is>
       </c>
-      <c r="AC48" t="inlineStr">
-        <is>
-          <t>Minst 30</t>
+      <c r="AB48" t="inlineStr">
+        <is>
+          <t>09:51</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5677,22 +5654,22 @@
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>124756778</v>
+        <v>124753577</v>
       </c>
       <c r="B49" t="n">
-        <v>78810</v>
+        <v>91166</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5705,21 +5682,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5729,10 +5706,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>452153</v>
+        <v>452833</v>
       </c>
       <c r="R49" t="n">
-        <v>6990834</v>
+        <v>6990388</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5762,19 +5739,9 @@
           <t>2025-05-03</t>
         </is>
       </c>
-      <c r="Z49" t="inlineStr">
-        <is>
-          <t>10:03</t>
-        </is>
-      </c>
       <c r="AA49" t="inlineStr">
         <is>
           <t>2025-05-03</t>
-        </is>
-      </c>
-      <c r="AB49" t="inlineStr">
-        <is>
-          <t>10:03</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5789,22 +5756,22 @@
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>124753638</v>
+        <v>124753579</v>
       </c>
       <c r="B50" t="n">
-        <v>78810</v>
+        <v>91166</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -5817,21 +5784,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5841,10 +5808,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>452823</v>
+        <v>452710</v>
       </c>
       <c r="R50" t="n">
-        <v>6990367</v>
+        <v>6990467</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5903,10 +5870,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>124756770</v>
+        <v>124756725</v>
       </c>
       <c r="B51" t="n">
-        <v>74899</v>
+        <v>78947</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -5915,41 +5882,38 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6486</v>
+        <v>6425</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Skuggnål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Chaenotheca sphaerocephala</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>Nádv.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
-      <c r="J51" t="inlineStr"/>
-      <c r="K51" t="inlineStr"/>
-      <c r="N51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
           <t>Häggsåsen N, Jmt</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>452339</v>
+        <v>452762</v>
       </c>
       <c r="R51" t="n">
-        <v>6990941</v>
+        <v>6990327</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5981,7 +5945,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>10:44</t>
+          <t>14:37</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -5991,7 +5955,7 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>10:44</t>
+          <t>14:37</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6000,43 +5964,8 @@
       <c r="AE51" t="b">
         <v>0</v>
       </c>
-      <c r="AF51" t="inlineStr">
-        <is>
-          <t>mikroskoperad</t>
-        </is>
-      </c>
       <c r="AG51" t="b">
         <v>0</v>
-      </c>
-      <c r="AH51" t="inlineStr">
-        <is>
-          <t>Blåbärsgranskog</t>
-        </is>
-      </c>
-      <c r="AI51" t="inlineStr">
-        <is>
-          <t>I hålighet vid basen av gammal gran i fuktig granskog.</t>
-        </is>
-      </c>
-      <c r="AJ51" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK51" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM51" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO51" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Picea abies</t>
-        </is>
       </c>
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
@@ -6053,10 +5982,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>124756776</v>
+        <v>124756774</v>
       </c>
       <c r="B52" t="n">
-        <v>78810</v>
+        <v>98269</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6065,28 +5994,40 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr"/>
+      <c r="L52" t="inlineStr"/>
+      <c r="N52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
           <t>Häggsåsen N, Jmt</t>
@@ -6128,7 +6069,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>10:23</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6138,7 +6079,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>10:23</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6147,6 +6088,7 @@
       <c r="AE52" t="b">
         <v>0</v>
       </c>
+      <c r="AF52" t="inlineStr"/>
       <c r="AG52" t="b">
         <v>0</v>
       </c>
@@ -6165,10 +6107,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>124756772</v>
+        <v>124753635</v>
       </c>
       <c r="B53" t="n">
-        <v>78810</v>
+        <v>91184</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6181,21 +6123,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -6205,10 +6147,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>452344</v>
+        <v>452732</v>
       </c>
       <c r="R53" t="n">
-        <v>6990942</v>
+        <v>6990486</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6238,19 +6180,9 @@
           <t>2025-05-03</t>
         </is>
       </c>
-      <c r="Z53" t="inlineStr">
-        <is>
-          <t>10:32</t>
-        </is>
-      </c>
       <c r="AA53" t="inlineStr">
         <is>
           <t>2025-05-03</t>
-        </is>
-      </c>
-      <c r="AB53" t="inlineStr">
-        <is>
-          <t>10:32</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6265,22 +6197,22 @@
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>124756755</v>
+        <v>124756739</v>
       </c>
       <c r="B54" t="n">
-        <v>91299</v>
+        <v>98269</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6289,38 +6221,50 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>658</v>
+        <v>220787</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
-        </is>
-      </c>
-      <c r="I54" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr"/>
+      <c r="L54" t="inlineStr"/>
+      <c r="N54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
           <t>Häggsåsen N, Jmt</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>452538</v>
+        <v>452711</v>
       </c>
       <c r="R54" t="n">
-        <v>6990659</v>
+        <v>6990473</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6352,7 +6296,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>11:58</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -6362,7 +6306,7 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>11:58</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6371,6 +6315,7 @@
       <c r="AE54" t="b">
         <v>0</v>
       </c>
+      <c r="AF54" t="inlineStr"/>
       <c r="AG54" t="b">
         <v>0</v>
       </c>
@@ -6389,10 +6334,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>124753579</v>
+        <v>124753607</v>
       </c>
       <c r="B55" t="n">
-        <v>91012</v>
+        <v>80028</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6405,21 +6350,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6429,10 +6374,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>452710</v>
+        <v>452734</v>
       </c>
       <c r="R55" t="n">
-        <v>6990467</v>
+        <v>6990356</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6491,10 +6436,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>124756733</v>
+        <v>124756734</v>
       </c>
       <c r="B56" t="n">
-        <v>79927</v>
+        <v>80028</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6503,25 +6448,25 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6464</v>
+        <v>6458</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6566,7 +6511,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -6576,7 +6521,7 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6618,10 +6563,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>124753622</v>
+        <v>124756740</v>
       </c>
       <c r="B57" t="n">
-        <v>98101</v>
+        <v>91617</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6634,21 +6579,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>220787</v>
+        <v>1209</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6658,10 +6603,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>452472</v>
+        <v>452701</v>
       </c>
       <c r="R57" t="n">
-        <v>6990821</v>
+        <v>6990475</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6691,14 +6636,19 @@
           <t>2025-05-03</t>
         </is>
       </c>
+      <c r="Z57" t="inlineStr">
+        <is>
+          <t>13:58</t>
+        </is>
+      </c>
       <c r="AA57" t="inlineStr">
         <is>
           <t>2025-05-03</t>
         </is>
       </c>
-      <c r="AC57" t="inlineStr">
-        <is>
-          <t>Minst 50</t>
+      <c r="AB57" t="inlineStr">
+        <is>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6713,22 +6663,22 @@
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>124753627</v>
+        <v>124756731</v>
       </c>
       <c r="B58" t="n">
-        <v>98101</v>
+        <v>91166</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -6737,25 +6687,25 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6765,10 +6715,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>452608</v>
+        <v>452672</v>
       </c>
       <c r="R58" t="n">
-        <v>6990927</v>
+        <v>6990427</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6798,14 +6748,19 @@
           <t>2025-05-03</t>
         </is>
       </c>
+      <c r="Z58" t="inlineStr">
+        <is>
+          <t>14:19</t>
+        </is>
+      </c>
       <c r="AA58" t="inlineStr">
         <is>
           <t>2025-05-03</t>
         </is>
       </c>
-      <c r="AC58" t="inlineStr">
-        <is>
-          <t>Minst 50</t>
+      <c r="AB58" t="inlineStr">
+        <is>
+          <t>14:19</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6820,22 +6775,22 @@
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>124756725</v>
+        <v>124756761</v>
       </c>
       <c r="B59" t="n">
-        <v>78810</v>
+        <v>78947</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -6872,10 +6827,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>452762</v>
+        <v>452532</v>
       </c>
       <c r="R59" t="n">
-        <v>6990327</v>
+        <v>6990825</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6907,7 +6862,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>14:37</t>
+          <t>11:26</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -6917,7 +6872,7 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>14:37</t>
+          <t>11:26</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -6944,10 +6899,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>124756754</v>
+        <v>124756738</v>
       </c>
       <c r="B60" t="n">
-        <v>78810</v>
+        <v>75023</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -6956,38 +6911,41 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6425</v>
+        <v>6486</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skuggnål</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca sphaerocephala</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Nádv.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
+      <c r="J60" t="inlineStr"/>
+      <c r="K60" t="inlineStr"/>
+      <c r="N60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
           <t>Häggsåsen N, Jmt</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>452544</v>
+        <v>452703</v>
       </c>
       <c r="R60" t="n">
-        <v>6990646</v>
+        <v>6990457</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -7019,7 +6977,7 @@
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>12:04</t>
+          <t>14:09</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
@@ -7029,7 +6987,7 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>12:04</t>
+          <t>14:09</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7037,6 +6995,11 @@
       </c>
       <c r="AE60" t="b">
         <v>0</v>
+      </c>
+      <c r="AF60" t="inlineStr">
+        <is>
+          <t>mikroskoperad</t>
+        </is>
       </c>
       <c r="AG60" t="b">
         <v>0</v>
@@ -7056,10 +7019,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>124753605</v>
+        <v>124753614</v>
       </c>
       <c r="B61" t="n">
-        <v>79892</v>
+        <v>98269</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -7068,25 +7031,25 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>2081</v>
+        <v>220787</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -7096,10 +7059,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>452408</v>
+        <v>452751</v>
       </c>
       <c r="R61" t="n">
-        <v>6990952</v>
+        <v>6990344</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7132,6 +7095,11 @@
       <c r="AA61" t="inlineStr">
         <is>
           <t>2025-05-03</t>
+        </is>
+      </c>
+      <c r="AC61" t="inlineStr">
+        <is>
+          <t>Minst 200</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7158,10 +7126,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>124753610</v>
+        <v>124753588</v>
       </c>
       <c r="B62" t="n">
-        <v>79891</v>
+        <v>91166</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -7174,21 +7142,21 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -7198,10 +7166,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>452435</v>
+        <v>452311</v>
       </c>
       <c r="R62" t="n">
-        <v>6990938</v>
+        <v>6990887</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7260,10 +7228,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>124753637</v>
+        <v>124756759</v>
       </c>
       <c r="B63" t="n">
-        <v>91030</v>
+        <v>91166</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -7276,21 +7244,21 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>5432</v>
+        <v>1202</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -7300,10 +7268,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>452696</v>
+        <v>452509</v>
       </c>
       <c r="R63" t="n">
-        <v>6990466</v>
+        <v>6990778</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7333,9 +7301,19 @@
           <t>2025-05-03</t>
         </is>
       </c>
+      <c r="Z63" t="inlineStr">
+        <is>
+          <t>11:39</t>
+        </is>
+      </c>
       <c r="AA63" t="inlineStr">
         <is>
           <t>2025-05-03</t>
+        </is>
+      </c>
+      <c r="AB63" t="inlineStr">
+        <is>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7350,22 +7328,22 @@
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>124753614</v>
+        <v>124756756</v>
       </c>
       <c r="B64" t="n">
-        <v>98101</v>
+        <v>78947</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7374,25 +7352,25 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7402,10 +7380,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>452751</v>
+        <v>452545</v>
       </c>
       <c r="R64" t="n">
-        <v>6990344</v>
+        <v>6990691</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7435,14 +7413,19 @@
           <t>2025-05-03</t>
         </is>
       </c>
+      <c r="Z64" t="inlineStr">
+        <is>
+          <t>11:54</t>
+        </is>
+      </c>
       <c r="AA64" t="inlineStr">
         <is>
           <t>2025-05-03</t>
         </is>
       </c>
-      <c r="AC64" t="inlineStr">
-        <is>
-          <t>Minst 200</t>
+      <c r="AB64" t="inlineStr">
+        <is>
+          <t>11:54</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7457,22 +7440,22 @@
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>124753592</v>
+        <v>124756688</v>
       </c>
       <c r="B65" t="n">
-        <v>57513</v>
+        <v>80028</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -7485,21 +7468,21 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7509,10 +7492,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>452396</v>
+        <v>452694</v>
       </c>
       <c r="R65" t="n">
-        <v>6990703</v>
+        <v>6990598</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7542,14 +7525,19 @@
           <t>2025-05-03</t>
         </is>
       </c>
+      <c r="Z65" t="inlineStr">
+        <is>
+          <t>20:19</t>
+        </is>
+      </c>
       <c r="AA65" t="inlineStr">
         <is>
           <t>2025-05-03</t>
         </is>
       </c>
-      <c r="AC65" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
+      <c r="AB65" t="inlineStr">
+        <is>
+          <t>20:19</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7564,22 +7552,22 @@
       <c r="AT65" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>124753607</v>
+        <v>124756730</v>
       </c>
       <c r="B66" t="n">
-        <v>79891</v>
+        <v>98269</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -7588,38 +7576,50 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I66" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="J66" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K66" t="inlineStr"/>
+      <c r="L66" t="inlineStr"/>
+      <c r="N66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
           <t>Häggsåsen N, Jmt</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>452734</v>
+        <v>452675</v>
       </c>
       <c r="R66" t="n">
-        <v>6990356</v>
+        <v>6990411</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7649,39 +7649,55 @@
           <t>2025-05-03</t>
         </is>
       </c>
+      <c r="Z66" t="inlineStr">
+        <is>
+          <t>14:20</t>
+        </is>
+      </c>
       <c r="AA66" t="inlineStr">
         <is>
           <t>2025-05-03</t>
         </is>
       </c>
+      <c r="AB66" t="inlineStr">
+        <is>
+          <t>14:20</t>
+        </is>
+      </c>
+      <c r="AC66" t="inlineStr">
+        <is>
+          <t>Min antal</t>
+        </is>
+      </c>
       <c r="AD66" t="b">
         <v>0</v>
       </c>
       <c r="AE66" t="b">
         <v>0</v>
       </c>
+      <c r="AF66" t="inlineStr"/>
       <c r="AG66" t="b">
         <v>0</v>
       </c>
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>124753620</v>
+        <v>124753586</v>
       </c>
       <c r="B67" t="n">
-        <v>98101</v>
+        <v>91166</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -7690,25 +7706,25 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7718,10 +7734,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>452554</v>
+        <v>452500</v>
       </c>
       <c r="R67" t="n">
-        <v>6990657</v>
+        <v>6990950</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7754,11 +7770,6 @@
       <c r="AA67" t="inlineStr">
         <is>
           <t>2025-05-03</t>
-        </is>
-      </c>
-      <c r="AC67" t="inlineStr">
-        <is>
-          <t>Minst 30</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7785,10 +7796,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>124753632</v>
+        <v>124753578</v>
       </c>
       <c r="B68" t="n">
-        <v>98101</v>
+        <v>91166</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -7797,25 +7808,25 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7825,10 +7836,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>452455</v>
+        <v>452743</v>
       </c>
       <c r="R68" t="n">
-        <v>6990942</v>
+        <v>6990405</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7861,11 +7872,6 @@
       <c r="AA68" t="inlineStr">
         <is>
           <t>2025-05-03</t>
-        </is>
-      </c>
-      <c r="AC68" t="inlineStr">
-        <is>
-          <t>Minst 30</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -7892,10 +7898,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>124756779</v>
+        <v>124756750</v>
       </c>
       <c r="B69" t="n">
-        <v>78810</v>
+        <v>98269</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -7904,38 +7910,50 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I69" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J69" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K69" t="inlineStr"/>
+      <c r="L69" t="inlineStr"/>
+      <c r="N69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
           <t>Häggsåsen N, Jmt</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>452143</v>
+        <v>452617</v>
       </c>
       <c r="R69" t="n">
-        <v>6990780</v>
+        <v>6990549</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7967,7 +7985,7 @@
       </c>
       <c r="Z69" t="inlineStr">
         <is>
-          <t>09:51</t>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
@@ -7977,7 +7995,7 @@
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>09:51</t>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -7986,6 +8004,7 @@
       <c r="AE69" t="b">
         <v>0</v>
       </c>
+      <c r="AF69" t="inlineStr"/>
       <c r="AG69" t="b">
         <v>0</v>
       </c>
@@ -8004,10 +8023,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>124756721</v>
+        <v>124756777</v>
       </c>
       <c r="B70" t="n">
-        <v>79891</v>
+        <v>98269</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -8016,38 +8035,50 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I70" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J70" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K70" t="inlineStr"/>
+      <c r="L70" t="inlineStr"/>
+      <c r="N70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
           <t>Häggsåsen N, Jmt</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>452823</v>
+        <v>452146</v>
       </c>
       <c r="R70" t="n">
-        <v>6990261</v>
+        <v>6990839</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -8079,7 +8110,7 @@
       </c>
       <c r="Z70" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>10:06</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
@@ -8089,7 +8120,7 @@
       </c>
       <c r="AB70" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>10:06</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8098,23 +8129,9 @@
       <c r="AE70" t="b">
         <v>0</v>
       </c>
+      <c r="AF70" t="inlineStr"/>
       <c r="AG70" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ70" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK70" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AO70" t="inlineStr">
-        <is>
-          <t>Omkullfallen grov stam # Salix caprea</t>
-        </is>
       </c>
       <c r="AT70" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
@@ -8131,10 +8148,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>124756765</v>
+        <v>124753639</v>
       </c>
       <c r="B71" t="n">
-        <v>78810</v>
+        <v>78947</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -8171,10 +8188,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>452432</v>
+        <v>452511</v>
       </c>
       <c r="R71" t="n">
-        <v>6990942</v>
+        <v>6990733</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -8204,19 +8221,9 @@
           <t>2025-05-03</t>
         </is>
       </c>
-      <c r="Z71" t="inlineStr">
-        <is>
-          <t>11:05</t>
-        </is>
-      </c>
       <c r="AA71" t="inlineStr">
         <is>
           <t>2025-05-03</t>
-        </is>
-      </c>
-      <c r="AB71" t="inlineStr">
-        <is>
-          <t>11:05</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -8231,22 +8238,22 @@
       <c r="AT71" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX71" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>124756766</v>
+        <v>124756770</v>
       </c>
       <c r="B72" t="n">
-        <v>79891</v>
+        <v>75023</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -8255,38 +8262,41 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>6458</v>
+        <v>6486</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skuggnål</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Chaenotheca sphaerocephala</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Nádv.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
+      <c r="J72" t="inlineStr"/>
+      <c r="K72" t="inlineStr"/>
+      <c r="N72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
           <t>Häggsåsen N, Jmt</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>452396</v>
+        <v>452339</v>
       </c>
       <c r="R72" t="n">
-        <v>6990981</v>
+        <v>6990941</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8318,7 +8328,7 @@
       </c>
       <c r="Z72" t="inlineStr">
         <is>
-          <t>10:58</t>
+          <t>10:44</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
@@ -8328,7 +8338,7 @@
       </c>
       <c r="AB72" t="inlineStr">
         <is>
-          <t>10:58</t>
+          <t>10:44</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8337,8 +8347,43 @@
       <c r="AE72" t="b">
         <v>0</v>
       </c>
+      <c r="AF72" t="inlineStr">
+        <is>
+          <t>mikroskoperad</t>
+        </is>
+      </c>
       <c r="AG72" t="b">
         <v>0</v>
+      </c>
+      <c r="AH72" t="inlineStr">
+        <is>
+          <t>Blåbärsgranskog</t>
+        </is>
+      </c>
+      <c r="AI72" t="inlineStr">
+        <is>
+          <t>I hålighet vid basen av gammal gran i fuktig granskog.</t>
+        </is>
+      </c>
+      <c r="AJ72" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK72" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM72" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO72" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Picea abies</t>
+        </is>
       </c>
       <c r="AT72" t="inlineStr"/>
       <c r="AW72" t="inlineStr">
@@ -8355,10 +8400,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>124756746</v>
+        <v>124753610</v>
       </c>
       <c r="B73" t="n">
-        <v>91012</v>
+        <v>80028</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -8371,21 +8416,21 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -8395,10 +8440,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>452639</v>
+        <v>452435</v>
       </c>
       <c r="R73" t="n">
-        <v>6990537</v>
+        <v>6990938</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8428,19 +8473,9 @@
           <t>2025-05-03</t>
         </is>
       </c>
-      <c r="Z73" t="inlineStr">
-        <is>
-          <t>13:36</t>
-        </is>
-      </c>
       <c r="AA73" t="inlineStr">
         <is>
           <t>2025-05-03</t>
-        </is>
-      </c>
-      <c r="AB73" t="inlineStr">
-        <is>
-          <t>13:36</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8455,22 +8490,22 @@
       <c r="AT73" t="inlineStr"/>
       <c r="AW73" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>124753582</v>
+        <v>124756766</v>
       </c>
       <c r="B74" t="n">
-        <v>91012</v>
+        <v>80028</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -8483,21 +8518,21 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -8507,10 +8542,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>452649</v>
+        <v>452396</v>
       </c>
       <c r="R74" t="n">
-        <v>6990621</v>
+        <v>6990981</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8540,9 +8575,19 @@
           <t>2025-05-03</t>
         </is>
       </c>
+      <c r="Z74" t="inlineStr">
+        <is>
+          <t>10:58</t>
+        </is>
+      </c>
       <c r="AA74" t="inlineStr">
         <is>
           <t>2025-05-03</t>
+        </is>
+      </c>
+      <c r="AB74" t="inlineStr">
+        <is>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8557,22 +8602,22 @@
       <c r="AT74" t="inlineStr"/>
       <c r="AW74" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX74" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>124753606</v>
+        <v>124753631</v>
       </c>
       <c r="B75" t="n">
-        <v>91299</v>
+        <v>98269</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -8581,25 +8626,25 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>658</v>
+        <v>220787</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8609,10 +8654,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>452165</v>
+        <v>452526</v>
       </c>
       <c r="R75" t="n">
-        <v>6990824</v>
+        <v>6990943</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8645,6 +8690,11 @@
       <c r="AA75" t="inlineStr">
         <is>
           <t>2025-05-03</t>
+        </is>
+      </c>
+      <c r="AC75" t="inlineStr">
+        <is>
+          <t>Minst 20</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -8671,10 +8721,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>124756767</v>
+        <v>124753606</v>
       </c>
       <c r="B76" t="n">
-        <v>78810</v>
+        <v>91459</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
@@ -8687,21 +8737,21 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>6425</v>
+        <v>658</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -8711,10 +8761,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>452362</v>
+        <v>452165</v>
       </c>
       <c r="R76" t="n">
-        <v>6991003</v>
+        <v>6990824</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8744,19 +8794,9 @@
           <t>2025-05-03</t>
         </is>
       </c>
-      <c r="Z76" t="inlineStr">
-        <is>
-          <t>10:55</t>
-        </is>
-      </c>
       <c r="AA76" t="inlineStr">
         <is>
           <t>2025-05-03</t>
-        </is>
-      </c>
-      <c r="AB76" t="inlineStr">
-        <is>
-          <t>10:55</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -8771,22 +8811,22 @@
       <c r="AT76" t="inlineStr"/>
       <c r="AW76" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX76" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>124753623</v>
+        <v>124753629</v>
       </c>
       <c r="B77" t="n">
-        <v>98101</v>
+        <v>98269</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -8823,10 +8863,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>452510</v>
+        <v>452576</v>
       </c>
       <c r="R77" t="n">
-        <v>6990873</v>
+        <v>6990924</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8863,7 +8903,7 @@
       </c>
       <c r="AC77" t="inlineStr">
         <is>
-          <t>Minst 50</t>
+          <t>Minst 30</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -8890,10 +8930,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>124756757</v>
+        <v>124753621</v>
       </c>
       <c r="B78" t="n">
-        <v>77743</v>
+        <v>98269</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -8902,25 +8942,25 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>228579</v>
+        <v>220787</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -8933,7 +8973,7 @@
         <v>452506</v>
       </c>
       <c r="R78" t="n">
-        <v>6990737</v>
+        <v>6990758</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8963,19 +9003,14 @@
           <t>2025-05-03</t>
         </is>
       </c>
-      <c r="Z78" t="inlineStr">
-        <is>
-          <t>11:47</t>
-        </is>
-      </c>
       <c r="AA78" t="inlineStr">
         <is>
           <t>2025-05-03</t>
         </is>
       </c>
-      <c r="AB78" t="inlineStr">
-        <is>
-          <t>11:47</t>
+      <c r="AC78" t="inlineStr">
+        <is>
+          <t>Minst 60</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -8990,22 +9025,22 @@
       <c r="AT78" t="inlineStr"/>
       <c r="AW78" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX78" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>124756751</v>
+        <v>124753624</v>
       </c>
       <c r="B79" t="n">
-        <v>98101</v>
+        <v>98269</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -9035,29 +9070,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I79" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J79" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K79" t="inlineStr"/>
-      <c r="L79" t="inlineStr"/>
-      <c r="N79" t="inlineStr"/>
+      <c r="I79" t="inlineStr"/>
       <c r="P79" t="inlineStr">
         <is>
           <t>Häggsåsen N, Jmt</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>452638</v>
+        <v>452528</v>
       </c>
       <c r="R79" t="n">
-        <v>6990559</v>
+        <v>6990882</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -9087,19 +9110,14 @@
           <t>2025-05-03</t>
         </is>
       </c>
-      <c r="Z79" t="inlineStr">
-        <is>
-          <t>12:23</t>
-        </is>
-      </c>
       <c r="AA79" t="inlineStr">
         <is>
           <t>2025-05-03</t>
         </is>
       </c>
-      <c r="AB79" t="inlineStr">
-        <is>
-          <t>12:23</t>
+      <c r="AC79" t="inlineStr">
+        <is>
+          <t>Minst 30</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -9108,29 +9126,28 @@
       <c r="AE79" t="b">
         <v>0</v>
       </c>
-      <c r="AF79" t="inlineStr"/>
       <c r="AG79" t="b">
         <v>0</v>
       </c>
       <c r="AT79" t="inlineStr"/>
       <c r="AW79" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX79" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>124753583</v>
+        <v>124753615</v>
       </c>
       <c r="B80" t="n">
-        <v>91012</v>
+        <v>98269</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
@@ -9139,25 +9156,25 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -9167,10 +9184,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>452606</v>
+        <v>452734</v>
       </c>
       <c r="R80" t="n">
-        <v>6990623</v>
+        <v>6990355</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -9203,6 +9220,11 @@
       <c r="AA80" t="inlineStr">
         <is>
           <t>2025-05-03</t>
+        </is>
+      </c>
+      <c r="AC80" t="inlineStr">
+        <is>
+          <t>Minst 30</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -9229,10 +9251,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>124756753</v>
+        <v>124756741</v>
       </c>
       <c r="B81" t="n">
-        <v>91012</v>
+        <v>79988</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
@@ -9241,25 +9263,25 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>1202</v>
+        <v>229497</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -9269,10 +9291,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>452608</v>
+        <v>452682</v>
       </c>
       <c r="R81" t="n">
-        <v>6990625</v>
+        <v>6990476</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -9304,7 +9326,7 @@
       </c>
       <c r="Z81" t="inlineStr">
         <is>
-          <t>12:07</t>
+          <t>13:54</t>
         </is>
       </c>
       <c r="AA81" t="inlineStr">
@@ -9314,7 +9336,7 @@
       </c>
       <c r="AB81" t="inlineStr">
         <is>
-          <t>12:07</t>
+          <t>13:54</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -9325,6 +9347,21 @@
       </c>
       <c r="AG81" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ81" t="inlineStr">
+        <is>
+          <t>rönn</t>
+        </is>
+      </c>
+      <c r="AK81" t="inlineStr">
+        <is>
+          <t>Sorbus aucuparia</t>
+        </is>
+      </c>
+      <c r="AO81" t="inlineStr">
+        <is>
+          <t>Sorbus aucuparia</t>
+        </is>
       </c>
       <c r="AT81" t="inlineStr"/>
       <c r="AW81" t="inlineStr">
@@ -9341,10 +9378,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>124753608</v>
+        <v>124756764</v>
       </c>
       <c r="B82" t="n">
-        <v>79891</v>
+        <v>78947</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
@@ -9357,21 +9394,21 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -9381,10 +9418,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>452731</v>
+        <v>452462</v>
       </c>
       <c r="R82" t="n">
-        <v>6990377</v>
+        <v>6990915</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -9414,9 +9451,19 @@
           <t>2025-05-03</t>
         </is>
       </c>
+      <c r="Z82" t="inlineStr">
+        <is>
+          <t>11:11</t>
+        </is>
+      </c>
       <c r="AA82" t="inlineStr">
         <is>
           <t>2025-05-03</t>
+        </is>
+      </c>
+      <c r="AB82" t="inlineStr">
+        <is>
+          <t>11:11</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -9431,22 +9478,22 @@
       <c r="AT82" t="inlineStr"/>
       <c r="AW82" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX82" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>124756774</v>
+        <v>124753627</v>
       </c>
       <c r="B83" t="n">
-        <v>98101</v>
+        <v>98269</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
@@ -9476,29 +9523,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I83" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="J83" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K83" t="inlineStr"/>
-      <c r="L83" t="inlineStr"/>
-      <c r="N83" t="inlineStr"/>
+      <c r="I83" t="inlineStr"/>
       <c r="P83" t="inlineStr">
         <is>
           <t>Häggsåsen N, Jmt</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>452308</v>
+        <v>452608</v>
       </c>
       <c r="R83" t="n">
-        <v>6990943</v>
+        <v>6990927</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9528,19 +9563,14 @@
           <t>2025-05-03</t>
         </is>
       </c>
-      <c r="Z83" t="inlineStr">
-        <is>
-          <t>10:23</t>
-        </is>
-      </c>
       <c r="AA83" t="inlineStr">
         <is>
           <t>2025-05-03</t>
         </is>
       </c>
-      <c r="AB83" t="inlineStr">
-        <is>
-          <t>10:23</t>
+      <c r="AC83" t="inlineStr">
+        <is>
+          <t>Minst 50</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -9549,29 +9579,28 @@
       <c r="AE83" t="b">
         <v>0</v>
       </c>
-      <c r="AF83" t="inlineStr"/>
       <c r="AG83" t="b">
         <v>0</v>
       </c>
       <c r="AT83" t="inlineStr"/>
       <c r="AW83" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX83" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>124753604</v>
+        <v>124753613</v>
       </c>
       <c r="B84" t="n">
-        <v>79892</v>
+        <v>98269</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
@@ -9580,25 +9609,25 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>2081</v>
+        <v>220787</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -9608,10 +9637,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>452435</v>
+        <v>452777</v>
       </c>
       <c r="R84" t="n">
-        <v>6990938</v>
+        <v>6990299</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9644,6 +9673,11 @@
       <c r="AA84" t="inlineStr">
         <is>
           <t>2025-05-03</t>
+        </is>
+      </c>
+      <c r="AC84" t="inlineStr">
+        <is>
+          <t>Minst 100</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -9670,10 +9704,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>124756727</v>
+        <v>124753612</v>
       </c>
       <c r="B85" t="n">
-        <v>79920</v>
+        <v>98269</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
@@ -9682,25 +9716,25 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>6462</v>
+        <v>220787</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -9710,10 +9744,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>452745</v>
+        <v>452924</v>
       </c>
       <c r="R85" t="n">
-        <v>6990359</v>
+        <v>6990397</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9743,19 +9777,14 @@
           <t>2025-05-03</t>
         </is>
       </c>
-      <c r="Z85" t="inlineStr">
-        <is>
-          <t>14:31</t>
-        </is>
-      </c>
       <c r="AA85" t="inlineStr">
         <is>
           <t>2025-05-03</t>
         </is>
       </c>
-      <c r="AB85" t="inlineStr">
-        <is>
-          <t>14:31</t>
+      <c r="AC85" t="inlineStr">
+        <is>
+          <t>Minst 20</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -9770,22 +9799,22 @@
       <c r="AT85" t="inlineStr"/>
       <c r="AW85" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX85" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>124756762</v>
+        <v>124756724</v>
       </c>
       <c r="B86" t="n">
-        <v>78810</v>
+        <v>91166</v>
       </c>
       <c r="C86" t="inlineStr">
         <is>
@@ -9798,21 +9827,21 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -9822,10 +9851,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>452508</v>
+        <v>452793</v>
       </c>
       <c r="R86" t="n">
-        <v>6990903</v>
+        <v>6990262</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9857,7 +9886,7 @@
       </c>
       <c r="Z86" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>14:44</t>
         </is>
       </c>
       <c r="AA86" t="inlineStr">
@@ -9867,7 +9896,7 @@
       </c>
       <c r="AB86" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>14:44</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -9894,10 +9923,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>124756748</v>
+        <v>124753583</v>
       </c>
       <c r="B87" t="n">
-        <v>78810</v>
+        <v>91166</v>
       </c>
       <c r="C87" t="inlineStr">
         <is>
@@ -9910,21 +9939,21 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
@@ -9934,10 +9963,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>452609</v>
+        <v>452606</v>
       </c>
       <c r="R87" t="n">
-        <v>6990543</v>
+        <v>6990623</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9967,19 +9996,9 @@
           <t>2025-05-03</t>
         </is>
       </c>
-      <c r="Z87" t="inlineStr">
-        <is>
-          <t>12:29</t>
-        </is>
-      </c>
       <c r="AA87" t="inlineStr">
         <is>
           <t>2025-05-03</t>
-        </is>
-      </c>
-      <c r="AB87" t="inlineStr">
-        <is>
-          <t>12:29</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -9994,22 +10013,22 @@
       <c r="AT87" t="inlineStr"/>
       <c r="AW87" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX87" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>124753631</v>
+        <v>124753584</v>
       </c>
       <c r="B88" t="n">
-        <v>98101</v>
+        <v>91166</v>
       </c>
       <c r="C88" t="inlineStr">
         <is>
@@ -10018,25 +10037,25 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
@@ -10046,10 +10065,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>452526</v>
+        <v>452444</v>
       </c>
       <c r="R88" t="n">
-        <v>6990943</v>
+        <v>6990774</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -10082,11 +10101,6 @@
       <c r="AA88" t="inlineStr">
         <is>
           <t>2025-05-03</t>
-        </is>
-      </c>
-      <c r="AC88" t="inlineStr">
-        <is>
-          <t>Minst 20</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -10113,10 +10127,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>124753612</v>
+        <v>124753585</v>
       </c>
       <c r="B89" t="n">
-        <v>98101</v>
+        <v>91166</v>
       </c>
       <c r="C89" t="inlineStr">
         <is>
@@ -10125,25 +10139,25 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
@@ -10153,10 +10167,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>452924</v>
+        <v>452595</v>
       </c>
       <c r="R89" t="n">
-        <v>6990397</v>
+        <v>6990913</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -10189,11 +10203,6 @@
       <c r="AA89" t="inlineStr">
         <is>
           <t>2025-05-03</t>
-        </is>
-      </c>
-      <c r="AC89" t="inlineStr">
-        <is>
-          <t>Minst 20</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -10220,10 +10229,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>124753586</v>
+        <v>124753592</v>
       </c>
       <c r="B90" t="n">
-        <v>91012</v>
+        <v>57635</v>
       </c>
       <c r="C90" t="inlineStr">
         <is>
@@ -10236,21 +10245,21 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
@@ -10260,10 +10269,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>452500</v>
+        <v>452396</v>
       </c>
       <c r="R90" t="n">
-        <v>6990950</v>
+        <v>6990703</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -10296,6 +10305,11 @@
       <c r="AA90" t="inlineStr">
         <is>
           <t>2025-05-03</t>
+        </is>
+      </c>
+      <c r="AC90" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD90" t="b">
@@ -10322,10 +10336,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>124753639</v>
+        <v>124753608</v>
       </c>
       <c r="B91" t="n">
-        <v>78810</v>
+        <v>80028</v>
       </c>
       <c r="C91" t="inlineStr">
         <is>
@@ -10338,21 +10352,21 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
@@ -10362,10 +10376,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>452511</v>
+        <v>452731</v>
       </c>
       <c r="R91" t="n">
-        <v>6990733</v>
+        <v>6990377</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -10424,10 +10438,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>124756764</v>
+        <v>124753620</v>
       </c>
       <c r="B92" t="n">
-        <v>78810</v>
+        <v>98269</v>
       </c>
       <c r="C92" t="inlineStr">
         <is>
@@ -10436,25 +10450,25 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
@@ -10464,10 +10478,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>452462</v>
+        <v>452554</v>
       </c>
       <c r="R92" t="n">
-        <v>6990915</v>
+        <v>6990657</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -10497,19 +10511,14 @@
           <t>2025-05-03</t>
         </is>
       </c>
-      <c r="Z92" t="inlineStr">
-        <is>
-          <t>11:11</t>
-        </is>
-      </c>
       <c r="AA92" t="inlineStr">
         <is>
           <t>2025-05-03</t>
         </is>
       </c>
-      <c r="AB92" t="inlineStr">
-        <is>
-          <t>11:11</t>
+      <c r="AC92" t="inlineStr">
+        <is>
+          <t>Minst 30</t>
         </is>
       </c>
       <c r="AD92" t="b">
@@ -10524,22 +10533,22 @@
       <c r="AT92" t="inlineStr"/>
       <c r="AW92" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX92" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>124756775</v>
+        <v>124756768</v>
       </c>
       <c r="B93" t="n">
-        <v>79891</v>
+        <v>77879</v>
       </c>
       <c r="C93" t="inlineStr">
         <is>
@@ -10552,21 +10561,21 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>6458</v>
+        <v>228579</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
@@ -10576,10 +10585,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>452308</v>
+        <v>452357</v>
       </c>
       <c r="R93" t="n">
-        <v>6990943</v>
+        <v>6990970</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -10611,7 +10620,7 @@
       </c>
       <c r="Z93" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>10:52</t>
         </is>
       </c>
       <c r="AA93" t="inlineStr">
@@ -10621,7 +10630,7 @@
       </c>
       <c r="AB93" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>10:52</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -10648,10 +10657,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>124756734</v>
+        <v>124753634</v>
       </c>
       <c r="B94" t="n">
-        <v>79891</v>
+        <v>91162</v>
       </c>
       <c r="C94" t="inlineStr">
         <is>
@@ -10664,21 +10673,21 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>6458</v>
+        <v>1108</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
@@ -10688,10 +10697,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>452675</v>
+        <v>452750</v>
       </c>
       <c r="R94" t="n">
-        <v>6990435</v>
+        <v>6990344</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -10721,21 +10730,11 @@
           <t>2025-05-03</t>
         </is>
       </c>
-      <c r="Z94" t="inlineStr">
-        <is>
-          <t>14:14</t>
-        </is>
-      </c>
       <c r="AA94" t="inlineStr">
         <is>
           <t>2025-05-03</t>
         </is>
       </c>
-      <c r="AB94" t="inlineStr">
-        <is>
-          <t>14:14</t>
-        </is>
-      </c>
       <c r="AD94" t="b">
         <v>0</v>
       </c>
@@ -10744,41 +10743,26 @@
       </c>
       <c r="AG94" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ94" t="inlineStr">
-        <is>
-          <t>rönn</t>
-        </is>
-      </c>
-      <c r="AK94" t="inlineStr">
-        <is>
-          <t>Sorbus aucuparia</t>
-        </is>
-      </c>
-      <c r="AO94" t="inlineStr">
-        <is>
-          <t>Sorbus aucuparia</t>
-        </is>
       </c>
       <c r="AT94" t="inlineStr"/>
       <c r="AW94" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX94" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY94" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>124753630</v>
+        <v>124756748</v>
       </c>
       <c r="B95" t="n">
-        <v>98101</v>
+        <v>78947</v>
       </c>
       <c r="C95" t="inlineStr">
         <is>
@@ -10787,25 +10771,25 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
@@ -10815,10 +10799,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>452273</v>
+        <v>452609</v>
       </c>
       <c r="R95" t="n">
-        <v>6990906</v>
+        <v>6990543</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10848,14 +10832,19 @@
           <t>2025-05-03</t>
         </is>
       </c>
+      <c r="Z95" t="inlineStr">
+        <is>
+          <t>12:29</t>
+        </is>
+      </c>
       <c r="AA95" t="inlineStr">
         <is>
           <t>2025-05-03</t>
         </is>
       </c>
-      <c r="AC95" t="inlineStr">
-        <is>
-          <t>Minst 10</t>
+      <c r="AB95" t="inlineStr">
+        <is>
+          <t>12:29</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -10870,22 +10859,22 @@
       <c r="AT95" t="inlineStr"/>
       <c r="AW95" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX95" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY95" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>124756749</v>
+        <v>124753625</v>
       </c>
       <c r="B96" t="n">
-        <v>91012</v>
+        <v>98269</v>
       </c>
       <c r="C96" t="inlineStr">
         <is>
@@ -10894,25 +10883,25 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E96" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
@@ -10922,10 +10911,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>452609</v>
+        <v>452550</v>
       </c>
       <c r="R96" t="n">
-        <v>6990543</v>
+        <v>6990907</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -10955,19 +10944,14 @@
           <t>2025-05-03</t>
         </is>
       </c>
-      <c r="Z96" t="inlineStr">
-        <is>
-          <t>12:29</t>
-        </is>
-      </c>
       <c r="AA96" t="inlineStr">
         <is>
           <t>2025-05-03</t>
         </is>
       </c>
-      <c r="AB96" t="inlineStr">
-        <is>
-          <t>12:29</t>
+      <c r="AC96" t="inlineStr">
+        <is>
+          <t>Minst 50</t>
         </is>
       </c>
       <c r="AD96" t="b">
@@ -10982,22 +10966,22 @@
       <c r="AT96" t="inlineStr"/>
       <c r="AW96" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX96" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY96" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>124756730</v>
+        <v>124756745</v>
       </c>
       <c r="B97" t="n">
-        <v>98101</v>
+        <v>98269</v>
       </c>
       <c r="C97" t="inlineStr">
         <is>
@@ -11029,7 +11013,7 @@
       </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t>200</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J97" t="inlineStr">
@@ -11046,10 +11030,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>452675</v>
+        <v>452657</v>
       </c>
       <c r="R97" t="n">
-        <v>6990411</v>
+        <v>6990491</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -11081,7 +11065,7 @@
       </c>
       <c r="Z97" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AA97" t="inlineStr">
@@ -11091,12 +11075,7 @@
       </c>
       <c r="AB97" t="inlineStr">
         <is>
-          <t>14:20</t>
-        </is>
-      </c>
-      <c r="AC97" t="inlineStr">
-        <is>
-          <t>Min antal</t>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AD97" t="b">
@@ -11124,10 +11103,10 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>124756736</v>
+        <v>124756752</v>
       </c>
       <c r="B98" t="n">
-        <v>98101</v>
+        <v>98269</v>
       </c>
       <c r="C98" t="inlineStr">
         <is>
@@ -11176,10 +11155,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>452691</v>
+        <v>452608</v>
       </c>
       <c r="R98" t="n">
-        <v>6990422</v>
+        <v>6990625</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -11211,7 +11190,7 @@
       </c>
       <c r="Z98" t="inlineStr">
         <is>
-          <t>14:13</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AA98" t="inlineStr">
@@ -11221,7 +11200,7 @@
       </c>
       <c r="AB98" t="inlineStr">
         <is>
-          <t>14:13</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AD98" t="b">
@@ -11249,10 +11228,10 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>124753613</v>
+        <v>124756736</v>
       </c>
       <c r="B99" t="n">
-        <v>98101</v>
+        <v>98269</v>
       </c>
       <c r="C99" t="inlineStr">
         <is>
@@ -11282,17 +11261,29 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I99" t="inlineStr"/>
+      <c r="I99" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J99" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K99" t="inlineStr"/>
+      <c r="L99" t="inlineStr"/>
+      <c r="N99" t="inlineStr"/>
       <c r="P99" t="inlineStr">
         <is>
           <t>Häggsåsen N, Jmt</t>
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>452777</v>
+        <v>452691</v>
       </c>
       <c r="R99" t="n">
-        <v>6990299</v>
+        <v>6990422</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -11322,14 +11313,19 @@
           <t>2025-05-03</t>
         </is>
       </c>
+      <c r="Z99" t="inlineStr">
+        <is>
+          <t>14:13</t>
+        </is>
+      </c>
       <c r="AA99" t="inlineStr">
         <is>
           <t>2025-05-03</t>
         </is>
       </c>
-      <c r="AC99" t="inlineStr">
-        <is>
-          <t>Minst 100</t>
+      <c r="AB99" t="inlineStr">
+        <is>
+          <t>14:13</t>
         </is>
       </c>
       <c r="AD99" t="b">
@@ -11338,28 +11334,29 @@
       <c r="AE99" t="b">
         <v>0</v>
       </c>
+      <c r="AF99" t="inlineStr"/>
       <c r="AG99" t="b">
         <v>0</v>
       </c>
       <c r="AT99" t="inlineStr"/>
       <c r="AW99" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX99" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY99" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>124753616</v>
+        <v>124753587</v>
       </c>
       <c r="B100" t="n">
-        <v>98101</v>
+        <v>91166</v>
       </c>
       <c r="C100" t="inlineStr">
         <is>
@@ -11368,25 +11365,25 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E100" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
@@ -11396,10 +11393,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>452742</v>
+        <v>452331</v>
       </c>
       <c r="R100" t="n">
-        <v>6990393</v>
+        <v>6990929</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -11432,11 +11429,6 @@
       <c r="AA100" t="inlineStr">
         <is>
           <t>2025-05-03</t>
-        </is>
-      </c>
-      <c r="AC100" t="inlineStr">
-        <is>
-          <t>Minst 60</t>
         </is>
       </c>
       <c r="AD100" t="b">
@@ -11463,10 +11455,10 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>124753617</v>
+        <v>124753633</v>
       </c>
       <c r="B101" t="n">
-        <v>98101</v>
+        <v>91162</v>
       </c>
       <c r="C101" t="inlineStr">
         <is>
@@ -11475,25 +11467,25 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E101" t="n">
-        <v>220787</v>
+        <v>1108</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
@@ -11503,10 +11495,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>452655</v>
+        <v>452772</v>
       </c>
       <c r="R101" t="n">
-        <v>6990482</v>
+        <v>6990321</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -11539,11 +11531,6 @@
       <c r="AA101" t="inlineStr">
         <is>
           <t>2025-05-03</t>
-        </is>
-      </c>
-      <c r="AC101" t="inlineStr">
-        <is>
-          <t>Minst 50</t>
         </is>
       </c>
       <c r="AD101" t="b">
@@ -11570,10 +11557,10 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>124753588</v>
+        <v>124756753</v>
       </c>
       <c r="B102" t="n">
-        <v>91012</v>
+        <v>91166</v>
       </c>
       <c r="C102" t="inlineStr">
         <is>
@@ -11610,10 +11597,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>452311</v>
+        <v>452608</v>
       </c>
       <c r="R102" t="n">
-        <v>6990887</v>
+        <v>6990625</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -11643,9 +11630,19 @@
           <t>2025-05-03</t>
         </is>
       </c>
+      <c r="Z102" t="inlineStr">
+        <is>
+          <t>12:07</t>
+        </is>
+      </c>
       <c r="AA102" t="inlineStr">
         <is>
           <t>2025-05-03</t>
+        </is>
+      </c>
+      <c r="AB102" t="inlineStr">
+        <is>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AD102" t="b">
@@ -11660,22 +11657,22 @@
       <c r="AT102" t="inlineStr"/>
       <c r="AW102" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX102" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY102" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>124756718</v>
+        <v>124753637</v>
       </c>
       <c r="B103" t="n">
-        <v>91030</v>
+        <v>91184</v>
       </c>
       <c r="C103" t="inlineStr">
         <is>
@@ -11712,10 +11709,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>452857</v>
+        <v>452696</v>
       </c>
       <c r="R103" t="n">
-        <v>6990267</v>
+        <v>6990466</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -11745,19 +11742,9 @@
           <t>2025-05-03</t>
         </is>
       </c>
-      <c r="Z103" t="inlineStr">
-        <is>
-          <t>15:03</t>
-        </is>
-      </c>
       <c r="AA103" t="inlineStr">
         <is>
           <t>2025-05-03</t>
-        </is>
-      </c>
-      <c r="AB103" t="inlineStr">
-        <is>
-          <t>15:03</t>
         </is>
       </c>
       <c r="AD103" t="b">
@@ -11772,22 +11759,22 @@
       <c r="AT103" t="inlineStr"/>
       <c r="AW103" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX103" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY103" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>124756731</v>
+        <v>124756772</v>
       </c>
       <c r="B104" t="n">
-        <v>91012</v>
+        <v>78947</v>
       </c>
       <c r="C104" t="inlineStr">
         <is>
@@ -11800,21 +11787,21 @@
         </is>
       </c>
       <c r="E104" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
@@ -11824,10 +11811,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>452672</v>
+        <v>452344</v>
       </c>
       <c r="R104" t="n">
-        <v>6990427</v>
+        <v>6990942</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -11859,7 +11846,7 @@
       </c>
       <c r="Z104" t="inlineStr">
         <is>
-          <t>14:19</t>
+          <t>10:32</t>
         </is>
       </c>
       <c r="AA104" t="inlineStr">
@@ -11869,7 +11856,7 @@
       </c>
       <c r="AB104" t="inlineStr">
         <is>
-          <t>14:19</t>
+          <t>10:32</t>
         </is>
       </c>
       <c r="AD104" t="b">
@@ -11896,10 +11883,10 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>124753578</v>
+        <v>124756778</v>
       </c>
       <c r="B105" t="n">
-        <v>91012</v>
+        <v>78947</v>
       </c>
       <c r="C105" t="inlineStr">
         <is>
@@ -11912,21 +11899,21 @@
         </is>
       </c>
       <c r="E105" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
@@ -11936,10 +11923,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>452743</v>
+        <v>452153</v>
       </c>
       <c r="R105" t="n">
-        <v>6990405</v>
+        <v>6990834</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -11969,9 +11956,19 @@
           <t>2025-05-03</t>
         </is>
       </c>
+      <c r="Z105" t="inlineStr">
+        <is>
+          <t>10:03</t>
+        </is>
+      </c>
       <c r="AA105" t="inlineStr">
         <is>
           <t>2025-05-03</t>
+        </is>
+      </c>
+      <c r="AB105" t="inlineStr">
+        <is>
+          <t>10:03</t>
         </is>
       </c>
       <c r="AD105" t="b">
@@ -11986,22 +11983,22 @@
       <c r="AT105" t="inlineStr"/>
       <c r="AW105" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX105" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY105" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>124753580</v>
+        <v>124756762</v>
       </c>
       <c r="B106" t="n">
-        <v>91012</v>
+        <v>78947</v>
       </c>
       <c r="C106" t="inlineStr">
         <is>
@@ -12014,21 +12011,21 @@
         </is>
       </c>
       <c r="E106" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
@@ -12038,10 +12035,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>452693</v>
+        <v>452508</v>
       </c>
       <c r="R106" t="n">
-        <v>6990472</v>
+        <v>6990903</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -12071,9 +12068,19 @@
           <t>2025-05-03</t>
         </is>
       </c>
+      <c r="Z106" t="inlineStr">
+        <is>
+          <t>11:20</t>
+        </is>
+      </c>
       <c r="AA106" t="inlineStr">
         <is>
           <t>2025-05-03</t>
+        </is>
+      </c>
+      <c r="AB106" t="inlineStr">
+        <is>
+          <t>11:20</t>
         </is>
       </c>
       <c r="AD106" t="b">
@@ -12088,22 +12095,22 @@
       <c r="AT106" t="inlineStr"/>
       <c r="AW106" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX106" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY106" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>124753584</v>
+        <v>124753638</v>
       </c>
       <c r="B107" t="n">
-        <v>91012</v>
+        <v>78947</v>
       </c>
       <c r="C107" t="inlineStr">
         <is>
@@ -12116,21 +12123,21 @@
         </is>
       </c>
       <c r="E107" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
@@ -12140,10 +12147,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>452444</v>
+        <v>452823</v>
       </c>
       <c r="R107" t="n">
-        <v>6990774</v>
+        <v>6990367</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -12202,10 +12209,10 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>124753581</v>
+        <v>124756754</v>
       </c>
       <c r="B108" t="n">
-        <v>91012</v>
+        <v>78947</v>
       </c>
       <c r="C108" t="inlineStr">
         <is>
@@ -12218,21 +12225,21 @@
         </is>
       </c>
       <c r="E108" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
@@ -12242,10 +12249,10 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>452643</v>
+        <v>452544</v>
       </c>
       <c r="R108" t="n">
-        <v>6990504</v>
+        <v>6990646</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -12275,9 +12282,19 @@
           <t>2025-05-03</t>
         </is>
       </c>
+      <c r="Z108" t="inlineStr">
+        <is>
+          <t>12:04</t>
+        </is>
+      </c>
       <c r="AA108" t="inlineStr">
         <is>
           <t>2025-05-03</t>
+        </is>
+      </c>
+      <c r="AB108" t="inlineStr">
+        <is>
+          <t>12:04</t>
         </is>
       </c>
       <c r="AD108" t="b">
@@ -12292,22 +12309,22 @@
       <c r="AT108" t="inlineStr"/>
       <c r="AW108" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX108" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY108" t="inlineStr"/>
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>124753576</v>
+        <v>124753630</v>
       </c>
       <c r="B109" t="n">
-        <v>91012</v>
+        <v>98269</v>
       </c>
       <c r="C109" t="inlineStr">
         <is>
@@ -12316,25 +12333,25 @@
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E109" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
@@ -12344,10 +12361,10 @@
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>452837</v>
+        <v>452273</v>
       </c>
       <c r="R109" t="n">
-        <v>6990384</v>
+        <v>6990906</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -12380,6 +12397,11 @@
       <c r="AA109" t="inlineStr">
         <is>
           <t>2025-05-03</t>
+        </is>
+      </c>
+      <c r="AC109" t="inlineStr">
+        <is>
+          <t>Minst 10</t>
         </is>
       </c>
       <c r="AD109" t="b">
@@ -12406,10 +12428,10 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>124753587</v>
+        <v>124753616</v>
       </c>
       <c r="B110" t="n">
-        <v>91012</v>
+        <v>98269</v>
       </c>
       <c r="C110" t="inlineStr">
         <is>
@@ -12418,25 +12440,25 @@
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E110" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
@@ -12446,10 +12468,10 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>452331</v>
+        <v>452742</v>
       </c>
       <c r="R110" t="n">
-        <v>6990929</v>
+        <v>6990393</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -12482,6 +12504,11 @@
       <c r="AA110" t="inlineStr">
         <is>
           <t>2025-05-03</t>
+        </is>
+      </c>
+      <c r="AC110" t="inlineStr">
+        <is>
+          <t>Minst 60</t>
         </is>
       </c>
       <c r="AD110" t="b">
@@ -12508,10 +12535,10 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>124753634</v>
+        <v>124753580</v>
       </c>
       <c r="B111" t="n">
-        <v>91008</v>
+        <v>91166</v>
       </c>
       <c r="C111" t="inlineStr">
         <is>
@@ -12524,21 +12551,21 @@
         </is>
       </c>
       <c r="E111" t="n">
-        <v>1108</v>
+        <v>1202</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
@@ -12548,10 +12575,10 @@
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>452750</v>
+        <v>452693</v>
       </c>
       <c r="R111" t="n">
-        <v>6990344</v>
+        <v>6990472</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -12610,10 +12637,10 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>124756719</v>
+        <v>124756721</v>
       </c>
       <c r="B112" t="n">
-        <v>79927</v>
+        <v>80028</v>
       </c>
       <c r="C112" t="inlineStr">
         <is>
@@ -12622,25 +12649,25 @@
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E112" t="n">
-        <v>6464</v>
+        <v>6458</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I112" t="inlineStr"/>
@@ -12685,7 +12712,7 @@
       </c>
       <c r="Z112" t="inlineStr">
         <is>
-          <t>14:59</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AA112" t="inlineStr">
@@ -12695,7 +12722,7 @@
       </c>
       <c r="AB112" t="inlineStr">
         <is>
-          <t>14:59</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AD112" t="b">
@@ -12706,6 +12733,21 @@
       </c>
       <c r="AG112" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ112" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK112" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO112" t="inlineStr">
+        <is>
+          <t>Omkullfallen grov stam # Salix caprea</t>
+        </is>
       </c>
       <c r="AT112" t="inlineStr"/>
       <c r="AW112" t="inlineStr">
@@ -12722,10 +12764,10 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>124756728</v>
+        <v>124756742</v>
       </c>
       <c r="B113" t="n">
-        <v>79891</v>
+        <v>80064</v>
       </c>
       <c r="C113" t="inlineStr">
         <is>
@@ -12734,25 +12776,25 @@
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E113" t="n">
-        <v>6458</v>
+        <v>6464</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
@@ -12762,10 +12804,10 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>452745</v>
+        <v>452682</v>
       </c>
       <c r="R113" t="n">
-        <v>6990359</v>
+        <v>6990476</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -12797,7 +12839,7 @@
       </c>
       <c r="Z113" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>13:53</t>
         </is>
       </c>
       <c r="AA113" t="inlineStr">
@@ -12807,7 +12849,7 @@
       </c>
       <c r="AB113" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>13:53</t>
         </is>
       </c>
       <c r="AD113" t="b">
@@ -12821,17 +12863,17 @@
       </c>
       <c r="AJ113" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>rönn</t>
         </is>
       </c>
       <c r="AK113" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Sorbus aucuparia</t>
         </is>
       </c>
       <c r="AO113" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Sorbus aucuparia</t>
         </is>
       </c>
       <c r="AT113" t="inlineStr"/>
@@ -12849,10 +12891,10 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>124756761</v>
+        <v>124756728</v>
       </c>
       <c r="B114" t="n">
-        <v>78810</v>
+        <v>80028</v>
       </c>
       <c r="C114" t="inlineStr">
         <is>
@@ -12865,21 +12907,21 @@
         </is>
       </c>
       <c r="E114" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
@@ -12889,10 +12931,10 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>452532</v>
+        <v>452745</v>
       </c>
       <c r="R114" t="n">
-        <v>6990825</v>
+        <v>6990359</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -12924,7 +12966,7 @@
       </c>
       <c r="Z114" t="inlineStr">
         <is>
-          <t>11:26</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AA114" t="inlineStr">
@@ -12934,7 +12976,7 @@
       </c>
       <c r="AB114" t="inlineStr">
         <is>
-          <t>11:26</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AD114" t="b">
@@ -12945,6 +12987,21 @@
       </c>
       <c r="AG114" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ114" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK114" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO114" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
       </c>
       <c r="AT114" t="inlineStr"/>
       <c r="AW114" t="inlineStr">
@@ -12961,10 +13018,10 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>124756750</v>
+        <v>124753604</v>
       </c>
       <c r="B115" t="n">
-        <v>98101</v>
+        <v>80029</v>
       </c>
       <c r="C115" t="inlineStr">
         <is>
@@ -12973,50 +13030,38 @@
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E115" t="n">
-        <v>220787</v>
+        <v>2081</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I115" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J115" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K115" t="inlineStr"/>
-      <c r="L115" t="inlineStr"/>
-      <c r="N115" t="inlineStr"/>
+          <t>(Scop.) DC.</t>
+        </is>
+      </c>
+      <c r="I115" t="inlineStr"/>
       <c r="P115" t="inlineStr">
         <is>
           <t>Häggsåsen N, Jmt</t>
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>452617</v>
+        <v>452435</v>
       </c>
       <c r="R115" t="n">
-        <v>6990549</v>
+        <v>6990938</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -13046,50 +13091,39 @@
           <t>2025-05-03</t>
         </is>
       </c>
-      <c r="Z115" t="inlineStr">
-        <is>
-          <t>12:28</t>
-        </is>
-      </c>
       <c r="AA115" t="inlineStr">
         <is>
           <t>2025-05-03</t>
         </is>
       </c>
-      <c r="AB115" t="inlineStr">
-        <is>
-          <t>12:28</t>
-        </is>
-      </c>
       <c r="AD115" t="b">
         <v>0</v>
       </c>
       <c r="AE115" t="b">
         <v>0</v>
       </c>
-      <c r="AF115" t="inlineStr"/>
       <c r="AG115" t="b">
         <v>0</v>
       </c>
       <c r="AT115" t="inlineStr"/>
       <c r="AW115" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX115" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY115" t="inlineStr"/>
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>124756777</v>
+        <v>124753581</v>
       </c>
       <c r="B116" t="n">
-        <v>98101</v>
+        <v>91166</v>
       </c>
       <c r="C116" t="inlineStr">
         <is>
@@ -13098,50 +13132,38 @@
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E116" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I116" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J116" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K116" t="inlineStr"/>
-      <c r="L116" t="inlineStr"/>
-      <c r="N116" t="inlineStr"/>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I116" t="inlineStr"/>
       <c r="P116" t="inlineStr">
         <is>
           <t>Häggsåsen N, Jmt</t>
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>452146</v>
+        <v>452643</v>
       </c>
       <c r="R116" t="n">
-        <v>6990839</v>
+        <v>6990504</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -13171,50 +13193,39 @@
           <t>2025-05-03</t>
         </is>
       </c>
-      <c r="Z116" t="inlineStr">
-        <is>
-          <t>10:06</t>
-        </is>
-      </c>
       <c r="AA116" t="inlineStr">
         <is>
           <t>2025-05-03</t>
         </is>
       </c>
-      <c r="AB116" t="inlineStr">
-        <is>
-          <t>10:06</t>
-        </is>
-      </c>
       <c r="AD116" t="b">
         <v>0</v>
       </c>
       <c r="AE116" t="b">
         <v>0</v>
       </c>
-      <c r="AF116" t="inlineStr"/>
       <c r="AG116" t="b">
         <v>0</v>
       </c>
       <c r="AT116" t="inlineStr"/>
       <c r="AW116" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX116" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY116" t="inlineStr"/>
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>124756768</v>
+        <v>124756775</v>
       </c>
       <c r="B117" t="n">
-        <v>77743</v>
+        <v>80028</v>
       </c>
       <c r="C117" t="inlineStr">
         <is>
@@ -13227,21 +13238,21 @@
         </is>
       </c>
       <c r="E117" t="n">
-        <v>228579</v>
+        <v>6458</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
@@ -13251,10 +13262,10 @@
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>452357</v>
+        <v>452308</v>
       </c>
       <c r="R117" t="n">
-        <v>6990970</v>
+        <v>6990943</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>
@@ -13286,7 +13297,7 @@
       </c>
       <c r="Z117" t="inlineStr">
         <is>
-          <t>10:52</t>
+          <t>10:22</t>
         </is>
       </c>
       <c r="AA117" t="inlineStr">
@@ -13296,7 +13307,7 @@
       </c>
       <c r="AB117" t="inlineStr">
         <is>
-          <t>10:52</t>
+          <t>10:22</t>
         </is>
       </c>
       <c r="AD117" t="b">
@@ -13323,10 +13334,10 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>124756739</v>
+        <v>124756727</v>
       </c>
       <c r="B118" t="n">
-        <v>98101</v>
+        <v>80057</v>
       </c>
       <c r="C118" t="inlineStr">
         <is>
@@ -13335,50 +13346,38 @@
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E118" t="n">
-        <v>220787</v>
+        <v>6462</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I118" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="J118" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K118" t="inlineStr"/>
-      <c r="L118" t="inlineStr"/>
-      <c r="N118" t="inlineStr"/>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
+      <c r="I118" t="inlineStr"/>
       <c r="P118" t="inlineStr">
         <is>
           <t>Häggsåsen N, Jmt</t>
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>452711</v>
+        <v>452745</v>
       </c>
       <c r="R118" t="n">
-        <v>6990473</v>
+        <v>6990359</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -13410,7 +13409,7 @@
       </c>
       <c r="Z118" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AA118" t="inlineStr">
@@ -13420,7 +13419,7 @@
       </c>
       <c r="AB118" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AD118" t="b">
@@ -13429,7 +13428,6 @@
       <c r="AE118" t="b">
         <v>0</v>
       </c>
-      <c r="AF118" t="inlineStr"/>
       <c r="AG118" t="b">
         <v>0</v>
       </c>
@@ -13448,10 +13446,10 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>124756756</v>
+        <v>124753582</v>
       </c>
       <c r="B119" t="n">
-        <v>78810</v>
+        <v>91166</v>
       </c>
       <c r="C119" t="inlineStr">
         <is>
@@ -13464,21 +13462,21 @@
         </is>
       </c>
       <c r="E119" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I119" t="inlineStr"/>
@@ -13488,10 +13486,10 @@
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>452545</v>
+        <v>452649</v>
       </c>
       <c r="R119" t="n">
-        <v>6990691</v>
+        <v>6990621</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -13521,19 +13519,9 @@
           <t>2025-05-03</t>
         </is>
       </c>
-      <c r="Z119" t="inlineStr">
-        <is>
-          <t>11:54</t>
-        </is>
-      </c>
       <c r="AA119" t="inlineStr">
         <is>
           <t>2025-05-03</t>
-        </is>
-      </c>
-      <c r="AB119" t="inlineStr">
-        <is>
-          <t>11:54</t>
         </is>
       </c>
       <c r="AD119" t="b">
@@ -13548,22 +13536,22 @@
       <c r="AT119" t="inlineStr"/>
       <c r="AW119" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX119" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY119" t="inlineStr"/>
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>124756688</v>
+        <v>124756743</v>
       </c>
       <c r="B120" t="n">
-        <v>79891</v>
+        <v>80028</v>
       </c>
       <c r="C120" t="inlineStr">
         <is>
@@ -13600,10 +13588,10 @@
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>452694</v>
+        <v>452682</v>
       </c>
       <c r="R120" t="n">
-        <v>6990598</v>
+        <v>6990476</v>
       </c>
       <c r="S120" t="n">
         <v>10</v>
@@ -13635,7 +13623,7 @@
       </c>
       <c r="Z120" t="inlineStr">
         <is>
-          <t>20:19</t>
+          <t>13:53</t>
         </is>
       </c>
       <c r="AA120" t="inlineStr">
@@ -13645,7 +13633,7 @@
       </c>
       <c r="AB120" t="inlineStr">
         <is>
-          <t>20:19</t>
+          <t>13:53</t>
         </is>
       </c>
       <c r="AD120" t="b">
@@ -13656,6 +13644,21 @@
       </c>
       <c r="AG120" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ120" t="inlineStr">
+        <is>
+          <t>rönn</t>
+        </is>
+      </c>
+      <c r="AK120" t="inlineStr">
+        <is>
+          <t>Sorbus aucuparia</t>
+        </is>
+      </c>
+      <c r="AO120" t="inlineStr">
+        <is>
+          <t>Sorbus aucuparia</t>
+        </is>
       </c>
       <c r="AT120" t="inlineStr"/>
       <c r="AW120" t="inlineStr">
@@ -13672,10 +13675,10 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>124753633</v>
+        <v>124753623</v>
       </c>
       <c r="B121" t="n">
-        <v>91008</v>
+        <v>98269</v>
       </c>
       <c r="C121" t="inlineStr">
         <is>
@@ -13684,25 +13687,25 @@
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E121" t="n">
-        <v>1108</v>
+        <v>220787</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
@@ -13712,10 +13715,10 @@
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>452772</v>
+        <v>452510</v>
       </c>
       <c r="R121" t="n">
-        <v>6990321</v>
+        <v>6990873</v>
       </c>
       <c r="S121" t="n">
         <v>10</v>
@@ -13748,6 +13751,11 @@
       <c r="AA121" t="inlineStr">
         <is>
           <t>2025-05-03</t>
+        </is>
+      </c>
+      <c r="AC121" t="inlineStr">
+        <is>
+          <t>Minst 50</t>
         </is>
       </c>
       <c r="AD121" t="b">
@@ -13774,10 +13782,10 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>124756763</v>
+        <v>124753617</v>
       </c>
       <c r="B122" t="n">
-        <v>98101</v>
+        <v>98269</v>
       </c>
       <c r="C122" t="inlineStr">
         <is>
@@ -13807,29 +13815,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I122" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J122" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K122" t="inlineStr"/>
-      <c r="L122" t="inlineStr"/>
-      <c r="N122" t="inlineStr"/>
+      <c r="I122" t="inlineStr"/>
       <c r="P122" t="inlineStr">
         <is>
           <t>Häggsåsen N, Jmt</t>
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>452478</v>
+        <v>452655</v>
       </c>
       <c r="R122" t="n">
-        <v>6990887</v>
+        <v>6990482</v>
       </c>
       <c r="S122" t="n">
         <v>10</v>
@@ -13859,19 +13855,14 @@
           <t>2025-05-03</t>
         </is>
       </c>
-      <c r="Z122" t="inlineStr">
-        <is>
-          <t>11:18</t>
-        </is>
-      </c>
       <c r="AA122" t="inlineStr">
         <is>
           <t>2025-05-03</t>
         </is>
       </c>
-      <c r="AB122" t="inlineStr">
-        <is>
-          <t>11:18</t>
+      <c r="AC122" t="inlineStr">
+        <is>
+          <t>Minst 50</t>
         </is>
       </c>
       <c r="AD122" t="b">
@@ -13880,29 +13871,28 @@
       <c r="AE122" t="b">
         <v>0</v>
       </c>
-      <c r="AF122" t="inlineStr"/>
       <c r="AG122" t="b">
         <v>0</v>
       </c>
       <c r="AT122" t="inlineStr"/>
       <c r="AW122" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX122" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY122" t="inlineStr"/>
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>124756740</v>
+        <v>124756749</v>
       </c>
       <c r="B123" t="n">
-        <v>91457</v>
+        <v>91166</v>
       </c>
       <c r="C123" t="inlineStr">
         <is>
@@ -13911,25 +13901,25 @@
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E123" t="n">
-        <v>1209</v>
+        <v>1202</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I123" t="inlineStr"/>
@@ -13939,10 +13929,10 @@
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>452701</v>
+        <v>452609</v>
       </c>
       <c r="R123" t="n">
-        <v>6990475</v>
+        <v>6990543</v>
       </c>
       <c r="S123" t="n">
         <v>10</v>
@@ -13974,7 +13964,7 @@
       </c>
       <c r="Z123" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>12:29</t>
         </is>
       </c>
       <c r="AA123" t="inlineStr">
@@ -13984,7 +13974,7 @@
       </c>
       <c r="AB123" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>12:29</t>
         </is>
       </c>
       <c r="AD123" t="b">
@@ -14011,10 +14001,10 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>124753585</v>
+        <v>124756746</v>
       </c>
       <c r="B124" t="n">
-        <v>91012</v>
+        <v>91166</v>
       </c>
       <c r="C124" t="inlineStr">
         <is>
@@ -14051,10 +14041,10 @@
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>452595</v>
+        <v>452639</v>
       </c>
       <c r="R124" t="n">
-        <v>6990913</v>
+        <v>6990537</v>
       </c>
       <c r="S124" t="n">
         <v>10</v>
@@ -14084,9 +14074,19 @@
           <t>2025-05-03</t>
         </is>
       </c>
+      <c r="Z124" t="inlineStr">
+        <is>
+          <t>13:36</t>
+        </is>
+      </c>
       <c r="AA124" t="inlineStr">
         <is>
           <t>2025-05-03</t>
+        </is>
+      </c>
+      <c r="AB124" t="inlineStr">
+        <is>
+          <t>13:36</t>
         </is>
       </c>
       <c r="AD124" t="b">
@@ -14101,22 +14101,22 @@
       <c r="AT124" t="inlineStr"/>
       <c r="AW124" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX124" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY124" t="inlineStr"/>
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>124756743</v>
+        <v>124753576</v>
       </c>
       <c r="B125" t="n">
-        <v>79891</v>
+        <v>91166</v>
       </c>
       <c r="C125" t="inlineStr">
         <is>
@@ -14129,21 +14129,21 @@
         </is>
       </c>
       <c r="E125" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I125" t="inlineStr"/>
@@ -14153,10 +14153,10 @@
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>452682</v>
+        <v>452837</v>
       </c>
       <c r="R125" t="n">
-        <v>6990476</v>
+        <v>6990384</v>
       </c>
       <c r="S125" t="n">
         <v>10</v>
@@ -14186,21 +14186,11 @@
           <t>2025-05-03</t>
         </is>
       </c>
-      <c r="Z125" t="inlineStr">
-        <is>
-          <t>13:53</t>
-        </is>
-      </c>
       <c r="AA125" t="inlineStr">
         <is>
           <t>2025-05-03</t>
         </is>
       </c>
-      <c r="AB125" t="inlineStr">
-        <is>
-          <t>13:53</t>
-        </is>
-      </c>
       <c r="AD125" t="b">
         <v>0</v>
       </c>
@@ -14209,41 +14199,26 @@
       </c>
       <c r="AG125" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ125" t="inlineStr">
-        <is>
-          <t>rönn</t>
-        </is>
-      </c>
-      <c r="AK125" t="inlineStr">
-        <is>
-          <t>Sorbus aucuparia</t>
-        </is>
-      </c>
-      <c r="AO125" t="inlineStr">
-        <is>
-          <t>Sorbus aucuparia</t>
-        </is>
       </c>
       <c r="AT125" t="inlineStr"/>
       <c r="AW125" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX125" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY125" t="inlineStr"/>
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>124753621</v>
+        <v>124756767</v>
       </c>
       <c r="B126" t="n">
-        <v>98101</v>
+        <v>78947</v>
       </c>
       <c r="C126" t="inlineStr">
         <is>
@@ -14252,25 +14227,25 @@
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E126" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I126" t="inlineStr"/>
@@ -14280,10 +14255,10 @@
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>452506</v>
+        <v>452362</v>
       </c>
       <c r="R126" t="n">
-        <v>6990758</v>
+        <v>6991003</v>
       </c>
       <c r="S126" t="n">
         <v>10</v>
@@ -14313,14 +14288,19 @@
           <t>2025-05-03</t>
         </is>
       </c>
+      <c r="Z126" t="inlineStr">
+        <is>
+          <t>10:55</t>
+        </is>
+      </c>
       <c r="AA126" t="inlineStr">
         <is>
           <t>2025-05-03</t>
         </is>
       </c>
-      <c r="AC126" t="inlineStr">
-        <is>
-          <t>Minst 60</t>
+      <c r="AB126" t="inlineStr">
+        <is>
+          <t>10:55</t>
         </is>
       </c>
       <c r="AD126" t="b">
@@ -14335,22 +14315,22 @@
       <c r="AT126" t="inlineStr"/>
       <c r="AW126" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX126" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY126" t="inlineStr"/>
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>124756745</v>
+        <v>124753632</v>
       </c>
       <c r="B127" t="n">
-        <v>98101</v>
+        <v>98269</v>
       </c>
       <c r="C127" t="inlineStr">
         <is>
@@ -14380,29 +14360,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I127" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J127" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K127" t="inlineStr"/>
-      <c r="L127" t="inlineStr"/>
-      <c r="N127" t="inlineStr"/>
+      <c r="I127" t="inlineStr"/>
       <c r="P127" t="inlineStr">
         <is>
           <t>Häggsåsen N, Jmt</t>
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>452657</v>
+        <v>452455</v>
       </c>
       <c r="R127" t="n">
-        <v>6990491</v>
+        <v>6990942</v>
       </c>
       <c r="S127" t="n">
         <v>10</v>
@@ -14432,19 +14400,14 @@
           <t>2025-05-03</t>
         </is>
       </c>
-      <c r="Z127" t="inlineStr">
-        <is>
-          <t>13:44</t>
-        </is>
-      </c>
       <c r="AA127" t="inlineStr">
         <is>
           <t>2025-05-03</t>
         </is>
       </c>
-      <c r="AB127" t="inlineStr">
-        <is>
-          <t>13:44</t>
+      <c r="AC127" t="inlineStr">
+        <is>
+          <t>Minst 30</t>
         </is>
       </c>
       <c r="AD127" t="b">
@@ -14453,29 +14416,28 @@
       <c r="AE127" t="b">
         <v>0</v>
       </c>
-      <c r="AF127" t="inlineStr"/>
       <c r="AG127" t="b">
         <v>0</v>
       </c>
       <c r="AT127" t="inlineStr"/>
       <c r="AW127" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX127" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY127" t="inlineStr"/>
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>124756724</v>
+        <v>124753611</v>
       </c>
       <c r="B128" t="n">
-        <v>91012</v>
+        <v>98269</v>
       </c>
       <c r="C128" t="inlineStr">
         <is>
@@ -14484,25 +14446,25 @@
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E128" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I128" t="inlineStr"/>
@@ -14512,10 +14474,10 @@
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>452793</v>
+        <v>452997</v>
       </c>
       <c r="R128" t="n">
-        <v>6990262</v>
+        <v>6990332</v>
       </c>
       <c r="S128" t="n">
         <v>10</v>
@@ -14545,19 +14507,14 @@
           <t>2025-05-03</t>
         </is>
       </c>
-      <c r="Z128" t="inlineStr">
-        <is>
-          <t>14:44</t>
-        </is>
-      </c>
       <c r="AA128" t="inlineStr">
         <is>
           <t>2025-05-03</t>
         </is>
       </c>
-      <c r="AB128" t="inlineStr">
-        <is>
-          <t>14:44</t>
+      <c r="AC128" t="inlineStr">
+        <is>
+          <t>Minst 100</t>
         </is>
       </c>
       <c r="AD128" t="b">
@@ -14572,22 +14529,22 @@
       <c r="AT128" t="inlineStr"/>
       <c r="AW128" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX128" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY128" t="inlineStr"/>
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>124756758</v>
+        <v>124756751</v>
       </c>
       <c r="B129" t="n">
-        <v>90962</v>
+        <v>98269</v>
       </c>
       <c r="C129" t="inlineStr">
         <is>
@@ -14596,38 +14553,50 @@
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E129" t="n">
-        <v>112</v>
+        <v>220787</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Stjärntagging</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Asterodon ferruginosus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>Pat.</t>
-        </is>
-      </c>
-      <c r="I129" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I129" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J129" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K129" t="inlineStr"/>
+      <c r="L129" t="inlineStr"/>
+      <c r="N129" t="inlineStr"/>
       <c r="P129" t="inlineStr">
         <is>
           <t>Häggsåsen N, Jmt</t>
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>452509</v>
+        <v>452638</v>
       </c>
       <c r="R129" t="n">
-        <v>6990778</v>
+        <v>6990559</v>
       </c>
       <c r="S129" t="n">
         <v>10</v>
@@ -14659,7 +14628,7 @@
       </c>
       <c r="Z129" t="inlineStr">
         <is>
-          <t>11:40</t>
+          <t>12:23</t>
         </is>
       </c>
       <c r="AA129" t="inlineStr">
@@ -14669,7 +14638,7 @@
       </c>
       <c r="AB129" t="inlineStr">
         <is>
-          <t>11:40</t>
+          <t>12:23</t>
         </is>
       </c>
       <c r="AD129" t="b">
@@ -14678,6 +14647,7 @@
       <c r="AE129" t="b">
         <v>0</v>
       </c>
+      <c r="AF129" t="inlineStr"/>
       <c r="AG129" t="b">
         <v>0</v>
       </c>
@@ -14696,10 +14666,10 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>124753635</v>
+        <v>124756758</v>
       </c>
       <c r="B130" t="n">
-        <v>91030</v>
+        <v>91116</v>
       </c>
       <c r="C130" t="inlineStr">
         <is>
@@ -14712,21 +14682,21 @@
         </is>
       </c>
       <c r="E130" t="n">
-        <v>5432</v>
+        <v>112</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Stjärntagging</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Asterodon ferruginosus</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>Pat.</t>
         </is>
       </c>
       <c r="I130" t="inlineStr"/>
@@ -14736,10 +14706,10 @@
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>452732</v>
+        <v>452509</v>
       </c>
       <c r="R130" t="n">
-        <v>6990486</v>
+        <v>6990778</v>
       </c>
       <c r="S130" t="n">
         <v>10</v>
@@ -14769,9 +14739,19 @@
           <t>2025-05-03</t>
         </is>
       </c>
+      <c r="Z130" t="inlineStr">
+        <is>
+          <t>11:40</t>
+        </is>
+      </c>
       <c r="AA130" t="inlineStr">
         <is>
           <t>2025-05-03</t>
+        </is>
+      </c>
+      <c r="AB130" t="inlineStr">
+        <is>
+          <t>11:40</t>
         </is>
       </c>
       <c r="AD130" t="b">
@@ -14786,22 +14766,22 @@
       <c r="AT130" t="inlineStr"/>
       <c r="AW130" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX130" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY130" t="inlineStr"/>
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>124753609</v>
+        <v>124753605</v>
       </c>
       <c r="B131" t="n">
-        <v>79891</v>
+        <v>80029</v>
       </c>
       <c r="C131" t="inlineStr">
         <is>
@@ -14814,21 +14794,21 @@
         </is>
       </c>
       <c r="E131" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I131" t="inlineStr"/>
@@ -14838,10 +14818,10 @@
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>452528</v>
+        <v>452408</v>
       </c>
       <c r="R131" t="n">
-        <v>6990710</v>
+        <v>6990952</v>
       </c>
       <c r="S131" t="n">
         <v>10</v>
@@ -14900,10 +14880,10 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>124753625</v>
+        <v>124756763</v>
       </c>
       <c r="B132" t="n">
-        <v>98101</v>
+        <v>98269</v>
       </c>
       <c r="C132" t="inlineStr">
         <is>
@@ -14933,17 +14913,29 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I132" t="inlineStr"/>
+      <c r="I132" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J132" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K132" t="inlineStr"/>
+      <c r="L132" t="inlineStr"/>
+      <c r="N132" t="inlineStr"/>
       <c r="P132" t="inlineStr">
         <is>
           <t>Häggsåsen N, Jmt</t>
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>452550</v>
+        <v>452478</v>
       </c>
       <c r="R132" t="n">
-        <v>6990907</v>
+        <v>6990887</v>
       </c>
       <c r="S132" t="n">
         <v>10</v>
@@ -14973,14 +14965,19 @@
           <t>2025-05-03</t>
         </is>
       </c>
+      <c r="Z132" t="inlineStr">
+        <is>
+          <t>11:18</t>
+        </is>
+      </c>
       <c r="AA132" t="inlineStr">
         <is>
           <t>2025-05-03</t>
         </is>
       </c>
-      <c r="AC132" t="inlineStr">
-        <is>
-          <t>Minst 50</t>
+      <c r="AB132" t="inlineStr">
+        <is>
+          <t>11:18</t>
         </is>
       </c>
       <c r="AD132" t="b">
@@ -14989,28 +14986,29 @@
       <c r="AE132" t="b">
         <v>0</v>
       </c>
+      <c r="AF132" t="inlineStr"/>
       <c r="AG132" t="b">
         <v>0</v>
       </c>
       <c r="AT132" t="inlineStr"/>
       <c r="AW132" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX132" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY132" t="inlineStr"/>
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>124756759</v>
+        <v>124756718</v>
       </c>
       <c r="B133" t="n">
-        <v>91012</v>
+        <v>91184</v>
       </c>
       <c r="C133" t="inlineStr">
         <is>
@@ -15023,21 +15021,21 @@
         </is>
       </c>
       <c r="E133" t="n">
-        <v>1202</v>
+        <v>5432</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I133" t="inlineStr"/>
@@ -15047,10 +15045,10 @@
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>452509</v>
+        <v>452857</v>
       </c>
       <c r="R133" t="n">
-        <v>6990778</v>
+        <v>6990267</v>
       </c>
       <c r="S133" t="n">
         <v>10</v>
@@ -15082,7 +15080,7 @@
       </c>
       <c r="Z133" t="inlineStr">
         <is>
-          <t>11:39</t>
+          <t>15:03</t>
         </is>
       </c>
       <c r="AA133" t="inlineStr">
@@ -15092,7 +15090,7 @@
       </c>
       <c r="AB133" t="inlineStr">
         <is>
-          <t>11:39</t>
+          <t>15:03</t>
         </is>
       </c>
       <c r="AD133" t="b">
@@ -15119,10 +15117,10 @@
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>124753577</v>
+        <v>124756719</v>
       </c>
       <c r="B134" t="n">
-        <v>91012</v>
+        <v>80064</v>
       </c>
       <c r="C134" t="inlineStr">
         <is>
@@ -15131,25 +15129,25 @@
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E134" t="n">
-        <v>1202</v>
+        <v>6464</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I134" t="inlineStr"/>
@@ -15159,10 +15157,10 @@
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>452833</v>
+        <v>452823</v>
       </c>
       <c r="R134" t="n">
-        <v>6990388</v>
+        <v>6990261</v>
       </c>
       <c r="S134" t="n">
         <v>10</v>
@@ -15192,9 +15190,19 @@
           <t>2025-05-03</t>
         </is>
       </c>
+      <c r="Z134" t="inlineStr">
+        <is>
+          <t>14:59</t>
+        </is>
+      </c>
       <c r="AA134" t="inlineStr">
         <is>
           <t>2025-05-03</t>
+        </is>
+      </c>
+      <c r="AB134" t="inlineStr">
+        <is>
+          <t>14:59</t>
         </is>
       </c>
       <c r="AD134" t="b">
@@ -15209,22 +15217,22 @@
       <c r="AT134" t="inlineStr"/>
       <c r="AW134" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX134" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY134" t="inlineStr"/>
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>124756742</v>
+        <v>124756765</v>
       </c>
       <c r="B135" t="n">
-        <v>79927</v>
+        <v>78947</v>
       </c>
       <c r="C135" t="inlineStr">
         <is>
@@ -15233,25 +15241,25 @@
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E135" t="n">
-        <v>6464</v>
+        <v>6425</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I135" t="inlineStr"/>
@@ -15261,10 +15269,10 @@
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>452682</v>
+        <v>452432</v>
       </c>
       <c r="R135" t="n">
-        <v>6990476</v>
+        <v>6990942</v>
       </c>
       <c r="S135" t="n">
         <v>10</v>
@@ -15296,7 +15304,7 @@
       </c>
       <c r="Z135" t="inlineStr">
         <is>
-          <t>13:53</t>
+          <t>11:05</t>
         </is>
       </c>
       <c r="AA135" t="inlineStr">
@@ -15306,7 +15314,7 @@
       </c>
       <c r="AB135" t="inlineStr">
         <is>
-          <t>13:53</t>
+          <t>11:05</t>
         </is>
       </c>
       <c r="AD135" t="b">
@@ -15317,21 +15325,6 @@
       </c>
       <c r="AG135" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ135" t="inlineStr">
-        <is>
-          <t>rönn</t>
-        </is>
-      </c>
-      <c r="AK135" t="inlineStr">
-        <is>
-          <t>Sorbus aucuparia</t>
-        </is>
-      </c>
-      <c r="AO135" t="inlineStr">
-        <is>
-          <t>Sorbus aucuparia</t>
-        </is>
       </c>
       <c r="AT135" t="inlineStr"/>
       <c r="AW135" t="inlineStr">
@@ -15348,10 +15341,10 @@
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>124756738</v>
+        <v>124756733</v>
       </c>
       <c r="B136" t="n">
-        <v>74899</v>
+        <v>80064</v>
       </c>
       <c r="C136" t="inlineStr">
         <is>
@@ -15360,41 +15353,38 @@
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E136" t="n">
-        <v>6486</v>
+        <v>6464</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Skuggnål</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Chaenotheca sphaerocephala</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>Nádv.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I136" t="inlineStr"/>
-      <c r="J136" t="inlineStr"/>
-      <c r="K136" t="inlineStr"/>
-      <c r="N136" t="inlineStr"/>
       <c r="P136" t="inlineStr">
         <is>
           <t>Häggsåsen N, Jmt</t>
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>452703</v>
+        <v>452675</v>
       </c>
       <c r="R136" t="n">
-        <v>6990457</v>
+        <v>6990435</v>
       </c>
       <c r="S136" t="n">
         <v>10</v>
@@ -15426,7 +15416,7 @@
       </c>
       <c r="Z136" t="inlineStr">
         <is>
-          <t>14:09</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="AA136" t="inlineStr">
@@ -15436,7 +15426,7 @@
       </c>
       <c r="AB136" t="inlineStr">
         <is>
-          <t>14:09</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="AD136" t="b">
@@ -15445,13 +15435,23 @@
       <c r="AE136" t="b">
         <v>0</v>
       </c>
-      <c r="AF136" t="inlineStr">
-        <is>
-          <t>mikroskoperad</t>
-        </is>
-      </c>
       <c r="AG136" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ136" t="inlineStr">
+        <is>
+          <t>rönn</t>
+        </is>
+      </c>
+      <c r="AK136" t="inlineStr">
+        <is>
+          <t>Sorbus aucuparia</t>
+        </is>
+      </c>
+      <c r="AO136" t="inlineStr">
+        <is>
+          <t>Sorbus aucuparia</t>
+        </is>
       </c>
       <c r="AT136" t="inlineStr"/>
       <c r="AW136" t="inlineStr">
@@ -15471,7 +15471,7 @@
         <v>124756720</v>
       </c>
       <c r="B137" t="n">
-        <v>79892</v>
+        <v>80029</v>
       </c>
       <c r="C137" t="inlineStr">
         <is>

--- a/artfynd/A 16493-2025 artfynd.xlsx
+++ b/artfynd/A 16493-2025 artfynd.xlsx
@@ -1748,10 +1748,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124705215</v>
+        <v>124689475</v>
       </c>
       <c r="B12" t="n">
-        <v>91166</v>
+        <v>57635</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1764,34 +1764,39 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Häggsåsen, Häggsåsen, Jmt</t>
+          <t>Tjärnflon, Tjärnflon, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>452850</v>
+        <v>452291</v>
       </c>
       <c r="R12" t="n">
-        <v>6990404</v>
+        <v>6990952</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1824,6 +1829,11 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-05-02</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1850,7 +1860,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124695424</v>
+        <v>124705215</v>
       </c>
       <c r="B13" t="n">
         <v>91166</v>
@@ -1886,14 +1896,14 @@
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Tjärnflon, Tjärnflon, Jmt</t>
+          <t>Häggsåsen, Häggsåsen, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>452642</v>
+        <v>452850</v>
       </c>
       <c r="R13" t="n">
-        <v>6990548</v>
+        <v>6990404</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2054,10 +2064,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124689475</v>
+        <v>124695424</v>
       </c>
       <c r="B15" t="n">
-        <v>57635</v>
+        <v>91166</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2070,39 +2080,34 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Tjärnflon, Tjärnflon, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>452291</v>
+        <v>452642</v>
       </c>
       <c r="R15" t="n">
-        <v>6990952</v>
+        <v>6990548</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2135,11 +2140,6 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-05-02</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2904,10 +2904,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>124689335</v>
+        <v>124688835</v>
       </c>
       <c r="B23" t="n">
-        <v>57635</v>
+        <v>78947</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2920,27 +2920,27 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
@@ -2949,10 +2949,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>452249</v>
+        <v>452142</v>
       </c>
       <c r="R23" t="n">
-        <v>6990921</v>
+        <v>6990800</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2985,11 +2985,6 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-05-02</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3016,10 +3011,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>124688835</v>
+        <v>124689335</v>
       </c>
       <c r="B24" t="n">
-        <v>78947</v>
+        <v>57635</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3032,27 +3027,27 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="K24" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
@@ -3061,10 +3056,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>452142</v>
+        <v>452249</v>
       </c>
       <c r="R24" t="n">
-        <v>6990800</v>
+        <v>6990921</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3097,6 +3092,11 @@
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-05-02</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3123,10 +3123,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>124693275</v>
+        <v>124689528</v>
       </c>
       <c r="B25" t="n">
-        <v>91180</v>
+        <v>57635</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3139,34 +3139,39 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1204</v>
+        <v>100109</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Tjärnflon, Tjärnflon, Jmt</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>452523</v>
+        <v>452301</v>
       </c>
       <c r="R25" t="n">
-        <v>6990595</v>
+        <v>6990964</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3199,6 +3204,11 @@
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-05-02</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3225,10 +3235,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>124691533</v>
+        <v>124689504</v>
       </c>
       <c r="B26" t="n">
-        <v>80028</v>
+        <v>57635</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3241,34 +3251,39 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Tjärnflon, Tjärnflon, Jmt</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>452427</v>
+        <v>452322</v>
       </c>
       <c r="R26" t="n">
-        <v>6990925</v>
+        <v>6990950</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3301,6 +3316,11 @@
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-05-02</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3327,10 +3347,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>124689528</v>
+        <v>124693275</v>
       </c>
       <c r="B27" t="n">
-        <v>57635</v>
+        <v>91180</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3343,39 +3363,34 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100109</v>
+        <v>1204</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>Tjärnflon, Tjärnflon, Jmt</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>452301</v>
+        <v>452523</v>
       </c>
       <c r="R27" t="n">
-        <v>6990964</v>
+        <v>6990595</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3408,11 +3423,6 @@
       <c r="AA27" t="inlineStr">
         <is>
           <t>2025-05-02</t>
-        </is>
-      </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3439,10 +3449,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>124689504</v>
+        <v>124691533</v>
       </c>
       <c r="B28" t="n">
-        <v>57635</v>
+        <v>80028</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3455,39 +3465,34 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P28" t="inlineStr">
         <is>
           <t>Tjärnflon, Tjärnflon, Jmt</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>452322</v>
+        <v>452427</v>
       </c>
       <c r="R28" t="n">
-        <v>6990950</v>
+        <v>6990925</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3520,11 +3525,6 @@
       <c r="AA28" t="inlineStr">
         <is>
           <t>2025-05-02</t>
-        </is>
-      </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3969,10 +3969,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>124702902</v>
+        <v>124701352</v>
       </c>
       <c r="B33" t="n">
-        <v>80028</v>
+        <v>80029</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -3985,34 +3985,39 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Häggsåsen, Häggsåsen, Jmt</t>
+          <t>Tjärnflon, Tjärnflon, Jmt</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>452734</v>
+        <v>452657</v>
       </c>
       <c r="R33" t="n">
-        <v>6990348</v>
+        <v>6990499</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4045,6 +4050,11 @@
       <c r="AA33" t="inlineStr">
         <is>
           <t>2025-05-02</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>Rikligt med skrovellav, APOTECHIER på en av bålarna</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4071,10 +4081,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>124701352</v>
+        <v>124702902</v>
       </c>
       <c r="B34" t="n">
-        <v>80029</v>
+        <v>80028</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4087,39 +4097,34 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>2081</v>
+        <v>6458</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
-      <c r="K34" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Tjärnflon, Tjärnflon, Jmt</t>
+          <t>Häggsåsen, Häggsåsen, Jmt</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>452657</v>
+        <v>452734</v>
       </c>
       <c r="R34" t="n">
-        <v>6990499</v>
+        <v>6990348</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4152,11 +4157,6 @@
       <c r="AA34" t="inlineStr">
         <is>
           <t>2025-05-02</t>
-        </is>
-      </c>
-      <c r="AC34" t="inlineStr">
-        <is>
-          <t>Rikligt med skrovellav, APOTECHIER på en av bålarna</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4387,10 +4387,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>124706585</v>
+        <v>124704581</v>
       </c>
       <c r="B37" t="n">
-        <v>77879</v>
+        <v>91459</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4403,21 +4403,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>228579</v>
+        <v>658</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4427,10 +4427,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>452913</v>
+        <v>452839</v>
       </c>
       <c r="R37" t="n">
-        <v>6990390</v>
+        <v>6990352</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4489,10 +4489,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>124704581</v>
+        <v>124706585</v>
       </c>
       <c r="B38" t="n">
-        <v>91459</v>
+        <v>77879</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4505,21 +4505,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>658</v>
+        <v>228579</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4529,10 +4529,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>452839</v>
+        <v>452913</v>
       </c>
       <c r="R38" t="n">
-        <v>6990352</v>
+        <v>6990390</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -5009,10 +5009,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>124756757</v>
+        <v>124753622</v>
       </c>
       <c r="B43" t="n">
-        <v>77879</v>
+        <v>98269</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5021,25 +5021,25 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>228579</v>
+        <v>220787</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5049,10 +5049,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>452506</v>
+        <v>452472</v>
       </c>
       <c r="R43" t="n">
-        <v>6990737</v>
+        <v>6990821</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5082,19 +5082,14 @@
           <t>2025-05-03</t>
         </is>
       </c>
-      <c r="Z43" t="inlineStr">
-        <is>
-          <t>11:47</t>
-        </is>
-      </c>
       <c r="AA43" t="inlineStr">
         <is>
           <t>2025-05-03</t>
         </is>
       </c>
-      <c r="AB43" t="inlineStr">
-        <is>
-          <t>11:47</t>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>Minst 50</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5109,22 +5104,22 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>124756755</v>
+        <v>124756757</v>
       </c>
       <c r="B44" t="n">
-        <v>91459</v>
+        <v>77879</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5137,21 +5132,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>658</v>
+        <v>228579</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5161,10 +5156,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>452538</v>
+        <v>452506</v>
       </c>
       <c r="R44" t="n">
-        <v>6990659</v>
+        <v>6990737</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5196,7 +5191,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>11:58</t>
+          <t>11:47</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5206,7 +5201,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>11:58</t>
+          <t>11:47</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5233,10 +5228,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>124753609</v>
+        <v>124756755</v>
       </c>
       <c r="B45" t="n">
-        <v>80028</v>
+        <v>91459</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5249,21 +5244,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6458</v>
+        <v>658</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5273,10 +5268,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>452528</v>
+        <v>452538</v>
       </c>
       <c r="R45" t="n">
-        <v>6990710</v>
+        <v>6990659</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5306,9 +5301,19 @@
           <t>2025-05-03</t>
         </is>
       </c>
+      <c r="Z45" t="inlineStr">
+        <is>
+          <t>11:58</t>
+        </is>
+      </c>
       <c r="AA45" t="inlineStr">
         <is>
           <t>2025-05-03</t>
+        </is>
+      </c>
+      <c r="AB45" t="inlineStr">
+        <is>
+          <t>11:58</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5323,22 +5328,22 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>124753622</v>
+        <v>124753609</v>
       </c>
       <c r="B46" t="n">
-        <v>98269</v>
+        <v>80028</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5347,25 +5352,25 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5375,10 +5380,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>452472</v>
+        <v>452528</v>
       </c>
       <c r="R46" t="n">
-        <v>6990821</v>
+        <v>6990710</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5411,11 +5416,6 @@
       <c r="AA46" t="inlineStr">
         <is>
           <t>2025-05-03</t>
-        </is>
-      </c>
-      <c r="AC46" t="inlineStr">
-        <is>
-          <t>Minst 50</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -7019,10 +7019,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>124753614</v>
+        <v>124753588</v>
       </c>
       <c r="B61" t="n">
-        <v>98269</v>
+        <v>91166</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -7031,25 +7031,25 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -7059,10 +7059,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>452751</v>
+        <v>452311</v>
       </c>
       <c r="R61" t="n">
-        <v>6990344</v>
+        <v>6990887</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7095,11 +7095,6 @@
       <c r="AA61" t="inlineStr">
         <is>
           <t>2025-05-03</t>
-        </is>
-      </c>
-      <c r="AC61" t="inlineStr">
-        <is>
-          <t>Minst 200</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7126,7 +7121,7 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>124753588</v>
+        <v>124756759</v>
       </c>
       <c r="B62" t="n">
         <v>91166</v>
@@ -7166,10 +7161,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>452311</v>
+        <v>452509</v>
       </c>
       <c r="R62" t="n">
-        <v>6990887</v>
+        <v>6990778</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7199,9 +7194,19 @@
           <t>2025-05-03</t>
         </is>
       </c>
+      <c r="Z62" t="inlineStr">
+        <is>
+          <t>11:39</t>
+        </is>
+      </c>
       <c r="AA62" t="inlineStr">
         <is>
           <t>2025-05-03</t>
+        </is>
+      </c>
+      <c r="AB62" t="inlineStr">
+        <is>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7216,22 +7221,22 @@
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>124756759</v>
+        <v>124756756</v>
       </c>
       <c r="B63" t="n">
-        <v>91166</v>
+        <v>78947</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -7244,21 +7249,21 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -7268,10 +7273,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>452509</v>
+        <v>452545</v>
       </c>
       <c r="R63" t="n">
-        <v>6990778</v>
+        <v>6990691</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7303,7 +7308,7 @@
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>11:39</t>
+          <t>11:54</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
@@ -7313,7 +7318,7 @@
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>11:39</t>
+          <t>11:54</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7340,10 +7345,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>124756756</v>
+        <v>124756688</v>
       </c>
       <c r="B64" t="n">
-        <v>78947</v>
+        <v>80028</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7356,21 +7361,21 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7380,10 +7385,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>452545</v>
+        <v>452694</v>
       </c>
       <c r="R64" t="n">
-        <v>6990691</v>
+        <v>6990598</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7415,7 +7420,7 @@
       </c>
       <c r="Z64" t="inlineStr">
         <is>
-          <t>11:54</t>
+          <t>20:19</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
@@ -7425,7 +7430,7 @@
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>11:54</t>
+          <t>20:19</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7452,10 +7457,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>124756688</v>
+        <v>124756730</v>
       </c>
       <c r="B65" t="n">
-        <v>80028</v>
+        <v>98269</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -7464,38 +7469,50 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I65" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="J65" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K65" t="inlineStr"/>
+      <c r="L65" t="inlineStr"/>
+      <c r="N65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
           <t>Häggsåsen N, Jmt</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>452694</v>
+        <v>452675</v>
       </c>
       <c r="R65" t="n">
-        <v>6990598</v>
+        <v>6990411</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7527,7 +7544,7 @@
       </c>
       <c r="Z65" t="inlineStr">
         <is>
-          <t>20:19</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
@@ -7537,7 +7554,12 @@
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>20:19</t>
+          <t>14:20</t>
+        </is>
+      </c>
+      <c r="AC65" t="inlineStr">
+        <is>
+          <t>Min antal</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7546,6 +7568,7 @@
       <c r="AE65" t="b">
         <v>0</v>
       </c>
+      <c r="AF65" t="inlineStr"/>
       <c r="AG65" t="b">
         <v>0</v>
       </c>
@@ -7564,7 +7587,7 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>124756730</v>
+        <v>124753614</v>
       </c>
       <c r="B66" t="n">
         <v>98269</v>
@@ -7597,29 +7620,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I66" t="inlineStr">
-        <is>
-          <t>200</t>
-        </is>
-      </c>
-      <c r="J66" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K66" t="inlineStr"/>
-      <c r="L66" t="inlineStr"/>
-      <c r="N66" t="inlineStr"/>
+      <c r="I66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
           <t>Häggsåsen N, Jmt</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>452675</v>
+        <v>452751</v>
       </c>
       <c r="R66" t="n">
-        <v>6990411</v>
+        <v>6990344</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7649,24 +7660,14 @@
           <t>2025-05-03</t>
         </is>
       </c>
-      <c r="Z66" t="inlineStr">
-        <is>
-          <t>14:20</t>
-        </is>
-      </c>
       <c r="AA66" t="inlineStr">
         <is>
           <t>2025-05-03</t>
         </is>
       </c>
-      <c r="AB66" t="inlineStr">
-        <is>
-          <t>14:20</t>
-        </is>
-      </c>
       <c r="AC66" t="inlineStr">
         <is>
-          <t>Min antal</t>
+          <t>Minst 200</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7675,19 +7676,18 @@
       <c r="AE66" t="b">
         <v>0</v>
       </c>
-      <c r="AF66" t="inlineStr"/>
       <c r="AG66" t="b">
         <v>0</v>
       </c>
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
@@ -13446,10 +13446,10 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>124753582</v>
+        <v>124756743</v>
       </c>
       <c r="B119" t="n">
-        <v>91166</v>
+        <v>80028</v>
       </c>
       <c r="C119" t="inlineStr">
         <is>
@@ -13462,21 +13462,21 @@
         </is>
       </c>
       <c r="E119" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I119" t="inlineStr"/>
@@ -13486,10 +13486,10 @@
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>452649</v>
+        <v>452682</v>
       </c>
       <c r="R119" t="n">
-        <v>6990621</v>
+        <v>6990476</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -13519,11 +13519,21 @@
           <t>2025-05-03</t>
         </is>
       </c>
+      <c r="Z119" t="inlineStr">
+        <is>
+          <t>13:53</t>
+        </is>
+      </c>
       <c r="AA119" t="inlineStr">
         <is>
           <t>2025-05-03</t>
         </is>
       </c>
+      <c r="AB119" t="inlineStr">
+        <is>
+          <t>13:53</t>
+        </is>
+      </c>
       <c r="AD119" t="b">
         <v>0</v>
       </c>
@@ -13532,26 +13542,41 @@
       </c>
       <c r="AG119" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ119" t="inlineStr">
+        <is>
+          <t>rönn</t>
+        </is>
+      </c>
+      <c r="AK119" t="inlineStr">
+        <is>
+          <t>Sorbus aucuparia</t>
+        </is>
+      </c>
+      <c r="AO119" t="inlineStr">
+        <is>
+          <t>Sorbus aucuparia</t>
+        </is>
       </c>
       <c r="AT119" t="inlineStr"/>
       <c r="AW119" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX119" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY119" t="inlineStr"/>
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>124756743</v>
+        <v>124753623</v>
       </c>
       <c r="B120" t="n">
-        <v>80028</v>
+        <v>98269</v>
       </c>
       <c r="C120" t="inlineStr">
         <is>
@@ -13560,25 +13585,25 @@
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E120" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
@@ -13588,10 +13613,10 @@
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>452682</v>
+        <v>452510</v>
       </c>
       <c r="R120" t="n">
-        <v>6990476</v>
+        <v>6990873</v>
       </c>
       <c r="S120" t="n">
         <v>10</v>
@@ -13621,19 +13646,14 @@
           <t>2025-05-03</t>
         </is>
       </c>
-      <c r="Z120" t="inlineStr">
-        <is>
-          <t>13:53</t>
-        </is>
-      </c>
       <c r="AA120" t="inlineStr">
         <is>
           <t>2025-05-03</t>
         </is>
       </c>
-      <c r="AB120" t="inlineStr">
-        <is>
-          <t>13:53</t>
+      <c r="AC120" t="inlineStr">
+        <is>
+          <t>Minst 50</t>
         </is>
       </c>
       <c r="AD120" t="b">
@@ -13644,38 +13664,23 @@
       </c>
       <c r="AG120" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ120" t="inlineStr">
-        <is>
-          <t>rönn</t>
-        </is>
-      </c>
-      <c r="AK120" t="inlineStr">
-        <is>
-          <t>Sorbus aucuparia</t>
-        </is>
-      </c>
-      <c r="AO120" t="inlineStr">
-        <is>
-          <t>Sorbus aucuparia</t>
-        </is>
       </c>
       <c r="AT120" t="inlineStr"/>
       <c r="AW120" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX120" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY120" t="inlineStr"/>
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>124753623</v>
+        <v>124753617</v>
       </c>
       <c r="B121" t="n">
         <v>98269</v>
@@ -13715,10 +13720,10 @@
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>452510</v>
+        <v>452655</v>
       </c>
       <c r="R121" t="n">
-        <v>6990873</v>
+        <v>6990482</v>
       </c>
       <c r="S121" t="n">
         <v>10</v>
@@ -13782,10 +13787,10 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>124753617</v>
+        <v>124753582</v>
       </c>
       <c r="B122" t="n">
-        <v>98269</v>
+        <v>91166</v>
       </c>
       <c r="C122" t="inlineStr">
         <is>
@@ -13794,25 +13799,25 @@
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E122" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I122" t="inlineStr"/>
@@ -13822,10 +13827,10 @@
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>452655</v>
+        <v>452649</v>
       </c>
       <c r="R122" t="n">
-        <v>6990482</v>
+        <v>6990621</v>
       </c>
       <c r="S122" t="n">
         <v>10</v>
@@ -13858,11 +13863,6 @@
       <c r="AA122" t="inlineStr">
         <is>
           <t>2025-05-03</t>
-        </is>
-      </c>
-      <c r="AC122" t="inlineStr">
-        <is>
-          <t>Minst 50</t>
         </is>
       </c>
       <c r="AD122" t="b">
@@ -13889,10 +13889,10 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>124756749</v>
+        <v>124756767</v>
       </c>
       <c r="B123" t="n">
-        <v>91166</v>
+        <v>78947</v>
       </c>
       <c r="C123" t="inlineStr">
         <is>
@@ -13905,21 +13905,21 @@
         </is>
       </c>
       <c r="E123" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I123" t="inlineStr"/>
@@ -13929,10 +13929,10 @@
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>452609</v>
+        <v>452362</v>
       </c>
       <c r="R123" t="n">
-        <v>6990543</v>
+        <v>6991003</v>
       </c>
       <c r="S123" t="n">
         <v>10</v>
@@ -13964,7 +13964,7 @@
       </c>
       <c r="Z123" t="inlineStr">
         <is>
-          <t>12:29</t>
+          <t>10:55</t>
         </is>
       </c>
       <c r="AA123" t="inlineStr">
@@ -13974,7 +13974,7 @@
       </c>
       <c r="AB123" t="inlineStr">
         <is>
-          <t>12:29</t>
+          <t>10:55</t>
         </is>
       </c>
       <c r="AD123" t="b">
@@ -14001,10 +14001,10 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>124756746</v>
+        <v>124753632</v>
       </c>
       <c r="B124" t="n">
-        <v>91166</v>
+        <v>98269</v>
       </c>
       <c r="C124" t="inlineStr">
         <is>
@@ -14013,25 +14013,25 @@
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E124" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I124" t="inlineStr"/>
@@ -14041,10 +14041,10 @@
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>452639</v>
+        <v>452455</v>
       </c>
       <c r="R124" t="n">
-        <v>6990537</v>
+        <v>6990942</v>
       </c>
       <c r="S124" t="n">
         <v>10</v>
@@ -14074,19 +14074,14 @@
           <t>2025-05-03</t>
         </is>
       </c>
-      <c r="Z124" t="inlineStr">
-        <is>
-          <t>13:36</t>
-        </is>
-      </c>
       <c r="AA124" t="inlineStr">
         <is>
           <t>2025-05-03</t>
         </is>
       </c>
-      <c r="AB124" t="inlineStr">
-        <is>
-          <t>13:36</t>
+      <c r="AC124" t="inlineStr">
+        <is>
+          <t>Minst 30</t>
         </is>
       </c>
       <c r="AD124" t="b">
@@ -14101,22 +14096,22 @@
       <c r="AT124" t="inlineStr"/>
       <c r="AW124" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX124" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY124" t="inlineStr"/>
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>124753576</v>
+        <v>124753611</v>
       </c>
       <c r="B125" t="n">
-        <v>91166</v>
+        <v>98269</v>
       </c>
       <c r="C125" t="inlineStr">
         <is>
@@ -14125,25 +14120,25 @@
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E125" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I125" t="inlineStr"/>
@@ -14153,10 +14148,10 @@
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>452837</v>
+        <v>452997</v>
       </c>
       <c r="R125" t="n">
-        <v>6990384</v>
+        <v>6990332</v>
       </c>
       <c r="S125" t="n">
         <v>10</v>
@@ -14189,6 +14184,11 @@
       <c r="AA125" t="inlineStr">
         <is>
           <t>2025-05-03</t>
+        </is>
+      </c>
+      <c r="AC125" t="inlineStr">
+        <is>
+          <t>Minst 100</t>
         </is>
       </c>
       <c r="AD125" t="b">
@@ -14215,10 +14215,10 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>124756767</v>
+        <v>124756751</v>
       </c>
       <c r="B126" t="n">
-        <v>78947</v>
+        <v>98269</v>
       </c>
       <c r="C126" t="inlineStr">
         <is>
@@ -14227,38 +14227,50 @@
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E126" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I126" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I126" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J126" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K126" t="inlineStr"/>
+      <c r="L126" t="inlineStr"/>
+      <c r="N126" t="inlineStr"/>
       <c r="P126" t="inlineStr">
         <is>
           <t>Häggsåsen N, Jmt</t>
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>452362</v>
+        <v>452638</v>
       </c>
       <c r="R126" t="n">
-        <v>6991003</v>
+        <v>6990559</v>
       </c>
       <c r="S126" t="n">
         <v>10</v>
@@ -14290,7 +14302,7 @@
       </c>
       <c r="Z126" t="inlineStr">
         <is>
-          <t>10:55</t>
+          <t>12:23</t>
         </is>
       </c>
       <c r="AA126" t="inlineStr">
@@ -14300,7 +14312,7 @@
       </c>
       <c r="AB126" t="inlineStr">
         <is>
-          <t>10:55</t>
+          <t>12:23</t>
         </is>
       </c>
       <c r="AD126" t="b">
@@ -14309,6 +14321,7 @@
       <c r="AE126" t="b">
         <v>0</v>
       </c>
+      <c r="AF126" t="inlineStr"/>
       <c r="AG126" t="b">
         <v>0</v>
       </c>
@@ -14327,10 +14340,10 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>124753632</v>
+        <v>124756758</v>
       </c>
       <c r="B127" t="n">
-        <v>98269</v>
+        <v>91116</v>
       </c>
       <c r="C127" t="inlineStr">
         <is>
@@ -14339,25 +14352,25 @@
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E127" t="n">
-        <v>220787</v>
+        <v>112</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Stjärntagging</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Asterodon ferruginosus</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Pat.</t>
         </is>
       </c>
       <c r="I127" t="inlineStr"/>
@@ -14367,10 +14380,10 @@
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>452455</v>
+        <v>452509</v>
       </c>
       <c r="R127" t="n">
-        <v>6990942</v>
+        <v>6990778</v>
       </c>
       <c r="S127" t="n">
         <v>10</v>
@@ -14400,14 +14413,19 @@
           <t>2025-05-03</t>
         </is>
       </c>
+      <c r="Z127" t="inlineStr">
+        <is>
+          <t>11:40</t>
+        </is>
+      </c>
       <c r="AA127" t="inlineStr">
         <is>
           <t>2025-05-03</t>
         </is>
       </c>
-      <c r="AC127" t="inlineStr">
-        <is>
-          <t>Minst 30</t>
+      <c r="AB127" t="inlineStr">
+        <is>
+          <t>11:40</t>
         </is>
       </c>
       <c r="AD127" t="b">
@@ -14422,22 +14440,22 @@
       <c r="AT127" t="inlineStr"/>
       <c r="AW127" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX127" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY127" t="inlineStr"/>
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>124753611</v>
+        <v>124753605</v>
       </c>
       <c r="B128" t="n">
-        <v>98269</v>
+        <v>80029</v>
       </c>
       <c r="C128" t="inlineStr">
         <is>
@@ -14446,25 +14464,25 @@
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E128" t="n">
-        <v>220787</v>
+        <v>2081</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I128" t="inlineStr"/>
@@ -14474,10 +14492,10 @@
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>452997</v>
+        <v>452408</v>
       </c>
       <c r="R128" t="n">
-        <v>6990332</v>
+        <v>6990952</v>
       </c>
       <c r="S128" t="n">
         <v>10</v>
@@ -14510,11 +14528,6 @@
       <c r="AA128" t="inlineStr">
         <is>
           <t>2025-05-03</t>
-        </is>
-      </c>
-      <c r="AC128" t="inlineStr">
-        <is>
-          <t>Minst 100</t>
         </is>
       </c>
       <c r="AD128" t="b">
@@ -14541,10 +14554,10 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>124756751</v>
+        <v>124756749</v>
       </c>
       <c r="B129" t="n">
-        <v>98269</v>
+        <v>91166</v>
       </c>
       <c r="C129" t="inlineStr">
         <is>
@@ -14553,50 +14566,38 @@
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E129" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I129" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J129" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K129" t="inlineStr"/>
-      <c r="L129" t="inlineStr"/>
-      <c r="N129" t="inlineStr"/>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I129" t="inlineStr"/>
       <c r="P129" t="inlineStr">
         <is>
           <t>Häggsåsen N, Jmt</t>
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>452638</v>
+        <v>452609</v>
       </c>
       <c r="R129" t="n">
-        <v>6990559</v>
+        <v>6990543</v>
       </c>
       <c r="S129" t="n">
         <v>10</v>
@@ -14628,7 +14629,7 @@
       </c>
       <c r="Z129" t="inlineStr">
         <is>
-          <t>12:23</t>
+          <t>12:29</t>
         </is>
       </c>
       <c r="AA129" t="inlineStr">
@@ -14638,7 +14639,7 @@
       </c>
       <c r="AB129" t="inlineStr">
         <is>
-          <t>12:23</t>
+          <t>12:29</t>
         </is>
       </c>
       <c r="AD129" t="b">
@@ -14647,7 +14648,6 @@
       <c r="AE129" t="b">
         <v>0</v>
       </c>
-      <c r="AF129" t="inlineStr"/>
       <c r="AG129" t="b">
         <v>0</v>
       </c>
@@ -14666,10 +14666,10 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>124756758</v>
+        <v>124756746</v>
       </c>
       <c r="B130" t="n">
-        <v>91116</v>
+        <v>91166</v>
       </c>
       <c r="C130" t="inlineStr">
         <is>
@@ -14682,21 +14682,21 @@
         </is>
       </c>
       <c r="E130" t="n">
-        <v>112</v>
+        <v>1202</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Stjärntagging</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Asterodon ferruginosus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>Pat.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I130" t="inlineStr"/>
@@ -14706,10 +14706,10 @@
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>452509</v>
+        <v>452639</v>
       </c>
       <c r="R130" t="n">
-        <v>6990778</v>
+        <v>6990537</v>
       </c>
       <c r="S130" t="n">
         <v>10</v>
@@ -14741,7 +14741,7 @@
       </c>
       <c r="Z130" t="inlineStr">
         <is>
-          <t>11:40</t>
+          <t>13:36</t>
         </is>
       </c>
       <c r="AA130" t="inlineStr">
@@ -14751,7 +14751,7 @@
       </c>
       <c r="AB130" t="inlineStr">
         <is>
-          <t>11:40</t>
+          <t>13:36</t>
         </is>
       </c>
       <c r="AD130" t="b">
@@ -14778,10 +14778,10 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>124753605</v>
+        <v>124753576</v>
       </c>
       <c r="B131" t="n">
-        <v>80029</v>
+        <v>91166</v>
       </c>
       <c r="C131" t="inlineStr">
         <is>
@@ -14794,21 +14794,21 @@
         </is>
       </c>
       <c r="E131" t="n">
-        <v>2081</v>
+        <v>1202</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I131" t="inlineStr"/>
@@ -14818,10 +14818,10 @@
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>452408</v>
+        <v>452837</v>
       </c>
       <c r="R131" t="n">
-        <v>6990952</v>
+        <v>6990384</v>
       </c>
       <c r="S131" t="n">
         <v>10</v>

--- a/artfynd/A 16493-2025 artfynd.xlsx
+++ b/artfynd/A 16493-2025 artfynd.xlsx
@@ -5009,7 +5009,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>124753622</v>
+        <v>124753630</v>
       </c>
       <c r="B43" t="n">
         <v>98269</v>
@@ -5049,10 +5049,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>452472</v>
+        <v>452273</v>
       </c>
       <c r="R43" t="n">
-        <v>6990821</v>
+        <v>6990906</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5089,7 +5089,7 @@
       </c>
       <c r="AC43" t="inlineStr">
         <is>
-          <t>Minst 50</t>
+          <t>Minst 10</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5116,10 +5116,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>124756757</v>
+        <v>124753612</v>
       </c>
       <c r="B44" t="n">
-        <v>77879</v>
+        <v>98269</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5128,25 +5128,25 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>228579</v>
+        <v>220787</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5156,10 +5156,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>452506</v>
+        <v>452924</v>
       </c>
       <c r="R44" t="n">
-        <v>6990737</v>
+        <v>6990397</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5189,19 +5189,14 @@
           <t>2025-05-03</t>
         </is>
       </c>
-      <c r="Z44" t="inlineStr">
-        <is>
-          <t>11:47</t>
-        </is>
-      </c>
       <c r="AA44" t="inlineStr">
         <is>
           <t>2025-05-03</t>
         </is>
       </c>
-      <c r="AB44" t="inlineStr">
-        <is>
-          <t>11:47</t>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>Minst 20</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5216,22 +5211,22 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>124756755</v>
+        <v>124756741</v>
       </c>
       <c r="B45" t="n">
-        <v>91459</v>
+        <v>79988</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5240,25 +5235,25 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>658</v>
+        <v>229497</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5268,10 +5263,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>452538</v>
+        <v>452682</v>
       </c>
       <c r="R45" t="n">
-        <v>6990659</v>
+        <v>6990476</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5303,7 +5298,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>11:58</t>
+          <t>13:54</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5313,7 +5308,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>11:58</t>
+          <t>13:54</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5324,6 +5319,21 @@
       </c>
       <c r="AG45" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ45" t="inlineStr">
+        <is>
+          <t>rönn</t>
+        </is>
+      </c>
+      <c r="AK45" t="inlineStr">
+        <is>
+          <t>Sorbus aucuparia</t>
+        </is>
+      </c>
+      <c r="AO45" t="inlineStr">
+        <is>
+          <t>Sorbus aucuparia</t>
+        </is>
       </c>
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
@@ -5340,10 +5350,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>124753609</v>
+        <v>124756757</v>
       </c>
       <c r="B46" t="n">
-        <v>80028</v>
+        <v>77879</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5356,21 +5366,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6458</v>
+        <v>228579</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5380,10 +5390,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>452528</v>
+        <v>452506</v>
       </c>
       <c r="R46" t="n">
-        <v>6990710</v>
+        <v>6990737</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5413,9 +5423,19 @@
           <t>2025-05-03</t>
         </is>
       </c>
+      <c r="Z46" t="inlineStr">
+        <is>
+          <t>11:47</t>
+        </is>
+      </c>
       <c r="AA46" t="inlineStr">
         <is>
           <t>2025-05-03</t>
+        </is>
+      </c>
+      <c r="AB46" t="inlineStr">
+        <is>
+          <t>11:47</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5430,19 +5450,19 @@
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>124756776</v>
+        <v>124756778</v>
       </c>
       <c r="B47" t="n">
         <v>78947</v>
@@ -5482,10 +5502,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>452308</v>
+        <v>452153</v>
       </c>
       <c r="R47" t="n">
-        <v>6990943</v>
+        <v>6990834</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5517,7 +5537,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>10:03</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5527,7 +5547,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>10:03</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5554,7 +5574,7 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>124756779</v>
+        <v>124756754</v>
       </c>
       <c r="B48" t="n">
         <v>78947</v>
@@ -5594,10 +5614,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>452143</v>
+        <v>452544</v>
       </c>
       <c r="R48" t="n">
-        <v>6990780</v>
+        <v>6990646</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5629,7 +5649,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>09:51</t>
+          <t>12:04</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -5639,7 +5659,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>09:51</t>
+          <t>12:04</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5666,10 +5686,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>124753577</v>
+        <v>124756772</v>
       </c>
       <c r="B49" t="n">
-        <v>91166</v>
+        <v>78947</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5682,21 +5702,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5706,10 +5726,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>452833</v>
+        <v>452344</v>
       </c>
       <c r="R49" t="n">
-        <v>6990388</v>
+        <v>6990942</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5739,9 +5759,19 @@
           <t>2025-05-03</t>
         </is>
       </c>
+      <c r="Z49" t="inlineStr">
+        <is>
+          <t>10:32</t>
+        </is>
+      </c>
       <c r="AA49" t="inlineStr">
         <is>
           <t>2025-05-03</t>
+        </is>
+      </c>
+      <c r="AB49" t="inlineStr">
+        <is>
+          <t>10:32</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5756,19 +5786,19 @@
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>124753579</v>
+        <v>124756731</v>
       </c>
       <c r="B50" t="n">
         <v>91166</v>
@@ -5808,10 +5838,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>452710</v>
+        <v>452672</v>
       </c>
       <c r="R50" t="n">
-        <v>6990467</v>
+        <v>6990427</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5841,9 +5871,19 @@
           <t>2025-05-03</t>
         </is>
       </c>
+      <c r="Z50" t="inlineStr">
+        <is>
+          <t>14:19</t>
+        </is>
+      </c>
       <c r="AA50" t="inlineStr">
         <is>
           <t>2025-05-03</t>
+        </is>
+      </c>
+      <c r="AB50" t="inlineStr">
+        <is>
+          <t>14:19</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5858,22 +5898,22 @@
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>124756725</v>
+        <v>124753581</v>
       </c>
       <c r="B51" t="n">
-        <v>78947</v>
+        <v>91166</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -5886,21 +5926,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5910,10 +5950,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>452762</v>
+        <v>452643</v>
       </c>
       <c r="R51" t="n">
-        <v>6990327</v>
+        <v>6990504</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5943,19 +5983,9 @@
           <t>2025-05-03</t>
         </is>
       </c>
-      <c r="Z51" t="inlineStr">
-        <is>
-          <t>14:37</t>
-        </is>
-      </c>
       <c r="AA51" t="inlineStr">
         <is>
           <t>2025-05-03</t>
-        </is>
-      </c>
-      <c r="AB51" t="inlineStr">
-        <is>
-          <t>14:37</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -5970,22 +6000,22 @@
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>124756774</v>
+        <v>124753582</v>
       </c>
       <c r="B52" t="n">
-        <v>98269</v>
+        <v>91166</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -5994,50 +6024,38 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="J52" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K52" t="inlineStr"/>
-      <c r="L52" t="inlineStr"/>
-      <c r="N52" t="inlineStr"/>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
           <t>Häggsåsen N, Jmt</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>452308</v>
+        <v>452649</v>
       </c>
       <c r="R52" t="n">
-        <v>6990943</v>
+        <v>6990621</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6067,50 +6085,39 @@
           <t>2025-05-03</t>
         </is>
       </c>
-      <c r="Z52" t="inlineStr">
-        <is>
-          <t>10:23</t>
-        </is>
-      </c>
       <c r="AA52" t="inlineStr">
         <is>
           <t>2025-05-03</t>
         </is>
       </c>
-      <c r="AB52" t="inlineStr">
-        <is>
-          <t>10:23</t>
-        </is>
-      </c>
       <c r="AD52" t="b">
         <v>0</v>
       </c>
       <c r="AE52" t="b">
         <v>0</v>
       </c>
-      <c r="AF52" t="inlineStr"/>
       <c r="AG52" t="b">
         <v>0</v>
       </c>
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>124753635</v>
+        <v>124756758</v>
       </c>
       <c r="B53" t="n">
-        <v>91184</v>
+        <v>91116</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6123,21 +6130,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>5432</v>
+        <v>112</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Stjärntagging</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Asterodon ferruginosus</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>Pat.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -6147,10 +6154,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>452732</v>
+        <v>452509</v>
       </c>
       <c r="R53" t="n">
-        <v>6990486</v>
+        <v>6990778</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6180,9 +6187,19 @@
           <t>2025-05-03</t>
         </is>
       </c>
+      <c r="Z53" t="inlineStr">
+        <is>
+          <t>11:40</t>
+        </is>
+      </c>
       <c r="AA53" t="inlineStr">
         <is>
           <t>2025-05-03</t>
+        </is>
+      </c>
+      <c r="AB53" t="inlineStr">
+        <is>
+          <t>11:40</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6197,22 +6214,22 @@
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>124756739</v>
+        <v>124756776</v>
       </c>
       <c r="B54" t="n">
-        <v>98269</v>
+        <v>78947</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6221,50 +6238,38 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I54" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="J54" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K54" t="inlineStr"/>
-      <c r="L54" t="inlineStr"/>
-      <c r="N54" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
           <t>Häggsåsen N, Jmt</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>452711</v>
+        <v>452308</v>
       </c>
       <c r="R54" t="n">
-        <v>6990473</v>
+        <v>6990943</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6296,7 +6301,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -6306,7 +6311,7 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6315,7 +6320,6 @@
       <c r="AE54" t="b">
         <v>0</v>
       </c>
-      <c r="AF54" t="inlineStr"/>
       <c r="AG54" t="b">
         <v>0</v>
       </c>
@@ -6334,10 +6338,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>124753607</v>
+        <v>124753623</v>
       </c>
       <c r="B55" t="n">
-        <v>80028</v>
+        <v>98269</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6346,25 +6350,25 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6374,10 +6378,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>452734</v>
+        <v>452510</v>
       </c>
       <c r="R55" t="n">
-        <v>6990356</v>
+        <v>6990873</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6410,6 +6414,11 @@
       <c r="AA55" t="inlineStr">
         <is>
           <t>2025-05-03</t>
+        </is>
+      </c>
+      <c r="AC55" t="inlineStr">
+        <is>
+          <t>Minst 50</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6436,10 +6445,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>124756734</v>
+        <v>124756777</v>
       </c>
       <c r="B56" t="n">
-        <v>80028</v>
+        <v>98269</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6448,38 +6457,50 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I56" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K56" t="inlineStr"/>
+      <c r="L56" t="inlineStr"/>
+      <c r="N56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
           <t>Häggsåsen N, Jmt</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>452675</v>
+        <v>452146</v>
       </c>
       <c r="R56" t="n">
-        <v>6990435</v>
+        <v>6990839</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6511,7 +6532,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>10:06</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -6521,7 +6542,7 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>10:06</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6530,23 +6551,9 @@
       <c r="AE56" t="b">
         <v>0</v>
       </c>
+      <c r="AF56" t="inlineStr"/>
       <c r="AG56" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ56" t="inlineStr">
-        <is>
-          <t>rönn</t>
-        </is>
-      </c>
-      <c r="AK56" t="inlineStr">
-        <is>
-          <t>Sorbus aucuparia</t>
-        </is>
-      </c>
-      <c r="AO56" t="inlineStr">
-        <is>
-          <t>Sorbus aucuparia</t>
-        </is>
       </c>
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
@@ -6675,7 +6682,7 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>124756731</v>
+        <v>124753586</v>
       </c>
       <c r="B58" t="n">
         <v>91166</v>
@@ -6715,10 +6722,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>452672</v>
+        <v>452500</v>
       </c>
       <c r="R58" t="n">
-        <v>6990427</v>
+        <v>6990950</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6748,19 +6755,9 @@
           <t>2025-05-03</t>
         </is>
       </c>
-      <c r="Z58" t="inlineStr">
-        <is>
-          <t>14:19</t>
-        </is>
-      </c>
       <c r="AA58" t="inlineStr">
         <is>
           <t>2025-05-03</t>
-        </is>
-      </c>
-      <c r="AB58" t="inlineStr">
-        <is>
-          <t>14:19</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6775,22 +6772,22 @@
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>124756761</v>
+        <v>124756755</v>
       </c>
       <c r="B59" t="n">
-        <v>78947</v>
+        <v>91459</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -6803,21 +6800,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6425</v>
+        <v>658</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6827,10 +6824,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>452532</v>
+        <v>452538</v>
       </c>
       <c r="R59" t="n">
-        <v>6990825</v>
+        <v>6990659</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6862,7 +6859,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>11:26</t>
+          <t>11:58</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -6872,7 +6869,7 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>11:26</t>
+          <t>11:58</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -6899,10 +6896,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>124756738</v>
+        <v>124753639</v>
       </c>
       <c r="B60" t="n">
-        <v>75023</v>
+        <v>78947</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -6911,41 +6908,38 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6486</v>
+        <v>6425</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Skuggnål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Chaenotheca sphaerocephala</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>Nádv.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
-      <c r="J60" t="inlineStr"/>
-      <c r="K60" t="inlineStr"/>
-      <c r="N60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
           <t>Häggsåsen N, Jmt</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>452703</v>
+        <v>452511</v>
       </c>
       <c r="R60" t="n">
-        <v>6990457</v>
+        <v>6990733</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6975,31 +6969,16 @@
           <t>2025-05-03</t>
         </is>
       </c>
-      <c r="Z60" t="inlineStr">
-        <is>
-          <t>14:09</t>
-        </is>
-      </c>
       <c r="AA60" t="inlineStr">
         <is>
           <t>2025-05-03</t>
         </is>
       </c>
-      <c r="AB60" t="inlineStr">
-        <is>
-          <t>14:09</t>
-        </is>
-      </c>
       <c r="AD60" t="b">
         <v>0</v>
       </c>
       <c r="AE60" t="b">
         <v>0</v>
-      </c>
-      <c r="AF60" t="inlineStr">
-        <is>
-          <t>mikroskoperad</t>
-        </is>
       </c>
       <c r="AG60" t="b">
         <v>0</v>
@@ -7007,22 +6986,22 @@
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>124753588</v>
+        <v>124756764</v>
       </c>
       <c r="B61" t="n">
-        <v>91166</v>
+        <v>78947</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -7035,21 +7014,21 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -7059,10 +7038,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>452311</v>
+        <v>452462</v>
       </c>
       <c r="R61" t="n">
-        <v>6990887</v>
+        <v>6990915</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7092,9 +7071,19 @@
           <t>2025-05-03</t>
         </is>
       </c>
+      <c r="Z61" t="inlineStr">
+        <is>
+          <t>11:11</t>
+        </is>
+      </c>
       <c r="AA61" t="inlineStr">
         <is>
           <t>2025-05-03</t>
+        </is>
+      </c>
+      <c r="AB61" t="inlineStr">
+        <is>
+          <t>11:11</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7109,22 +7098,22 @@
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>124756759</v>
+        <v>124756748</v>
       </c>
       <c r="B62" t="n">
-        <v>91166</v>
+        <v>78947</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -7137,21 +7126,21 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -7161,10 +7150,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>452509</v>
+        <v>452609</v>
       </c>
       <c r="R62" t="n">
-        <v>6990778</v>
+        <v>6990543</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7196,7 +7185,7 @@
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>11:39</t>
+          <t>12:29</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
@@ -7206,7 +7195,7 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>11:39</t>
+          <t>12:29</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7233,7 +7222,7 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>124756756</v>
+        <v>124756779</v>
       </c>
       <c r="B63" t="n">
         <v>78947</v>
@@ -7273,10 +7262,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>452545</v>
+        <v>452143</v>
       </c>
       <c r="R63" t="n">
-        <v>6990691</v>
+        <v>6990780</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7308,7 +7297,7 @@
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>11:54</t>
+          <t>09:51</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
@@ -7318,7 +7307,7 @@
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>11:54</t>
+          <t>09:51</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7345,10 +7334,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>124756688</v>
+        <v>124756725</v>
       </c>
       <c r="B64" t="n">
-        <v>80028</v>
+        <v>78947</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7361,21 +7350,21 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7385,10 +7374,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>452694</v>
+        <v>452762</v>
       </c>
       <c r="R64" t="n">
-        <v>6990598</v>
+        <v>6990327</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7420,7 +7409,7 @@
       </c>
       <c r="Z64" t="inlineStr">
         <is>
-          <t>20:19</t>
+          <t>14:37</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
@@ -7430,7 +7419,7 @@
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>20:19</t>
+          <t>14:37</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7457,7 +7446,7 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>124756730</v>
+        <v>124753632</v>
       </c>
       <c r="B65" t="n">
         <v>98269</v>
@@ -7490,29 +7479,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I65" t="inlineStr">
-        <is>
-          <t>200</t>
-        </is>
-      </c>
-      <c r="J65" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K65" t="inlineStr"/>
-      <c r="L65" t="inlineStr"/>
-      <c r="N65" t="inlineStr"/>
+      <c r="I65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
           <t>Häggsåsen N, Jmt</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>452675</v>
+        <v>452455</v>
       </c>
       <c r="R65" t="n">
-        <v>6990411</v>
+        <v>6990942</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7542,24 +7519,14 @@
           <t>2025-05-03</t>
         </is>
       </c>
-      <c r="Z65" t="inlineStr">
-        <is>
-          <t>14:20</t>
-        </is>
-      </c>
       <c r="AA65" t="inlineStr">
         <is>
           <t>2025-05-03</t>
         </is>
       </c>
-      <c r="AB65" t="inlineStr">
-        <is>
-          <t>14:20</t>
-        </is>
-      </c>
       <c r="AC65" t="inlineStr">
         <is>
-          <t>Min antal</t>
+          <t>Minst 30</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7568,26 +7535,25 @@
       <c r="AE65" t="b">
         <v>0</v>
       </c>
-      <c r="AF65" t="inlineStr"/>
       <c r="AG65" t="b">
         <v>0</v>
       </c>
       <c r="AT65" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>124753614</v>
+        <v>124753622</v>
       </c>
       <c r="B66" t="n">
         <v>98269</v>
@@ -7627,10 +7593,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>452751</v>
+        <v>452472</v>
       </c>
       <c r="R66" t="n">
-        <v>6990344</v>
+        <v>6990821</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7667,7 +7633,7 @@
       </c>
       <c r="AC66" t="inlineStr">
         <is>
-          <t>Minst 200</t>
+          <t>Minst 50</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7694,10 +7660,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>124753586</v>
+        <v>124753627</v>
       </c>
       <c r="B67" t="n">
-        <v>91166</v>
+        <v>98269</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -7706,25 +7672,25 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7734,10 +7700,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>452500</v>
+        <v>452608</v>
       </c>
       <c r="R67" t="n">
-        <v>6990950</v>
+        <v>6990927</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7770,6 +7736,11 @@
       <c r="AA67" t="inlineStr">
         <is>
           <t>2025-05-03</t>
+        </is>
+      </c>
+      <c r="AC67" t="inlineStr">
+        <is>
+          <t>Minst 50</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7796,10 +7767,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>124753578</v>
+        <v>124756768</v>
       </c>
       <c r="B68" t="n">
-        <v>91166</v>
+        <v>77879</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -7812,21 +7783,21 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>1202</v>
+        <v>228579</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7836,10 +7807,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>452743</v>
+        <v>452357</v>
       </c>
       <c r="R68" t="n">
-        <v>6990405</v>
+        <v>6990970</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7869,9 +7840,19 @@
           <t>2025-05-03</t>
         </is>
       </c>
+      <c r="Z68" t="inlineStr">
+        <is>
+          <t>10:52</t>
+        </is>
+      </c>
       <c r="AA68" t="inlineStr">
         <is>
           <t>2025-05-03</t>
+        </is>
+      </c>
+      <c r="AB68" t="inlineStr">
+        <is>
+          <t>10:52</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -7886,22 +7867,22 @@
       <c r="AT68" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>124756750</v>
+        <v>124756770</v>
       </c>
       <c r="B69" t="n">
-        <v>98269</v>
+        <v>75023</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -7914,35 +7895,26 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>220787</v>
+        <v>6486</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Skuggnål</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Chaenotheca sphaerocephala</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I69" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J69" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>Nádv.</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr"/>
+      <c r="J69" t="inlineStr"/>
       <c r="K69" t="inlineStr"/>
-      <c r="L69" t="inlineStr"/>
       <c r="N69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
@@ -7950,10 +7922,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>452617</v>
+        <v>452339</v>
       </c>
       <c r="R69" t="n">
-        <v>6990549</v>
+        <v>6990941</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7985,7 +7957,7 @@
       </c>
       <c r="Z69" t="inlineStr">
         <is>
-          <t>12:28</t>
+          <t>10:44</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
@@ -7995,7 +7967,7 @@
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>12:28</t>
+          <t>10:44</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -8004,9 +7976,43 @@
       <c r="AE69" t="b">
         <v>0</v>
       </c>
-      <c r="AF69" t="inlineStr"/>
+      <c r="AF69" t="inlineStr">
+        <is>
+          <t>mikroskoperad</t>
+        </is>
+      </c>
       <c r="AG69" t="b">
         <v>0</v>
+      </c>
+      <c r="AH69" t="inlineStr">
+        <is>
+          <t>Blåbärsgranskog</t>
+        </is>
+      </c>
+      <c r="AI69" t="inlineStr">
+        <is>
+          <t>I hålighet vid basen av gammal gran i fuktig granskog.</t>
+        </is>
+      </c>
+      <c r="AJ69" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK69" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM69" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO69" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Picea abies</t>
+        </is>
       </c>
       <c r="AT69" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
@@ -8023,7 +8029,7 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>124756777</v>
+        <v>124753611</v>
       </c>
       <c r="B70" t="n">
         <v>98269</v>
@@ -8056,29 +8062,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I70" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J70" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K70" t="inlineStr"/>
-      <c r="L70" t="inlineStr"/>
-      <c r="N70" t="inlineStr"/>
+      <c r="I70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
           <t>Häggsåsen N, Jmt</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>452146</v>
+        <v>452997</v>
       </c>
       <c r="R70" t="n">
-        <v>6990839</v>
+        <v>6990332</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -8108,19 +8102,14 @@
           <t>2025-05-03</t>
         </is>
       </c>
-      <c r="Z70" t="inlineStr">
-        <is>
-          <t>10:06</t>
-        </is>
-      </c>
       <c r="AA70" t="inlineStr">
         <is>
           <t>2025-05-03</t>
         </is>
       </c>
-      <c r="AB70" t="inlineStr">
-        <is>
-          <t>10:06</t>
+      <c r="AC70" t="inlineStr">
+        <is>
+          <t>Minst 100</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8129,29 +8118,28 @@
       <c r="AE70" t="b">
         <v>0</v>
       </c>
-      <c r="AF70" t="inlineStr"/>
       <c r="AG70" t="b">
         <v>0</v>
       </c>
       <c r="AT70" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>124753639</v>
+        <v>124753613</v>
       </c>
       <c r="B71" t="n">
-        <v>78947</v>
+        <v>98269</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -8160,25 +8148,25 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -8188,10 +8176,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>452511</v>
+        <v>452777</v>
       </c>
       <c r="R71" t="n">
-        <v>6990733</v>
+        <v>6990299</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -8224,6 +8212,11 @@
       <c r="AA71" t="inlineStr">
         <is>
           <t>2025-05-03</t>
+        </is>
+      </c>
+      <c r="AC71" t="inlineStr">
+        <is>
+          <t>Minst 100</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -8250,10 +8243,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>124756770</v>
+        <v>124756736</v>
       </c>
       <c r="B72" t="n">
-        <v>75023</v>
+        <v>98269</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -8266,26 +8259,35 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>6486</v>
+        <v>220787</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Skuggnål</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Chaenotheca sphaerocephala</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>Nádv.</t>
-        </is>
-      </c>
-      <c r="I72" t="inlineStr"/>
-      <c r="J72" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J72" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="K72" t="inlineStr"/>
+      <c r="L72" t="inlineStr"/>
       <c r="N72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
@@ -8293,10 +8295,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>452339</v>
+        <v>452691</v>
       </c>
       <c r="R72" t="n">
-        <v>6990941</v>
+        <v>6990422</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8328,7 +8330,7 @@
       </c>
       <c r="Z72" t="inlineStr">
         <is>
-          <t>10:44</t>
+          <t>14:13</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
@@ -8338,7 +8340,7 @@
       </c>
       <c r="AB72" t="inlineStr">
         <is>
-          <t>10:44</t>
+          <t>14:13</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8347,43 +8349,9 @@
       <c r="AE72" t="b">
         <v>0</v>
       </c>
-      <c r="AF72" t="inlineStr">
-        <is>
-          <t>mikroskoperad</t>
-        </is>
-      </c>
+      <c r="AF72" t="inlineStr"/>
       <c r="AG72" t="b">
         <v>0</v>
-      </c>
-      <c r="AH72" t="inlineStr">
-        <is>
-          <t>Blåbärsgranskog</t>
-        </is>
-      </c>
-      <c r="AI72" t="inlineStr">
-        <is>
-          <t>I hålighet vid basen av gammal gran i fuktig granskog.</t>
-        </is>
-      </c>
-      <c r="AJ72" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK72" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM72" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO72" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Picea abies</t>
-        </is>
       </c>
       <c r="AT72" t="inlineStr"/>
       <c r="AW72" t="inlineStr">
@@ -8400,10 +8368,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>124753610</v>
+        <v>124756718</v>
       </c>
       <c r="B73" t="n">
-        <v>80028</v>
+        <v>91184</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -8416,21 +8384,21 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>6458</v>
+        <v>5432</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -8440,10 +8408,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>452435</v>
+        <v>452857</v>
       </c>
       <c r="R73" t="n">
-        <v>6990938</v>
+        <v>6990267</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8473,9 +8441,19 @@
           <t>2025-05-03</t>
         </is>
       </c>
+      <c r="Z73" t="inlineStr">
+        <is>
+          <t>15:03</t>
+        </is>
+      </c>
       <c r="AA73" t="inlineStr">
         <is>
           <t>2025-05-03</t>
+        </is>
+      </c>
+      <c r="AB73" t="inlineStr">
+        <is>
+          <t>15:03</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8490,22 +8468,22 @@
       <c r="AT73" t="inlineStr"/>
       <c r="AW73" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>124756766</v>
+        <v>124753605</v>
       </c>
       <c r="B74" t="n">
-        <v>80028</v>
+        <v>80029</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -8518,21 +8496,21 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -8542,10 +8520,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>452396</v>
+        <v>452408</v>
       </c>
       <c r="R74" t="n">
-        <v>6990981</v>
+        <v>6990952</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8575,19 +8553,9 @@
           <t>2025-05-03</t>
         </is>
       </c>
-      <c r="Z74" t="inlineStr">
-        <is>
-          <t>10:58</t>
-        </is>
-      </c>
       <c r="AA74" t="inlineStr">
         <is>
           <t>2025-05-03</t>
-        </is>
-      </c>
-      <c r="AB74" t="inlineStr">
-        <is>
-          <t>10:58</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8602,22 +8570,22 @@
       <c r="AT74" t="inlineStr"/>
       <c r="AW74" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX74" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>124753631</v>
+        <v>124753587</v>
       </c>
       <c r="B75" t="n">
-        <v>98269</v>
+        <v>91166</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -8626,25 +8594,25 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8654,10 +8622,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>452526</v>
+        <v>452331</v>
       </c>
       <c r="R75" t="n">
-        <v>6990943</v>
+        <v>6990929</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8690,11 +8658,6 @@
       <c r="AA75" t="inlineStr">
         <is>
           <t>2025-05-03</t>
-        </is>
-      </c>
-      <c r="AC75" t="inlineStr">
-        <is>
-          <t>Minst 20</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -8721,10 +8684,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>124753606</v>
+        <v>124753621</v>
       </c>
       <c r="B76" t="n">
-        <v>91459</v>
+        <v>98269</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
@@ -8733,25 +8696,25 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>658</v>
+        <v>220787</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -8761,10 +8724,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>452165</v>
+        <v>452506</v>
       </c>
       <c r="R76" t="n">
-        <v>6990824</v>
+        <v>6990758</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8797,6 +8760,11 @@
       <c r="AA76" t="inlineStr">
         <is>
           <t>2025-05-03</t>
+        </is>
+      </c>
+      <c r="AC76" t="inlineStr">
+        <is>
+          <t>Minst 60</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -8823,10 +8791,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>124753629</v>
+        <v>124756719</v>
       </c>
       <c r="B77" t="n">
-        <v>98269</v>
+        <v>80064</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -8835,25 +8803,25 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>220787</v>
+        <v>6464</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -8863,10 +8831,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>452576</v>
+        <v>452823</v>
       </c>
       <c r="R77" t="n">
-        <v>6990924</v>
+        <v>6990261</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8896,14 +8864,19 @@
           <t>2025-05-03</t>
         </is>
       </c>
+      <c r="Z77" t="inlineStr">
+        <is>
+          <t>14:59</t>
+        </is>
+      </c>
       <c r="AA77" t="inlineStr">
         <is>
           <t>2025-05-03</t>
         </is>
       </c>
-      <c r="AC77" t="inlineStr">
-        <is>
-          <t>Minst 30</t>
+      <c r="AB77" t="inlineStr">
+        <is>
+          <t>14:59</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -8918,22 +8891,22 @@
       <c r="AT77" t="inlineStr"/>
       <c r="AW77" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX77" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>124753621</v>
+        <v>124753608</v>
       </c>
       <c r="B78" t="n">
-        <v>98269</v>
+        <v>80028</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -8942,25 +8915,25 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -8970,10 +8943,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>452506</v>
+        <v>452731</v>
       </c>
       <c r="R78" t="n">
-        <v>6990758</v>
+        <v>6990377</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -9006,11 +8979,6 @@
       <c r="AA78" t="inlineStr">
         <is>
           <t>2025-05-03</t>
-        </is>
-      </c>
-      <c r="AC78" t="inlineStr">
-        <is>
-          <t>Minst 60</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -9037,10 +9005,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>124753624</v>
+        <v>124753588</v>
       </c>
       <c r="B79" t="n">
-        <v>98269</v>
+        <v>91166</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -9049,25 +9017,25 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -9077,10 +9045,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>452528</v>
+        <v>452311</v>
       </c>
       <c r="R79" t="n">
-        <v>6990882</v>
+        <v>6990887</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -9113,11 +9081,6 @@
       <c r="AA79" t="inlineStr">
         <is>
           <t>2025-05-03</t>
-        </is>
-      </c>
-      <c r="AC79" t="inlineStr">
-        <is>
-          <t>Minst 30</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -9144,10 +9107,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>124753615</v>
+        <v>124753577</v>
       </c>
       <c r="B80" t="n">
-        <v>98269</v>
+        <v>91166</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
@@ -9156,25 +9119,25 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -9184,10 +9147,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>452734</v>
+        <v>452833</v>
       </c>
       <c r="R80" t="n">
-        <v>6990355</v>
+        <v>6990388</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -9220,11 +9183,6 @@
       <c r="AA80" t="inlineStr">
         <is>
           <t>2025-05-03</t>
-        </is>
-      </c>
-      <c r="AC80" t="inlineStr">
-        <is>
-          <t>Minst 30</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -9251,10 +9209,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>124756741</v>
+        <v>124753625</v>
       </c>
       <c r="B81" t="n">
-        <v>79988</v>
+        <v>98269</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
@@ -9263,25 +9221,25 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>229497</v>
+        <v>220787</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -9291,10 +9249,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>452682</v>
+        <v>452550</v>
       </c>
       <c r="R81" t="n">
-        <v>6990476</v>
+        <v>6990907</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -9324,19 +9282,14 @@
           <t>2025-05-03</t>
         </is>
       </c>
-      <c r="Z81" t="inlineStr">
-        <is>
-          <t>13:54</t>
-        </is>
-      </c>
       <c r="AA81" t="inlineStr">
         <is>
           <t>2025-05-03</t>
         </is>
       </c>
-      <c r="AB81" t="inlineStr">
-        <is>
-          <t>13:54</t>
+      <c r="AC81" t="inlineStr">
+        <is>
+          <t>Minst 50</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -9347,41 +9300,26 @@
       </c>
       <c r="AG81" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ81" t="inlineStr">
-        <is>
-          <t>rönn</t>
-        </is>
-      </c>
-      <c r="AK81" t="inlineStr">
-        <is>
-          <t>Sorbus aucuparia</t>
-        </is>
-      </c>
-      <c r="AO81" t="inlineStr">
-        <is>
-          <t>Sorbus aucuparia</t>
-        </is>
       </c>
       <c r="AT81" t="inlineStr"/>
       <c r="AW81" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX81" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>124756764</v>
+        <v>124756738</v>
       </c>
       <c r="B82" t="n">
-        <v>78947</v>
+        <v>75023</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
@@ -9390,38 +9328,41 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>6425</v>
+        <v>6486</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skuggnål</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca sphaerocephala</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Nádv.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
+      <c r="J82" t="inlineStr"/>
+      <c r="K82" t="inlineStr"/>
+      <c r="N82" t="inlineStr"/>
       <c r="P82" t="inlineStr">
         <is>
           <t>Häggsåsen N, Jmt</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>452462</v>
+        <v>452703</v>
       </c>
       <c r="R82" t="n">
-        <v>6990915</v>
+        <v>6990457</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -9453,7 +9394,7 @@
       </c>
       <c r="Z82" t="inlineStr">
         <is>
-          <t>11:11</t>
+          <t>14:09</t>
         </is>
       </c>
       <c r="AA82" t="inlineStr">
@@ -9463,7 +9404,7 @@
       </c>
       <c r="AB82" t="inlineStr">
         <is>
-          <t>11:11</t>
+          <t>14:09</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -9471,6 +9412,11 @@
       </c>
       <c r="AE82" t="b">
         <v>0</v>
+      </c>
+      <c r="AF82" t="inlineStr">
+        <is>
+          <t>mikroskoperad</t>
+        </is>
       </c>
       <c r="AG82" t="b">
         <v>0</v>
@@ -9490,10 +9436,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>124753627</v>
+        <v>124753583</v>
       </c>
       <c r="B83" t="n">
-        <v>98269</v>
+        <v>91166</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
@@ -9502,25 +9448,25 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -9530,10 +9476,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>452608</v>
+        <v>452606</v>
       </c>
       <c r="R83" t="n">
-        <v>6990927</v>
+        <v>6990623</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9566,11 +9512,6 @@
       <c r="AA83" t="inlineStr">
         <is>
           <t>2025-05-03</t>
-        </is>
-      </c>
-      <c r="AC83" t="inlineStr">
-        <is>
-          <t>Minst 50</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -9597,7 +9538,7 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>124753613</v>
+        <v>124753620</v>
       </c>
       <c r="B84" t="n">
         <v>98269</v>
@@ -9637,10 +9578,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>452777</v>
+        <v>452554</v>
       </c>
       <c r="R84" t="n">
-        <v>6990299</v>
+        <v>6990657</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9677,7 +9618,7 @@
       </c>
       <c r="AC84" t="inlineStr">
         <is>
-          <t>Minst 100</t>
+          <t>Minst 30</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -9704,7 +9645,7 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>124753612</v>
+        <v>124756751</v>
       </c>
       <c r="B85" t="n">
         <v>98269</v>
@@ -9737,17 +9678,29 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I85" t="inlineStr"/>
+      <c r="I85" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J85" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K85" t="inlineStr"/>
+      <c r="L85" t="inlineStr"/>
+      <c r="N85" t="inlineStr"/>
       <c r="P85" t="inlineStr">
         <is>
           <t>Häggsåsen N, Jmt</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>452924</v>
+        <v>452638</v>
       </c>
       <c r="R85" t="n">
-        <v>6990397</v>
+        <v>6990559</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9777,14 +9730,19 @@
           <t>2025-05-03</t>
         </is>
       </c>
+      <c r="Z85" t="inlineStr">
+        <is>
+          <t>12:23</t>
+        </is>
+      </c>
       <c r="AA85" t="inlineStr">
         <is>
           <t>2025-05-03</t>
         </is>
       </c>
-      <c r="AC85" t="inlineStr">
-        <is>
-          <t>Minst 20</t>
+      <c r="AB85" t="inlineStr">
+        <is>
+          <t>12:23</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -9793,28 +9751,29 @@
       <c r="AE85" t="b">
         <v>0</v>
       </c>
+      <c r="AF85" t="inlineStr"/>
       <c r="AG85" t="b">
         <v>0</v>
       </c>
       <c r="AT85" t="inlineStr"/>
       <c r="AW85" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX85" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>124756724</v>
+        <v>124756743</v>
       </c>
       <c r="B86" t="n">
-        <v>91166</v>
+        <v>80028</v>
       </c>
       <c r="C86" t="inlineStr">
         <is>
@@ -9827,21 +9786,21 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -9851,10 +9810,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>452793</v>
+        <v>452682</v>
       </c>
       <c r="R86" t="n">
-        <v>6990262</v>
+        <v>6990476</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9886,7 +9845,7 @@
       </c>
       <c r="Z86" t="inlineStr">
         <is>
-          <t>14:44</t>
+          <t>13:53</t>
         </is>
       </c>
       <c r="AA86" t="inlineStr">
@@ -9896,7 +9855,7 @@
       </c>
       <c r="AB86" t="inlineStr">
         <is>
-          <t>14:44</t>
+          <t>13:53</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -9907,6 +9866,21 @@
       </c>
       <c r="AG86" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ86" t="inlineStr">
+        <is>
+          <t>rönn</t>
+        </is>
+      </c>
+      <c r="AK86" t="inlineStr">
+        <is>
+          <t>Sorbus aucuparia</t>
+        </is>
+      </c>
+      <c r="AO86" t="inlineStr">
+        <is>
+          <t>Sorbus aucuparia</t>
+        </is>
       </c>
       <c r="AT86" t="inlineStr"/>
       <c r="AW86" t="inlineStr">
@@ -9923,10 +9897,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>124753583</v>
+        <v>124753633</v>
       </c>
       <c r="B87" t="n">
-        <v>91166</v>
+        <v>91162</v>
       </c>
       <c r="C87" t="inlineStr">
         <is>
@@ -9939,21 +9913,21 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>1202</v>
+        <v>1108</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
@@ -9963,10 +9937,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>452606</v>
+        <v>452772</v>
       </c>
       <c r="R87" t="n">
-        <v>6990623</v>
+        <v>6990321</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -10127,10 +10101,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>124753585</v>
+        <v>124753637</v>
       </c>
       <c r="B89" t="n">
-        <v>91166</v>
+        <v>91184</v>
       </c>
       <c r="C89" t="inlineStr">
         <is>
@@ -10143,21 +10117,21 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>1202</v>
+        <v>5432</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
@@ -10167,10 +10141,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>452595</v>
+        <v>452696</v>
       </c>
       <c r="R89" t="n">
-        <v>6990913</v>
+        <v>6990466</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -10229,10 +10203,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>124753592</v>
+        <v>124756688</v>
       </c>
       <c r="B90" t="n">
-        <v>57635</v>
+        <v>80028</v>
       </c>
       <c r="C90" t="inlineStr">
         <is>
@@ -10245,21 +10219,21 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
@@ -10269,10 +10243,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>452396</v>
+        <v>452694</v>
       </c>
       <c r="R90" t="n">
-        <v>6990703</v>
+        <v>6990598</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -10302,14 +10276,19 @@
           <t>2025-05-03</t>
         </is>
       </c>
+      <c r="Z90" t="inlineStr">
+        <is>
+          <t>20:19</t>
+        </is>
+      </c>
       <c r="AA90" t="inlineStr">
         <is>
           <t>2025-05-03</t>
         </is>
       </c>
-      <c r="AC90" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
+      <c r="AB90" t="inlineStr">
+        <is>
+          <t>20:19</t>
         </is>
       </c>
       <c r="AD90" t="b">
@@ -10324,22 +10303,22 @@
       <c r="AT90" t="inlineStr"/>
       <c r="AW90" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX90" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>124753608</v>
+        <v>124756749</v>
       </c>
       <c r="B91" t="n">
-        <v>80028</v>
+        <v>91166</v>
       </c>
       <c r="C91" t="inlineStr">
         <is>
@@ -10352,21 +10331,21 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
@@ -10376,10 +10355,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>452731</v>
+        <v>452609</v>
       </c>
       <c r="R91" t="n">
-        <v>6990377</v>
+        <v>6990543</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -10409,9 +10388,19 @@
           <t>2025-05-03</t>
         </is>
       </c>
+      <c r="Z91" t="inlineStr">
+        <is>
+          <t>12:29</t>
+        </is>
+      </c>
       <c r="AA91" t="inlineStr">
         <is>
           <t>2025-05-03</t>
+        </is>
+      </c>
+      <c r="AB91" t="inlineStr">
+        <is>
+          <t>12:29</t>
         </is>
       </c>
       <c r="AD91" t="b">
@@ -10426,19 +10415,19 @@
       <c r="AT91" t="inlineStr"/>
       <c r="AW91" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX91" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>124753620</v>
+        <v>124753629</v>
       </c>
       <c r="B92" t="n">
         <v>98269</v>
@@ -10478,10 +10467,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>452554</v>
+        <v>452576</v>
       </c>
       <c r="R92" t="n">
-        <v>6990657</v>
+        <v>6990924</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -10545,10 +10534,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>124756768</v>
+        <v>124753624</v>
       </c>
       <c r="B93" t="n">
-        <v>77879</v>
+        <v>98269</v>
       </c>
       <c r="C93" t="inlineStr">
         <is>
@@ -10557,25 +10546,25 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>228579</v>
+        <v>220787</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
@@ -10585,10 +10574,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>452357</v>
+        <v>452528</v>
       </c>
       <c r="R93" t="n">
-        <v>6990970</v>
+        <v>6990882</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -10618,19 +10607,14 @@
           <t>2025-05-03</t>
         </is>
       </c>
-      <c r="Z93" t="inlineStr">
-        <is>
-          <t>10:52</t>
-        </is>
-      </c>
       <c r="AA93" t="inlineStr">
         <is>
           <t>2025-05-03</t>
         </is>
       </c>
-      <c r="AB93" t="inlineStr">
-        <is>
-          <t>10:52</t>
+      <c r="AC93" t="inlineStr">
+        <is>
+          <t>Minst 30</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -10645,22 +10629,22 @@
       <c r="AT93" t="inlineStr"/>
       <c r="AW93" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX93" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY93" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>124753634</v>
+        <v>124753617</v>
       </c>
       <c r="B94" t="n">
-        <v>91162</v>
+        <v>98269</v>
       </c>
       <c r="C94" t="inlineStr">
         <is>
@@ -10669,25 +10653,25 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E94" t="n">
-        <v>1108</v>
+        <v>220787</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
@@ -10697,10 +10681,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>452750</v>
+        <v>452655</v>
       </c>
       <c r="R94" t="n">
-        <v>6990344</v>
+        <v>6990482</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -10733,6 +10717,11 @@
       <c r="AA94" t="inlineStr">
         <is>
           <t>2025-05-03</t>
+        </is>
+      </c>
+      <c r="AC94" t="inlineStr">
+        <is>
+          <t>Minst 50</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -10759,10 +10748,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>124756748</v>
+        <v>124756752</v>
       </c>
       <c r="B95" t="n">
-        <v>78947</v>
+        <v>98269</v>
       </c>
       <c r="C95" t="inlineStr">
         <is>
@@ -10771,38 +10760,50 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I95" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I95" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J95" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K95" t="inlineStr"/>
+      <c r="L95" t="inlineStr"/>
+      <c r="N95" t="inlineStr"/>
       <c r="P95" t="inlineStr">
         <is>
           <t>Häggsåsen N, Jmt</t>
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>452609</v>
+        <v>452608</v>
       </c>
       <c r="R95" t="n">
-        <v>6990543</v>
+        <v>6990625</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10834,7 +10835,7 @@
       </c>
       <c r="Z95" t="inlineStr">
         <is>
-          <t>12:29</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AA95" t="inlineStr">
@@ -10844,7 +10845,7 @@
       </c>
       <c r="AB95" t="inlineStr">
         <is>
-          <t>12:29</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -10853,6 +10854,7 @@
       <c r="AE95" t="b">
         <v>0</v>
       </c>
+      <c r="AF95" t="inlineStr"/>
       <c r="AG95" t="b">
         <v>0</v>
       </c>
@@ -10871,7 +10873,7 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>124753625</v>
+        <v>124756745</v>
       </c>
       <c r="B96" t="n">
         <v>98269</v>
@@ -10904,17 +10906,29 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I96" t="inlineStr"/>
+      <c r="I96" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J96" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K96" t="inlineStr"/>
+      <c r="L96" t="inlineStr"/>
+      <c r="N96" t="inlineStr"/>
       <c r="P96" t="inlineStr">
         <is>
           <t>Häggsåsen N, Jmt</t>
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>452550</v>
+        <v>452657</v>
       </c>
       <c r="R96" t="n">
-        <v>6990907</v>
+        <v>6990491</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -10944,14 +10958,19 @@
           <t>2025-05-03</t>
         </is>
       </c>
+      <c r="Z96" t="inlineStr">
+        <is>
+          <t>13:44</t>
+        </is>
+      </c>
       <c r="AA96" t="inlineStr">
         <is>
           <t>2025-05-03</t>
         </is>
       </c>
-      <c r="AC96" t="inlineStr">
-        <is>
-          <t>Minst 50</t>
+      <c r="AB96" t="inlineStr">
+        <is>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AD96" t="b">
@@ -10960,25 +10979,26 @@
       <c r="AE96" t="b">
         <v>0</v>
       </c>
+      <c r="AF96" t="inlineStr"/>
       <c r="AG96" t="b">
         <v>0</v>
       </c>
       <c r="AT96" t="inlineStr"/>
       <c r="AW96" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX96" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY96" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>124756745</v>
+        <v>124756750</v>
       </c>
       <c r="B97" t="n">
         <v>98269</v>
@@ -11013,7 +11033,7 @@
       </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J97" t="inlineStr">
@@ -11030,10 +11050,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>452657</v>
+        <v>452617</v>
       </c>
       <c r="R97" t="n">
-        <v>6990491</v>
+        <v>6990549</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -11065,7 +11085,7 @@
       </c>
       <c r="Z97" t="inlineStr">
         <is>
-          <t>13:44</t>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AA97" t="inlineStr">
@@ -11075,7 +11095,7 @@
       </c>
       <c r="AB97" t="inlineStr">
         <is>
-          <t>13:44</t>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AD97" t="b">
@@ -11103,7 +11123,7 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>124756752</v>
+        <v>124756730</v>
       </c>
       <c r="B98" t="n">
         <v>98269</v>
@@ -11138,7 +11158,7 @@
       </c>
       <c r="I98" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>200</t>
         </is>
       </c>
       <c r="J98" t="inlineStr">
@@ -11155,10 +11175,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>452608</v>
+        <v>452675</v>
       </c>
       <c r="R98" t="n">
-        <v>6990625</v>
+        <v>6990411</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -11190,7 +11210,7 @@
       </c>
       <c r="Z98" t="inlineStr">
         <is>
-          <t>12:07</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="AA98" t="inlineStr">
@@ -11200,7 +11220,12 @@
       </c>
       <c r="AB98" t="inlineStr">
         <is>
-          <t>12:07</t>
+          <t>14:20</t>
+        </is>
+      </c>
+      <c r="AC98" t="inlineStr">
+        <is>
+          <t>Min antal</t>
         </is>
       </c>
       <c r="AD98" t="b">
@@ -11228,10 +11253,10 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>124756736</v>
+        <v>124753638</v>
       </c>
       <c r="B99" t="n">
-        <v>98269</v>
+        <v>78947</v>
       </c>
       <c r="C99" t="inlineStr">
         <is>
@@ -11240,50 +11265,38 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E99" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I99" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J99" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K99" t="inlineStr"/>
-      <c r="L99" t="inlineStr"/>
-      <c r="N99" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I99" t="inlineStr"/>
       <c r="P99" t="inlineStr">
         <is>
           <t>Häggsåsen N, Jmt</t>
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>452691</v>
+        <v>452823</v>
       </c>
       <c r="R99" t="n">
-        <v>6990422</v>
+        <v>6990367</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -11313,50 +11326,39 @@
           <t>2025-05-03</t>
         </is>
       </c>
-      <c r="Z99" t="inlineStr">
-        <is>
-          <t>14:13</t>
-        </is>
-      </c>
       <c r="AA99" t="inlineStr">
         <is>
           <t>2025-05-03</t>
         </is>
       </c>
-      <c r="AB99" t="inlineStr">
-        <is>
-          <t>14:13</t>
-        </is>
-      </c>
       <c r="AD99" t="b">
         <v>0</v>
       </c>
       <c r="AE99" t="b">
         <v>0</v>
       </c>
-      <c r="AF99" t="inlineStr"/>
       <c r="AG99" t="b">
         <v>0</v>
       </c>
       <c r="AT99" t="inlineStr"/>
       <c r="AW99" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX99" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY99" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>124753587</v>
+        <v>124756775</v>
       </c>
       <c r="B100" t="n">
-        <v>91166</v>
+        <v>80028</v>
       </c>
       <c r="C100" t="inlineStr">
         <is>
@@ -11369,21 +11371,21 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
@@ -11393,10 +11395,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>452331</v>
+        <v>452308</v>
       </c>
       <c r="R100" t="n">
-        <v>6990929</v>
+        <v>6990943</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -11426,9 +11428,19 @@
           <t>2025-05-03</t>
         </is>
       </c>
+      <c r="Z100" t="inlineStr">
+        <is>
+          <t>10:22</t>
+        </is>
+      </c>
       <c r="AA100" t="inlineStr">
         <is>
           <t>2025-05-03</t>
+        </is>
+      </c>
+      <c r="AB100" t="inlineStr">
+        <is>
+          <t>10:22</t>
         </is>
       </c>
       <c r="AD100" t="b">
@@ -11443,22 +11455,22 @@
       <c r="AT100" t="inlineStr"/>
       <c r="AW100" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX100" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY100" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>124753633</v>
+        <v>124756765</v>
       </c>
       <c r="B101" t="n">
-        <v>91162</v>
+        <v>78947</v>
       </c>
       <c r="C101" t="inlineStr">
         <is>
@@ -11471,21 +11483,21 @@
         </is>
       </c>
       <c r="E101" t="n">
-        <v>1108</v>
+        <v>6425</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
@@ -11495,10 +11507,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>452772</v>
+        <v>452432</v>
       </c>
       <c r="R101" t="n">
-        <v>6990321</v>
+        <v>6990942</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -11528,9 +11540,19 @@
           <t>2025-05-03</t>
         </is>
       </c>
+      <c r="Z101" t="inlineStr">
+        <is>
+          <t>11:05</t>
+        </is>
+      </c>
       <c r="AA101" t="inlineStr">
         <is>
           <t>2025-05-03</t>
+        </is>
+      </c>
+      <c r="AB101" t="inlineStr">
+        <is>
+          <t>11:05</t>
         </is>
       </c>
       <c r="AD101" t="b">
@@ -11545,22 +11567,22 @@
       <c r="AT101" t="inlineStr"/>
       <c r="AW101" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX101" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY101" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>124756753</v>
+        <v>124756756</v>
       </c>
       <c r="B102" t="n">
-        <v>91166</v>
+        <v>78947</v>
       </c>
       <c r="C102" t="inlineStr">
         <is>
@@ -11573,21 +11595,21 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
@@ -11597,10 +11619,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>452608</v>
+        <v>452545</v>
       </c>
       <c r="R102" t="n">
-        <v>6990625</v>
+        <v>6990691</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -11632,7 +11654,7 @@
       </c>
       <c r="Z102" t="inlineStr">
         <is>
-          <t>12:07</t>
+          <t>11:54</t>
         </is>
       </c>
       <c r="AA102" t="inlineStr">
@@ -11642,7 +11664,7 @@
       </c>
       <c r="AB102" t="inlineStr">
         <is>
-          <t>12:07</t>
+          <t>11:54</t>
         </is>
       </c>
       <c r="AD102" t="b">
@@ -11669,10 +11691,10 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>124753637</v>
+        <v>124756734</v>
       </c>
       <c r="B103" t="n">
-        <v>91184</v>
+        <v>80028</v>
       </c>
       <c r="C103" t="inlineStr">
         <is>
@@ -11685,21 +11707,21 @@
         </is>
       </c>
       <c r="E103" t="n">
-        <v>5432</v>
+        <v>6458</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
@@ -11709,10 +11731,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>452696</v>
+        <v>452675</v>
       </c>
       <c r="R103" t="n">
-        <v>6990466</v>
+        <v>6990435</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -11742,11 +11764,21 @@
           <t>2025-05-03</t>
         </is>
       </c>
+      <c r="Z103" t="inlineStr">
+        <is>
+          <t>14:14</t>
+        </is>
+      </c>
       <c r="AA103" t="inlineStr">
         <is>
           <t>2025-05-03</t>
         </is>
       </c>
+      <c r="AB103" t="inlineStr">
+        <is>
+          <t>14:14</t>
+        </is>
+      </c>
       <c r="AD103" t="b">
         <v>0</v>
       </c>
@@ -11755,23 +11787,38 @@
       </c>
       <c r="AG103" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ103" t="inlineStr">
+        <is>
+          <t>rönn</t>
+        </is>
+      </c>
+      <c r="AK103" t="inlineStr">
+        <is>
+          <t>Sorbus aucuparia</t>
+        </is>
+      </c>
+      <c r="AO103" t="inlineStr">
+        <is>
+          <t>Sorbus aucuparia</t>
+        </is>
       </c>
       <c r="AT103" t="inlineStr"/>
       <c r="AW103" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX103" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY103" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>124756772</v>
+        <v>124756762</v>
       </c>
       <c r="B104" t="n">
         <v>78947</v>
@@ -11811,10 +11858,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>452344</v>
+        <v>452508</v>
       </c>
       <c r="R104" t="n">
-        <v>6990942</v>
+        <v>6990903</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -11846,7 +11893,7 @@
       </c>
       <c r="Z104" t="inlineStr">
         <is>
-          <t>10:32</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="AA104" t="inlineStr">
@@ -11856,7 +11903,7 @@
       </c>
       <c r="AB104" t="inlineStr">
         <is>
-          <t>10:32</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="AD104" t="b">
@@ -11883,10 +11930,10 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>124756778</v>
+        <v>124753614</v>
       </c>
       <c r="B105" t="n">
-        <v>78947</v>
+        <v>98269</v>
       </c>
       <c r="C105" t="inlineStr">
         <is>
@@ -11895,25 +11942,25 @@
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E105" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
@@ -11923,10 +11970,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>452153</v>
+        <v>452751</v>
       </c>
       <c r="R105" t="n">
-        <v>6990834</v>
+        <v>6990344</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -11956,19 +12003,14 @@
           <t>2025-05-03</t>
         </is>
       </c>
-      <c r="Z105" t="inlineStr">
-        <is>
-          <t>10:03</t>
-        </is>
-      </c>
       <c r="AA105" t="inlineStr">
         <is>
           <t>2025-05-03</t>
         </is>
       </c>
-      <c r="AB105" t="inlineStr">
-        <is>
-          <t>10:03</t>
+      <c r="AC105" t="inlineStr">
+        <is>
+          <t>Minst 200</t>
         </is>
       </c>
       <c r="AD105" t="b">
@@ -11983,22 +12025,22 @@
       <c r="AT105" t="inlineStr"/>
       <c r="AW105" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX105" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY105" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>124756762</v>
+        <v>124753615</v>
       </c>
       <c r="B106" t="n">
-        <v>78947</v>
+        <v>98269</v>
       </c>
       <c r="C106" t="inlineStr">
         <is>
@@ -12007,25 +12049,25 @@
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E106" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
@@ -12035,10 +12077,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>452508</v>
+        <v>452734</v>
       </c>
       <c r="R106" t="n">
-        <v>6990903</v>
+        <v>6990355</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -12068,19 +12110,14 @@
           <t>2025-05-03</t>
         </is>
       </c>
-      <c r="Z106" t="inlineStr">
-        <is>
-          <t>11:20</t>
-        </is>
-      </c>
       <c r="AA106" t="inlineStr">
         <is>
           <t>2025-05-03</t>
         </is>
       </c>
-      <c r="AB106" t="inlineStr">
-        <is>
-          <t>11:20</t>
+      <c r="AC106" t="inlineStr">
+        <is>
+          <t>Minst 30</t>
         </is>
       </c>
       <c r="AD106" t="b">
@@ -12095,22 +12132,22 @@
       <c r="AT106" t="inlineStr"/>
       <c r="AW106" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX106" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY106" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>124753638</v>
+        <v>124756763</v>
       </c>
       <c r="B107" t="n">
-        <v>78947</v>
+        <v>98269</v>
       </c>
       <c r="C107" t="inlineStr">
         <is>
@@ -12119,38 +12156,50 @@
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E107" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I107" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I107" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J107" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K107" t="inlineStr"/>
+      <c r="L107" t="inlineStr"/>
+      <c r="N107" t="inlineStr"/>
       <c r="P107" t="inlineStr">
         <is>
           <t>Häggsåsen N, Jmt</t>
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>452823</v>
+        <v>452478</v>
       </c>
       <c r="R107" t="n">
-        <v>6990367</v>
+        <v>6990887</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -12180,39 +12229,50 @@
           <t>2025-05-03</t>
         </is>
       </c>
+      <c r="Z107" t="inlineStr">
+        <is>
+          <t>11:18</t>
+        </is>
+      </c>
       <c r="AA107" t="inlineStr">
         <is>
           <t>2025-05-03</t>
         </is>
       </c>
+      <c r="AB107" t="inlineStr">
+        <is>
+          <t>11:18</t>
+        </is>
+      </c>
       <c r="AD107" t="b">
         <v>0</v>
       </c>
       <c r="AE107" t="b">
         <v>0</v>
       </c>
+      <c r="AF107" t="inlineStr"/>
       <c r="AG107" t="b">
         <v>0</v>
       </c>
       <c r="AT107" t="inlineStr"/>
       <c r="AW107" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX107" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY107" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>124756754</v>
+        <v>124756721</v>
       </c>
       <c r="B108" t="n">
-        <v>78947</v>
+        <v>80028</v>
       </c>
       <c r="C108" t="inlineStr">
         <is>
@@ -12225,21 +12285,21 @@
         </is>
       </c>
       <c r="E108" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
@@ -12249,10 +12309,10 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>452544</v>
+        <v>452823</v>
       </c>
       <c r="R108" t="n">
-        <v>6990646</v>
+        <v>6990261</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -12284,7 +12344,7 @@
       </c>
       <c r="Z108" t="inlineStr">
         <is>
-          <t>12:04</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AA108" t="inlineStr">
@@ -12294,7 +12354,7 @@
       </c>
       <c r="AB108" t="inlineStr">
         <is>
-          <t>12:04</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AD108" t="b">
@@ -12305,6 +12365,21 @@
       </c>
       <c r="AG108" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ108" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK108" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO108" t="inlineStr">
+        <is>
+          <t>Omkullfallen grov stam # Salix caprea</t>
+        </is>
       </c>
       <c r="AT108" t="inlineStr"/>
       <c r="AW108" t="inlineStr">
@@ -12321,10 +12396,10 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>124753630</v>
+        <v>124756724</v>
       </c>
       <c r="B109" t="n">
-        <v>98269</v>
+        <v>91166</v>
       </c>
       <c r="C109" t="inlineStr">
         <is>
@@ -12333,25 +12408,25 @@
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E109" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
@@ -12361,10 +12436,10 @@
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>452273</v>
+        <v>452793</v>
       </c>
       <c r="R109" t="n">
-        <v>6990906</v>
+        <v>6990262</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -12394,14 +12469,19 @@
           <t>2025-05-03</t>
         </is>
       </c>
+      <c r="Z109" t="inlineStr">
+        <is>
+          <t>14:44</t>
+        </is>
+      </c>
       <c r="AA109" t="inlineStr">
         <is>
           <t>2025-05-03</t>
         </is>
       </c>
-      <c r="AC109" t="inlineStr">
-        <is>
-          <t>Minst 10</t>
+      <c r="AB109" t="inlineStr">
+        <is>
+          <t>14:44</t>
         </is>
       </c>
       <c r="AD109" t="b">
@@ -12416,22 +12496,22 @@
       <c r="AT109" t="inlineStr"/>
       <c r="AW109" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX109" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY109" t="inlineStr"/>
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>124753616</v>
+        <v>124756728</v>
       </c>
       <c r="B110" t="n">
-        <v>98269</v>
+        <v>80028</v>
       </c>
       <c r="C110" t="inlineStr">
         <is>
@@ -12440,25 +12520,25 @@
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E110" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
@@ -12468,10 +12548,10 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>452742</v>
+        <v>452745</v>
       </c>
       <c r="R110" t="n">
-        <v>6990393</v>
+        <v>6990359</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -12501,14 +12581,19 @@
           <t>2025-05-03</t>
         </is>
       </c>
+      <c r="Z110" t="inlineStr">
+        <is>
+          <t>14:30</t>
+        </is>
+      </c>
       <c r="AA110" t="inlineStr">
         <is>
           <t>2025-05-03</t>
         </is>
       </c>
-      <c r="AC110" t="inlineStr">
-        <is>
-          <t>Minst 60</t>
+      <c r="AB110" t="inlineStr">
+        <is>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AD110" t="b">
@@ -12519,26 +12604,41 @@
       </c>
       <c r="AG110" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ110" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK110" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO110" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
       </c>
       <c r="AT110" t="inlineStr"/>
       <c r="AW110" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX110" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY110" t="inlineStr"/>
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>124753580</v>
+        <v>124756742</v>
       </c>
       <c r="B111" t="n">
-        <v>91166</v>
+        <v>80064</v>
       </c>
       <c r="C111" t="inlineStr">
         <is>
@@ -12547,25 +12647,25 @@
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E111" t="n">
-        <v>1202</v>
+        <v>6464</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
@@ -12575,10 +12675,10 @@
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>452693</v>
+        <v>452682</v>
       </c>
       <c r="R111" t="n">
-        <v>6990472</v>
+        <v>6990476</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -12608,11 +12708,21 @@
           <t>2025-05-03</t>
         </is>
       </c>
+      <c r="Z111" t="inlineStr">
+        <is>
+          <t>13:53</t>
+        </is>
+      </c>
       <c r="AA111" t="inlineStr">
         <is>
           <t>2025-05-03</t>
         </is>
       </c>
+      <c r="AB111" t="inlineStr">
+        <is>
+          <t>13:53</t>
+        </is>
+      </c>
       <c r="AD111" t="b">
         <v>0</v>
       </c>
@@ -12621,26 +12731,41 @@
       </c>
       <c r="AG111" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ111" t="inlineStr">
+        <is>
+          <t>rönn</t>
+        </is>
+      </c>
+      <c r="AK111" t="inlineStr">
+        <is>
+          <t>Sorbus aucuparia</t>
+        </is>
+      </c>
+      <c r="AO111" t="inlineStr">
+        <is>
+          <t>Sorbus aucuparia</t>
+        </is>
       </c>
       <c r="AT111" t="inlineStr"/>
       <c r="AW111" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX111" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY111" t="inlineStr"/>
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>124756721</v>
+        <v>124756767</v>
       </c>
       <c r="B112" t="n">
-        <v>80028</v>
+        <v>78947</v>
       </c>
       <c r="C112" t="inlineStr">
         <is>
@@ -12653,21 +12778,21 @@
         </is>
       </c>
       <c r="E112" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I112" t="inlineStr"/>
@@ -12677,10 +12802,10 @@
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>452823</v>
+        <v>452362</v>
       </c>
       <c r="R112" t="n">
-        <v>6990261</v>
+        <v>6991003</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -12712,7 +12837,7 @@
       </c>
       <c r="Z112" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>10:55</t>
         </is>
       </c>
       <c r="AA112" t="inlineStr">
@@ -12722,7 +12847,7 @@
       </c>
       <c r="AB112" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>10:55</t>
         </is>
       </c>
       <c r="AD112" t="b">
@@ -12733,21 +12858,6 @@
       </c>
       <c r="AG112" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ112" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK112" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AO112" t="inlineStr">
-        <is>
-          <t>Omkullfallen grov stam # Salix caprea</t>
-        </is>
       </c>
       <c r="AT112" t="inlineStr"/>
       <c r="AW112" t="inlineStr">
@@ -12764,10 +12874,10 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>124756742</v>
+        <v>124753631</v>
       </c>
       <c r="B113" t="n">
-        <v>80064</v>
+        <v>98269</v>
       </c>
       <c r="C113" t="inlineStr">
         <is>
@@ -12776,25 +12886,25 @@
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E113" t="n">
-        <v>6464</v>
+        <v>220787</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
@@ -12804,10 +12914,10 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>452682</v>
+        <v>452526</v>
       </c>
       <c r="R113" t="n">
-        <v>6990476</v>
+        <v>6990943</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -12837,19 +12947,14 @@
           <t>2025-05-03</t>
         </is>
       </c>
-      <c r="Z113" t="inlineStr">
-        <is>
-          <t>13:53</t>
-        </is>
-      </c>
       <c r="AA113" t="inlineStr">
         <is>
           <t>2025-05-03</t>
         </is>
       </c>
-      <c r="AB113" t="inlineStr">
-        <is>
-          <t>13:53</t>
+      <c r="AC113" t="inlineStr">
+        <is>
+          <t>Minst 20</t>
         </is>
       </c>
       <c r="AD113" t="b">
@@ -12860,41 +12965,26 @@
       </c>
       <c r="AG113" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ113" t="inlineStr">
-        <is>
-          <t>rönn</t>
-        </is>
-      </c>
-      <c r="AK113" t="inlineStr">
-        <is>
-          <t>Sorbus aucuparia</t>
-        </is>
-      </c>
-      <c r="AO113" t="inlineStr">
-        <is>
-          <t>Sorbus aucuparia</t>
-        </is>
       </c>
       <c r="AT113" t="inlineStr"/>
       <c r="AW113" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX113" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY113" t="inlineStr"/>
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>124756728</v>
+        <v>124756759</v>
       </c>
       <c r="B114" t="n">
-        <v>80028</v>
+        <v>91166</v>
       </c>
       <c r="C114" t="inlineStr">
         <is>
@@ -12907,21 +12997,21 @@
         </is>
       </c>
       <c r="E114" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
@@ -12931,10 +13021,10 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>452745</v>
+        <v>452509</v>
       </c>
       <c r="R114" t="n">
-        <v>6990359</v>
+        <v>6990778</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -12966,7 +13056,7 @@
       </c>
       <c r="Z114" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AA114" t="inlineStr">
@@ -12976,7 +13066,7 @@
       </c>
       <c r="AB114" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AD114" t="b">
@@ -12987,21 +13077,6 @@
       </c>
       <c r="AG114" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ114" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK114" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AO114" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
       </c>
       <c r="AT114" t="inlineStr"/>
       <c r="AW114" t="inlineStr">
@@ -13018,10 +13093,10 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>124753604</v>
+        <v>124756746</v>
       </c>
       <c r="B115" t="n">
-        <v>80029</v>
+        <v>91166</v>
       </c>
       <c r="C115" t="inlineStr">
         <is>
@@ -13034,21 +13109,21 @@
         </is>
       </c>
       <c r="E115" t="n">
-        <v>2081</v>
+        <v>1202</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
@@ -13058,10 +13133,10 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>452435</v>
+        <v>452639</v>
       </c>
       <c r="R115" t="n">
-        <v>6990938</v>
+        <v>6990537</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -13091,9 +13166,19 @@
           <t>2025-05-03</t>
         </is>
       </c>
+      <c r="Z115" t="inlineStr">
+        <is>
+          <t>13:36</t>
+        </is>
+      </c>
       <c r="AA115" t="inlineStr">
         <is>
           <t>2025-05-03</t>
+        </is>
+      </c>
+      <c r="AB115" t="inlineStr">
+        <is>
+          <t>13:36</t>
         </is>
       </c>
       <c r="AD115" t="b">
@@ -13108,22 +13193,22 @@
       <c r="AT115" t="inlineStr"/>
       <c r="AW115" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX115" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY115" t="inlineStr"/>
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>124753581</v>
+        <v>124753635</v>
       </c>
       <c r="B116" t="n">
-        <v>91166</v>
+        <v>91184</v>
       </c>
       <c r="C116" t="inlineStr">
         <is>
@@ -13136,21 +13221,21 @@
         </is>
       </c>
       <c r="E116" t="n">
-        <v>1202</v>
+        <v>5432</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
@@ -13160,10 +13245,10 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>452643</v>
+        <v>452732</v>
       </c>
       <c r="R116" t="n">
-        <v>6990504</v>
+        <v>6990486</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -13222,10 +13307,10 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>124756775</v>
+        <v>124753585</v>
       </c>
       <c r="B117" t="n">
-        <v>80028</v>
+        <v>91166</v>
       </c>
       <c r="C117" t="inlineStr">
         <is>
@@ -13238,21 +13323,21 @@
         </is>
       </c>
       <c r="E117" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
@@ -13262,10 +13347,10 @@
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>452308</v>
+        <v>452595</v>
       </c>
       <c r="R117" t="n">
-        <v>6990943</v>
+        <v>6990913</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>
@@ -13295,19 +13380,9 @@
           <t>2025-05-03</t>
         </is>
       </c>
-      <c r="Z117" t="inlineStr">
-        <is>
-          <t>10:22</t>
-        </is>
-      </c>
       <c r="AA117" t="inlineStr">
         <is>
           <t>2025-05-03</t>
-        </is>
-      </c>
-      <c r="AB117" t="inlineStr">
-        <is>
-          <t>10:22</t>
         </is>
       </c>
       <c r="AD117" t="b">
@@ -13322,22 +13397,22 @@
       <c r="AT117" t="inlineStr"/>
       <c r="AW117" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX117" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY117" t="inlineStr"/>
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>124756727</v>
+        <v>124753606</v>
       </c>
       <c r="B118" t="n">
-        <v>80057</v>
+        <v>91459</v>
       </c>
       <c r="C118" t="inlineStr">
         <is>
@@ -13346,25 +13421,25 @@
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E118" t="n">
-        <v>6462</v>
+        <v>658</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
@@ -13374,10 +13449,10 @@
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>452745</v>
+        <v>452165</v>
       </c>
       <c r="R118" t="n">
-        <v>6990359</v>
+        <v>6990824</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -13407,19 +13482,9 @@
           <t>2025-05-03</t>
         </is>
       </c>
-      <c r="Z118" t="inlineStr">
-        <is>
-          <t>14:31</t>
-        </is>
-      </c>
       <c r="AA118" t="inlineStr">
         <is>
           <t>2025-05-03</t>
-        </is>
-      </c>
-      <c r="AB118" t="inlineStr">
-        <is>
-          <t>14:31</t>
         </is>
       </c>
       <c r="AD118" t="b">
@@ -13434,22 +13499,22 @@
       <c r="AT118" t="inlineStr"/>
       <c r="AW118" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX118" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY118" t="inlineStr"/>
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>124756743</v>
+        <v>124756739</v>
       </c>
       <c r="B119" t="n">
-        <v>80028</v>
+        <v>98269</v>
       </c>
       <c r="C119" t="inlineStr">
         <is>
@@ -13458,38 +13523,50 @@
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E119" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I119" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I119" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="J119" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K119" t="inlineStr"/>
+      <c r="L119" t="inlineStr"/>
+      <c r="N119" t="inlineStr"/>
       <c r="P119" t="inlineStr">
         <is>
           <t>Häggsåsen N, Jmt</t>
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>452682</v>
+        <v>452711</v>
       </c>
       <c r="R119" t="n">
-        <v>6990476</v>
+        <v>6990473</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -13521,7 +13598,7 @@
       </c>
       <c r="Z119" t="inlineStr">
         <is>
-          <t>13:53</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AA119" t="inlineStr">
@@ -13531,7 +13608,7 @@
       </c>
       <c r="AB119" t="inlineStr">
         <is>
-          <t>13:53</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AD119" t="b">
@@ -13540,23 +13617,9 @@
       <c r="AE119" t="b">
         <v>0</v>
       </c>
+      <c r="AF119" t="inlineStr"/>
       <c r="AG119" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ119" t="inlineStr">
-        <is>
-          <t>rönn</t>
-        </is>
-      </c>
-      <c r="AK119" t="inlineStr">
-        <is>
-          <t>Sorbus aucuparia</t>
-        </is>
-      </c>
-      <c r="AO119" t="inlineStr">
-        <is>
-          <t>Sorbus aucuparia</t>
-        </is>
       </c>
       <c r="AT119" t="inlineStr"/>
       <c r="AW119" t="inlineStr">
@@ -13573,10 +13636,10 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>124753623</v>
+        <v>124753580</v>
       </c>
       <c r="B120" t="n">
-        <v>98269</v>
+        <v>91166</v>
       </c>
       <c r="C120" t="inlineStr">
         <is>
@@ -13585,25 +13648,25 @@
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E120" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
@@ -13613,10 +13676,10 @@
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>452510</v>
+        <v>452693</v>
       </c>
       <c r="R120" t="n">
-        <v>6990873</v>
+        <v>6990472</v>
       </c>
       <c r="S120" t="n">
         <v>10</v>
@@ -13649,11 +13712,6 @@
       <c r="AA120" t="inlineStr">
         <is>
           <t>2025-05-03</t>
-        </is>
-      </c>
-      <c r="AC120" t="inlineStr">
-        <is>
-          <t>Minst 50</t>
         </is>
       </c>
       <c r="AD120" t="b">
@@ -13680,10 +13738,10 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>124753617</v>
+        <v>124753592</v>
       </c>
       <c r="B121" t="n">
-        <v>98269</v>
+        <v>57635</v>
       </c>
       <c r="C121" t="inlineStr">
         <is>
@@ -13692,25 +13750,25 @@
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E121" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
@@ -13720,10 +13778,10 @@
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>452655</v>
+        <v>452396</v>
       </c>
       <c r="R121" t="n">
-        <v>6990482</v>
+        <v>6990703</v>
       </c>
       <c r="S121" t="n">
         <v>10</v>
@@ -13760,7 +13818,7 @@
       </c>
       <c r="AC121" t="inlineStr">
         <is>
-          <t>Minst 50</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD121" t="b">
@@ -13787,10 +13845,10 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>124753582</v>
+        <v>124756761</v>
       </c>
       <c r="B122" t="n">
-        <v>91166</v>
+        <v>78947</v>
       </c>
       <c r="C122" t="inlineStr">
         <is>
@@ -13803,21 +13861,21 @@
         </is>
       </c>
       <c r="E122" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I122" t="inlineStr"/>
@@ -13827,10 +13885,10 @@
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>452649</v>
+        <v>452532</v>
       </c>
       <c r="R122" t="n">
-        <v>6990621</v>
+        <v>6990825</v>
       </c>
       <c r="S122" t="n">
         <v>10</v>
@@ -13860,9 +13918,19 @@
           <t>2025-05-03</t>
         </is>
       </c>
+      <c r="Z122" t="inlineStr">
+        <is>
+          <t>11:26</t>
+        </is>
+      </c>
       <c r="AA122" t="inlineStr">
         <is>
           <t>2025-05-03</t>
+        </is>
+      </c>
+      <c r="AB122" t="inlineStr">
+        <is>
+          <t>11:26</t>
         </is>
       </c>
       <c r="AD122" t="b">
@@ -13877,22 +13945,22 @@
       <c r="AT122" t="inlineStr"/>
       <c r="AW122" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX122" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY122" t="inlineStr"/>
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>124756767</v>
+        <v>124756766</v>
       </c>
       <c r="B123" t="n">
-        <v>78947</v>
+        <v>80028</v>
       </c>
       <c r="C123" t="inlineStr">
         <is>
@@ -13905,21 +13973,21 @@
         </is>
       </c>
       <c r="E123" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I123" t="inlineStr"/>
@@ -13929,10 +13997,10 @@
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>452362</v>
+        <v>452396</v>
       </c>
       <c r="R123" t="n">
-        <v>6991003</v>
+        <v>6990981</v>
       </c>
       <c r="S123" t="n">
         <v>10</v>
@@ -13964,7 +14032,7 @@
       </c>
       <c r="Z123" t="inlineStr">
         <is>
-          <t>10:55</t>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AA123" t="inlineStr">
@@ -13974,7 +14042,7 @@
       </c>
       <c r="AB123" t="inlineStr">
         <is>
-          <t>10:55</t>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AD123" t="b">
@@ -14001,10 +14069,10 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>124753632</v>
+        <v>124753607</v>
       </c>
       <c r="B124" t="n">
-        <v>98269</v>
+        <v>80028</v>
       </c>
       <c r="C124" t="inlineStr">
         <is>
@@ -14013,25 +14081,25 @@
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E124" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I124" t="inlineStr"/>
@@ -14041,10 +14109,10 @@
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>452455</v>
+        <v>452734</v>
       </c>
       <c r="R124" t="n">
-        <v>6990942</v>
+        <v>6990356</v>
       </c>
       <c r="S124" t="n">
         <v>10</v>
@@ -14077,11 +14145,6 @@
       <c r="AA124" t="inlineStr">
         <is>
           <t>2025-05-03</t>
-        </is>
-      </c>
-      <c r="AC124" t="inlineStr">
-        <is>
-          <t>Minst 30</t>
         </is>
       </c>
       <c r="AD124" t="b">
@@ -14108,10 +14171,10 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>124753611</v>
+        <v>124756727</v>
       </c>
       <c r="B125" t="n">
-        <v>98269</v>
+        <v>80057</v>
       </c>
       <c r="C125" t="inlineStr">
         <is>
@@ -14120,25 +14183,25 @@
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E125" t="n">
-        <v>220787</v>
+        <v>6462</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I125" t="inlineStr"/>
@@ -14148,10 +14211,10 @@
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>452997</v>
+        <v>452745</v>
       </c>
       <c r="R125" t="n">
-        <v>6990332</v>
+        <v>6990359</v>
       </c>
       <c r="S125" t="n">
         <v>10</v>
@@ -14181,14 +14244,19 @@
           <t>2025-05-03</t>
         </is>
       </c>
+      <c r="Z125" t="inlineStr">
+        <is>
+          <t>14:31</t>
+        </is>
+      </c>
       <c r="AA125" t="inlineStr">
         <is>
           <t>2025-05-03</t>
         </is>
       </c>
-      <c r="AC125" t="inlineStr">
-        <is>
-          <t>Minst 100</t>
+      <c r="AB125" t="inlineStr">
+        <is>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AD125" t="b">
@@ -14203,22 +14271,22 @@
       <c r="AT125" t="inlineStr"/>
       <c r="AW125" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX125" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY125" t="inlineStr"/>
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>124756751</v>
+        <v>124753579</v>
       </c>
       <c r="B126" t="n">
-        <v>98269</v>
+        <v>91166</v>
       </c>
       <c r="C126" t="inlineStr">
         <is>
@@ -14227,50 +14295,38 @@
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E126" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I126" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J126" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K126" t="inlineStr"/>
-      <c r="L126" t="inlineStr"/>
-      <c r="N126" t="inlineStr"/>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I126" t="inlineStr"/>
       <c r="P126" t="inlineStr">
         <is>
           <t>Häggsåsen N, Jmt</t>
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>452638</v>
+        <v>452710</v>
       </c>
       <c r="R126" t="n">
-        <v>6990559</v>
+        <v>6990467</v>
       </c>
       <c r="S126" t="n">
         <v>10</v>
@@ -14300,50 +14356,39 @@
           <t>2025-05-03</t>
         </is>
       </c>
-      <c r="Z126" t="inlineStr">
-        <is>
-          <t>12:23</t>
-        </is>
-      </c>
       <c r="AA126" t="inlineStr">
         <is>
           <t>2025-05-03</t>
         </is>
       </c>
-      <c r="AB126" t="inlineStr">
-        <is>
-          <t>12:23</t>
-        </is>
-      </c>
       <c r="AD126" t="b">
         <v>0</v>
       </c>
       <c r="AE126" t="b">
         <v>0</v>
       </c>
-      <c r="AF126" t="inlineStr"/>
       <c r="AG126" t="b">
         <v>0</v>
       </c>
       <c r="AT126" t="inlineStr"/>
       <c r="AW126" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX126" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY126" t="inlineStr"/>
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>124756758</v>
+        <v>124753634</v>
       </c>
       <c r="B127" t="n">
-        <v>91116</v>
+        <v>91162</v>
       </c>
       <c r="C127" t="inlineStr">
         <is>
@@ -14356,21 +14401,21 @@
         </is>
       </c>
       <c r="E127" t="n">
-        <v>112</v>
+        <v>1108</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Stjärntagging</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Asterodon ferruginosus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>Pat.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I127" t="inlineStr"/>
@@ -14380,10 +14425,10 @@
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>452509</v>
+        <v>452750</v>
       </c>
       <c r="R127" t="n">
-        <v>6990778</v>
+        <v>6990344</v>
       </c>
       <c r="S127" t="n">
         <v>10</v>
@@ -14413,19 +14458,9 @@
           <t>2025-05-03</t>
         </is>
       </c>
-      <c r="Z127" t="inlineStr">
-        <is>
-          <t>11:40</t>
-        </is>
-      </c>
       <c r="AA127" t="inlineStr">
         <is>
           <t>2025-05-03</t>
-        </is>
-      </c>
-      <c r="AB127" t="inlineStr">
-        <is>
-          <t>11:40</t>
         </is>
       </c>
       <c r="AD127" t="b">
@@ -14440,22 +14475,22 @@
       <c r="AT127" t="inlineStr"/>
       <c r="AW127" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX127" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY127" t="inlineStr"/>
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>124753605</v>
+        <v>124753578</v>
       </c>
       <c r="B128" t="n">
-        <v>80029</v>
+        <v>91166</v>
       </c>
       <c r="C128" t="inlineStr">
         <is>
@@ -14468,21 +14503,21 @@
         </is>
       </c>
       <c r="E128" t="n">
-        <v>2081</v>
+        <v>1202</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I128" t="inlineStr"/>
@@ -14492,10 +14527,10 @@
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>452408</v>
+        <v>452743</v>
       </c>
       <c r="R128" t="n">
-        <v>6990952</v>
+        <v>6990405</v>
       </c>
       <c r="S128" t="n">
         <v>10</v>
@@ -14554,10 +14589,10 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>124756749</v>
+        <v>124753610</v>
       </c>
       <c r="B129" t="n">
-        <v>91166</v>
+        <v>80028</v>
       </c>
       <c r="C129" t="inlineStr">
         <is>
@@ -14570,21 +14605,21 @@
         </is>
       </c>
       <c r="E129" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I129" t="inlineStr"/>
@@ -14594,10 +14629,10 @@
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>452609</v>
+        <v>452435</v>
       </c>
       <c r="R129" t="n">
-        <v>6990543</v>
+        <v>6990938</v>
       </c>
       <c r="S129" t="n">
         <v>10</v>
@@ -14627,19 +14662,9 @@
           <t>2025-05-03</t>
         </is>
       </c>
-      <c r="Z129" t="inlineStr">
-        <is>
-          <t>12:29</t>
-        </is>
-      </c>
       <c r="AA129" t="inlineStr">
         <is>
           <t>2025-05-03</t>
-        </is>
-      </c>
-      <c r="AB129" t="inlineStr">
-        <is>
-          <t>12:29</t>
         </is>
       </c>
       <c r="AD129" t="b">
@@ -14654,19 +14679,19 @@
       <c r="AT129" t="inlineStr"/>
       <c r="AW129" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX129" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY129" t="inlineStr"/>
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>124756746</v>
+        <v>124756753</v>
       </c>
       <c r="B130" t="n">
         <v>91166</v>
@@ -14706,10 +14731,10 @@
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>452639</v>
+        <v>452608</v>
       </c>
       <c r="R130" t="n">
-        <v>6990537</v>
+        <v>6990625</v>
       </c>
       <c r="S130" t="n">
         <v>10</v>
@@ -14741,7 +14766,7 @@
       </c>
       <c r="Z130" t="inlineStr">
         <is>
-          <t>13:36</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AA130" t="inlineStr">
@@ -14751,7 +14776,7 @@
       </c>
       <c r="AB130" t="inlineStr">
         <is>
-          <t>13:36</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AD130" t="b">
@@ -14778,10 +14803,10 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>124753576</v>
+        <v>124753616</v>
       </c>
       <c r="B131" t="n">
-        <v>91166</v>
+        <v>98269</v>
       </c>
       <c r="C131" t="inlineStr">
         <is>
@@ -14790,25 +14815,25 @@
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E131" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I131" t="inlineStr"/>
@@ -14818,10 +14843,10 @@
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>452837</v>
+        <v>452742</v>
       </c>
       <c r="R131" t="n">
-        <v>6990384</v>
+        <v>6990393</v>
       </c>
       <c r="S131" t="n">
         <v>10</v>
@@ -14854,6 +14879,11 @@
       <c r="AA131" t="inlineStr">
         <is>
           <t>2025-05-03</t>
+        </is>
+      </c>
+      <c r="AC131" t="inlineStr">
+        <is>
+          <t>Minst 60</t>
         </is>
       </c>
       <c r="AD131" t="b">
@@ -14880,7 +14910,7 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>124756763</v>
+        <v>124756774</v>
       </c>
       <c r="B132" t="n">
         <v>98269</v>
@@ -14915,7 +14945,7 @@
       </c>
       <c r="I132" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>6</t>
         </is>
       </c>
       <c r="J132" t="inlineStr">
@@ -14932,10 +14962,10 @@
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>452478</v>
+        <v>452308</v>
       </c>
       <c r="R132" t="n">
-        <v>6990887</v>
+        <v>6990943</v>
       </c>
       <c r="S132" t="n">
         <v>10</v>
@@ -14967,7 +14997,7 @@
       </c>
       <c r="Z132" t="inlineStr">
         <is>
-          <t>11:18</t>
+          <t>10:23</t>
         </is>
       </c>
       <c r="AA132" t="inlineStr">
@@ -14977,7 +15007,7 @@
       </c>
       <c r="AB132" t="inlineStr">
         <is>
-          <t>11:18</t>
+          <t>10:23</t>
         </is>
       </c>
       <c r="AD132" t="b">
@@ -15005,10 +15035,10 @@
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>124756718</v>
+        <v>124756733</v>
       </c>
       <c r="B133" t="n">
-        <v>91184</v>
+        <v>80064</v>
       </c>
       <c r="C133" t="inlineStr">
         <is>
@@ -15017,25 +15047,25 @@
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E133" t="n">
-        <v>5432</v>
+        <v>6464</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I133" t="inlineStr"/>
@@ -15045,10 +15075,10 @@
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>452857</v>
+        <v>452675</v>
       </c>
       <c r="R133" t="n">
-        <v>6990267</v>
+        <v>6990435</v>
       </c>
       <c r="S133" t="n">
         <v>10</v>
@@ -15080,7 +15110,7 @@
       </c>
       <c r="Z133" t="inlineStr">
         <is>
-          <t>15:03</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="AA133" t="inlineStr">
@@ -15090,7 +15120,7 @@
       </c>
       <c r="AB133" t="inlineStr">
         <is>
-          <t>15:03</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="AD133" t="b">
@@ -15101,6 +15131,21 @@
       </c>
       <c r="AG133" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ133" t="inlineStr">
+        <is>
+          <t>rönn</t>
+        </is>
+      </c>
+      <c r="AK133" t="inlineStr">
+        <is>
+          <t>Sorbus aucuparia</t>
+        </is>
+      </c>
+      <c r="AO133" t="inlineStr">
+        <is>
+          <t>Sorbus aucuparia</t>
+        </is>
       </c>
       <c r="AT133" t="inlineStr"/>
       <c r="AW133" t="inlineStr">
@@ -15117,10 +15162,10 @@
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>124756719</v>
+        <v>124753609</v>
       </c>
       <c r="B134" t="n">
-        <v>80064</v>
+        <v>80028</v>
       </c>
       <c r="C134" t="inlineStr">
         <is>
@@ -15129,25 +15174,25 @@
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E134" t="n">
-        <v>6464</v>
+        <v>6458</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I134" t="inlineStr"/>
@@ -15157,10 +15202,10 @@
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>452823</v>
+        <v>452528</v>
       </c>
       <c r="R134" t="n">
-        <v>6990261</v>
+        <v>6990710</v>
       </c>
       <c r="S134" t="n">
         <v>10</v>
@@ -15190,19 +15235,9 @@
           <t>2025-05-03</t>
         </is>
       </c>
-      <c r="Z134" t="inlineStr">
-        <is>
-          <t>14:59</t>
-        </is>
-      </c>
       <c r="AA134" t="inlineStr">
         <is>
           <t>2025-05-03</t>
-        </is>
-      </c>
-      <c r="AB134" t="inlineStr">
-        <is>
-          <t>14:59</t>
         </is>
       </c>
       <c r="AD134" t="b">
@@ -15217,22 +15252,22 @@
       <c r="AT134" t="inlineStr"/>
       <c r="AW134" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX134" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY134" t="inlineStr"/>
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>124756765</v>
+        <v>124753604</v>
       </c>
       <c r="B135" t="n">
-        <v>78947</v>
+        <v>80029</v>
       </c>
       <c r="C135" t="inlineStr">
         <is>
@@ -15245,21 +15280,21 @@
         </is>
       </c>
       <c r="E135" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I135" t="inlineStr"/>
@@ -15269,10 +15304,10 @@
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>452432</v>
+        <v>452435</v>
       </c>
       <c r="R135" t="n">
-        <v>6990942</v>
+        <v>6990938</v>
       </c>
       <c r="S135" t="n">
         <v>10</v>
@@ -15302,19 +15337,9 @@
           <t>2025-05-03</t>
         </is>
       </c>
-      <c r="Z135" t="inlineStr">
-        <is>
-          <t>11:05</t>
-        </is>
-      </c>
       <c r="AA135" t="inlineStr">
         <is>
           <t>2025-05-03</t>
-        </is>
-      </c>
-      <c r="AB135" t="inlineStr">
-        <is>
-          <t>11:05</t>
         </is>
       </c>
       <c r="AD135" t="b">
@@ -15329,22 +15354,22 @@
       <c r="AT135" t="inlineStr"/>
       <c r="AW135" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX135" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY135" t="inlineStr"/>
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>124756733</v>
+        <v>124753576</v>
       </c>
       <c r="B136" t="n">
-        <v>80064</v>
+        <v>91166</v>
       </c>
       <c r="C136" t="inlineStr">
         <is>
@@ -15353,25 +15378,25 @@
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E136" t="n">
-        <v>6464</v>
+        <v>1202</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I136" t="inlineStr"/>
@@ -15381,10 +15406,10 @@
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>452675</v>
+        <v>452837</v>
       </c>
       <c r="R136" t="n">
-        <v>6990435</v>
+        <v>6990384</v>
       </c>
       <c r="S136" t="n">
         <v>10</v>
@@ -15414,21 +15439,11 @@
           <t>2025-05-03</t>
         </is>
       </c>
-      <c r="Z136" t="inlineStr">
-        <is>
-          <t>14:15</t>
-        </is>
-      </c>
       <c r="AA136" t="inlineStr">
         <is>
           <t>2025-05-03</t>
         </is>
       </c>
-      <c r="AB136" t="inlineStr">
-        <is>
-          <t>14:15</t>
-        </is>
-      </c>
       <c r="AD136" t="b">
         <v>0</v>
       </c>
@@ -15437,31 +15452,16 @@
       </c>
       <c r="AG136" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ136" t="inlineStr">
-        <is>
-          <t>rönn</t>
-        </is>
-      </c>
-      <c r="AK136" t="inlineStr">
-        <is>
-          <t>Sorbus aucuparia</t>
-        </is>
-      </c>
-      <c r="AO136" t="inlineStr">
-        <is>
-          <t>Sorbus aucuparia</t>
-        </is>
       </c>
       <c r="AT136" t="inlineStr"/>
       <c r="AW136" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX136" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY136" t="inlineStr"/>

--- a/artfynd/A 16493-2025 artfynd.xlsx
+++ b/artfynd/A 16493-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>124694574</v>
       </c>
       <c r="B2" t="n">
-        <v>57651</v>
+        <v>57652</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>124689546</v>
       </c>
       <c r="B3" t="n">
-        <v>57651</v>
+        <v>57652</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -892,7 +892,7 @@
         <v>124721354</v>
       </c>
       <c r="B4" t="n">
-        <v>57651</v>
+        <v>57652</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -999,7 +999,7 @@
         <v>124705813</v>
       </c>
       <c r="B5" t="n">
-        <v>57651</v>
+        <v>57652</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1731,7 +1731,7 @@
         <v>124689475</v>
       </c>
       <c r="B12" t="n">
-        <v>57651</v>
+        <v>57652</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2246,7 +2246,7 @@
         <v>124706864</v>
       </c>
       <c r="B17" t="n">
-        <v>57651</v>
+        <v>57652</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2765,7 +2765,7 @@
         <v>124721401</v>
       </c>
       <c r="B22" t="n">
-        <v>57651</v>
+        <v>57652</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2979,7 +2979,7 @@
         <v>124689335</v>
       </c>
       <c r="B24" t="n">
-        <v>57651</v>
+        <v>57652</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3086,7 +3086,7 @@
         <v>124689528</v>
       </c>
       <c r="B25" t="n">
-        <v>57651</v>
+        <v>57652</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3193,7 +3193,7 @@
         <v>124689504</v>
       </c>
       <c r="B26" t="n">
-        <v>57651</v>
+        <v>57652</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3504,7 +3504,7 @@
         <v>124704478</v>
       </c>
       <c r="B29" t="n">
-        <v>57651</v>
+        <v>57652</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -4641,7 +4641,7 @@
         <v>124689574</v>
       </c>
       <c r="B40" t="n">
-        <v>57651</v>
+        <v>57652</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -13681,7 +13681,7 @@
         <v>124753592</v>
       </c>
       <c r="B121" t="n">
-        <v>57651</v>
+        <v>57652</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>

--- a/artfynd/A 16493-2025 artfynd.xlsx
+++ b/artfynd/A 16493-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>124694574</v>
       </c>
       <c r="B2" t="n">
-        <v>57652</v>
+        <v>57656</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>124689546</v>
       </c>
       <c r="B3" t="n">
-        <v>57652</v>
+        <v>57656</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -892,7 +892,7 @@
         <v>124721354</v>
       </c>
       <c r="B4" t="n">
-        <v>57652</v>
+        <v>57656</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -999,7 +999,7 @@
         <v>124705813</v>
       </c>
       <c r="B5" t="n">
-        <v>57652</v>
+        <v>57656</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1731,7 +1731,7 @@
         <v>124689475</v>
       </c>
       <c r="B12" t="n">
-        <v>57652</v>
+        <v>57656</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2246,7 +2246,7 @@
         <v>124706864</v>
       </c>
       <c r="B17" t="n">
-        <v>57652</v>
+        <v>57656</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2765,7 +2765,7 @@
         <v>124721401</v>
       </c>
       <c r="B22" t="n">
-        <v>57652</v>
+        <v>57656</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2979,7 +2979,7 @@
         <v>124689335</v>
       </c>
       <c r="B24" t="n">
-        <v>57652</v>
+        <v>57656</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3086,7 +3086,7 @@
         <v>124689528</v>
       </c>
       <c r="B25" t="n">
-        <v>57652</v>
+        <v>57656</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3193,7 +3193,7 @@
         <v>124689504</v>
       </c>
       <c r="B26" t="n">
-        <v>57652</v>
+        <v>57656</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3504,7 +3504,7 @@
         <v>124704478</v>
       </c>
       <c r="B29" t="n">
-        <v>57652</v>
+        <v>57656</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -4641,7 +4641,7 @@
         <v>124689574</v>
       </c>
       <c r="B40" t="n">
-        <v>57652</v>
+        <v>57656</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -13681,7 +13681,7 @@
         <v>124753592</v>
       </c>
       <c r="B121" t="n">
-        <v>57652</v>
+        <v>57656</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>

--- a/artfynd/A 16493-2025 artfynd.xlsx
+++ b/artfynd/A 16493-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>124694574</v>
       </c>
       <c r="B2" t="n">
-        <v>57656</v>
+        <v>57657</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>124689546</v>
       </c>
       <c r="B3" t="n">
-        <v>57656</v>
+        <v>57657</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -892,7 +892,7 @@
         <v>124721354</v>
       </c>
       <c r="B4" t="n">
-        <v>57656</v>
+        <v>57657</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -999,7 +999,7 @@
         <v>124705813</v>
       </c>
       <c r="B5" t="n">
-        <v>57656</v>
+        <v>57657</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1731,7 +1731,7 @@
         <v>124689475</v>
       </c>
       <c r="B12" t="n">
-        <v>57656</v>
+        <v>57657</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2246,7 +2246,7 @@
         <v>124706864</v>
       </c>
       <c r="B17" t="n">
-        <v>57656</v>
+        <v>57657</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2765,7 +2765,7 @@
         <v>124721401</v>
       </c>
       <c r="B22" t="n">
-        <v>57656</v>
+        <v>57657</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2979,7 +2979,7 @@
         <v>124689335</v>
       </c>
       <c r="B24" t="n">
-        <v>57656</v>
+        <v>57657</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3086,7 +3086,7 @@
         <v>124689528</v>
       </c>
       <c r="B25" t="n">
-        <v>57656</v>
+        <v>57657</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3193,7 +3193,7 @@
         <v>124689504</v>
       </c>
       <c r="B26" t="n">
-        <v>57656</v>
+        <v>57657</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3504,7 +3504,7 @@
         <v>124704478</v>
       </c>
       <c r="B29" t="n">
-        <v>57656</v>
+        <v>57657</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -4641,7 +4641,7 @@
         <v>124689574</v>
       </c>
       <c r="B40" t="n">
-        <v>57656</v>
+        <v>57657</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -13681,7 +13681,7 @@
         <v>124753592</v>
       </c>
       <c r="B121" t="n">
-        <v>57656</v>
+        <v>57657</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>

--- a/artfynd/A 16493-2025 artfynd.xlsx
+++ b/artfynd/A 16493-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY137"/>
+  <dimension ref="A1:AY140"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -15528,6 +15528,324 @@
       </c>
       <c r="AY137" t="inlineStr"/>
     </row>
+    <row r="138">
+      <c r="A138" t="n">
+        <v>125249934</v>
+      </c>
+      <c r="B138" t="n">
+        <v>57727</v>
+      </c>
+      <c r="D138" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E138" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F138" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G138" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H138" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I138" t="inlineStr"/>
+      <c r="K138" t="inlineStr"/>
+      <c r="L138" t="inlineStr"/>
+      <c r="M138" t="inlineStr"/>
+      <c r="N138" t="inlineStr"/>
+      <c r="P138" t="inlineStr">
+        <is>
+          <t>Nedom Häggsåsberget, Jmt</t>
+        </is>
+      </c>
+      <c r="Q138" t="n">
+        <v>452102</v>
+      </c>
+      <c r="R138" t="n">
+        <v>6990790</v>
+      </c>
+      <c r="S138" t="n">
+        <v>1</v>
+      </c>
+      <c r="T138" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U138" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V138" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W138" t="inlineStr">
+        <is>
+          <t>Oviken</t>
+        </is>
+      </c>
+      <c r="Y138" t="inlineStr">
+        <is>
+          <t>2025-05-17</t>
+        </is>
+      </c>
+      <c r="Z138" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="AA138" t="inlineStr">
+        <is>
+          <t>2025-05-17</t>
+        </is>
+      </c>
+      <c r="AB138" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="AC138" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
+        </is>
+      </c>
+      <c r="AD138" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE138" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG138" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT138" t="inlineStr"/>
+      <c r="AW138" t="inlineStr">
+        <is>
+          <t>Mona Olsson</t>
+        </is>
+      </c>
+      <c r="AX138" t="inlineStr">
+        <is>
+          <t>Mona Olsson</t>
+        </is>
+      </c>
+      <c r="AY138" t="inlineStr"/>
+    </row>
+    <row r="139">
+      <c r="A139" t="n">
+        <v>125250029</v>
+      </c>
+      <c r="B139" t="n">
+        <v>79041</v>
+      </c>
+      <c r="D139" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E139" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F139" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G139" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H139" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I139" t="inlineStr"/>
+      <c r="J139" t="inlineStr"/>
+      <c r="K139" t="inlineStr"/>
+      <c r="N139" t="inlineStr"/>
+      <c r="P139" t="inlineStr">
+        <is>
+          <t>Nedom Häggsåsberget , Jmt</t>
+        </is>
+      </c>
+      <c r="Q139" t="n">
+        <v>452118</v>
+      </c>
+      <c r="R139" t="n">
+        <v>6990840</v>
+      </c>
+      <c r="S139" t="n">
+        <v>1</v>
+      </c>
+      <c r="T139" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U139" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V139" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W139" t="inlineStr">
+        <is>
+          <t>Oviken</t>
+        </is>
+      </c>
+      <c r="Y139" t="inlineStr">
+        <is>
+          <t>2025-05-17</t>
+        </is>
+      </c>
+      <c r="AA139" t="inlineStr">
+        <is>
+          <t>2025-05-17</t>
+        </is>
+      </c>
+      <c r="AD139" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE139" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF139" t="inlineStr"/>
+      <c r="AG139" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT139" t="inlineStr"/>
+      <c r="AW139" t="inlineStr">
+        <is>
+          <t>Mona Olsson</t>
+        </is>
+      </c>
+      <c r="AX139" t="inlineStr">
+        <is>
+          <t>Mona Olsson</t>
+        </is>
+      </c>
+      <c r="AY139" t="inlineStr"/>
+    </row>
+    <row r="140">
+      <c r="A140" t="n">
+        <v>125250039</v>
+      </c>
+      <c r="B140" t="n">
+        <v>79041</v>
+      </c>
+      <c r="D140" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E140" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F140" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G140" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H140" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I140" t="inlineStr"/>
+      <c r="J140" t="inlineStr"/>
+      <c r="K140" t="inlineStr"/>
+      <c r="N140" t="inlineStr"/>
+      <c r="P140" t="inlineStr">
+        <is>
+          <t>Nedom Häggsåsberget , Jmt</t>
+        </is>
+      </c>
+      <c r="Q140" t="n">
+        <v>452475</v>
+      </c>
+      <c r="R140" t="n">
+        <v>6990588</v>
+      </c>
+      <c r="S140" t="n">
+        <v>1</v>
+      </c>
+      <c r="T140" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U140" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V140" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W140" t="inlineStr">
+        <is>
+          <t>Oviken</t>
+        </is>
+      </c>
+      <c r="Y140" t="inlineStr">
+        <is>
+          <t>2025-05-17</t>
+        </is>
+      </c>
+      <c r="AA140" t="inlineStr">
+        <is>
+          <t>2025-05-17</t>
+        </is>
+      </c>
+      <c r="AD140" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE140" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF140" t="inlineStr"/>
+      <c r="AG140" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT140" t="inlineStr"/>
+      <c r="AW140" t="inlineStr">
+        <is>
+          <t>Mona Olsson</t>
+        </is>
+      </c>
+      <c r="AX140" t="inlineStr">
+        <is>
+          <t>Mona Olsson</t>
+        </is>
+      </c>
+      <c r="AY140" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 16493-2025 artfynd.xlsx
+++ b/artfynd/A 16493-2025 artfynd.xlsx
@@ -15649,7 +15649,7 @@
         <v>125250029</v>
       </c>
       <c r="B139" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -15750,7 +15750,7 @@
         <v>125250039</v>
       </c>
       <c r="B140" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>

--- a/artfynd/A 16493-2025 artfynd.xlsx
+++ b/artfynd/A 16493-2025 artfynd.xlsx
@@ -15649,7 +15649,7 @@
         <v>125250029</v>
       </c>
       <c r="B139" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -15750,7 +15750,7 @@
         <v>125250039</v>
       </c>
       <c r="B140" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>

--- a/artfynd/A 16493-2025 artfynd.xlsx
+++ b/artfynd/A 16493-2025 artfynd.xlsx
@@ -15533,7 +15533,7 @@
         <v>125249934</v>
       </c>
       <c r="B138" t="n">
-        <v>57727</v>
+        <v>57730</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -15649,7 +15649,7 @@
         <v>125250029</v>
       </c>
       <c r="B139" t="n">
-        <v>79044</v>
+        <v>79070</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -15750,7 +15750,7 @@
         <v>125250039</v>
       </c>
       <c r="B140" t="n">
-        <v>79044</v>
+        <v>79070</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>

--- a/artfynd/A 16493-2025 artfynd.xlsx
+++ b/artfynd/A 16493-2025 artfynd.xlsx
@@ -15533,7 +15533,7 @@
         <v>125249934</v>
       </c>
       <c r="B138" t="n">
-        <v>57730</v>
+        <v>57735</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -15649,7 +15649,7 @@
         <v>125250029</v>
       </c>
       <c r="B139" t="n">
-        <v>79070</v>
+        <v>79075</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -15750,7 +15750,7 @@
         <v>125250039</v>
       </c>
       <c r="B140" t="n">
-        <v>79070</v>
+        <v>79075</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>

--- a/artfynd/A 16493-2025 artfynd.xlsx
+++ b/artfynd/A 16493-2025 artfynd.xlsx
@@ -15533,7 +15533,7 @@
         <v>125249934</v>
       </c>
       <c r="B138" t="n">
-        <v>57735</v>
+        <v>57736</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -15649,7 +15649,7 @@
         <v>125250029</v>
       </c>
       <c r="B139" t="n">
-        <v>79075</v>
+        <v>79076</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -15750,7 +15750,7 @@
         <v>125250039</v>
       </c>
       <c r="B140" t="n">
-        <v>79075</v>
+        <v>79076</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>

--- a/artfynd/A 16493-2025 artfynd.xlsx
+++ b/artfynd/A 16493-2025 artfynd.xlsx
@@ -15649,7 +15649,7 @@
         <v>125250029</v>
       </c>
       <c r="B139" t="n">
-        <v>79076</v>
+        <v>79081</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -15750,7 +15750,7 @@
         <v>125250039</v>
       </c>
       <c r="B140" t="n">
-        <v>79076</v>
+        <v>79081</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>

--- a/artfynd/A 16493-2025 artfynd.xlsx
+++ b/artfynd/A 16493-2025 artfynd.xlsx
@@ -15533,7 +15533,7 @@
         <v>125249934</v>
       </c>
       <c r="B138" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>

--- a/artfynd/A 16493-2025 artfynd.xlsx
+++ b/artfynd/A 16493-2025 artfynd.xlsx
@@ -15533,7 +15533,7 @@
         <v>125249934</v>
       </c>
       <c r="B138" t="n">
-        <v>57737</v>
+        <v>57740</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>

--- a/artfynd/A 16493-2025 artfynd.xlsx
+++ b/artfynd/A 16493-2025 artfynd.xlsx
@@ -15533,7 +15533,7 @@
         <v>125249934</v>
       </c>
       <c r="B138" t="n">
-        <v>57741</v>
+        <v>57826</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>

--- a/artfynd/A 16493-2025 artfynd.xlsx
+++ b/artfynd/A 16493-2025 artfynd.xlsx
@@ -999,7 +999,7 @@
         <v>124705813</v>
       </c>
       <c r="B5" t="n">
-        <v>57657</v>
+        <v>57864</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 16493-2025 artfynd.xlsx
+++ b/artfynd/A 16493-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY139"/>
+  <dimension ref="A1:AZ139"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -779,6 +784,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124756758</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -876,6 +886,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124689655</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -973,6 +988,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124701516</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1070,6 +1090,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124703242</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1167,6 +1192,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124704581</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1264,6 +1294,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124753606</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1371,6 +1406,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124756755</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1468,6 +1508,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124703646</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1565,6 +1610,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124753633</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1662,6 +1712,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124753634</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1759,6 +1814,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124689645</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1856,6 +1916,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124691378</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1953,6 +2018,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124693950</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2050,6 +2120,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124695424</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2147,6 +2222,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124704608</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2244,6 +2324,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124704726</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2341,6 +2426,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124705215</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2438,6 +2528,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124753576</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2535,6 +2630,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124753577</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2632,6 +2732,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124753578</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2729,6 +2834,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124753579</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2826,6 +2936,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124753580</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -2923,6 +3038,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124753581</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3020,6 +3140,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124753582</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3117,6 +3242,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124753583</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3214,6 +3344,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124753584</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3311,6 +3446,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124753585</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3408,6 +3548,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124753586</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3505,6 +3650,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124753587</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3602,6 +3752,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124753588</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -3709,6 +3864,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124756724</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -3816,6 +3976,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124756731</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -3923,6 +4088,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124756746</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4030,6 +4200,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124756749</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4137,6 +4312,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124756753</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4244,6 +4424,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124756759</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4341,6 +4526,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124693275</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4448,6 +4638,11 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124756740</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -4545,6 +4740,11 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124695367</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -4642,6 +4842,11 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124691528</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -4739,6 +4944,11 @@
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124699720</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -4846,6 +5056,11 @@
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124701352</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -4943,6 +5158,11 @@
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124753604</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -5040,6 +5260,11 @@
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124753605</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -5167,6 +5392,11 @@
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124756720</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -5269,6 +5499,11 @@
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124688835</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -5366,6 +5601,11 @@
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124753638</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -5463,6 +5703,11 @@
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124753639</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -5570,6 +5815,11 @@
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124756722</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -5677,6 +5927,11 @@
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124756725</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -5784,6 +6039,11 @@
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124756748</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -5891,6 +6151,11 @@
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124756754</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -5998,6 +6263,11 @@
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
+      <c r="AZ54" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124756756</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -6105,6 +6375,11 @@
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
+      <c r="AZ55" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124756761</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -6212,6 +6487,11 @@
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
+      <c r="AZ56" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124756762</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -6319,6 +6599,11 @@
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
+      <c r="AZ57" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124756764</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -6426,6 +6711,11 @@
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
+      <c r="AZ58" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124756765</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -6533,6 +6823,11 @@
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
+      <c r="AZ59" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124756767</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -6640,6 +6935,11 @@
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
+      <c r="AZ60" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124756772</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -6747,6 +7047,11 @@
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
+      <c r="AZ61" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124756776</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -6854,6 +7159,11 @@
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
+      <c r="AZ62" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124756778</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -6961,6 +7271,11 @@
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
+      <c r="AZ63" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124756779</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -7062,6 +7377,11 @@
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
+      <c r="AZ64" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125250029</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
@@ -7163,6 +7483,11 @@
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
+      <c r="AZ65" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125250039</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
@@ -7260,6 +7585,11 @@
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
+      <c r="AZ66" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124688930</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
@@ -7357,6 +7687,11 @@
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
+      <c r="AZ67" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124691533</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
@@ -7454,6 +7789,11 @@
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
+      <c r="AZ68" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124699728</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
@@ -7551,6 +7891,11 @@
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
+      <c r="AZ69" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124702530</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
@@ -7648,6 +7993,11 @@
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
+      <c r="AZ70" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124702770</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
@@ -7745,6 +8095,11 @@
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
+      <c r="AZ71" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124702902</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
@@ -7842,6 +8197,11 @@
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
+      <c r="AZ72" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124753607</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
@@ -7939,6 +8299,11 @@
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
+      <c r="AZ73" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124753608</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
@@ -8036,6 +8401,11 @@
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
+      <c r="AZ74" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124753609</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
@@ -8133,6 +8503,11 @@
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
+      <c r="AZ75" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124753610</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
@@ -8240,6 +8615,11 @@
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
+      <c r="AZ76" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124756688</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
@@ -8362,6 +8742,11 @@
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
+      <c r="AZ77" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124756721</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
@@ -8484,6 +8869,11 @@
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
+      <c r="AZ78" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124756728</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
@@ -8606,6 +8996,11 @@
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
+      <c r="AZ79" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124756734</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
@@ -8728,6 +9123,11 @@
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>
+      <c r="AZ80" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124756743</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
@@ -8835,6 +9235,11 @@
         </is>
       </c>
       <c r="AY81" t="inlineStr"/>
+      <c r="AZ81" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124756766</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
@@ -8942,6 +9347,11 @@
         </is>
       </c>
       <c r="AY82" t="inlineStr"/>
+      <c r="AZ82" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124756775</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
@@ -9049,6 +9459,11 @@
         </is>
       </c>
       <c r="AY83" t="inlineStr"/>
+      <c r="AZ83" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124756727</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
@@ -9156,6 +9571,11 @@
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
+      <c r="AZ84" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124756719</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
@@ -9278,6 +9698,11 @@
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>
+      <c r="AZ85" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124756733</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
@@ -9400,6 +9825,11 @@
         </is>
       </c>
       <c r="AY86" t="inlineStr"/>
+      <c r="AZ86" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124756742</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
@@ -9515,6 +9945,11 @@
         </is>
       </c>
       <c r="AY87" t="inlineStr"/>
+      <c r="AZ87" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124756738</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
@@ -9660,6 +10095,11 @@
         </is>
       </c>
       <c r="AY88" t="inlineStr"/>
+      <c r="AZ88" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124756770</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
@@ -9767,6 +10207,11 @@
         </is>
       </c>
       <c r="AY89" t="inlineStr"/>
+      <c r="AZ89" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124689335</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
@@ -9874,6 +10319,11 @@
         </is>
       </c>
       <c r="AY90" t="inlineStr"/>
+      <c r="AZ90" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124689475</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
@@ -9981,6 +10431,11 @@
         </is>
       </c>
       <c r="AY91" t="inlineStr"/>
+      <c r="AZ91" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124689504</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
@@ -10088,6 +10543,11 @@
         </is>
       </c>
       <c r="AY92" t="inlineStr"/>
+      <c r="AZ92" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124689528</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="n">
@@ -10195,6 +10655,11 @@
         </is>
       </c>
       <c r="AY93" t="inlineStr"/>
+      <c r="AZ93" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124689546</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="n">
@@ -10302,6 +10767,11 @@
         </is>
       </c>
       <c r="AY94" t="inlineStr"/>
+      <c r="AZ94" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124689574</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="n">
@@ -10409,6 +10879,11 @@
         </is>
       </c>
       <c r="AY95" t="inlineStr"/>
+      <c r="AZ95" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124694574</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="n">
@@ -10516,6 +10991,11 @@
         </is>
       </c>
       <c r="AY96" t="inlineStr"/>
+      <c r="AZ96" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124704478</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="n">
@@ -10623,6 +11103,11 @@
         </is>
       </c>
       <c r="AY97" t="inlineStr"/>
+      <c r="AZ97" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124705813</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="n">
@@ -10730,6 +11215,11 @@
         </is>
       </c>
       <c r="AY98" t="inlineStr"/>
+      <c r="AZ98" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124706864</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="n">
@@ -10837,6 +11327,11 @@
         </is>
       </c>
       <c r="AY99" t="inlineStr"/>
+      <c r="AZ99" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124721354</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="n">
@@ -10944,6 +11439,11 @@
         </is>
       </c>
       <c r="AY100" t="inlineStr"/>
+      <c r="AZ100" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124721401</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="n">
@@ -11046,6 +11546,11 @@
         </is>
       </c>
       <c r="AY101" t="inlineStr"/>
+      <c r="AZ101" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124753592</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="n">
@@ -11162,6 +11667,11 @@
         </is>
       </c>
       <c r="AY102" t="inlineStr"/>
+      <c r="AZ102" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125249851</t>
+        </is>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="n">
@@ -11278,6 +11788,11 @@
         </is>
       </c>
       <c r="AY103" t="inlineStr"/>
+      <c r="AZ103" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125249934</t>
+        </is>
+      </c>
     </row>
     <row r="104">
       <c r="A104" t="n">
@@ -11384,6 +11899,11 @@
         </is>
       </c>
       <c r="AY104" t="inlineStr"/>
+      <c r="AZ104" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124691814</t>
+        </is>
+      </c>
     </row>
     <row r="105">
       <c r="A105" t="n">
@@ -11485,6 +12005,11 @@
         </is>
       </c>
       <c r="AY105" t="inlineStr"/>
+      <c r="AZ105" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124695256</t>
+        </is>
+      </c>
     </row>
     <row r="106">
       <c r="A106" t="n">
@@ -11586,6 +12111,11 @@
         </is>
       </c>
       <c r="AY106" t="inlineStr"/>
+      <c r="AZ106" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124706950</t>
+        </is>
+      </c>
     </row>
     <row r="107">
       <c r="A107" t="n">
@@ -11688,6 +12218,11 @@
         </is>
       </c>
       <c r="AY107" t="inlineStr"/>
+      <c r="AZ107" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124753611</t>
+        </is>
+      </c>
     </row>
     <row r="108">
       <c r="A108" t="n">
@@ -11790,6 +12325,11 @@
         </is>
       </c>
       <c r="AY108" t="inlineStr"/>
+      <c r="AZ108" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124753612</t>
+        </is>
+      </c>
     </row>
     <row r="109">
       <c r="A109" t="n">
@@ -11892,6 +12432,11 @@
         </is>
       </c>
       <c r="AY109" t="inlineStr"/>
+      <c r="AZ109" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124753613</t>
+        </is>
+      </c>
     </row>
     <row r="110">
       <c r="A110" t="n">
@@ -11994,6 +12539,11 @@
         </is>
       </c>
       <c r="AY110" t="inlineStr"/>
+      <c r="AZ110" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124753614</t>
+        </is>
+      </c>
     </row>
     <row r="111">
       <c r="A111" t="n">
@@ -12096,6 +12646,11 @@
         </is>
       </c>
       <c r="AY111" t="inlineStr"/>
+      <c r="AZ111" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124753615</t>
+        </is>
+      </c>
     </row>
     <row r="112">
       <c r="A112" t="n">
@@ -12198,6 +12753,11 @@
         </is>
       </c>
       <c r="AY112" t="inlineStr"/>
+      <c r="AZ112" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124753616</t>
+        </is>
+      </c>
     </row>
     <row r="113">
       <c r="A113" t="n">
@@ -12300,6 +12860,11 @@
         </is>
       </c>
       <c r="AY113" t="inlineStr"/>
+      <c r="AZ113" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124753617</t>
+        </is>
+      </c>
     </row>
     <row r="114">
       <c r="A114" t="n">
@@ -12402,6 +12967,11 @@
         </is>
       </c>
       <c r="AY114" t="inlineStr"/>
+      <c r="AZ114" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124753620</t>
+        </is>
+      </c>
     </row>
     <row r="115">
       <c r="A115" t="n">
@@ -12504,6 +13074,11 @@
         </is>
       </c>
       <c r="AY115" t="inlineStr"/>
+      <c r="AZ115" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124753621</t>
+        </is>
+      </c>
     </row>
     <row r="116">
       <c r="A116" t="n">
@@ -12606,6 +13181,11 @@
         </is>
       </c>
       <c r="AY116" t="inlineStr"/>
+      <c r="AZ116" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124753622</t>
+        </is>
+      </c>
     </row>
     <row r="117">
       <c r="A117" t="n">
@@ -12708,6 +13288,11 @@
         </is>
       </c>
       <c r="AY117" t="inlineStr"/>
+      <c r="AZ117" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124753623</t>
+        </is>
+      </c>
     </row>
     <row r="118">
       <c r="A118" t="n">
@@ -12810,6 +13395,11 @@
         </is>
       </c>
       <c r="AY118" t="inlineStr"/>
+      <c r="AZ118" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124753624</t>
+        </is>
+      </c>
     </row>
     <row r="119">
       <c r="A119" t="n">
@@ -12912,6 +13502,11 @@
         </is>
       </c>
       <c r="AY119" t="inlineStr"/>
+      <c r="AZ119" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124753625</t>
+        </is>
+      </c>
     </row>
     <row r="120">
       <c r="A120" t="n">
@@ -13014,6 +13609,11 @@
         </is>
       </c>
       <c r="AY120" t="inlineStr"/>
+      <c r="AZ120" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124753627</t>
+        </is>
+      </c>
     </row>
     <row r="121">
       <c r="A121" t="n">
@@ -13116,6 +13716,11 @@
         </is>
       </c>
       <c r="AY121" t="inlineStr"/>
+      <c r="AZ121" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124753629</t>
+        </is>
+      </c>
     </row>
     <row r="122">
       <c r="A122" t="n">
@@ -13218,6 +13823,11 @@
         </is>
       </c>
       <c r="AY122" t="inlineStr"/>
+      <c r="AZ122" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124753630</t>
+        </is>
+      </c>
     </row>
     <row r="123">
       <c r="A123" t="n">
@@ -13320,6 +13930,11 @@
         </is>
       </c>
       <c r="AY123" t="inlineStr"/>
+      <c r="AZ123" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124753631</t>
+        </is>
+      </c>
     </row>
     <row r="124">
       <c r="A124" t="n">
@@ -13422,6 +14037,11 @@
         </is>
       </c>
       <c r="AY124" t="inlineStr"/>
+      <c r="AZ124" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124753632</t>
+        </is>
+      </c>
     </row>
     <row r="125">
       <c r="A125" t="n">
@@ -13547,6 +14167,11 @@
         </is>
       </c>
       <c r="AY125" t="inlineStr"/>
+      <c r="AZ125" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124756730</t>
+        </is>
+      </c>
     </row>
     <row r="126">
       <c r="A126" t="n">
@@ -13667,6 +14292,11 @@
         </is>
       </c>
       <c r="AY126" t="inlineStr"/>
+      <c r="AZ126" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124756736</t>
+        </is>
+      </c>
     </row>
     <row r="127">
       <c r="A127" t="n">
@@ -13787,6 +14417,11 @@
         </is>
       </c>
       <c r="AY127" t="inlineStr"/>
+      <c r="AZ127" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124756739</t>
+        </is>
+      </c>
     </row>
     <row r="128">
       <c r="A128" t="n">
@@ -13907,6 +14542,11 @@
         </is>
       </c>
       <c r="AY128" t="inlineStr"/>
+      <c r="AZ128" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124756745</t>
+        </is>
+      </c>
     </row>
     <row r="129">
       <c r="A129" t="n">
@@ -14027,6 +14667,11 @@
         </is>
       </c>
       <c r="AY129" t="inlineStr"/>
+      <c r="AZ129" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124756750</t>
+        </is>
+      </c>
     </row>
     <row r="130">
       <c r="A130" t="n">
@@ -14147,6 +14792,11 @@
         </is>
       </c>
       <c r="AY130" t="inlineStr"/>
+      <c r="AZ130" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124756751</t>
+        </is>
+      </c>
     </row>
     <row r="131">
       <c r="A131" t="n">
@@ -14267,6 +14917,11 @@
         </is>
       </c>
       <c r="AY131" t="inlineStr"/>
+      <c r="AZ131" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124756752</t>
+        </is>
+      </c>
     </row>
     <row r="132">
       <c r="A132" t="n">
@@ -14387,6 +15042,11 @@
         </is>
       </c>
       <c r="AY132" t="inlineStr"/>
+      <c r="AZ132" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124756763</t>
+        </is>
+      </c>
     </row>
     <row r="133">
       <c r="A133" t="n">
@@ -14507,6 +15167,11 @@
         </is>
       </c>
       <c r="AY133" t="inlineStr"/>
+      <c r="AZ133" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124756774</t>
+        </is>
+      </c>
     </row>
     <row r="134">
       <c r="A134" t="n">
@@ -14627,6 +15292,11 @@
         </is>
       </c>
       <c r="AY134" t="inlineStr"/>
+      <c r="AZ134" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124756777</t>
+        </is>
+      </c>
     </row>
     <row r="135">
       <c r="A135" t="n">
@@ -14724,6 +15394,11 @@
         </is>
       </c>
       <c r="AY135" t="inlineStr"/>
+      <c r="AZ135" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124706585</t>
+        </is>
+      </c>
     </row>
     <row r="136">
       <c r="A136" t="n">
@@ -14831,6 +15506,11 @@
         </is>
       </c>
       <c r="AY136" t="inlineStr"/>
+      <c r="AZ136" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124756757</t>
+        </is>
+      </c>
     </row>
     <row r="137">
       <c r="A137" t="n">
@@ -14938,6 +15618,11 @@
         </is>
       </c>
       <c r="AY137" t="inlineStr"/>
+      <c r="AZ137" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124756768</t>
+        </is>
+      </c>
     </row>
     <row r="138">
       <c r="A138" t="n">
@@ -15060,6 +15745,11 @@
         </is>
       </c>
       <c r="AY138" t="inlineStr"/>
+      <c r="AZ138" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124756741</t>
+        </is>
+      </c>
     </row>
     <row r="139">
       <c r="A139" t="n">
@@ -15190,8 +15880,153 @@
         </is>
       </c>
       <c r="AY139" t="inlineStr"/>
+      <c r="AZ139" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124756747</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ57" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ58" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ59" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ60" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ61" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ62" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ63" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ64" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ65" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ66" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ67" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ68" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ69" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ70" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ71" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ72" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ73" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ74" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ75" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ76" r:id="rId75"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ77" r:id="rId76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ78" r:id="rId77"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ79" r:id="rId78"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ80" r:id="rId79"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ81" r:id="rId80"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ82" r:id="rId81"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ83" r:id="rId82"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ84" r:id="rId83"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ85" r:id="rId84"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ86" r:id="rId85"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ87" r:id="rId86"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ88" r:id="rId87"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ89" r:id="rId88"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ90" r:id="rId89"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ91" r:id="rId90"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ92" r:id="rId91"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ93" r:id="rId92"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ94" r:id="rId93"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ95" r:id="rId94"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ96" r:id="rId95"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ97" r:id="rId96"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ98" r:id="rId97"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ99" r:id="rId98"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ100" r:id="rId99"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ101" r:id="rId100"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ102" r:id="rId101"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ103" r:id="rId102"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ104" r:id="rId103"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ105" r:id="rId104"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ106" r:id="rId105"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ107" r:id="rId106"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ108" r:id="rId107"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ109" r:id="rId108"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ110" r:id="rId109"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ111" r:id="rId110"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ112" r:id="rId111"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ113" r:id="rId112"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ114" r:id="rId113"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ115" r:id="rId114"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ116" r:id="rId115"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ117" r:id="rId116"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ118" r:id="rId117"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ119" r:id="rId118"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ120" r:id="rId119"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ121" r:id="rId120"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ122" r:id="rId121"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ123" r:id="rId122"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ124" r:id="rId123"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ125" r:id="rId124"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ126" r:id="rId125"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ127" r:id="rId126"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ128" r:id="rId127"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ129" r:id="rId128"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ130" r:id="rId129"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ131" r:id="rId130"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ132" r:id="rId131"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ133" r:id="rId132"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ134" r:id="rId133"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ135" r:id="rId134"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ136" r:id="rId135"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ137" r:id="rId136"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ138" r:id="rId137"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ139" r:id="rId138"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>